--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95446CF0-D3F7-487A-A1A6-D47FDD6A0E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07FD907-0FA4-44F4-9297-4419DCA4C587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -15124,7 +15124,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -16400,13 +16400,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16946,13 +16946,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G57" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17648,13 +17648,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="G84" s="2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H84" s="2">
-        <v>628</v>
+        <v>624</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="G97" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H97" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18168,13 +18168,13 @@
         <v>2144</v>
       </c>
       <c r="F104" s="2">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G104" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H104" s="2">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -32406,13 +32406,13 @@
         <v>2136</v>
       </c>
       <c r="F652" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G652" s="2">
         <v>0</v>
       </c>
       <c r="H652" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="653" spans="1:8" x14ac:dyDescent="0.25">
@@ -32952,13 +32952,13 @@
         <v>2619</v>
       </c>
       <c r="F673" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G673" s="2">
         <v>0</v>
       </c>
       <c r="H673" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
@@ -32978,13 +32978,13 @@
         <v>2619</v>
       </c>
       <c r="F674" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G674" s="2">
         <v>0</v>
       </c>
       <c r="H674" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="675" spans="1:8" x14ac:dyDescent="0.25">
@@ -34694,13 +34694,13 @@
         <v>2284</v>
       </c>
       <c r="F740" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G740" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H740" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
@@ -34824,13 +34824,13 @@
         <v>2284</v>
       </c>
       <c r="F745" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G745" s="2">
         <v>0</v>
       </c>
       <c r="H745" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="746" spans="1:8" x14ac:dyDescent="0.25">
@@ -48756,13 +48756,13 @@
         <v>2205</v>
       </c>
       <c r="F1281" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1281" s="2">
         <v>0</v>
       </c>
       <c r="H1281" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1282" spans="1:8" x14ac:dyDescent="0.25">
@@ -48860,13 +48860,13 @@
         <v>2205</v>
       </c>
       <c r="F1285" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1285" s="2">
         <v>0</v>
       </c>
       <c r="H1285" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1286" spans="1:8" x14ac:dyDescent="0.25">
@@ -50966,13 +50966,13 @@
         <v>3317</v>
       </c>
       <c r="F1366" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1366" s="2">
         <v>0</v>
       </c>
       <c r="H1366" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1367" spans="1:8" x14ac:dyDescent="0.25">
@@ -75458,13 +75458,13 @@
         <v>4410</v>
       </c>
       <c r="F2308" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G2308" s="2">
         <v>0</v>
       </c>
       <c r="H2308" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2309" spans="1:8" x14ac:dyDescent="0.25">
@@ -88716,13 +88716,13 @@
         <v>2113</v>
       </c>
       <c r="F2818" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G2818" s="2">
         <v>0</v>
       </c>
       <c r="H2818" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2819" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07FD907-0FA4-44F4-9297-4419DCA4C587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79E96B7-6916-49B9-AA94-FAD829F1BFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -16400,13 +16400,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16946,13 +16946,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17076,13 +17076,13 @@
         <v>2118</v>
       </c>
       <c r="F62" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -17648,13 +17648,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>629</v>
+        <v>612</v>
       </c>
       <c r="G84" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>624</v>
+        <v>612</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17960,13 +17960,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G96" s="2">
         <v>0</v>
       </c>
       <c r="H96" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="G97" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18038,13 +18038,13 @@
         <v>2103</v>
       </c>
       <c r="F99" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
       </c>
       <c r="H99" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -18168,13 +18168,13 @@
         <v>2144</v>
       </c>
       <c r="F104" s="2">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G104" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H104" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -28562,13 +28562,13 @@
         <v>2136</v>
       </c>
       <c r="F504" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G504" s="2">
         <v>0</v>
       </c>
       <c r="H504" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
@@ -32224,13 +32224,13 @@
         <v>2619</v>
       </c>
       <c r="F645" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G645" s="2">
         <v>0</v>
       </c>
       <c r="H645" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
@@ -32952,13 +32952,13 @@
         <v>2619</v>
       </c>
       <c r="F673" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G673" s="2">
         <v>0</v>
       </c>
       <c r="H673" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
@@ -34278,13 +34278,13 @@
         <v>2619</v>
       </c>
       <c r="F724" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G724" s="2">
         <v>0</v>
       </c>
       <c r="H724" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="725" spans="1:8" x14ac:dyDescent="0.25">
@@ -34694,13 +34694,13 @@
         <v>2284</v>
       </c>
       <c r="F740" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G740" s="2">
         <v>0</v>
       </c>
       <c r="H740" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
@@ -34954,13 +34954,13 @@
         <v>2284</v>
       </c>
       <c r="F750" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G750" s="2">
         <v>0</v>
       </c>
       <c r="H750" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="751" spans="1:8" x14ac:dyDescent="0.25">
@@ -37892,13 +37892,13 @@
         <v>2122</v>
       </c>
       <c r="F863" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G863" s="2">
         <v>0</v>
       </c>
       <c r="H863" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="864" spans="1:8" x14ac:dyDescent="0.25">
@@ -38932,13 +38932,13 @@
         <v>2566</v>
       </c>
       <c r="F903" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G903" s="2">
         <v>0</v>
       </c>
       <c r="H903" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="904" spans="1:8" x14ac:dyDescent="0.25">
@@ -39088,13 +39088,13 @@
         <v>2957</v>
       </c>
       <c r="F909" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G909" s="2">
         <v>0</v>
       </c>
       <c r="H909" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="910" spans="1:8" x14ac:dyDescent="0.25">
@@ -44546,13 +44546,13 @@
         <v>3112</v>
       </c>
       <c r="F1119" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G1119" s="2">
         <v>0</v>
       </c>
       <c r="H1119" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1120" spans="1:8" x14ac:dyDescent="0.25">
@@ -45480,13 +45480,13 @@
         <v>2196</v>
       </c>
       <c r="F1155" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1155" s="2">
         <v>0</v>
       </c>
       <c r="H1155" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1156" spans="1:8" x14ac:dyDescent="0.25">
@@ -48678,13 +48678,13 @@
         <v>2636</v>
       </c>
       <c r="F1278" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1278" s="2">
         <v>0</v>
       </c>
       <c r="H1278" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1279" spans="1:8" x14ac:dyDescent="0.25">
@@ -48756,13 +48756,13 @@
         <v>2205</v>
       </c>
       <c r="F1281" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1281" s="2">
         <v>0</v>
       </c>
       <c r="H1281" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1282" spans="1:8" x14ac:dyDescent="0.25">
@@ -48860,13 +48860,13 @@
         <v>2205</v>
       </c>
       <c r="F1285" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1285" s="2">
         <v>0</v>
       </c>
       <c r="H1285" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1286" spans="1:8" x14ac:dyDescent="0.25">
@@ -50966,13 +50966,13 @@
         <v>3317</v>
       </c>
       <c r="F1366" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G1366" s="2">
         <v>0</v>
       </c>
       <c r="H1366" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1367" spans="1:8" x14ac:dyDescent="0.25">
@@ -53306,13 +53306,13 @@
         <v>2464</v>
       </c>
       <c r="F1456" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G1456" s="2">
         <v>0</v>
       </c>
       <c r="H1456" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1457" spans="1:8" x14ac:dyDescent="0.25">
@@ -75458,13 +75458,13 @@
         <v>4410</v>
       </c>
       <c r="F2308" s="2">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G2308" s="2">
         <v>0</v>
       </c>
       <c r="H2308" s="2">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2309" spans="1:8" x14ac:dyDescent="0.25">
@@ -81644,13 +81644,13 @@
         <v>2108</v>
       </c>
       <c r="F2546" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2546" s="2">
         <v>0</v>
       </c>
       <c r="H2546" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2547" spans="1:8" x14ac:dyDescent="0.25">
@@ -85024,13 +85024,13 @@
         <v>2174</v>
       </c>
       <c r="F2676" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2676" s="2">
         <v>0</v>
       </c>
       <c r="H2676" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2677" spans="1:8" x14ac:dyDescent="0.25">
@@ -86714,13 +86714,13 @@
         <v>2174</v>
       </c>
       <c r="F2741" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2741" s="2">
         <v>0</v>
       </c>
       <c r="H2741" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2742" spans="1:8" x14ac:dyDescent="0.25">
@@ -88508,13 +88508,13 @@
         <v>2174</v>
       </c>
       <c r="F2810" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G2810" s="2">
         <v>0</v>
       </c>
       <c r="H2810" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2811" spans="1:8" x14ac:dyDescent="0.25">
@@ -88716,13 +88716,13 @@
         <v>2113</v>
       </c>
       <c r="F2818" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G2818" s="2">
         <v>0</v>
       </c>
       <c r="H2818" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2819" spans="1:8" x14ac:dyDescent="0.25">
@@ -89132,13 +89132,13 @@
         <v>2113</v>
       </c>
       <c r="F2834" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G2834" s="2">
         <v>0</v>
       </c>
       <c r="H2834" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2835" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79E96B7-6916-49B9-AA94-FAD829F1BFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B5F42D-039E-4734-B80B-701B9FE8BE2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -16403,10 +16403,10 @@
         <v>38</v>
       </c>
       <c r="G36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16946,13 +16946,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17469,10 +17469,10 @@
         <v>129</v>
       </c>
       <c r="G77" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17648,13 +17648,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>612</v>
+        <v>584</v>
       </c>
       <c r="G84" s="2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H84" s="2">
-        <v>612</v>
+        <v>570</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17960,13 +17960,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G96" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" s="2">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="G97" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H97" s="2">
-        <v>450</v>
+        <v>439</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18168,13 +18168,13 @@
         <v>2144</v>
       </c>
       <c r="F104" s="2">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G104" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H104" s="2">
-        <v>44</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -27290,13 +27290,13 @@
         <v>2136</v>
       </c>
       <c r="F455" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G455" s="2">
         <v>0</v>
       </c>
       <c r="H455" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.25">
@@ -28562,13 +28562,13 @@
         <v>2136</v>
       </c>
       <c r="F504" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G504" s="2">
         <v>0</v>
       </c>
       <c r="H504" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
@@ -32406,13 +32406,13 @@
         <v>2136</v>
       </c>
       <c r="F652" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G652" s="2">
         <v>0</v>
       </c>
       <c r="H652" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="653" spans="1:8" x14ac:dyDescent="0.25">
@@ -34824,13 +34824,13 @@
         <v>2284</v>
       </c>
       <c r="F745" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G745" s="2">
         <v>0</v>
       </c>
       <c r="H745" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="746" spans="1:8" x14ac:dyDescent="0.25">
@@ -44546,13 +44546,13 @@
         <v>3112</v>
       </c>
       <c r="F1119" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G1119" s="2">
         <v>0</v>
       </c>
       <c r="H1119" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1120" spans="1:8" x14ac:dyDescent="0.25">
@@ -75458,13 +75458,13 @@
         <v>4410</v>
       </c>
       <c r="F2308" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G2308" s="2">
         <v>0</v>
       </c>
       <c r="H2308" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2309" spans="1:8" x14ac:dyDescent="0.25">
@@ -81852,13 +81852,13 @@
         <v>4714</v>
       </c>
       <c r="F2554" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2554" s="2">
         <v>0</v>
       </c>
       <c r="H2554" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2555" spans="1:8" x14ac:dyDescent="0.25">
@@ -85024,13 +85024,13 @@
         <v>2174</v>
       </c>
       <c r="F2676" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2676" s="2">
         <v>0</v>
       </c>
       <c r="H2676" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2677" spans="1:8" x14ac:dyDescent="0.25">
@@ -85492,13 +85492,13 @@
         <v>2113</v>
       </c>
       <c r="F2694" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G2694" s="2">
         <v>0</v>
       </c>
       <c r="H2694" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2695" spans="1:8" x14ac:dyDescent="0.25">
@@ -87390,13 +87390,13 @@
         <v>2106</v>
       </c>
       <c r="F2767" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2767" s="2">
         <v>0</v>
       </c>
       <c r="H2767" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2768" spans="1:8" x14ac:dyDescent="0.25">
@@ -87468,13 +87468,13 @@
         <v>3356</v>
       </c>
       <c r="F2770" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G2770" s="2">
         <v>0</v>
       </c>
       <c r="H2770" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2771" spans="1:8" x14ac:dyDescent="0.25">
@@ -87598,13 +87598,13 @@
         <v>3288</v>
       </c>
       <c r="F2775" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G2775" s="2">
         <v>0</v>
       </c>
       <c r="H2775" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2776" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B5F42D-039E-4734-B80B-701B9FE8BE2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3286A11-40AA-455C-86F3-E24DCD56EE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -15958,13 +15958,13 @@
         <v>2106</v>
       </c>
       <c r="F19" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
       </c>
       <c r="H19" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -16400,13 +16400,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="G36" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>37</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -17466,13 +17466,13 @@
         <v>2144</v>
       </c>
       <c r="F77" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17648,13 +17648,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>584</v>
+        <v>539</v>
       </c>
       <c r="G84" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H84" s="2">
-        <v>570</v>
+        <v>529</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17960,13 +17960,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G96" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H96" s="2">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="G97" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>439</v>
+        <v>427</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18038,13 +18038,13 @@
         <v>2103</v>
       </c>
       <c r="F99" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
       </c>
       <c r="H99" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -18168,13 +18168,13 @@
         <v>2144</v>
       </c>
       <c r="F104" s="2">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G104" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H104" s="2">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -18272,13 +18272,13 @@
         <v>2144</v>
       </c>
       <c r="F108" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
       </c>
       <c r="H108" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -18684,13 +18684,13 @@
         <v>2161</v>
       </c>
       <c r="F124" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G124" s="2">
         <v>0</v>
       </c>
       <c r="H124" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -27550,13 +27550,13 @@
         <v>2196</v>
       </c>
       <c r="F465" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G465" s="2">
         <v>0</v>
       </c>
       <c r="H465" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.25">
@@ -27628,13 +27628,13 @@
         <v>2136</v>
       </c>
       <c r="F468" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G468" s="2">
         <v>0</v>
       </c>
       <c r="H468" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.25">
@@ -27680,13 +27680,13 @@
         <v>2136</v>
       </c>
       <c r="F470" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G470" s="2">
         <v>0</v>
       </c>
       <c r="H470" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.25">
@@ -28018,13 +28018,13 @@
         <v>2606</v>
       </c>
       <c r="F483" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G483" s="2">
         <v>0</v>
       </c>
       <c r="H483" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.25">
@@ -28562,13 +28562,13 @@
         <v>2136</v>
       </c>
       <c r="F504" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G504" s="2">
         <v>0</v>
       </c>
       <c r="H504" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
@@ -31732,13 +31732,13 @@
         <v>2722</v>
       </c>
       <c r="F626" s="2">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="G626" s="2">
         <v>0</v>
       </c>
       <c r="H626" s="2">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="627" spans="1:8" x14ac:dyDescent="0.25">
@@ -32692,13 +32692,13 @@
         <v>2619</v>
       </c>
       <c r="F663" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G663" s="2">
         <v>0</v>
       </c>
       <c r="H663" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="664" spans="1:8" x14ac:dyDescent="0.25">
@@ -32952,13 +32952,13 @@
         <v>2619</v>
       </c>
       <c r="F673" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G673" s="2">
         <v>0</v>
       </c>
       <c r="H673" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
@@ -34694,13 +34694,13 @@
         <v>2284</v>
       </c>
       <c r="F740" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G740" s="2">
         <v>0</v>
       </c>
       <c r="H740" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
@@ -35006,13 +35006,13 @@
         <v>2284</v>
       </c>
       <c r="F752" s="2">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="G752" s="2">
         <v>0</v>
       </c>
       <c r="H752" s="2">
-        <v>68</v>
+        <v>28</v>
       </c>
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.25">
@@ -39088,13 +39088,13 @@
         <v>2957</v>
       </c>
       <c r="F909" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G909" s="2">
         <v>0</v>
       </c>
       <c r="H909" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="910" spans="1:8" x14ac:dyDescent="0.25">
@@ -39530,13 +39530,13 @@
         <v>2968</v>
       </c>
       <c r="F926" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G926" s="2">
         <v>0</v>
       </c>
       <c r="H926" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="927" spans="1:8" x14ac:dyDescent="0.25">
@@ -44546,13 +44546,13 @@
         <v>3112</v>
       </c>
       <c r="F1119" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G1119" s="2">
         <v>0</v>
       </c>
       <c r="H1119" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1120" spans="1:8" x14ac:dyDescent="0.25">
@@ -53202,13 +53202,13 @@
         <v>2464</v>
       </c>
       <c r="F1452" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G1452" s="2">
         <v>0</v>
       </c>
       <c r="H1452" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1453" spans="1:8" x14ac:dyDescent="0.25">
@@ -62952,13 +62952,13 @@
         <v>3848</v>
       </c>
       <c r="F1827" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1827" s="2">
         <v>0</v>
       </c>
       <c r="H1827" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1828" spans="1:8" x14ac:dyDescent="0.25">
@@ -66826,10 +66826,10 @@
         <v>2106</v>
       </c>
       <c r="F1976" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1976" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1976" s="2">
         <v>0</v>
@@ -68984,10 +68984,10 @@
         <v>2122</v>
       </c>
       <c r="F2059" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2059" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2059" s="2">
         <v>0</v>
@@ -75458,13 +75458,13 @@
         <v>4410</v>
       </c>
       <c r="F2308" s="2">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G2308" s="2">
         <v>0</v>
       </c>
       <c r="H2308" s="2">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2309" spans="1:8" x14ac:dyDescent="0.25">
@@ -78058,10 +78058,10 @@
         <v>2101</v>
       </c>
       <c r="F2408" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2408" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2408" s="2">
         <v>0</v>
@@ -81228,13 +81228,13 @@
         <v>3356</v>
       </c>
       <c r="F2530" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2530" s="2">
         <v>0</v>
       </c>
       <c r="H2530" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2531" spans="1:8" x14ac:dyDescent="0.25">
@@ -85206,13 +85206,13 @@
         <v>2174</v>
       </c>
       <c r="F2683" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G2683" s="2">
         <v>0</v>
       </c>
       <c r="H2683" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2684" spans="1:8" x14ac:dyDescent="0.25">
@@ -85492,13 +85492,13 @@
         <v>2113</v>
       </c>
       <c r="F2694" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2694" s="2">
         <v>0</v>
       </c>
       <c r="H2694" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2695" spans="1:8" x14ac:dyDescent="0.25">
@@ -86714,13 +86714,13 @@
         <v>2174</v>
       </c>
       <c r="F2741" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2741" s="2">
         <v>0</v>
       </c>
       <c r="H2741" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2742" spans="1:8" x14ac:dyDescent="0.25">
@@ -89132,13 +89132,13 @@
         <v>2113</v>
       </c>
       <c r="F2834" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G2834" s="2">
         <v>0</v>
       </c>
       <c r="H2834" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2835" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3286A11-40AA-455C-86F3-E24DCD56EE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579FA345-A064-4197-A98F-A7660702BEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -16400,13 +16400,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16946,13 +16946,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17076,13 +17076,13 @@
         <v>2118</v>
       </c>
       <c r="F62" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -17648,13 +17648,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>539</v>
+        <v>481</v>
       </c>
       <c r="G84" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H84" s="2">
-        <v>529</v>
+        <v>474</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17960,13 +17960,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G96" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H96" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="G97" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H97" s="2">
-        <v>427</v>
+        <v>411</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18038,13 +18038,13 @@
         <v>2103</v>
       </c>
       <c r="F99" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
       </c>
       <c r="H99" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -18064,13 +18064,13 @@
         <v>2103</v>
       </c>
       <c r="F100" s="2">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G100" s="2">
         <v>0</v>
       </c>
       <c r="H100" s="2">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -18168,13 +18168,13 @@
         <v>2144</v>
       </c>
       <c r="F104" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G104" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H104" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -21310,13 +21310,13 @@
         <v>2136</v>
       </c>
       <c r="F225" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G225" s="2">
         <v>0</v>
       </c>
       <c r="H225" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
@@ -24586,13 +24586,13 @@
         <v>2090</v>
       </c>
       <c r="F351" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G351" s="2">
         <v>0</v>
       </c>
       <c r="H351" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.25">
@@ -27810,13 +27810,13 @@
         <v>2606</v>
       </c>
       <c r="F475" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G475" s="2">
         <v>0</v>
       </c>
       <c r="H475" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.25">
@@ -28562,13 +28562,13 @@
         <v>2136</v>
       </c>
       <c r="F504" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G504" s="2">
         <v>0</v>
       </c>
       <c r="H504" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
@@ -28588,13 +28588,13 @@
         <v>2627</v>
       </c>
       <c r="F505" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G505" s="2">
         <v>0</v>
       </c>
       <c r="H505" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
@@ -32224,13 +32224,13 @@
         <v>2619</v>
       </c>
       <c r="F645" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G645" s="2">
         <v>0</v>
       </c>
       <c r="H645" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
@@ -32250,13 +32250,13 @@
         <v>2619</v>
       </c>
       <c r="F646" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G646" s="2">
         <v>0</v>
       </c>
       <c r="H646" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.25">
@@ -32406,13 +32406,13 @@
         <v>2136</v>
       </c>
       <c r="F652" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G652" s="2">
         <v>0</v>
       </c>
       <c r="H652" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="653" spans="1:8" x14ac:dyDescent="0.25">
@@ -32952,13 +32952,13 @@
         <v>2619</v>
       </c>
       <c r="F673" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G673" s="2">
         <v>0</v>
       </c>
       <c r="H673" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
@@ -34278,13 +34278,13 @@
         <v>2619</v>
       </c>
       <c r="F724" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G724" s="2">
         <v>0</v>
       </c>
       <c r="H724" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="725" spans="1:8" x14ac:dyDescent="0.25">
@@ -34382,13 +34382,13 @@
         <v>2619</v>
       </c>
       <c r="F728" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G728" s="2">
         <v>0</v>
       </c>
       <c r="H728" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="729" spans="1:8" x14ac:dyDescent="0.25">
@@ -34694,13 +34694,13 @@
         <v>2284</v>
       </c>
       <c r="F740" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G740" s="2">
         <v>0</v>
       </c>
       <c r="H740" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
@@ -34798,13 +34798,13 @@
         <v>2284</v>
       </c>
       <c r="F744" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G744" s="2">
         <v>0</v>
       </c>
       <c r="H744" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.25">
@@ -34824,13 +34824,13 @@
         <v>2284</v>
       </c>
       <c r="F745" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G745" s="2">
         <v>0</v>
       </c>
       <c r="H745" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="746" spans="1:8" x14ac:dyDescent="0.25">
@@ -34954,13 +34954,13 @@
         <v>2284</v>
       </c>
       <c r="F750" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G750" s="2">
         <v>0</v>
       </c>
       <c r="H750" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="751" spans="1:8" x14ac:dyDescent="0.25">
@@ -37892,13 +37892,13 @@
         <v>2122</v>
       </c>
       <c r="F863" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G863" s="2">
         <v>0</v>
       </c>
       <c r="H863" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="864" spans="1:8" x14ac:dyDescent="0.25">
@@ -38932,13 +38932,13 @@
         <v>2566</v>
       </c>
       <c r="F903" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G903" s="2">
         <v>0</v>
       </c>
       <c r="H903" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="904" spans="1:8" x14ac:dyDescent="0.25">
@@ -39088,13 +39088,13 @@
         <v>2957</v>
       </c>
       <c r="F909" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G909" s="2">
         <v>0</v>
       </c>
       <c r="H909" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="910" spans="1:8" x14ac:dyDescent="0.25">
@@ -39530,13 +39530,13 @@
         <v>2968</v>
       </c>
       <c r="F926" s="2">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="G926" s="2">
         <v>0</v>
       </c>
       <c r="H926" s="2">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="927" spans="1:8" x14ac:dyDescent="0.25">
@@ -48860,13 +48860,13 @@
         <v>2205</v>
       </c>
       <c r="F1285" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1285" s="2">
         <v>0</v>
       </c>
       <c r="H1285" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1286" spans="1:8" x14ac:dyDescent="0.25">
@@ -50992,13 +50992,13 @@
         <v>3356</v>
       </c>
       <c r="F1367" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1367" s="2">
         <v>0</v>
       </c>
       <c r="H1367" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1368" spans="1:8" x14ac:dyDescent="0.25">
@@ -51044,13 +51044,13 @@
         <v>3317</v>
       </c>
       <c r="F1369" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1369" s="2">
         <v>0</v>
       </c>
       <c r="H1369" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1370" spans="1:8" x14ac:dyDescent="0.25">
@@ -53202,13 +53202,13 @@
         <v>2464</v>
       </c>
       <c r="F1452" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G1452" s="2">
         <v>0</v>
       </c>
       <c r="H1452" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1453" spans="1:8" x14ac:dyDescent="0.25">
@@ -75458,13 +75458,13 @@
         <v>4410</v>
       </c>
       <c r="F2308" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G2308" s="2">
         <v>0</v>
       </c>
       <c r="H2308" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2309" spans="1:8" x14ac:dyDescent="0.25">
@@ -84738,13 +84738,13 @@
         <v>2174</v>
       </c>
       <c r="F2665" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2665" s="2">
         <v>0</v>
       </c>
       <c r="H2665" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2666" spans="1:8" x14ac:dyDescent="0.25">
@@ -85024,13 +85024,13 @@
         <v>2174</v>
       </c>
       <c r="F2676" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2676" s="2">
         <v>0</v>
       </c>
       <c r="H2676" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2677" spans="1:8" x14ac:dyDescent="0.25">
@@ -85206,13 +85206,13 @@
         <v>2174</v>
       </c>
       <c r="F2683" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G2683" s="2">
         <v>0</v>
       </c>
       <c r="H2683" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2684" spans="1:8" x14ac:dyDescent="0.25">
@@ -85492,13 +85492,13 @@
         <v>2113</v>
       </c>
       <c r="F2694" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G2694" s="2">
         <v>0</v>
       </c>
       <c r="H2694" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2695" spans="1:8" x14ac:dyDescent="0.25">
@@ -85830,13 +85830,13 @@
         <v>2448</v>
       </c>
       <c r="F2707" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2707" s="2">
         <v>0</v>
       </c>
       <c r="H2707" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2708" spans="1:8" x14ac:dyDescent="0.25">
@@ -86662,13 +86662,13 @@
         <v>4939</v>
       </c>
       <c r="F2739" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G2739" s="2">
         <v>0</v>
       </c>
       <c r="H2739" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2740" spans="1:8" x14ac:dyDescent="0.25">
@@ -86714,13 +86714,13 @@
         <v>2174</v>
       </c>
       <c r="F2741" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2741" s="2">
         <v>0</v>
       </c>
       <c r="H2741" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2742" spans="1:8" x14ac:dyDescent="0.25">
@@ -88508,13 +88508,13 @@
         <v>2174</v>
       </c>
       <c r="F2810" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G2810" s="2">
         <v>0</v>
       </c>
       <c r="H2810" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2811" spans="1:8" x14ac:dyDescent="0.25">
@@ -88716,13 +88716,13 @@
         <v>2113</v>
       </c>
       <c r="F2818" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G2818" s="2">
         <v>0</v>
       </c>
       <c r="H2818" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2819" spans="1:8" x14ac:dyDescent="0.25">
@@ -89132,13 +89132,13 @@
         <v>2113</v>
       </c>
       <c r="F2834" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G2834" s="2">
         <v>0</v>
       </c>
       <c r="H2834" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2835" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579FA345-A064-4197-A98F-A7660702BEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B128B731-81B6-4AC4-8596-F14B4BA398F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -16400,13 +16400,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16946,13 +16946,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17466,13 +17466,13 @@
         <v>2144</v>
       </c>
       <c r="F77" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17648,13 +17648,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>481</v>
+        <v>447</v>
       </c>
       <c r="G84" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>474</v>
+        <v>447</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17960,13 +17960,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G96" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="G97" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18064,13 +18064,13 @@
         <v>2103</v>
       </c>
       <c r="F100" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G100" s="2">
         <v>0</v>
       </c>
       <c r="H100" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -20556,13 +20556,13 @@
         <v>2086</v>
       </c>
       <c r="F196" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G196" s="2">
         <v>0</v>
       </c>
       <c r="H196" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
@@ -29290,13 +29290,13 @@
         <v>2373</v>
       </c>
       <c r="F532" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G532" s="2">
         <v>0</v>
       </c>
       <c r="H532" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.25">
@@ -32952,13 +32952,13 @@
         <v>2619</v>
       </c>
       <c r="F673" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G673" s="2">
         <v>0</v>
       </c>
       <c r="H673" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
@@ -34694,13 +34694,13 @@
         <v>2284</v>
       </c>
       <c r="F740" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G740" s="2">
         <v>0</v>
       </c>
       <c r="H740" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
@@ -35006,13 +35006,13 @@
         <v>2284</v>
       </c>
       <c r="F752" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G752" s="2">
         <v>0</v>
       </c>
       <c r="H752" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.25">
@@ -48626,13 +48626,13 @@
         <v>2116</v>
       </c>
       <c r="F1276" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1276" s="2">
         <v>0</v>
       </c>
       <c r="H1276" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1277" spans="1:8" x14ac:dyDescent="0.25">
@@ -48756,13 +48756,13 @@
         <v>2205</v>
       </c>
       <c r="F1281" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1281" s="2">
         <v>0</v>
       </c>
       <c r="H1281" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1282" spans="1:8" x14ac:dyDescent="0.25">
@@ -75458,13 +75458,13 @@
         <v>4410</v>
       </c>
       <c r="F2308" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G2308" s="2">
         <v>0</v>
       </c>
       <c r="H2308" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2309" spans="1:8" x14ac:dyDescent="0.25">
@@ -84738,13 +84738,13 @@
         <v>2174</v>
       </c>
       <c r="F2665" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G2665" s="2">
         <v>0</v>
       </c>
       <c r="H2665" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2666" spans="1:8" x14ac:dyDescent="0.25">
@@ -85024,13 +85024,13 @@
         <v>2174</v>
       </c>
       <c r="F2676" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2676" s="2">
         <v>0</v>
       </c>
       <c r="H2676" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2677" spans="1:8" x14ac:dyDescent="0.25">
@@ -86662,13 +86662,13 @@
         <v>4939</v>
       </c>
       <c r="F2739" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2739" s="2">
         <v>0</v>
       </c>
       <c r="H2739" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2740" spans="1:8" x14ac:dyDescent="0.25">
@@ -89132,13 +89132,13 @@
         <v>2113</v>
       </c>
       <c r="F2834" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2834" s="2">
         <v>0</v>
       </c>
       <c r="H2834" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2835" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B128B731-81B6-4AC4-8596-F14B4BA398F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0004EE81-676E-4CEB-9CC0-4EF93AD9187A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -16946,13 +16946,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17466,13 +17466,13 @@
         <v>2144</v>
       </c>
       <c r="F77" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17492,13 +17492,13 @@
         <v>2144</v>
       </c>
       <c r="F78" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17648,13 +17648,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>447</v>
+        <v>431</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17960,13 +17960,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G96" s="2">
         <v>0</v>
       </c>
       <c r="H96" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>401</v>
+        <v>390</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18064,13 +18064,13 @@
         <v>2103</v>
       </c>
       <c r="F100" s="2">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G100" s="2">
         <v>0</v>
       </c>
       <c r="H100" s="2">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -35006,13 +35006,13 @@
         <v>2284</v>
       </c>
       <c r="F752" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G752" s="2">
         <v>0</v>
       </c>
       <c r="H752" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.25">
@@ -45610,13 +45610,13 @@
         <v>3118</v>
       </c>
       <c r="F1160" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G1160" s="2">
         <v>0</v>
       </c>
       <c r="H1160" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1161" spans="1:8" x14ac:dyDescent="0.25">
@@ -48756,13 +48756,13 @@
         <v>2205</v>
       </c>
       <c r="F1281" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1281" s="2">
         <v>0</v>
       </c>
       <c r="H1281" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1282" spans="1:8" x14ac:dyDescent="0.25">
@@ -53202,13 +53202,13 @@
         <v>2464</v>
       </c>
       <c r="F1452" s="2">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G1452" s="2">
         <v>0</v>
       </c>
       <c r="H1452" s="2">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1453" spans="1:8" x14ac:dyDescent="0.25">
@@ -84738,13 +84738,13 @@
         <v>2174</v>
       </c>
       <c r="F2665" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2665" s="2">
         <v>0</v>
       </c>
       <c r="H2665" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2666" spans="1:8" x14ac:dyDescent="0.25">
@@ -86662,13 +86662,13 @@
         <v>4939</v>
       </c>
       <c r="F2739" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2739" s="2">
         <v>0</v>
       </c>
       <c r="H2739" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2740" spans="1:8" x14ac:dyDescent="0.25">
@@ -86714,13 +86714,13 @@
         <v>2174</v>
       </c>
       <c r="F2741" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2741" s="2">
         <v>0</v>
       </c>
       <c r="H2741" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2742" spans="1:8" x14ac:dyDescent="0.25">
@@ -89132,13 +89132,13 @@
         <v>2113</v>
       </c>
       <c r="F2834" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G2834" s="2">
         <v>0</v>
       </c>
       <c r="H2834" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2835" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0004EE81-676E-4CEB-9CC0-4EF93AD9187A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0F473E-ACC3-420E-A47D-36E11FF9DEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -16764,13 +16764,13 @@
         <v>2113</v>
       </c>
       <c r="F50" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G50" s="2">
         <v>0</v>
       </c>
       <c r="H50" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -17466,13 +17466,13 @@
         <v>2144</v>
       </c>
       <c r="F77" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G77" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17492,13 +17492,13 @@
         <v>2144</v>
       </c>
       <c r="F78" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17648,13 +17648,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>431</v>
+        <v>408</v>
       </c>
       <c r="G84" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H84" s="2">
-        <v>431</v>
+        <v>406</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17960,13 +17960,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G96" s="2">
         <v>0</v>
       </c>
       <c r="H96" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="G97" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97" s="2">
-        <v>390</v>
+        <v>377</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18064,13 +18064,13 @@
         <v>2103</v>
       </c>
       <c r="F100" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G100" s="2">
         <v>0</v>
       </c>
       <c r="H100" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -32588,13 +32588,13 @@
         <v>2619</v>
       </c>
       <c r="F659" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G659" s="2">
         <v>0</v>
       </c>
       <c r="H659" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="660" spans="1:8" x14ac:dyDescent="0.25">
@@ -32692,13 +32692,13 @@
         <v>2619</v>
       </c>
       <c r="F663" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G663" s="2">
         <v>0</v>
       </c>
       <c r="H663" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="664" spans="1:8" x14ac:dyDescent="0.25">
@@ -32952,13 +32952,13 @@
         <v>2619</v>
       </c>
       <c r="F673" s="2">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="G673" s="2">
         <v>0</v>
       </c>
       <c r="H673" s="2">
-        <v>4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
@@ -33238,13 +33238,13 @@
         <v>2606</v>
       </c>
       <c r="F684" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G684" s="2">
         <v>0</v>
       </c>
       <c r="H684" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="685" spans="1:8" x14ac:dyDescent="0.25">
@@ -34304,13 +34304,13 @@
         <v>2619</v>
       </c>
       <c r="F725" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G725" s="2">
         <v>0</v>
       </c>
       <c r="H725" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="726" spans="1:8" x14ac:dyDescent="0.25">
@@ -34694,13 +34694,13 @@
         <v>2284</v>
       </c>
       <c r="F740" s="2">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="G740" s="2">
         <v>0</v>
       </c>
       <c r="H740" s="2">
-        <v>1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
@@ -34798,13 +34798,13 @@
         <v>2284</v>
       </c>
       <c r="F744" s="2">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="G744" s="2">
         <v>0</v>
       </c>
       <c r="H744" s="2">
-        <v>48</v>
+        <v>88</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.25">
@@ -34824,13 +34824,13 @@
         <v>2284</v>
       </c>
       <c r="F745" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G745" s="2">
         <v>0</v>
       </c>
       <c r="H745" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="746" spans="1:8" x14ac:dyDescent="0.25">
@@ -38932,13 +38932,13 @@
         <v>2566</v>
       </c>
       <c r="F903" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G903" s="2">
         <v>0</v>
       </c>
       <c r="H903" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="904" spans="1:8" x14ac:dyDescent="0.25">
@@ -39530,13 +39530,13 @@
         <v>2968</v>
       </c>
       <c r="F926" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G926" s="2">
         <v>0</v>
       </c>
       <c r="H926" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="927" spans="1:8" x14ac:dyDescent="0.25">
@@ -45610,13 +45610,13 @@
         <v>3118</v>
       </c>
       <c r="F1160" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G1160" s="2">
         <v>0</v>
       </c>
       <c r="H1160" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1161" spans="1:8" x14ac:dyDescent="0.25">
@@ -55438,13 +55438,13 @@
         <v>2116</v>
       </c>
       <c r="F1538" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G1538" s="2">
         <v>0</v>
       </c>
       <c r="H1538" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1539" spans="1:8" x14ac:dyDescent="0.25">
@@ -75458,13 +75458,13 @@
         <v>4410</v>
       </c>
       <c r="F2308" s="2">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G2308" s="2">
         <v>0</v>
       </c>
       <c r="H2308" s="2">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2309" spans="1:8" x14ac:dyDescent="0.25">
@@ -77226,13 +77226,13 @@
         <v>2389</v>
       </c>
       <c r="F2376" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2376" s="2">
         <v>0</v>
       </c>
       <c r="H2376" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2377" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0F473E-ACC3-420E-A47D-36E11FF9DEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3CD9079-BF5C-4632-AFD2-923A958F6A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -16400,13 +16400,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16894,13 +16894,13 @@
         <v>2116</v>
       </c>
       <c r="F55" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G55" s="2">
         <v>0</v>
       </c>
       <c r="H55" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -17466,13 +17466,13 @@
         <v>2144</v>
       </c>
       <c r="F77" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17492,13 +17492,13 @@
         <v>2144</v>
       </c>
       <c r="F78" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17648,13 +17648,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="G84" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H84" s="2">
-        <v>406</v>
+        <v>389</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17960,13 +17960,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G96" s="2">
         <v>0</v>
       </c>
       <c r="H96" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="G97" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>377</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18064,13 +18064,13 @@
         <v>2103</v>
       </c>
       <c r="F100" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G100" s="2">
         <v>0</v>
       </c>
       <c r="H100" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -18272,13 +18272,13 @@
         <v>2144</v>
       </c>
       <c r="F108" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
       </c>
       <c r="H108" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -28562,13 +28562,13 @@
         <v>2136</v>
       </c>
       <c r="F504" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G504" s="2">
         <v>0</v>
       </c>
       <c r="H504" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
@@ -32952,13 +32952,13 @@
         <v>2619</v>
       </c>
       <c r="F673" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G673" s="2">
         <v>0</v>
       </c>
       <c r="H673" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
@@ -34382,13 +34382,13 @@
         <v>2619</v>
       </c>
       <c r="F728" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G728" s="2">
         <v>0</v>
       </c>
       <c r="H728" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="729" spans="1:8" x14ac:dyDescent="0.25">
@@ -34694,13 +34694,13 @@
         <v>2284</v>
       </c>
       <c r="F740" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G740" s="2">
         <v>0</v>
       </c>
       <c r="H740" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
@@ -34954,13 +34954,13 @@
         <v>2284</v>
       </c>
       <c r="F750" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G750" s="2">
         <v>0</v>
       </c>
       <c r="H750" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="751" spans="1:8" x14ac:dyDescent="0.25">
@@ -38932,13 +38932,13 @@
         <v>2566</v>
       </c>
       <c r="F903" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G903" s="2">
         <v>0</v>
       </c>
       <c r="H903" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="904" spans="1:8" x14ac:dyDescent="0.25">
@@ -44546,13 +44546,13 @@
         <v>3112</v>
       </c>
       <c r="F1119" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G1119" s="2">
         <v>0</v>
       </c>
       <c r="H1119" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1120" spans="1:8" x14ac:dyDescent="0.25">
@@ -63056,13 +63056,13 @@
         <v>3850</v>
       </c>
       <c r="F1831" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1831" s="2">
         <v>0</v>
       </c>
       <c r="H1831" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1832" spans="1:8" x14ac:dyDescent="0.25">
@@ -75458,13 +75458,13 @@
         <v>4410</v>
       </c>
       <c r="F2308" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G2308" s="2">
         <v>0</v>
       </c>
       <c r="H2308" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2309" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3CD9079-BF5C-4632-AFD2-923A958F6A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED733A23-FFE3-4BEF-8334-77F97B3ACAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -16946,13 +16946,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17466,13 +17466,13 @@
         <v>2144</v>
       </c>
       <c r="F77" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17492,13 +17492,13 @@
         <v>2144</v>
       </c>
       <c r="F78" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17648,13 +17648,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>390</v>
+        <v>357</v>
       </c>
       <c r="G84" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>389</v>
+        <v>357</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17960,13 +17960,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G96" s="2">
         <v>0</v>
       </c>
       <c r="H96" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>362</v>
+        <v>351</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -28562,13 +28562,13 @@
         <v>2136</v>
       </c>
       <c r="F504" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G504" s="2">
         <v>0</v>
       </c>
       <c r="H504" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
@@ -35058,13 +35058,13 @@
         <v>2284</v>
       </c>
       <c r="F754" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G754" s="2">
         <v>0</v>
       </c>
       <c r="H754" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="755" spans="1:8" x14ac:dyDescent="0.25">
@@ -37892,13 +37892,13 @@
         <v>2122</v>
       </c>
       <c r="F863" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G863" s="2">
         <v>0</v>
       </c>
       <c r="H863" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="864" spans="1:8" x14ac:dyDescent="0.25">
@@ -50966,13 +50966,13 @@
         <v>3317</v>
       </c>
       <c r="F1366" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1366" s="2">
         <v>0</v>
       </c>
       <c r="H1366" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1367" spans="1:8" x14ac:dyDescent="0.25">
@@ -63056,13 +63056,13 @@
         <v>3850</v>
       </c>
       <c r="F1831" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1831" s="2">
         <v>0</v>
       </c>
       <c r="H1831" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1832" spans="1:8" x14ac:dyDescent="0.25">
@@ -75458,13 +75458,13 @@
         <v>4410</v>
       </c>
       <c r="F2308" s="2">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G2308" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2308" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2309" spans="1:8" x14ac:dyDescent="0.25">
@@ -85492,13 +85492,13 @@
         <v>2113</v>
       </c>
       <c r="F2694" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2694" s="2">
         <v>0</v>
       </c>
       <c r="H2694" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2695" spans="1:8" x14ac:dyDescent="0.25">
@@ -88716,13 +88716,13 @@
         <v>2113</v>
       </c>
       <c r="F2818" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G2818" s="2">
         <v>0</v>
       </c>
       <c r="H2818" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2819" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED733A23-FFE3-4BEF-8334-77F97B3ACAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2D737F-3209-437D-BFCD-12CC4CD1BA7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -16140,13 +16140,13 @@
         <v>2109</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G26" s="2">
         <v>0</v>
       </c>
       <c r="H26" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -16400,13 +16400,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16946,13 +16946,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>76</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17050,13 +17050,13 @@
         <v>2113</v>
       </c>
       <c r="F61" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G61" s="2">
         <v>0</v>
       </c>
       <c r="H61" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -17466,13 +17466,13 @@
         <v>2144</v>
       </c>
       <c r="F77" s="2">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17492,13 +17492,13 @@
         <v>2144</v>
       </c>
       <c r="F78" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17518,13 +17518,13 @@
         <v>2144</v>
       </c>
       <c r="F79" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G79" s="2">
         <v>0</v>
       </c>
       <c r="H79" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -17648,13 +17648,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>357</v>
+        <v>254</v>
       </c>
       <c r="G84" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" s="2">
-        <v>357</v>
+        <v>253</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17960,13 +17960,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G96" s="2">
         <v>0</v>
       </c>
       <c r="H96" s="2">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>351</v>
+        <v>289</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>351</v>
+        <v>289</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18038,13 +18038,13 @@
         <v>2103</v>
       </c>
       <c r="F99" s="2">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
       </c>
       <c r="H99" s="2">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -18272,13 +18272,13 @@
         <v>2144</v>
       </c>
       <c r="F108" s="2">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
       </c>
       <c r="H108" s="2">
-        <v>43</v>
+        <v>60</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -22353,10 +22353,10 @@
         <v>1</v>
       </c>
       <c r="G265" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H265" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
@@ -28562,13 +28562,13 @@
         <v>2136</v>
       </c>
       <c r="F504" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G504" s="2">
         <v>0</v>
       </c>
       <c r="H504" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
@@ -32250,13 +32250,13 @@
         <v>2619</v>
       </c>
       <c r="F646" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G646" s="2">
         <v>0</v>
       </c>
       <c r="H646" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.25">
@@ -32406,13 +32406,13 @@
         <v>2136</v>
       </c>
       <c r="F652" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G652" s="2">
         <v>0</v>
       </c>
       <c r="H652" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="653" spans="1:8" x14ac:dyDescent="0.25">
@@ -32796,13 +32796,13 @@
         <v>2619</v>
       </c>
       <c r="F667" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G667" s="2">
         <v>0</v>
       </c>
       <c r="H667" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="668" spans="1:8" x14ac:dyDescent="0.25">
@@ -32926,13 +32926,13 @@
         <v>2619</v>
       </c>
       <c r="F672" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G672" s="2">
         <v>0</v>
       </c>
       <c r="H672" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="673" spans="1:8" x14ac:dyDescent="0.25">
@@ -32952,13 +32952,13 @@
         <v>2619</v>
       </c>
       <c r="F673" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G673" s="2">
         <v>0</v>
       </c>
       <c r="H673" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
@@ -32978,13 +32978,13 @@
         <v>2619</v>
       </c>
       <c r="F674" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G674" s="2">
         <v>0</v>
       </c>
       <c r="H674" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="675" spans="1:8" x14ac:dyDescent="0.25">
@@ -34174,13 +34174,13 @@
         <v>2106</v>
       </c>
       <c r="F720" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G720" s="2">
         <v>0</v>
       </c>
       <c r="H720" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.25">
@@ -34200,13 +34200,13 @@
         <v>2106</v>
       </c>
       <c r="F721" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G721" s="2">
         <v>0</v>
       </c>
       <c r="H721" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="722" spans="1:8" x14ac:dyDescent="0.25">
@@ -34694,13 +34694,13 @@
         <v>2284</v>
       </c>
       <c r="F740" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="G740" s="2">
         <v>0</v>
       </c>
       <c r="H740" s="2">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
@@ -34798,13 +34798,13 @@
         <v>2284</v>
       </c>
       <c r="F744" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G744" s="2">
         <v>0</v>
       </c>
       <c r="H744" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.25">
@@ -34824,13 +34824,13 @@
         <v>2284</v>
       </c>
       <c r="F745" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G745" s="2">
         <v>0</v>
       </c>
       <c r="H745" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="746" spans="1:8" x14ac:dyDescent="0.25">
@@ -34954,13 +34954,13 @@
         <v>2284</v>
       </c>
       <c r="F750" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G750" s="2">
         <v>0</v>
       </c>
       <c r="H750" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="751" spans="1:8" x14ac:dyDescent="0.25">
@@ -35058,13 +35058,13 @@
         <v>2284</v>
       </c>
       <c r="F754" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G754" s="2">
         <v>0</v>
       </c>
       <c r="H754" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="755" spans="1:8" x14ac:dyDescent="0.25">
@@ -38932,13 +38932,13 @@
         <v>2566</v>
       </c>
       <c r="F903" s="2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G903" s="2">
         <v>0</v>
       </c>
       <c r="H903" s="2">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="904" spans="1:8" x14ac:dyDescent="0.25">
@@ -39088,13 +39088,13 @@
         <v>2957</v>
       </c>
       <c r="F909" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G909" s="2">
         <v>0</v>
       </c>
       <c r="H909" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="910" spans="1:8" x14ac:dyDescent="0.25">
@@ -39504,13 +39504,13 @@
         <v>2968</v>
       </c>
       <c r="F925" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G925" s="2">
         <v>0</v>
       </c>
       <c r="H925" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="926" spans="1:8" x14ac:dyDescent="0.25">
@@ -44546,13 +44546,13 @@
         <v>3112</v>
       </c>
       <c r="F1119" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G1119" s="2">
         <v>0</v>
       </c>
       <c r="H1119" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1120" spans="1:8" x14ac:dyDescent="0.25">
@@ -50966,13 +50966,13 @@
         <v>3317</v>
       </c>
       <c r="F1366" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G1366" s="2">
         <v>0</v>
       </c>
       <c r="H1366" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1367" spans="1:8" x14ac:dyDescent="0.25">
@@ -53306,13 +53306,13 @@
         <v>2464</v>
       </c>
       <c r="F1456" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1456" s="2">
         <v>0</v>
       </c>
       <c r="H1456" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1457" spans="1:8" x14ac:dyDescent="0.25">
@@ -62978,13 +62978,13 @@
         <v>2106</v>
       </c>
       <c r="F1828" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1828" s="2">
         <v>0</v>
       </c>
       <c r="H1828" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1829" spans="1:8" x14ac:dyDescent="0.25">
@@ -75458,13 +75458,13 @@
         <v>4410</v>
       </c>
       <c r="F2308" s="2">
-        <v>92</v>
+        <v>175</v>
       </c>
       <c r="G2308" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2308" s="2">
-        <v>91</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2309" spans="1:8" x14ac:dyDescent="0.25">
@@ -84738,13 +84738,13 @@
         <v>2174</v>
       </c>
       <c r="F2665" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2665" s="2">
         <v>0</v>
       </c>
       <c r="H2665" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2666" spans="1:8" x14ac:dyDescent="0.25">
@@ -85492,13 +85492,13 @@
         <v>2113</v>
       </c>
       <c r="F2694" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2694" s="2">
         <v>0</v>
       </c>
       <c r="H2694" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2695" spans="1:8" x14ac:dyDescent="0.25">
@@ -86662,13 +86662,13 @@
         <v>4939</v>
       </c>
       <c r="F2739" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2739" s="2">
         <v>0</v>
       </c>
       <c r="H2739" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2740" spans="1:8" x14ac:dyDescent="0.25">
@@ -88508,13 +88508,13 @@
         <v>2174</v>
       </c>
       <c r="F2810" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G2810" s="2">
         <v>0</v>
       </c>
       <c r="H2810" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2811" spans="1:8" x14ac:dyDescent="0.25">
@@ -88716,13 +88716,13 @@
         <v>2113</v>
       </c>
       <c r="F2818" s="2">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="G2818" s="2">
         <v>0</v>
       </c>
       <c r="H2818" s="2">
-        <v>30</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2819" spans="1:8" x14ac:dyDescent="0.25">
@@ -89132,13 +89132,13 @@
         <v>2113</v>
       </c>
       <c r="F2834" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G2834" s="2">
         <v>0</v>
       </c>
       <c r="H2834" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2835" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\ILHAM GUSRIANTO\DATA SUMBER\Dashboar Bundling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2D737F-3209-437D-BFCD-12CC4CD1BA7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9799EDFD-EA33-4DDD-BCF8-4DDC797B5F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -16400,13 +16400,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16712,13 +16712,13 @@
         <v>2113</v>
       </c>
       <c r="F48" s="2">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="2">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -16946,13 +16946,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>117</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17076,13 +17076,13 @@
         <v>2118</v>
       </c>
       <c r="F62" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -17466,13 +17466,13 @@
         <v>2144</v>
       </c>
       <c r="F77" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17492,13 +17492,13 @@
         <v>2144</v>
       </c>
       <c r="F78" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17518,13 +17518,13 @@
         <v>2144</v>
       </c>
       <c r="F79" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G79" s="2">
         <v>0</v>
       </c>
       <c r="H79" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -17648,13 +17648,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>254</v>
+        <v>764</v>
       </c>
       <c r="G84" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H84" s="2">
-        <v>253</v>
+        <v>761</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17960,13 +17960,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G96" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H96" s="2">
-        <v>10</v>
+        <v>105</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>289</v>
+        <v>254</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>289</v>
+        <v>254</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18038,13 +18038,13 @@
         <v>2103</v>
       </c>
       <c r="F99" s="2">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
       </c>
       <c r="H99" s="2">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -18064,13 +18064,13 @@
         <v>2103</v>
       </c>
       <c r="F100" s="2">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="G100" s="2">
         <v>0</v>
       </c>
       <c r="H100" s="2">
-        <v>0</v>
+        <v>239</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -18168,13 +18168,13 @@
         <v>2144</v>
       </c>
       <c r="F104" s="2">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="G104" s="2">
         <v>0</v>
       </c>
       <c r="H104" s="2">
-        <v>0</v>
+        <v>421</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -18272,13 +18272,13 @@
         <v>2144</v>
       </c>
       <c r="F108" s="2">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
       </c>
       <c r="H108" s="2">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -19022,13 +19022,13 @@
         <v>2176</v>
       </c>
       <c r="F137" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137" s="2">
         <v>0</v>
       </c>
       <c r="H137" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -22246,13 +22246,13 @@
         <v>2090</v>
       </c>
       <c r="F261" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G261" s="2">
         <v>0</v>
       </c>
       <c r="H261" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
@@ -22350,10 +22350,10 @@
         <v>2090</v>
       </c>
       <c r="F265" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G265" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H265" s="2">
         <v>0</v>
@@ -26224,13 +26224,13 @@
         <v>2106</v>
       </c>
       <c r="F414" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G414" s="2">
         <v>0</v>
       </c>
       <c r="H414" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.25">
@@ -27680,13 +27680,13 @@
         <v>2136</v>
       </c>
       <c r="F470" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G470" s="2">
         <v>0</v>
       </c>
       <c r="H470" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.25">
@@ -27810,13 +27810,13 @@
         <v>2606</v>
       </c>
       <c r="F475" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G475" s="2">
         <v>0</v>
       </c>
       <c r="H475" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.25">
@@ -27914,13 +27914,13 @@
         <v>2237</v>
       </c>
       <c r="F479" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G479" s="2">
         <v>0</v>
       </c>
       <c r="H479" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
@@ -28562,13 +28562,13 @@
         <v>2136</v>
       </c>
       <c r="F504" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G504" s="2">
         <v>0</v>
       </c>
       <c r="H504" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
@@ -28588,13 +28588,13 @@
         <v>2627</v>
       </c>
       <c r="F505" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G505" s="2">
         <v>0</v>
       </c>
       <c r="H505" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
@@ -28744,13 +28744,13 @@
         <v>2627</v>
       </c>
       <c r="F511" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G511" s="2">
         <v>0</v>
       </c>
       <c r="H511" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512" spans="1:8" x14ac:dyDescent="0.25">
@@ -29290,13 +29290,13 @@
         <v>2373</v>
       </c>
       <c r="F532" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G532" s="2">
         <v>0</v>
       </c>
       <c r="H532" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.25">
@@ -32224,13 +32224,13 @@
         <v>2619</v>
       </c>
       <c r="F645" s="2">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G645" s="2">
         <v>0</v>
       </c>
       <c r="H645" s="2">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
@@ -32250,13 +32250,13 @@
         <v>2619</v>
       </c>
       <c r="F646" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G646" s="2">
         <v>0</v>
       </c>
       <c r="H646" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.25">
@@ -32406,13 +32406,13 @@
         <v>2136</v>
       </c>
       <c r="F652" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G652" s="2">
         <v>0</v>
       </c>
       <c r="H652" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="653" spans="1:8" x14ac:dyDescent="0.25">
@@ -32614,13 +32614,13 @@
         <v>2619</v>
       </c>
       <c r="F660" s="2">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G660" s="2">
         <v>0</v>
       </c>
       <c r="H660" s="2">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
@@ -32692,13 +32692,13 @@
         <v>2619</v>
       </c>
       <c r="F663" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G663" s="2">
         <v>0</v>
       </c>
       <c r="H663" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="664" spans="1:8" x14ac:dyDescent="0.25">
@@ -32926,13 +32926,13 @@
         <v>2619</v>
       </c>
       <c r="F672" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G672" s="2">
         <v>0</v>
       </c>
       <c r="H672" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="673" spans="1:8" x14ac:dyDescent="0.25">
@@ -32952,13 +32952,13 @@
         <v>2619</v>
       </c>
       <c r="F673" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G673" s="2">
         <v>0</v>
       </c>
       <c r="H673" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
@@ -33004,13 +33004,13 @@
         <v>2108</v>
       </c>
       <c r="F675" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G675" s="2">
         <v>0</v>
       </c>
       <c r="H675" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="676" spans="1:8" x14ac:dyDescent="0.25">
@@ -33056,13 +33056,13 @@
         <v>2103</v>
       </c>
       <c r="F677" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G677" s="2">
         <v>0</v>
       </c>
       <c r="H677" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="678" spans="1:8" x14ac:dyDescent="0.25">
@@ -33108,13 +33108,13 @@
         <v>2619</v>
       </c>
       <c r="F679" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G679" s="2">
         <v>0</v>
       </c>
       <c r="H679" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="680" spans="1:8" x14ac:dyDescent="0.25">
@@ -33134,13 +33134,13 @@
         <v>2619</v>
       </c>
       <c r="F680" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G680" s="2">
         <v>0</v>
       </c>
       <c r="H680" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="681" spans="1:8" x14ac:dyDescent="0.25">
@@ -34174,13 +34174,13 @@
         <v>2106</v>
       </c>
       <c r="F720" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G720" s="2">
         <v>0</v>
       </c>
       <c r="H720" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.25">
@@ -34200,13 +34200,13 @@
         <v>2106</v>
       </c>
       <c r="F721" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G721" s="2">
         <v>0</v>
       </c>
       <c r="H721" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="722" spans="1:8" x14ac:dyDescent="0.25">
@@ -34304,13 +34304,13 @@
         <v>2619</v>
       </c>
       <c r="F725" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G725" s="2">
         <v>0</v>
       </c>
       <c r="H725" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="726" spans="1:8" x14ac:dyDescent="0.25">
@@ -34382,13 +34382,13 @@
         <v>2619</v>
       </c>
       <c r="F728" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G728" s="2">
         <v>0</v>
       </c>
       <c r="H728" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="729" spans="1:8" x14ac:dyDescent="0.25">
@@ -34694,13 +34694,13 @@
         <v>2284</v>
       </c>
       <c r="F740" s="2">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="G740" s="2">
         <v>0</v>
       </c>
       <c r="H740" s="2">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
@@ -34798,13 +34798,13 @@
         <v>2284</v>
       </c>
       <c r="F744" s="2">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G744" s="2">
         <v>0</v>
       </c>
       <c r="H744" s="2">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.25">
@@ -34824,13 +34824,13 @@
         <v>2284</v>
       </c>
       <c r="F745" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G745" s="2">
         <v>0</v>
       </c>
       <c r="H745" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="746" spans="1:8" x14ac:dyDescent="0.25">
@@ -34954,13 +34954,13 @@
         <v>2284</v>
       </c>
       <c r="F750" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G750" s="2">
         <v>0</v>
       </c>
       <c r="H750" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="751" spans="1:8" x14ac:dyDescent="0.25">
@@ -35006,13 +35006,13 @@
         <v>2284</v>
       </c>
       <c r="F752" s="2">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G752" s="2">
         <v>0</v>
       </c>
       <c r="H752" s="2">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.25">
@@ -35110,13 +35110,13 @@
         <v>2284</v>
       </c>
       <c r="F756" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G756" s="2">
         <v>0</v>
       </c>
       <c r="H756" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="757" spans="1:8" x14ac:dyDescent="0.25">
@@ -36618,13 +36618,13 @@
         <v>2122</v>
       </c>
       <c r="F814" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G814" s="2">
         <v>0</v>
       </c>
       <c r="H814" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="815" spans="1:8" x14ac:dyDescent="0.25">
@@ -38932,13 +38932,13 @@
         <v>2566</v>
       </c>
       <c r="F903" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G903" s="2">
         <v>0</v>
       </c>
       <c r="H903" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="904" spans="1:8" x14ac:dyDescent="0.25">
@@ -39088,13 +39088,13 @@
         <v>2957</v>
       </c>
       <c r="F909" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G909" s="2">
         <v>0</v>
       </c>
       <c r="H909" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="910" spans="1:8" x14ac:dyDescent="0.25">
@@ -39530,13 +39530,13 @@
         <v>2968</v>
       </c>
       <c r="F926" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G926" s="2">
         <v>0</v>
       </c>
       <c r="H926" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="927" spans="1:8" x14ac:dyDescent="0.25">
@@ -44546,13 +44546,13 @@
         <v>3112</v>
       </c>
       <c r="F1119" s="2">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="G1119" s="2">
         <v>0</v>
       </c>
       <c r="H1119" s="2">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1120" spans="1:8" x14ac:dyDescent="0.25">
@@ -48860,13 +48860,13 @@
         <v>2205</v>
       </c>
       <c r="F1285" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1285" s="2">
         <v>0</v>
       </c>
       <c r="H1285" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1286" spans="1:8" x14ac:dyDescent="0.25">
@@ -50966,13 +50966,13 @@
         <v>3317</v>
       </c>
       <c r="F1366" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G1366" s="2">
         <v>0</v>
       </c>
       <c r="H1366" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1367" spans="1:8" x14ac:dyDescent="0.25">
@@ -51044,13 +51044,13 @@
         <v>3317</v>
       </c>
       <c r="F1369" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1369" s="2">
         <v>0</v>
       </c>
       <c r="H1369" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1370" spans="1:8" x14ac:dyDescent="0.25">
@@ -53176,13 +53176,13 @@
         <v>2464</v>
       </c>
       <c r="F1451" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G1451" s="2">
         <v>0</v>
       </c>
       <c r="H1451" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1452" spans="1:8" x14ac:dyDescent="0.25">
@@ -53202,13 +53202,13 @@
         <v>2464</v>
       </c>
       <c r="F1452" s="2">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="G1452" s="2">
         <v>0</v>
       </c>
       <c r="H1452" s="2">
-        <v>49</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1453" spans="1:8" x14ac:dyDescent="0.25">
@@ -55438,13 +55438,13 @@
         <v>2116</v>
       </c>
       <c r="F1538" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G1538" s="2">
         <v>0</v>
       </c>
       <c r="H1538" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1539" spans="1:8" x14ac:dyDescent="0.25">
@@ -55490,13 +55490,13 @@
         <v>2108</v>
       </c>
       <c r="F1540" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G1540" s="2">
         <v>0</v>
       </c>
       <c r="H1540" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1541" spans="1:8" x14ac:dyDescent="0.25">
@@ -63056,13 +63056,13 @@
         <v>3850</v>
       </c>
       <c r="F1831" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1831" s="2">
         <v>0</v>
       </c>
       <c r="H1831" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1832" spans="1:8" x14ac:dyDescent="0.25">
@@ -67762,13 +67762,13 @@
         <v>2113</v>
       </c>
       <c r="F2012" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2012" s="2">
         <v>0</v>
       </c>
       <c r="H2012" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2013" spans="1:8" x14ac:dyDescent="0.25">
@@ -74470,13 +74470,13 @@
         <v>3844</v>
       </c>
       <c r="F2270" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2270" s="2">
         <v>0</v>
       </c>
       <c r="H2270" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2271" spans="1:8" x14ac:dyDescent="0.25">
@@ -75458,13 +75458,13 @@
         <v>4410</v>
       </c>
       <c r="F2308" s="2">
-        <v>175</v>
+        <v>94</v>
       </c>
       <c r="G2308" s="2">
         <v>0</v>
       </c>
       <c r="H2308" s="2">
-        <v>175</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2309" spans="1:8" x14ac:dyDescent="0.25">
@@ -77226,13 +77226,13 @@
         <v>2389</v>
       </c>
       <c r="F2376" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2376" s="2">
         <v>0</v>
       </c>
       <c r="H2376" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2377" spans="1:8" x14ac:dyDescent="0.25">
@@ -81332,13 +81332,13 @@
         <v>3356</v>
       </c>
       <c r="F2534" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2534" s="2">
         <v>0</v>
       </c>
       <c r="H2534" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2535" spans="1:8" x14ac:dyDescent="0.25">
@@ -84738,13 +84738,13 @@
         <v>2174</v>
       </c>
       <c r="F2665" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G2665" s="2">
         <v>0</v>
       </c>
       <c r="H2665" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2666" spans="1:8" x14ac:dyDescent="0.25">
@@ -85024,13 +85024,13 @@
         <v>2174</v>
       </c>
       <c r="F2676" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2676" s="2">
         <v>0</v>
       </c>
       <c r="H2676" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2677" spans="1:8" x14ac:dyDescent="0.25">
@@ -85206,13 +85206,13 @@
         <v>2174</v>
       </c>
       <c r="F2683" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2683" s="2">
         <v>0</v>
       </c>
       <c r="H2683" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2684" spans="1:8" x14ac:dyDescent="0.25">
@@ -85232,13 +85232,13 @@
         <v>2174</v>
       </c>
       <c r="F2684" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2684" s="2">
         <v>0</v>
       </c>
       <c r="H2684" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2685" spans="1:8" x14ac:dyDescent="0.25">
@@ -85492,13 +85492,13 @@
         <v>2113</v>
       </c>
       <c r="F2694" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G2694" s="2">
         <v>0</v>
       </c>
       <c r="H2694" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2695" spans="1:8" x14ac:dyDescent="0.25">
@@ -86662,13 +86662,13 @@
         <v>4939</v>
       </c>
       <c r="F2739" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G2739" s="2">
         <v>0</v>
       </c>
       <c r="H2739" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2740" spans="1:8" x14ac:dyDescent="0.25">
@@ -86688,13 +86688,13 @@
         <v>4939</v>
       </c>
       <c r="F2740" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G2740" s="2">
         <v>0</v>
       </c>
       <c r="H2740" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2741" spans="1:8" x14ac:dyDescent="0.25">
@@ -87312,13 +87312,13 @@
         <v>2106</v>
       </c>
       <c r="F2764" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2764" s="2">
         <v>0</v>
       </c>
       <c r="H2764" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2765" spans="1:8" x14ac:dyDescent="0.25">
@@ -87520,13 +87520,13 @@
         <v>2106</v>
       </c>
       <c r="F2772" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2772" s="2">
         <v>0</v>
       </c>
       <c r="H2772" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2773" spans="1:8" x14ac:dyDescent="0.25">
@@ -88508,13 +88508,13 @@
         <v>2174</v>
       </c>
       <c r="F2810" s="2">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="G2810" s="2">
         <v>0</v>
       </c>
       <c r="H2810" s="2">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2811" spans="1:8" x14ac:dyDescent="0.25">
@@ -88716,13 +88716,13 @@
         <v>2113</v>
       </c>
       <c r="F2818" s="2">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G2818" s="2">
         <v>0</v>
       </c>
       <c r="H2818" s="2">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2819" spans="1:8" x14ac:dyDescent="0.25">
@@ -88768,13 +88768,13 @@
         <v>2113</v>
       </c>
       <c r="F2820" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G2820" s="2">
         <v>0</v>
       </c>
       <c r="H2820" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2821" spans="1:8" x14ac:dyDescent="0.25">
@@ -88794,13 +88794,13 @@
         <v>2113</v>
       </c>
       <c r="F2821" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G2821" s="2">
         <v>0</v>
       </c>
       <c r="H2821" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2822" spans="1:8" x14ac:dyDescent="0.25">
@@ -89106,13 +89106,13 @@
         <v>2090</v>
       </c>
       <c r="F2833" s="2">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G2833" s="2">
         <v>0</v>
       </c>
       <c r="H2833" s="2">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2834" spans="1:8" x14ac:dyDescent="0.25">
@@ -89132,13 +89132,13 @@
         <v>2113</v>
       </c>
       <c r="F2834" s="2">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G2834" s="2">
         <v>0</v>
       </c>
       <c r="H2834" s="2">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2835" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\ILHAM GUSRIANTO\DATA SUMBER\Dashboar Bundling\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PSD-SAA\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9799EDFD-EA33-4DDD-BCF8-4DDC797B5F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DFBAFD1-9402-49E1-9A97-DA1A93BACA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -15124,7 +15124,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -15958,13 +15958,13 @@
         <v>2106</v>
       </c>
       <c r="F19" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
       </c>
       <c r="H19" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -16400,13 +16400,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>61</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16504,13 +16504,13 @@
         <v>2114</v>
       </c>
       <c r="F40" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
       </c>
       <c r="H40" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -16712,13 +16712,13 @@
         <v>2113</v>
       </c>
       <c r="F48" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -16946,13 +16946,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G57" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17076,13 +17076,13 @@
         <v>2118</v>
       </c>
       <c r="F62" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -17466,13 +17466,13 @@
         <v>2144</v>
       </c>
       <c r="F77" s="2">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17492,13 +17492,13 @@
         <v>2144</v>
       </c>
       <c r="F78" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G78" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="2">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17518,13 +17518,13 @@
         <v>2144</v>
       </c>
       <c r="F79" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G79" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -17648,13 +17648,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>764</v>
+        <v>640</v>
       </c>
       <c r="G84" s="2">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H84" s="2">
-        <v>761</v>
+        <v>618</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17960,13 +17960,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="G96" s="2">
         <v>2</v>
       </c>
       <c r="H96" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>254</v>
+        <v>195</v>
       </c>
       <c r="G97" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H97" s="2">
-        <v>254</v>
+        <v>192</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18038,13 +18038,13 @@
         <v>2103</v>
       </c>
       <c r="F99" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G99" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99" s="2">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -18168,13 +18168,13 @@
         <v>2144</v>
       </c>
       <c r="F104" s="2">
-        <v>421</v>
+        <v>355</v>
       </c>
       <c r="G104" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H104" s="2">
-        <v>421</v>
+        <v>347</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -18272,13 +18272,13 @@
         <v>2144</v>
       </c>
       <c r="F108" s="2">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
       </c>
       <c r="H108" s="2">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -20504,13 +20504,13 @@
         <v>2086</v>
       </c>
       <c r="F194" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G194" s="2">
         <v>0</v>
       </c>
       <c r="H194" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
@@ -21443,10 +21443,10 @@
         <v>3</v>
       </c>
       <c r="G230" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H230" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
@@ -22116,13 +22116,13 @@
         <v>2103</v>
       </c>
       <c r="F256" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G256" s="2">
         <v>0</v>
       </c>
       <c r="H256" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
@@ -24404,13 +24404,13 @@
         <v>2106</v>
       </c>
       <c r="F344" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G344" s="2">
         <v>0</v>
       </c>
       <c r="H344" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.25">
@@ -24872,13 +24872,13 @@
         <v>2090</v>
       </c>
       <c r="F362" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G362" s="2">
         <v>0</v>
       </c>
       <c r="H362" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.25">
@@ -27810,13 +27810,13 @@
         <v>2606</v>
       </c>
       <c r="F475" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G475" s="2">
         <v>0</v>
       </c>
       <c r="H475" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.25">
@@ -27914,13 +27914,13 @@
         <v>2237</v>
       </c>
       <c r="F479" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G479" s="2">
         <v>0</v>
       </c>
       <c r="H479" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
@@ -28588,13 +28588,13 @@
         <v>2627</v>
       </c>
       <c r="F505" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G505" s="2">
         <v>0</v>
       </c>
       <c r="H505" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
@@ -29290,13 +29290,13 @@
         <v>2373</v>
       </c>
       <c r="F532" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G532" s="2">
         <v>0</v>
       </c>
       <c r="H532" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.25">
@@ -32224,13 +32224,13 @@
         <v>2619</v>
       </c>
       <c r="F645" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G645" s="2">
         <v>0</v>
       </c>
       <c r="H645" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
@@ -32614,13 +32614,13 @@
         <v>2619</v>
       </c>
       <c r="F660" s="2">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G660" s="2">
         <v>0</v>
       </c>
       <c r="H660" s="2">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
@@ -32692,13 +32692,13 @@
         <v>2619</v>
       </c>
       <c r="F663" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G663" s="2">
         <v>0</v>
       </c>
       <c r="H663" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="664" spans="1:8" x14ac:dyDescent="0.25">
@@ -32952,13 +32952,13 @@
         <v>2619</v>
       </c>
       <c r="F673" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G673" s="2">
         <v>0</v>
       </c>
       <c r="H673" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
@@ -33108,13 +33108,13 @@
         <v>2619</v>
       </c>
       <c r="F679" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G679" s="2">
         <v>0</v>
       </c>
       <c r="H679" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="680" spans="1:8" x14ac:dyDescent="0.25">
@@ -34200,13 +34200,13 @@
         <v>2106</v>
       </c>
       <c r="F721" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G721" s="2">
         <v>0</v>
       </c>
       <c r="H721" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="722" spans="1:8" x14ac:dyDescent="0.25">
@@ -34304,13 +34304,13 @@
         <v>2619</v>
       </c>
       <c r="F725" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G725" s="2">
         <v>0</v>
       </c>
       <c r="H725" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="726" spans="1:8" x14ac:dyDescent="0.25">
@@ -34694,13 +34694,13 @@
         <v>2284</v>
       </c>
       <c r="F740" s="2">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="G740" s="2">
         <v>0</v>
       </c>
       <c r="H740" s="2">
-        <v>71</v>
+        <v>56</v>
       </c>
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
@@ -34798,13 +34798,13 @@
         <v>2284</v>
       </c>
       <c r="F744" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G744" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H744" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.25">
@@ -34902,13 +34902,13 @@
         <v>2284</v>
       </c>
       <c r="F748" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G748" s="2">
         <v>0</v>
       </c>
       <c r="H748" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="749" spans="1:8" x14ac:dyDescent="0.25">
@@ -35006,13 +35006,13 @@
         <v>2284</v>
       </c>
       <c r="F752" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G752" s="2">
         <v>0</v>
       </c>
       <c r="H752" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.25">
@@ -35058,13 +35058,13 @@
         <v>2284</v>
       </c>
       <c r="F754" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G754" s="2">
         <v>0</v>
       </c>
       <c r="H754" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="755" spans="1:8" x14ac:dyDescent="0.25">
@@ -39088,13 +39088,13 @@
         <v>2957</v>
       </c>
       <c r="F909" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G909" s="2">
         <v>0</v>
       </c>
       <c r="H909" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="910" spans="1:8" x14ac:dyDescent="0.25">
@@ -39530,13 +39530,13 @@
         <v>2968</v>
       </c>
       <c r="F926" s="2">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="G926" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H926" s="2">
-        <v>83</v>
+        <v>55</v>
       </c>
     </row>
     <row r="927" spans="1:8" x14ac:dyDescent="0.25">
@@ -44546,13 +44546,13 @@
         <v>3112</v>
       </c>
       <c r="F1119" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G1119" s="2">
         <v>0</v>
       </c>
       <c r="H1119" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1120" spans="1:8" x14ac:dyDescent="0.25">
@@ -49952,13 +49952,13 @@
         <v>2205</v>
       </c>
       <c r="F1327" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1327" s="2">
         <v>0</v>
       </c>
       <c r="H1327" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1328" spans="1:8" x14ac:dyDescent="0.25">
@@ -50966,13 +50966,13 @@
         <v>3317</v>
       </c>
       <c r="F1366" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G1366" s="2">
         <v>0</v>
       </c>
       <c r="H1366" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1367" spans="1:8" x14ac:dyDescent="0.25">
@@ -53202,13 +53202,13 @@
         <v>2464</v>
       </c>
       <c r="F1452" s="2">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G1452" s="2">
         <v>0</v>
       </c>
       <c r="H1452" s="2">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1453" spans="1:8" x14ac:dyDescent="0.25">
@@ -55438,13 +55438,13 @@
         <v>2116</v>
       </c>
       <c r="F1538" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1538" s="2">
         <v>0</v>
       </c>
       <c r="H1538" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1539" spans="1:8" x14ac:dyDescent="0.25">
@@ -62692,13 +62692,13 @@
         <v>2196</v>
       </c>
       <c r="F1817" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1817" s="2">
         <v>0</v>
       </c>
       <c r="H1817" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1818" spans="1:8" x14ac:dyDescent="0.25">
@@ -65266,13 +65266,13 @@
         <v>2196</v>
       </c>
       <c r="F1916" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1916" s="2">
         <v>0</v>
       </c>
       <c r="H1916" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1917" spans="1:8" x14ac:dyDescent="0.25">
@@ -67606,13 +67606,13 @@
         <v>2113</v>
       </c>
       <c r="F2006" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2006" s="2">
         <v>0</v>
       </c>
       <c r="H2006" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2007" spans="1:8" x14ac:dyDescent="0.25">
@@ -75458,13 +75458,13 @@
         <v>4410</v>
       </c>
       <c r="F2308" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="G2308" s="2">
         <v>0</v>
       </c>
       <c r="H2308" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2309" spans="1:8" x14ac:dyDescent="0.25">
@@ -81566,13 +81566,13 @@
         <v>3356</v>
       </c>
       <c r="F2543" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2543" s="2">
         <v>0</v>
       </c>
       <c r="H2543" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2544" spans="1:8" x14ac:dyDescent="0.25">
@@ -85232,13 +85232,13 @@
         <v>2174</v>
       </c>
       <c r="F2684" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2684" s="2">
         <v>0</v>
       </c>
       <c r="H2684" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2685" spans="1:8" x14ac:dyDescent="0.25">
@@ -85336,13 +85336,13 @@
         <v>2448</v>
       </c>
       <c r="F2688" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2688" s="2">
         <v>0</v>
       </c>
       <c r="H2688" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2689" spans="1:8" x14ac:dyDescent="0.25">
@@ -85492,13 +85492,13 @@
         <v>2113</v>
       </c>
       <c r="F2694" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2694" s="2">
         <v>0</v>
       </c>
       <c r="H2694" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2695" spans="1:8" x14ac:dyDescent="0.25">
@@ -86662,13 +86662,13 @@
         <v>4939</v>
       </c>
       <c r="F2739" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2739" s="2">
         <v>0</v>
       </c>
       <c r="H2739" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2740" spans="1:8" x14ac:dyDescent="0.25">
@@ -87338,13 +87338,13 @@
         <v>2106</v>
       </c>
       <c r="F2765" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2765" s="2">
         <v>0</v>
       </c>
       <c r="H2765" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2766" spans="1:8" x14ac:dyDescent="0.25">
@@ -88508,13 +88508,13 @@
         <v>2174</v>
       </c>
       <c r="F2810" s="2">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G2810" s="2">
         <v>0</v>
       </c>
       <c r="H2810" s="2">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2811" spans="1:8" x14ac:dyDescent="0.25">
@@ -88716,13 +88716,13 @@
         <v>2113</v>
       </c>
       <c r="F2818" s="2">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G2818" s="2">
         <v>0</v>
       </c>
       <c r="H2818" s="2">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2819" spans="1:8" x14ac:dyDescent="0.25">
@@ -89132,13 +89132,13 @@
         <v>2113</v>
       </c>
       <c r="F2834" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G2834" s="2">
         <v>0</v>
       </c>
       <c r="H2834" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2835" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PSD-SAA\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DFBAFD1-9402-49E1-9A97-DA1A93BACA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6FBFAAB-07DD-4F7B-9AA2-7E802D702532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
+    <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11295" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -15124,7 +15124,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -16400,13 +16400,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16712,13 +16712,13 @@
         <v>2113</v>
       </c>
       <c r="F48" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -16894,13 +16894,13 @@
         <v>2116</v>
       </c>
       <c r="F55" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G55" s="2">
         <v>0</v>
       </c>
       <c r="H55" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -16946,13 +16946,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G57" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17050,13 +17050,13 @@
         <v>2113</v>
       </c>
       <c r="F61" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G61" s="2">
         <v>0</v>
       </c>
       <c r="H61" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -17466,13 +17466,13 @@
         <v>2144</v>
       </c>
       <c r="F77" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17492,13 +17492,13 @@
         <v>2144</v>
       </c>
       <c r="F78" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G78" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17518,13 +17518,13 @@
         <v>2144</v>
       </c>
       <c r="F79" s="2">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G79" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -17648,13 +17648,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>640</v>
+        <v>540</v>
       </c>
       <c r="G84" s="2">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H84" s="2">
-        <v>618</v>
+        <v>539</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17960,13 +17960,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="G96" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H96" s="2">
-        <v>82</v>
+        <v>66</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>195</v>
+        <v>149</v>
       </c>
       <c r="G97" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>192</v>
+        <v>149</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18038,13 +18038,13 @@
         <v>2103</v>
       </c>
       <c r="F99" s="2">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G99" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -18168,13 +18168,13 @@
         <v>2144</v>
       </c>
       <c r="F104" s="2">
-        <v>355</v>
+        <v>314</v>
       </c>
       <c r="G104" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H104" s="2">
-        <v>347</v>
+        <v>314</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -18272,13 +18272,13 @@
         <v>2144</v>
       </c>
       <c r="F108" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
       </c>
       <c r="H108" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -19386,13 +19386,13 @@
         <v>2196</v>
       </c>
       <c r="F151" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G151" s="2">
         <v>0</v>
       </c>
       <c r="H151" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -24586,13 +24586,13 @@
         <v>2090</v>
       </c>
       <c r="F351" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G351" s="2">
         <v>0</v>
       </c>
       <c r="H351" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.25">
@@ -26224,13 +26224,13 @@
         <v>2106</v>
       </c>
       <c r="F414" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G414" s="2">
         <v>0</v>
       </c>
       <c r="H414" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.25">
@@ -27810,13 +27810,13 @@
         <v>2606</v>
       </c>
       <c r="F475" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G475" s="2">
         <v>0</v>
       </c>
       <c r="H475" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.25">
@@ -28588,13 +28588,13 @@
         <v>2627</v>
       </c>
       <c r="F505" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G505" s="2">
         <v>0</v>
       </c>
       <c r="H505" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
@@ -32224,13 +32224,13 @@
         <v>2619</v>
       </c>
       <c r="F645" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G645" s="2">
         <v>0</v>
       </c>
       <c r="H645" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
@@ -32614,13 +32614,13 @@
         <v>2619</v>
       </c>
       <c r="F660" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G660" s="2">
         <v>0</v>
       </c>
       <c r="H660" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
@@ -32692,13 +32692,13 @@
         <v>2619</v>
       </c>
       <c r="F663" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G663" s="2">
         <v>0</v>
       </c>
       <c r="H663" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="664" spans="1:8" x14ac:dyDescent="0.25">
@@ -32952,13 +32952,13 @@
         <v>2619</v>
       </c>
       <c r="F673" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G673" s="2">
         <v>0</v>
       </c>
       <c r="H673" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
@@ -33108,13 +33108,13 @@
         <v>2619</v>
       </c>
       <c r="F679" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G679" s="2">
         <v>0</v>
       </c>
       <c r="H679" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="680" spans="1:8" x14ac:dyDescent="0.25">
@@ -34174,13 +34174,13 @@
         <v>2106</v>
       </c>
       <c r="F720" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G720" s="2">
         <v>0</v>
       </c>
       <c r="H720" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.25">
@@ -34694,13 +34694,13 @@
         <v>2284</v>
       </c>
       <c r="F740" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G740" s="2">
         <v>0</v>
       </c>
       <c r="H740" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
@@ -34798,10 +34798,10 @@
         <v>2284</v>
       </c>
       <c r="F744" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G744" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H744" s="2">
         <v>83</v>
@@ -35006,13 +35006,13 @@
         <v>2284</v>
       </c>
       <c r="F752" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G752" s="2">
         <v>0</v>
       </c>
       <c r="H752" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.25">
@@ -35058,13 +35058,13 @@
         <v>2284</v>
       </c>
       <c r="F754" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G754" s="2">
         <v>0</v>
       </c>
       <c r="H754" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="755" spans="1:8" x14ac:dyDescent="0.25">
@@ -39530,13 +39530,13 @@
         <v>2968</v>
       </c>
       <c r="F926" s="2">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="G926" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H926" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="927" spans="1:8" x14ac:dyDescent="0.25">
@@ -48678,13 +48678,13 @@
         <v>2636</v>
       </c>
       <c r="F1278" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1278" s="2">
         <v>0</v>
       </c>
       <c r="H1278" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1279" spans="1:8" x14ac:dyDescent="0.25">
@@ -75458,13 +75458,13 @@
         <v>4410</v>
       </c>
       <c r="F2308" s="2">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="G2308" s="2">
         <v>0</v>
       </c>
       <c r="H2308" s="2">
-        <v>77</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2309" spans="1:8" x14ac:dyDescent="0.25">
@@ -81280,13 +81280,13 @@
         <v>3356</v>
       </c>
       <c r="F2532" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2532" s="2">
         <v>0</v>
       </c>
       <c r="H2532" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2533" spans="1:8" x14ac:dyDescent="0.25">
@@ -85232,13 +85232,13 @@
         <v>2174</v>
       </c>
       <c r="F2684" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2684" s="2">
         <v>0</v>
       </c>
       <c r="H2684" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2685" spans="1:8" x14ac:dyDescent="0.25">
@@ -86662,13 +86662,13 @@
         <v>4939</v>
       </c>
       <c r="F2739" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2739" s="2">
         <v>0</v>
       </c>
       <c r="H2739" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2740" spans="1:8" x14ac:dyDescent="0.25">
@@ -89132,13 +89132,13 @@
         <v>2113</v>
       </c>
       <c r="F2834" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2834" s="2">
         <v>0</v>
       </c>
       <c r="H2834" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2835" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PSD-SAA\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6FBFAAB-07DD-4F7B-9AA2-7E802D702532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F895A77-953B-4B86-92F5-0737E4DB91B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11295" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -16400,13 +16400,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16715,10 +16715,10 @@
         <v>13</v>
       </c>
       <c r="G48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -16894,13 +16894,13 @@
         <v>2116</v>
       </c>
       <c r="F55" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G55" s="2">
         <v>0</v>
       </c>
       <c r="H55" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -17466,13 +17466,13 @@
         <v>2144</v>
       </c>
       <c r="F77" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17492,13 +17492,13 @@
         <v>2144</v>
       </c>
       <c r="F78" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17648,13 +17648,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>540</v>
+        <v>470</v>
       </c>
       <c r="G84" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H84" s="2">
-        <v>539</v>
+        <v>464</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17960,13 +17960,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
       </c>
       <c r="H96" s="2">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="G97" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97" s="2">
-        <v>149</v>
+        <v>124</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18168,13 +18168,13 @@
         <v>2144</v>
       </c>
       <c r="F104" s="2">
-        <v>314</v>
+        <v>286</v>
       </c>
       <c r="G104" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H104" s="2">
-        <v>314</v>
+        <v>282</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -18275,10 +18275,10 @@
         <v>43</v>
       </c>
       <c r="G108" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H108" s="2">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -19386,13 +19386,13 @@
         <v>2196</v>
       </c>
       <c r="F151" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G151" s="2">
         <v>0</v>
       </c>
       <c r="H151" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -27810,13 +27810,13 @@
         <v>2606</v>
       </c>
       <c r="F475" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G475" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H475" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.25">
@@ -32224,13 +32224,13 @@
         <v>2619</v>
       </c>
       <c r="F645" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G645" s="2">
         <v>0</v>
       </c>
       <c r="H645" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
@@ -32614,13 +32614,13 @@
         <v>2619</v>
       </c>
       <c r="F660" s="2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G660" s="2">
         <v>0</v>
       </c>
       <c r="H660" s="2">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
@@ -32952,13 +32952,13 @@
         <v>2619</v>
       </c>
       <c r="F673" s="2">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G673" s="2">
         <v>0</v>
       </c>
       <c r="H673" s="2">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
@@ -33108,13 +33108,13 @@
         <v>2619</v>
       </c>
       <c r="F679" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G679" s="2">
         <v>0</v>
       </c>
       <c r="H679" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="680" spans="1:8" x14ac:dyDescent="0.25">
@@ -34174,13 +34174,13 @@
         <v>2106</v>
       </c>
       <c r="F720" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G720" s="2">
         <v>0</v>
       </c>
       <c r="H720" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.25">
@@ -34694,13 +34694,13 @@
         <v>2284</v>
       </c>
       <c r="F740" s="2">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G740" s="2">
         <v>0</v>
       </c>
       <c r="H740" s="2">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
@@ -34798,13 +34798,13 @@
         <v>2284</v>
       </c>
       <c r="F744" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G744" s="2">
         <v>0</v>
       </c>
       <c r="H744" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.25">
@@ -35006,13 +35006,13 @@
         <v>2284</v>
       </c>
       <c r="F752" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G752" s="2">
         <v>0</v>
       </c>
       <c r="H752" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.25">
@@ -38932,13 +38932,13 @@
         <v>2566</v>
       </c>
       <c r="F903" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G903" s="2">
         <v>0</v>
       </c>
       <c r="H903" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="904" spans="1:8" x14ac:dyDescent="0.25">
@@ -39530,13 +39530,13 @@
         <v>2968</v>
       </c>
       <c r="F926" s="2">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G926" s="2">
         <v>0</v>
       </c>
       <c r="H926" s="2">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="927" spans="1:8" x14ac:dyDescent="0.25">
@@ -44546,13 +44546,13 @@
         <v>3112</v>
       </c>
       <c r="F1119" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G1119" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1119" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1120" spans="1:8" x14ac:dyDescent="0.25">
@@ -50966,13 +50966,13 @@
         <v>3317</v>
       </c>
       <c r="F1366" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1366" s="2">
         <v>0</v>
       </c>
       <c r="H1366" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1367" spans="1:8" x14ac:dyDescent="0.25">
@@ -75458,13 +75458,13 @@
         <v>4410</v>
       </c>
       <c r="F2308" s="2">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G2308" s="2">
         <v>0</v>
       </c>
       <c r="H2308" s="2">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2309" spans="1:8" x14ac:dyDescent="0.25">
@@ -81514,13 +81514,13 @@
         <v>3356</v>
       </c>
       <c r="F2541" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2541" s="2">
         <v>0</v>
       </c>
       <c r="H2541" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2542" spans="1:8" x14ac:dyDescent="0.25">
@@ -88508,13 +88508,13 @@
         <v>2174</v>
       </c>
       <c r="F2810" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2810" s="2">
         <v>0</v>
       </c>
       <c r="H2810" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2811" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PSD-SAA\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F895A77-953B-4B86-92F5-0737E4DB91B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F61815A-E1CC-458D-B271-C78788C94E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -16400,13 +16400,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16712,10 +16712,10 @@
         <v>2113</v>
       </c>
       <c r="F48" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="2">
         <v>12</v>
@@ -16946,13 +16946,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17466,13 +17466,13 @@
         <v>2144</v>
       </c>
       <c r="F77" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17492,13 +17492,13 @@
         <v>2144</v>
       </c>
       <c r="F78" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17648,13 +17648,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>470</v>
+        <v>436</v>
       </c>
       <c r="G84" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H84" s="2">
-        <v>464</v>
+        <v>435</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17960,13 +17960,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
       </c>
       <c r="H96" s="2">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="G97" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18168,13 +18168,13 @@
         <v>2144</v>
       </c>
       <c r="F104" s="2">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="G104" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H104" s="2">
-        <v>282</v>
+        <v>269</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -18272,10 +18272,10 @@
         <v>2144</v>
       </c>
       <c r="F108" s="2">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G108" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H108" s="2">
         <v>33</v>
@@ -27810,10 +27810,10 @@
         <v>2606</v>
       </c>
       <c r="F475" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G475" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H475" s="2">
         <v>9</v>
@@ -32224,13 +32224,13 @@
         <v>2619</v>
       </c>
       <c r="F645" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G645" s="2">
         <v>0</v>
       </c>
       <c r="H645" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
@@ -34174,13 +34174,13 @@
         <v>2106</v>
       </c>
       <c r="F720" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G720" s="2">
         <v>0</v>
       </c>
       <c r="H720" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.25">
@@ -39530,13 +39530,13 @@
         <v>2968</v>
       </c>
       <c r="F926" s="2">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G926" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H926" s="2">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="927" spans="1:8" x14ac:dyDescent="0.25">
@@ -44546,10 +44546,10 @@
         <v>3112</v>
       </c>
       <c r="F1119" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G1119" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1119" s="2">
         <v>27</v>
@@ -50966,13 +50966,13 @@
         <v>3317</v>
       </c>
       <c r="F1366" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1366" s="2">
         <v>0</v>
       </c>
       <c r="H1366" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1367" spans="1:8" x14ac:dyDescent="0.25">
@@ -75458,13 +75458,13 @@
         <v>4410</v>
       </c>
       <c r="F2308" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G2308" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2308" s="2">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2309" spans="1:8" x14ac:dyDescent="0.25">
@@ -88508,13 +88508,13 @@
         <v>2174</v>
       </c>
       <c r="F2810" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G2810" s="2">
         <v>0</v>
       </c>
       <c r="H2810" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2811" spans="1:8" x14ac:dyDescent="0.25">
@@ -88716,13 +88716,13 @@
         <v>2113</v>
       </c>
       <c r="F2818" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G2818" s="2">
         <v>0</v>
       </c>
       <c r="H2818" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2819" spans="1:8" x14ac:dyDescent="0.25">
@@ -89132,13 +89132,13 @@
         <v>2113</v>
       </c>
       <c r="F2834" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2834" s="2">
         <v>0</v>
       </c>
       <c r="H2834" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2835" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PSD-SAA\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F61815A-E1CC-458D-B271-C78788C94E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA6AE70-94A3-4EB9-93BA-26D297EAD346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -15124,7 +15124,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -16400,13 +16400,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16504,13 +16504,13 @@
         <v>2114</v>
       </c>
       <c r="F40" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
       </c>
       <c r="H40" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -16946,13 +16946,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17050,13 +17050,13 @@
         <v>2113</v>
       </c>
       <c r="F61" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G61" s="2">
         <v>0</v>
       </c>
       <c r="H61" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -17076,13 +17076,13 @@
         <v>2118</v>
       </c>
       <c r="F62" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -17469,10 +17469,10 @@
         <v>90</v>
       </c>
       <c r="G77" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17492,13 +17492,13 @@
         <v>2144</v>
       </c>
       <c r="F78" s="2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17648,13 +17648,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>436</v>
+        <v>415</v>
       </c>
       <c r="G84" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H84" s="2">
-        <v>435</v>
+        <v>410</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17960,13 +17960,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
       </c>
       <c r="H96" s="2">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="G97" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H97" s="2">
-        <v>110</v>
+        <v>96</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18038,13 +18038,13 @@
         <v>2103</v>
       </c>
       <c r="F99" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
       </c>
       <c r="H99" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -18168,13 +18168,13 @@
         <v>2144</v>
       </c>
       <c r="F104" s="2">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="G104" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H104" s="2">
-        <v>269</v>
+        <v>254</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -18272,13 +18272,13 @@
         <v>2144</v>
       </c>
       <c r="F108" s="2">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
       </c>
       <c r="H108" s="2">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -28562,13 +28562,13 @@
         <v>2136</v>
       </c>
       <c r="F504" s="2">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G504" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H504" s="2">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
@@ -28744,13 +28744,13 @@
         <v>2627</v>
       </c>
       <c r="F511" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G511" s="2">
         <v>0</v>
       </c>
       <c r="H511" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="512" spans="1:8" x14ac:dyDescent="0.25">
@@ -29290,13 +29290,13 @@
         <v>2373</v>
       </c>
       <c r="F532" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G532" s="2">
         <v>0</v>
       </c>
       <c r="H532" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.25">
@@ -32276,13 +32276,13 @@
         <v>2619</v>
       </c>
       <c r="F647" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G647" s="2">
         <v>0</v>
       </c>
       <c r="H647" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="648" spans="1:8" x14ac:dyDescent="0.25">
@@ -32614,13 +32614,13 @@
         <v>2619</v>
       </c>
       <c r="F660" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G660" s="2">
         <v>0</v>
       </c>
       <c r="H660" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
@@ -32952,13 +32952,13 @@
         <v>2619</v>
       </c>
       <c r="F673" s="2">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="G673" s="2">
         <v>0</v>
       </c>
       <c r="H673" s="2">
-        <v>35</v>
+        <v>63</v>
       </c>
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
@@ -33004,13 +33004,13 @@
         <v>2108</v>
       </c>
       <c r="F675" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G675" s="2">
         <v>0</v>
       </c>
       <c r="H675" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="676" spans="1:8" x14ac:dyDescent="0.25">
@@ -33108,13 +33108,13 @@
         <v>2619</v>
       </c>
       <c r="F679" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G679" s="2">
         <v>0</v>
       </c>
       <c r="H679" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="680" spans="1:8" x14ac:dyDescent="0.25">
@@ -34304,13 +34304,13 @@
         <v>2619</v>
       </c>
       <c r="F725" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G725" s="2">
         <v>0</v>
       </c>
       <c r="H725" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="726" spans="1:8" x14ac:dyDescent="0.25">
@@ -34694,13 +34694,13 @@
         <v>2284</v>
       </c>
       <c r="F740" s="2">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="G740" s="2">
         <v>0</v>
       </c>
       <c r="H740" s="2">
-        <v>52</v>
+        <v>78</v>
       </c>
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
@@ -38932,13 +38932,13 @@
         <v>2566</v>
       </c>
       <c r="F903" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G903" s="2">
         <v>0</v>
       </c>
       <c r="H903" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="904" spans="1:8" x14ac:dyDescent="0.25">
@@ -39088,13 +39088,13 @@
         <v>2957</v>
       </c>
       <c r="F909" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G909" s="2">
         <v>0</v>
       </c>
       <c r="H909" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="910" spans="1:8" x14ac:dyDescent="0.25">
@@ -39530,13 +39530,13 @@
         <v>2968</v>
       </c>
       <c r="F926" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G926" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H926" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="927" spans="1:8" x14ac:dyDescent="0.25">
@@ -44546,13 +44546,13 @@
         <v>3112</v>
       </c>
       <c r="F1119" s="2">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="G1119" s="2">
         <v>0</v>
       </c>
       <c r="H1119" s="2">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1120" spans="1:8" x14ac:dyDescent="0.25">
@@ -45480,13 +45480,13 @@
         <v>2196</v>
       </c>
       <c r="F1155" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G1155" s="2">
         <v>0</v>
       </c>
       <c r="H1155" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1156" spans="1:8" x14ac:dyDescent="0.25">
@@ -48808,13 +48808,13 @@
         <v>2106</v>
       </c>
       <c r="F1283" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1283" s="2">
         <v>0</v>
       </c>
       <c r="H1283" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1284" spans="1:8" x14ac:dyDescent="0.25">
@@ -48860,13 +48860,13 @@
         <v>2205</v>
       </c>
       <c r="F1285" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1285" s="2">
         <v>0</v>
       </c>
       <c r="H1285" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1286" spans="1:8" x14ac:dyDescent="0.25">
@@ -49874,13 +49874,13 @@
         <v>2205</v>
       </c>
       <c r="F1324" s="2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G1324" s="2">
         <v>0</v>
       </c>
       <c r="H1324" s="2">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1325" spans="1:8" x14ac:dyDescent="0.25">
@@ -50966,13 +50966,13 @@
         <v>3317</v>
       </c>
       <c r="F1366" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1366" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1366" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1367" spans="1:8" x14ac:dyDescent="0.25">
@@ -53202,13 +53202,13 @@
         <v>2464</v>
       </c>
       <c r="F1452" s="2">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G1452" s="2">
         <v>0</v>
       </c>
       <c r="H1452" s="2">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1453" spans="1:8" x14ac:dyDescent="0.25">
@@ -75458,13 +75458,13 @@
         <v>4410</v>
       </c>
       <c r="F2308" s="2">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G2308" s="2">
         <v>2</v>
       </c>
       <c r="H2308" s="2">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2309" spans="1:8" x14ac:dyDescent="0.25">
@@ -85206,13 +85206,13 @@
         <v>2174</v>
       </c>
       <c r="F2683" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G2683" s="2">
         <v>0</v>
       </c>
       <c r="H2683" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2684" spans="1:8" x14ac:dyDescent="0.25">
@@ -86662,13 +86662,13 @@
         <v>4939</v>
       </c>
       <c r="F2739" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G2739" s="2">
         <v>0</v>
       </c>
       <c r="H2739" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2740" spans="1:8" x14ac:dyDescent="0.25">
@@ -88508,13 +88508,13 @@
         <v>2174</v>
       </c>
       <c r="F2810" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G2810" s="2">
         <v>0</v>
       </c>
       <c r="H2810" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2811" spans="1:8" x14ac:dyDescent="0.25">
@@ -88716,13 +88716,13 @@
         <v>2113</v>
       </c>
       <c r="F2818" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G2818" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2818" s="2">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2819" spans="1:8" x14ac:dyDescent="0.25">
@@ -89132,13 +89132,13 @@
         <v>2113</v>
       </c>
       <c r="F2834" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G2834" s="2">
         <v>0</v>
       </c>
       <c r="H2834" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2835" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PSD-SAA\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA6AE70-94A3-4EB9-93BA-26D297EAD346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2925864D-0FBD-41B5-89CE-9AF84F0DE0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -15124,7 +15124,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -17466,13 +17466,13 @@
         <v>2144</v>
       </c>
       <c r="F77" s="2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17492,13 +17492,13 @@
         <v>2144</v>
       </c>
       <c r="F78" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17518,13 +17518,13 @@
         <v>2144</v>
       </c>
       <c r="F79" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G79" s="2">
         <v>0</v>
       </c>
       <c r="H79" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -17648,13 +17648,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>415</v>
+        <v>384</v>
       </c>
       <c r="G84" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H84" s="2">
-        <v>410</v>
+        <v>383</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17960,13 +17960,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
       </c>
       <c r="H96" s="2">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="G97" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18168,13 +18168,13 @@
         <v>2144</v>
       </c>
       <c r="F104" s="2">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="G104" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H104" s="2">
-        <v>254</v>
+        <v>239</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -22116,13 +22116,13 @@
         <v>2103</v>
       </c>
       <c r="F256" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G256" s="2">
         <v>0</v>
       </c>
       <c r="H256" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
@@ -28562,10 +28562,10 @@
         <v>2136</v>
       </c>
       <c r="F504" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G504" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H504" s="2">
         <v>54</v>
@@ -32224,13 +32224,13 @@
         <v>2619</v>
       </c>
       <c r="F645" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G645" s="2">
         <v>0</v>
       </c>
       <c r="H645" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
@@ -32614,13 +32614,13 @@
         <v>2619</v>
       </c>
       <c r="F660" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G660" s="2">
         <v>0</v>
       </c>
       <c r="H660" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
@@ -32952,13 +32952,13 @@
         <v>2619</v>
       </c>
       <c r="F673" s="2">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G673" s="2">
         <v>0</v>
       </c>
       <c r="H673" s="2">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
@@ -34174,13 +34174,13 @@
         <v>2106</v>
       </c>
       <c r="F720" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G720" s="2">
         <v>0</v>
       </c>
       <c r="H720" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.25">
@@ -34694,13 +34694,13 @@
         <v>2284</v>
       </c>
       <c r="F740" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G740" s="2">
         <v>0</v>
       </c>
       <c r="H740" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
@@ -39530,10 +39530,10 @@
         <v>2968</v>
       </c>
       <c r="F926" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G926" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H926" s="2">
         <v>42</v>
@@ -44546,13 +44546,13 @@
         <v>3112</v>
       </c>
       <c r="F1119" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G1119" s="2">
         <v>0</v>
       </c>
       <c r="H1119" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1120" spans="1:8" x14ac:dyDescent="0.25">
@@ -50966,13 +50966,13 @@
         <v>3317</v>
       </c>
       <c r="F1366" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1366" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1366" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1367" spans="1:8" x14ac:dyDescent="0.25">
@@ -75458,13 +75458,13 @@
         <v>4410</v>
       </c>
       <c r="F2308" s="2">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G2308" s="2">
         <v>2</v>
       </c>
       <c r="H2308" s="2">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2309" spans="1:8" x14ac:dyDescent="0.25">
@@ -86974,13 +86974,13 @@
         <v>2106</v>
       </c>
       <c r="F2751" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2751" s="2">
         <v>0</v>
       </c>
       <c r="H2751" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2752" spans="1:8" x14ac:dyDescent="0.25">
@@ -88222,13 +88222,13 @@
         <v>2106</v>
       </c>
       <c r="F2799" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2799" s="2">
         <v>0</v>
       </c>
       <c r="H2799" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2800" spans="1:8" x14ac:dyDescent="0.25">
@@ -88716,13 +88716,13 @@
         <v>2113</v>
       </c>
       <c r="F2818" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G2818" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2818" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2819" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2925864D-0FBD-41B5-89CE-9AF84F0DE0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E9FDE7-065F-494B-BD38-AFC98140396B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -17518,13 +17518,13 @@
         <v>2144</v>
       </c>
       <c r="F79" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G79" s="2">
         <v>0</v>
       </c>
       <c r="H79" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -17648,13 +17648,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>384</v>
+        <v>361</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
       </c>
       <c r="H84" s="2">
-        <v>383</v>
+        <v>360</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17960,13 +17960,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
       </c>
       <c r="H96" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18064,13 +18064,13 @@
         <v>2103</v>
       </c>
       <c r="F100" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G100" s="2">
         <v>0</v>
       </c>
       <c r="H100" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -18168,13 +18168,13 @@
         <v>2144</v>
       </c>
       <c r="F104" s="2">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="G104" s="2">
         <v>0</v>
       </c>
       <c r="H104" s="2">
-        <v>239</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -27914,13 +27914,13 @@
         <v>2237</v>
       </c>
       <c r="F479" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G479" s="2">
         <v>0</v>
       </c>
       <c r="H479" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
@@ -28562,13 +28562,13 @@
         <v>2136</v>
       </c>
       <c r="F504" s="2">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G504" s="2">
         <v>0</v>
       </c>
       <c r="H504" s="2">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
@@ -32614,13 +32614,13 @@
         <v>2619</v>
       </c>
       <c r="F660" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G660" s="2">
         <v>0</v>
       </c>
       <c r="H660" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
@@ -32952,13 +32952,13 @@
         <v>2619</v>
       </c>
       <c r="F673" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G673" s="2">
         <v>0</v>
       </c>
       <c r="H673" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
@@ -34174,13 +34174,13 @@
         <v>2106</v>
       </c>
       <c r="F720" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G720" s="2">
         <v>0</v>
       </c>
       <c r="H720" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.25">
@@ -34200,13 +34200,13 @@
         <v>2106</v>
       </c>
       <c r="F721" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G721" s="2">
         <v>0</v>
       </c>
       <c r="H721" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="722" spans="1:8" x14ac:dyDescent="0.25">
@@ -34694,13 +34694,13 @@
         <v>2284</v>
       </c>
       <c r="F740" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G740" s="2">
         <v>0</v>
       </c>
       <c r="H740" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
@@ -34798,13 +34798,13 @@
         <v>2284</v>
       </c>
       <c r="F744" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G744" s="2">
         <v>0</v>
       </c>
       <c r="H744" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.25">
@@ -39530,13 +39530,13 @@
         <v>2968</v>
       </c>
       <c r="F926" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G926" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H926" s="2">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="927" spans="1:8" x14ac:dyDescent="0.25">
@@ -75458,13 +75458,13 @@
         <v>4410</v>
       </c>
       <c r="F2308" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G2308" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2308" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2309" spans="1:8" x14ac:dyDescent="0.25">
@@ -88196,13 +88196,13 @@
         <v>2106</v>
       </c>
       <c r="F2798" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2798" s="2">
         <v>0</v>
       </c>
       <c r="H2798" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2799" spans="1:8" x14ac:dyDescent="0.25">
@@ -88508,13 +88508,13 @@
         <v>2174</v>
       </c>
       <c r="F2810" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2810" s="2">
         <v>0</v>
       </c>
       <c r="H2810" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2811" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PSD-SAA\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E9FDE7-065F-494B-BD38-AFC98140396B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B290404-6E3A-4A0D-BCA5-0A377467B697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -16400,13 +16400,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16712,13 +16712,13 @@
         <v>2113</v>
       </c>
       <c r="F48" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -16946,13 +16946,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17466,13 +17466,13 @@
         <v>2144</v>
       </c>
       <c r="F77" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17492,13 +17492,13 @@
         <v>2144</v>
       </c>
       <c r="F78" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17648,13 +17648,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>361</v>
+        <v>335</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
       </c>
       <c r="H84" s="2">
-        <v>360</v>
+        <v>334</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17960,13 +17960,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
       </c>
       <c r="H96" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="G97" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97" s="2">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18168,13 +18168,13 @@
         <v>2144</v>
       </c>
       <c r="F104" s="2">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="G104" s="2">
         <v>0</v>
       </c>
       <c r="H104" s="2">
-        <v>227</v>
+        <v>211</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -18272,13 +18272,13 @@
         <v>2144</v>
       </c>
       <c r="F108" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
       </c>
       <c r="H108" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -32224,13 +32224,13 @@
         <v>2619</v>
       </c>
       <c r="F645" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G645" s="2">
         <v>0</v>
       </c>
       <c r="H645" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
@@ -39088,13 +39088,13 @@
         <v>2957</v>
       </c>
       <c r="F909" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G909" s="2">
         <v>0</v>
       </c>
       <c r="H909" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="910" spans="1:8" x14ac:dyDescent="0.25">
@@ -39530,13 +39530,13 @@
         <v>2968</v>
       </c>
       <c r="F926" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G926" s="2">
         <v>0</v>
       </c>
       <c r="H926" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="927" spans="1:8" x14ac:dyDescent="0.25">
@@ -45480,13 +45480,13 @@
         <v>2196</v>
       </c>
       <c r="F1155" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G1155" s="2">
         <v>0</v>
       </c>
       <c r="H1155" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1156" spans="1:8" x14ac:dyDescent="0.25">
@@ -50969,10 +50969,10 @@
         <v>2</v>
       </c>
       <c r="G1366" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1366" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1367" spans="1:8" x14ac:dyDescent="0.25">
@@ -85336,13 +85336,13 @@
         <v>2448</v>
       </c>
       <c r="F2688" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2688" s="2">
         <v>0</v>
       </c>
       <c r="H2688" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2689" spans="1:8" x14ac:dyDescent="0.25">
@@ -86662,13 +86662,13 @@
         <v>4939</v>
       </c>
       <c r="F2739" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2739" s="2">
         <v>0</v>
       </c>
       <c r="H2739" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2740" spans="1:8" x14ac:dyDescent="0.25">
@@ -88508,13 +88508,13 @@
         <v>2174</v>
       </c>
       <c r="F2810" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2810" s="2">
         <v>0</v>
       </c>
       <c r="H2810" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2811" spans="1:8" x14ac:dyDescent="0.25">
@@ -88716,13 +88716,13 @@
         <v>2113</v>
       </c>
       <c r="F2818" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G2818" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2818" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2819" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PSD-SAA\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B290404-6E3A-4A0D-BCA5-0A377467B697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2A9666-0262-46A9-93D0-F4FDC034A053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -16400,13 +16400,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -17076,13 +17076,13 @@
         <v>2118</v>
       </c>
       <c r="F62" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -17466,13 +17466,13 @@
         <v>2144</v>
       </c>
       <c r="F77" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17648,13 +17648,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>335</v>
+        <v>309</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
       </c>
       <c r="H84" s="2">
-        <v>334</v>
+        <v>308</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17960,13 +17960,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
       </c>
       <c r="H96" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G97" s="2">
         <v>1</v>
       </c>
       <c r="H97" s="2">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18168,13 +18168,13 @@
         <v>2144</v>
       </c>
       <c r="F104" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G104" s="2">
         <v>0</v>
       </c>
       <c r="H104" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -18272,13 +18272,13 @@
         <v>2144</v>
       </c>
       <c r="F108" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
       </c>
       <c r="H108" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -22012,13 +22012,13 @@
         <v>2103</v>
       </c>
       <c r="F252" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G252" s="2">
         <v>0</v>
       </c>
       <c r="H252" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
@@ -28562,13 +28562,13 @@
         <v>2136</v>
       </c>
       <c r="F504" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G504" s="2">
         <v>0</v>
       </c>
       <c r="H504" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
@@ -28588,13 +28588,13 @@
         <v>2627</v>
       </c>
       <c r="F505" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G505" s="2">
         <v>0</v>
       </c>
       <c r="H505" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
@@ -32224,13 +32224,13 @@
         <v>2619</v>
       </c>
       <c r="F645" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G645" s="2">
         <v>0</v>
       </c>
       <c r="H645" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
@@ -32614,13 +32614,13 @@
         <v>2619</v>
       </c>
       <c r="F660" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G660" s="2">
         <v>0</v>
       </c>
       <c r="H660" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
@@ -32952,13 +32952,13 @@
         <v>2619</v>
       </c>
       <c r="F673" s="2">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G673" s="2">
         <v>0</v>
       </c>
       <c r="H673" s="2">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
@@ -33108,13 +33108,13 @@
         <v>2619</v>
       </c>
       <c r="F679" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G679" s="2">
         <v>0</v>
       </c>
       <c r="H679" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="680" spans="1:8" x14ac:dyDescent="0.25">
@@ -34694,13 +34694,13 @@
         <v>2284</v>
       </c>
       <c r="F740" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G740" s="2">
         <v>0</v>
       </c>
       <c r="H740" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
@@ -34798,13 +34798,13 @@
         <v>2284</v>
       </c>
       <c r="F744" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G744" s="2">
         <v>0</v>
       </c>
       <c r="H744" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.25">
@@ -35006,13 +35006,13 @@
         <v>2284</v>
       </c>
       <c r="F752" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G752" s="2">
         <v>0</v>
       </c>
       <c r="H752" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.25">
@@ -39530,13 +39530,13 @@
         <v>2968</v>
       </c>
       <c r="F926" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G926" s="2">
         <v>0</v>
       </c>
       <c r="H926" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="927" spans="1:8" x14ac:dyDescent="0.25">
@@ -50966,13 +50966,13 @@
         <v>3317</v>
       </c>
       <c r="F1366" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1366" s="2">
         <v>1</v>
       </c>
       <c r="H1366" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1367" spans="1:8" x14ac:dyDescent="0.25">
@@ -75458,13 +75458,13 @@
         <v>4410</v>
       </c>
       <c r="F2308" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G2308" s="2">
         <v>0</v>
       </c>
       <c r="H2308" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2309" spans="1:8" x14ac:dyDescent="0.25">
@@ -88716,13 +88716,13 @@
         <v>2113</v>
       </c>
       <c r="F2818" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G2818" s="2">
         <v>1</v>
       </c>
       <c r="H2818" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2819" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E29F4D8-C6AE-4B60-9FA9-0F61C8CBFF10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8EBAE7-3722-4F66-AD46-36E45232C0C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -16403,13 +16403,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="G36" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>85</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16507,10 +16507,10 @@
         <v>2114</v>
       </c>
       <c r="F40" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G40" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H40" s="2">
         <v>21</v>
@@ -16715,13 +16715,13 @@
         <v>2113</v>
       </c>
       <c r="F48" s="2">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="2">
-        <v>31</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -16949,13 +16949,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="G57" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17079,13 +17079,13 @@
         <v>2118</v>
       </c>
       <c r="F62" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -17469,13 +17469,13 @@
         <v>2144</v>
       </c>
       <c r="F77" s="2">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="G77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>78</v>
+        <v>55</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17495,13 +17495,13 @@
         <v>2144</v>
       </c>
       <c r="F78" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G78" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17521,13 +17521,13 @@
         <v>2144</v>
       </c>
       <c r="F79" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G79" s="2">
         <v>0</v>
       </c>
       <c r="H79" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -17651,13 +17651,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="G84" s="2">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H84" s="2">
-        <v>275</v>
+        <v>297</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17963,13 +17963,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G96" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H96" s="2">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17989,13 +17989,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>46</v>
+        <v>354</v>
       </c>
       <c r="G97" s="2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>28</v>
+        <v>354</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18041,13 +18041,13 @@
         <v>2103</v>
       </c>
       <c r="F99" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
       </c>
       <c r="H99" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -18171,13 +18171,13 @@
         <v>2144</v>
       </c>
       <c r="F104" s="2">
-        <v>202</v>
+        <v>130</v>
       </c>
       <c r="G104" s="2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H104" s="2">
-        <v>184</v>
+        <v>130</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -18275,13 +18275,13 @@
         <v>2144</v>
       </c>
       <c r="F108" s="2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G108" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H108" s="2">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -22249,13 +22249,13 @@
         <v>2090</v>
       </c>
       <c r="F261" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G261" s="2">
         <v>0</v>
       </c>
       <c r="H261" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
@@ -24641,13 +24641,13 @@
         <v>2103</v>
       </c>
       <c r="F353" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G353" s="2">
         <v>0</v>
       </c>
       <c r="H353" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
@@ -25707,13 +25707,13 @@
         <v>2114</v>
       </c>
       <c r="F394" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G394" s="2">
         <v>0</v>
       </c>
       <c r="H394" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.25">
@@ -26019,13 +26019,13 @@
         <v>2114</v>
       </c>
       <c r="F406" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G406" s="2">
         <v>0</v>
       </c>
       <c r="H406" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.25">
@@ -26201,13 +26201,13 @@
         <v>2237</v>
       </c>
       <c r="F413" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G413" s="2">
         <v>0</v>
       </c>
       <c r="H413" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.25">
@@ -28565,13 +28565,13 @@
         <v>2136</v>
       </c>
       <c r="F504" s="2">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="G504" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H504" s="2">
-        <v>85</v>
+        <v>26</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
@@ -28591,13 +28591,13 @@
         <v>2627</v>
       </c>
       <c r="F505" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G505" s="2">
         <v>0</v>
       </c>
       <c r="H505" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
@@ -28643,13 +28643,13 @@
         <v>2136</v>
       </c>
       <c r="F507" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G507" s="2">
         <v>0</v>
       </c>
       <c r="H507" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.25">
@@ -28747,13 +28747,13 @@
         <v>2627</v>
       </c>
       <c r="F511" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G511" s="2">
         <v>0</v>
       </c>
       <c r="H511" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="512" spans="1:8" x14ac:dyDescent="0.25">
@@ -29293,13 +29293,13 @@
         <v>2373</v>
       </c>
       <c r="F532" s="2">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G532" s="2">
         <v>0</v>
       </c>
       <c r="H532" s="2">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.25">
@@ -29319,13 +29319,13 @@
         <v>2106</v>
       </c>
       <c r="F533" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G533" s="2">
         <v>0</v>
       </c>
       <c r="H533" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.25">
@@ -32253,13 +32253,13 @@
         <v>2619</v>
       </c>
       <c r="F646" s="2">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="G646" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H646" s="2">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.25">
@@ -32279,13 +32279,13 @@
         <v>2619</v>
       </c>
       <c r="F647" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G647" s="2">
         <v>0</v>
       </c>
       <c r="H647" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="648" spans="1:8" x14ac:dyDescent="0.25">
@@ -32305,13 +32305,13 @@
         <v>2619</v>
       </c>
       <c r="F648" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G648" s="2">
         <v>0</v>
       </c>
       <c r="H648" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="649" spans="1:8" x14ac:dyDescent="0.25">
@@ -32643,13 +32643,13 @@
         <v>2619</v>
       </c>
       <c r="F661" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G661" s="2">
         <v>0</v>
       </c>
       <c r="H661" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.25">
@@ -32825,13 +32825,13 @@
         <v>2619</v>
       </c>
       <c r="F668" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G668" s="2">
         <v>0</v>
       </c>
       <c r="H668" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="669" spans="1:8" x14ac:dyDescent="0.25">
@@ -32981,13 +32981,13 @@
         <v>2619</v>
       </c>
       <c r="F674" s="2">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G674" s="2">
         <v>0</v>
       </c>
       <c r="H674" s="2">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="675" spans="1:8" x14ac:dyDescent="0.25">
@@ -33033,13 +33033,13 @@
         <v>2108</v>
       </c>
       <c r="F676" s="2">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G676" s="2">
         <v>0</v>
       </c>
       <c r="H676" s="2">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="677" spans="1:8" x14ac:dyDescent="0.25">
@@ -33137,13 +33137,13 @@
         <v>2619</v>
       </c>
       <c r="F680" s="2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G680" s="2">
         <v>0</v>
       </c>
       <c r="H680" s="2">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="681" spans="1:8" x14ac:dyDescent="0.25">
@@ -33163,13 +33163,13 @@
         <v>2619</v>
       </c>
       <c r="F681" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G681" s="2">
         <v>0</v>
       </c>
       <c r="H681" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="682" spans="1:8" x14ac:dyDescent="0.25">
@@ -34203,10 +34203,10 @@
         <v>2106</v>
       </c>
       <c r="F721" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G721" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H721" s="2">
         <v>0</v>
@@ -34307,13 +34307,13 @@
         <v>2619</v>
       </c>
       <c r="F725" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G725" s="2">
         <v>0</v>
       </c>
       <c r="H725" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="726" spans="1:8" x14ac:dyDescent="0.25">
@@ -34333,13 +34333,13 @@
         <v>2619</v>
       </c>
       <c r="F726" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G726" s="2">
         <v>0</v>
       </c>
       <c r="H726" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="727" spans="1:8" x14ac:dyDescent="0.25">
@@ -34723,13 +34723,13 @@
         <v>2284</v>
       </c>
       <c r="F741" s="2">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="G741" s="2">
         <v>0</v>
       </c>
       <c r="H741" s="2">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="742" spans="1:8" x14ac:dyDescent="0.25">
@@ -34827,13 +34827,13 @@
         <v>2284</v>
       </c>
       <c r="F745" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G745" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H745" s="2">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="746" spans="1:8" x14ac:dyDescent="0.25">
@@ -34983,13 +34983,13 @@
         <v>2284</v>
       </c>
       <c r="F751" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G751" s="2">
         <v>0</v>
       </c>
       <c r="H751" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="752" spans="1:8" x14ac:dyDescent="0.25">
@@ -35035,13 +35035,13 @@
         <v>2284</v>
       </c>
       <c r="F753" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G753" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H753" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="754" spans="1:8" x14ac:dyDescent="0.25">
@@ -37921,13 +37921,13 @@
         <v>2122</v>
       </c>
       <c r="F864" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G864" s="2">
         <v>0</v>
       </c>
       <c r="H864" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="865" spans="1:8" x14ac:dyDescent="0.25">
@@ -38961,13 +38961,13 @@
         <v>2566</v>
       </c>
       <c r="F904" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G904" s="2">
         <v>0</v>
       </c>
       <c r="H904" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="905" spans="1:8" x14ac:dyDescent="0.25">
@@ -39117,13 +39117,13 @@
         <v>2957</v>
       </c>
       <c r="F910" s="2">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G910" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H910" s="2">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="911" spans="1:8" x14ac:dyDescent="0.25">
@@ -39455,13 +39455,13 @@
         <v>2968</v>
       </c>
       <c r="F923" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G923" s="2">
         <v>0</v>
       </c>
       <c r="H923" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="924" spans="1:8" x14ac:dyDescent="0.25">
@@ -39559,13 +39559,13 @@
         <v>2968</v>
       </c>
       <c r="F927" s="2">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G927" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H927" s="2">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="928" spans="1:8" x14ac:dyDescent="0.25">
@@ -44575,13 +44575,13 @@
         <v>3112</v>
       </c>
       <c r="F1120" s="2">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G1120" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H1120" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1121" spans="1:8" x14ac:dyDescent="0.25">
@@ -45509,13 +45509,13 @@
         <v>2196</v>
       </c>
       <c r="F1156" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G1156" s="2">
         <v>0</v>
       </c>
       <c r="H1156" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1157" spans="1:8" x14ac:dyDescent="0.25">
@@ -48785,13 +48785,13 @@
         <v>2205</v>
       </c>
       <c r="F1282" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G1282" s="2">
         <v>0</v>
       </c>
       <c r="H1282" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1283" spans="1:8" x14ac:dyDescent="0.25">
@@ -48889,13 +48889,13 @@
         <v>2205</v>
       </c>
       <c r="F1286" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1286" s="2">
         <v>0</v>
       </c>
       <c r="H1286" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1287" spans="1:8" x14ac:dyDescent="0.25">
@@ -48941,13 +48941,13 @@
         <v>2116</v>
       </c>
       <c r="F1288" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1288" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1288" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1289" spans="1:8" x14ac:dyDescent="0.25">
@@ -49903,13 +49903,13 @@
         <v>2205</v>
       </c>
       <c r="F1325" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G1325" s="2">
         <v>0</v>
       </c>
       <c r="H1325" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1326" spans="1:8" x14ac:dyDescent="0.25">
@@ -49981,13 +49981,13 @@
         <v>2205</v>
       </c>
       <c r="F1328" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G1328" s="2">
         <v>0</v>
       </c>
       <c r="H1328" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1329" spans="1:8" x14ac:dyDescent="0.25">
@@ -50033,10 +50033,10 @@
         <v>2136</v>
       </c>
       <c r="F1330" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1330" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1330" s="2">
         <v>0</v>
@@ -53231,13 +53231,13 @@
         <v>2464</v>
       </c>
       <c r="F1453" s="2">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G1453" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1453" s="2">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1454" spans="1:8" x14ac:dyDescent="0.25">
@@ -62643,13 +62643,13 @@
         <v>2086</v>
       </c>
       <c r="F1815" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1815" s="2">
         <v>0</v>
       </c>
       <c r="H1815" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1816" spans="1:8" x14ac:dyDescent="0.25">
@@ -75487,13 +75487,13 @@
         <v>4410</v>
       </c>
       <c r="F2309" s="2">
-        <v>29</v>
+        <v>102</v>
       </c>
       <c r="G2309" s="2">
         <v>0</v>
       </c>
       <c r="H2309" s="2">
-        <v>29</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2310" spans="1:8" x14ac:dyDescent="0.25">
@@ -85521,13 +85521,13 @@
         <v>2113</v>
       </c>
       <c r="F2695" s="2">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G2695" s="2">
         <v>0</v>
       </c>
       <c r="H2695" s="2">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2696" spans="1:8" x14ac:dyDescent="0.25">
@@ -85599,13 +85599,13 @@
         <v>2448</v>
       </c>
       <c r="F2698" s="2">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="G2698" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2698" s="2">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2699" spans="1:8" x14ac:dyDescent="0.25">
@@ -88277,13 +88277,13 @@
         <v>2106</v>
       </c>
       <c r="F2801" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2801" s="2">
         <v>0</v>
       </c>
       <c r="H2801" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2802" spans="1:8" x14ac:dyDescent="0.25">
@@ -88407,13 +88407,13 @@
         <v>2136</v>
       </c>
       <c r="F2806" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G2806" s="2">
         <v>0</v>
       </c>
       <c r="H2806" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2807" spans="1:8" x14ac:dyDescent="0.25">
@@ -88745,13 +88745,13 @@
         <v>2113</v>
       </c>
       <c r="F2819" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G2819" s="2">
         <v>0</v>
       </c>
       <c r="H2819" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2820" spans="1:8" x14ac:dyDescent="0.25">
@@ -89161,13 +89161,13 @@
         <v>2113</v>
       </c>
       <c r="F2835" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G2835" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2835" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2836" spans="1:8" x14ac:dyDescent="0.25">
@@ -89187,13 +89187,13 @@
         <v>2106</v>
       </c>
       <c r="F2836" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G2836" s="2">
         <v>0</v>
       </c>
       <c r="H2836" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8EBAE7-3722-4F66-AD46-36E45232C0C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27C6912D-ADA9-4576-90D5-0E1D076B7C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -17651,13 +17651,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
       </c>
       <c r="H84" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17966,10 +17966,10 @@
         <v>2</v>
       </c>
       <c r="G96" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H96" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -17989,13 +17989,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18171,13 +18171,13 @@
         <v>2144</v>
       </c>
       <c r="F104" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G104" s="2">
         <v>0</v>
       </c>
       <c r="H104" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -32279,13 +32279,13 @@
         <v>2619</v>
       </c>
       <c r="F647" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G647" s="2">
         <v>0</v>
       </c>
       <c r="H647" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="648" spans="1:8" x14ac:dyDescent="0.25">
@@ -75487,13 +75487,13 @@
         <v>4410</v>
       </c>
       <c r="F2309" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G2309" s="2">
         <v>0</v>
       </c>
       <c r="H2309" s="2">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2310" spans="1:8" x14ac:dyDescent="0.25">
@@ -85521,13 +85521,13 @@
         <v>2113</v>
       </c>
       <c r="F2695" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G2695" s="2">
         <v>0</v>
       </c>
       <c r="H2695" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2696" spans="1:8" x14ac:dyDescent="0.25">
@@ -87991,13 +87991,13 @@
         <v>2106</v>
       </c>
       <c r="F2790" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2790" s="2">
         <v>0</v>
       </c>
       <c r="H2790" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2791" spans="1:8" x14ac:dyDescent="0.25">
@@ -88069,13 +88069,13 @@
         <v>2106</v>
       </c>
       <c r="F2793" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2793" s="2">
         <v>0</v>
       </c>
       <c r="H2793" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2794" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27C6912D-ADA9-4576-90D5-0E1D076B7C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44976A96-1809-498F-9ADA-01089AD9C9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
+    <workbookView xWindow="2340" yWindow="1725" windowWidth="9870" windowHeight="14475" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -16403,13 +16403,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16715,13 +16715,13 @@
         <v>2113</v>
       </c>
       <c r="F48" s="2">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="2">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -16949,13 +16949,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17079,13 +17079,13 @@
         <v>2118</v>
       </c>
       <c r="F62" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -17651,13 +17651,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="G84" s="2">
         <v>1</v>
       </c>
       <c r="H84" s="2">
-        <v>294</v>
+        <v>276</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17989,13 +17989,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>344</v>
+        <v>253</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>344</v>
+        <v>253</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18041,13 +18041,13 @@
         <v>2103</v>
       </c>
       <c r="F99" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
       </c>
       <c r="H99" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -18171,13 +18171,13 @@
         <v>2144</v>
       </c>
       <c r="F104" s="2">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="G104" s="2">
         <v>0</v>
       </c>
       <c r="H104" s="2">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -27917,13 +27917,13 @@
         <v>2237</v>
       </c>
       <c r="F479" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G479" s="2">
         <v>0</v>
       </c>
       <c r="H479" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
@@ -28565,13 +28565,13 @@
         <v>2136</v>
       </c>
       <c r="F504" s="2">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G504" s="2">
         <v>0</v>
       </c>
       <c r="H504" s="2">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
@@ -29293,13 +29293,13 @@
         <v>2373</v>
       </c>
       <c r="F532" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G532" s="2">
         <v>0</v>
       </c>
       <c r="H532" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.25">
@@ -32253,13 +32253,13 @@
         <v>2619</v>
       </c>
       <c r="F646" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G646" s="2">
         <v>0</v>
       </c>
       <c r="H646" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.25">
@@ -32279,13 +32279,13 @@
         <v>2619</v>
       </c>
       <c r="F647" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G647" s="2">
         <v>0</v>
       </c>
       <c r="H647" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="648" spans="1:8" x14ac:dyDescent="0.25">
@@ -32305,13 +32305,13 @@
         <v>2619</v>
       </c>
       <c r="F648" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G648" s="2">
         <v>0</v>
       </c>
       <c r="H648" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="649" spans="1:8" x14ac:dyDescent="0.25">
@@ -32643,13 +32643,13 @@
         <v>2619</v>
       </c>
       <c r="F661" s="2">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G661" s="2">
         <v>0</v>
       </c>
       <c r="H661" s="2">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.25">
@@ -32799,13 +32799,13 @@
         <v>2619</v>
       </c>
       <c r="F667" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G667" s="2">
         <v>0</v>
       </c>
       <c r="H667" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="668" spans="1:8" x14ac:dyDescent="0.25">
@@ -32955,13 +32955,13 @@
         <v>2619</v>
       </c>
       <c r="F673" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G673" s="2">
         <v>0</v>
       </c>
       <c r="H673" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
@@ -32981,13 +32981,13 @@
         <v>2619</v>
       </c>
       <c r="F674" s="2">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G674" s="2">
         <v>0</v>
       </c>
       <c r="H674" s="2">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="675" spans="1:8" x14ac:dyDescent="0.25">
@@ -33137,13 +33137,13 @@
         <v>2619</v>
       </c>
       <c r="F680" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G680" s="2">
         <v>0</v>
       </c>
       <c r="H680" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="681" spans="1:8" x14ac:dyDescent="0.25">
@@ -34307,13 +34307,13 @@
         <v>2619</v>
       </c>
       <c r="F725" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G725" s="2">
         <v>0</v>
       </c>
       <c r="H725" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="726" spans="1:8" x14ac:dyDescent="0.25">
@@ -34411,13 +34411,13 @@
         <v>2619</v>
       </c>
       <c r="F729" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G729" s="2">
         <v>0</v>
       </c>
       <c r="H729" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="730" spans="1:8" x14ac:dyDescent="0.25">
@@ -34723,13 +34723,13 @@
         <v>2284</v>
       </c>
       <c r="F741" s="2">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="G741" s="2">
         <v>0</v>
       </c>
       <c r="H741" s="2">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="742" spans="1:8" x14ac:dyDescent="0.25">
@@ -35035,13 +35035,13 @@
         <v>2284</v>
       </c>
       <c r="F753" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G753" s="2">
         <v>0</v>
       </c>
       <c r="H753" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="754" spans="1:8" x14ac:dyDescent="0.25">
@@ -35217,13 +35217,13 @@
         <v>2284</v>
       </c>
       <c r="F760" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G760" s="2">
         <v>0</v>
       </c>
       <c r="H760" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="761" spans="1:8" x14ac:dyDescent="0.25">
@@ -38961,13 +38961,13 @@
         <v>2566</v>
       </c>
       <c r="F904" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G904" s="2">
         <v>0</v>
       </c>
       <c r="H904" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="905" spans="1:8" x14ac:dyDescent="0.25">
@@ -39117,13 +39117,13 @@
         <v>2957</v>
       </c>
       <c r="F910" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G910" s="2">
         <v>0</v>
       </c>
       <c r="H910" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="911" spans="1:8" x14ac:dyDescent="0.25">
@@ -39559,13 +39559,13 @@
         <v>2968</v>
       </c>
       <c r="F927" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G927" s="2">
         <v>0</v>
       </c>
       <c r="H927" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="928" spans="1:8" x14ac:dyDescent="0.25">
@@ -48889,13 +48889,13 @@
         <v>2205</v>
       </c>
       <c r="F1286" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1286" s="2">
         <v>0</v>
       </c>
       <c r="H1286" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1287" spans="1:8" x14ac:dyDescent="0.25">
@@ -49981,13 +49981,13 @@
         <v>2205</v>
       </c>
       <c r="F1328" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1328" s="2">
         <v>0</v>
       </c>
       <c r="H1328" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1329" spans="1:8" x14ac:dyDescent="0.25">
@@ -51073,13 +51073,13 @@
         <v>3317</v>
       </c>
       <c r="F1370" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1370" s="2">
         <v>0</v>
       </c>
       <c r="H1370" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1371" spans="1:8" x14ac:dyDescent="0.25">
@@ -53231,13 +53231,13 @@
         <v>2464</v>
       </c>
       <c r="F1453" s="2">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G1453" s="2">
         <v>0</v>
       </c>
       <c r="H1453" s="2">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1454" spans="1:8" x14ac:dyDescent="0.25">
@@ -55519,13 +55519,13 @@
         <v>2108</v>
       </c>
       <c r="F1541" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G1541" s="2">
         <v>0</v>
       </c>
       <c r="H1541" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1542" spans="1:8" x14ac:dyDescent="0.25">
@@ -75487,13 +75487,13 @@
         <v>4410</v>
       </c>
       <c r="F2309" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="G2309" s="2">
         <v>0</v>
       </c>
       <c r="H2309" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2310" spans="1:8" x14ac:dyDescent="0.25">
@@ -84767,13 +84767,13 @@
         <v>2174</v>
       </c>
       <c r="F2666" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G2666" s="2">
         <v>0</v>
       </c>
       <c r="H2666" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2667" spans="1:8" x14ac:dyDescent="0.25">
@@ -85521,13 +85521,13 @@
         <v>2113</v>
       </c>
       <c r="F2695" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G2695" s="2">
         <v>0</v>
       </c>
       <c r="H2695" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2696" spans="1:8" x14ac:dyDescent="0.25">
@@ -85599,13 +85599,13 @@
         <v>2448</v>
       </c>
       <c r="F2698" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G2698" s="2">
         <v>0</v>
       </c>
       <c r="H2698" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2699" spans="1:8" x14ac:dyDescent="0.25">
@@ -86691,13 +86691,13 @@
         <v>4939</v>
       </c>
       <c r="F2740" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G2740" s="2">
         <v>0</v>
       </c>
       <c r="H2740" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2741" spans="1:8" x14ac:dyDescent="0.25">
@@ -88745,13 +88745,13 @@
         <v>2113</v>
       </c>
       <c r="F2819" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G2819" s="2">
         <v>0</v>
       </c>
       <c r="H2819" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2820" spans="1:8" x14ac:dyDescent="0.25">
@@ -89161,13 +89161,13 @@
         <v>2113</v>
       </c>
       <c r="F2835" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G2835" s="2">
         <v>0</v>
       </c>
       <c r="H2835" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2836" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44976A96-1809-498F-9ADA-01089AD9C9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396231A1-2837-46F2-8BAD-9F121C1CAF0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1725" windowWidth="9870" windowHeight="14475" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -15127,7 +15127,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -16403,13 +16403,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="2">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16507,13 +16507,13 @@
         <v>2114</v>
       </c>
       <c r="F40" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
       </c>
       <c r="H40" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -16897,13 +16897,13 @@
         <v>2116</v>
       </c>
       <c r="F55" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G55" s="2">
         <v>0</v>
       </c>
       <c r="H55" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -16949,13 +16949,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G57" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H57" s="2">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17469,13 +17469,13 @@
         <v>2144</v>
       </c>
       <c r="F77" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17651,13 +17651,13 @@
         <v>2144</v>
       </c>
       <c r="F84" s="2">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="G84" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H84" s="2">
-        <v>276</v>
+        <v>256</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17989,13 +17989,13 @@
         <v>2144</v>
       </c>
       <c r="F97" s="2">
-        <v>253</v>
+        <v>210</v>
       </c>
       <c r="G97" s="2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H97" s="2">
-        <v>253</v>
+        <v>189</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18044,10 +18044,10 @@
         <v>45</v>
       </c>
       <c r="G99" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -18171,13 +18171,13 @@
         <v>2144</v>
       </c>
       <c r="F104" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G104" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H104" s="2">
-        <v>91</v>
+        <v>73</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -22041,13 +22041,13 @@
         <v>2237</v>
       </c>
       <c r="F253" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G253" s="2">
         <v>0</v>
       </c>
       <c r="H253" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
@@ -22122,10 +22122,10 @@
         <v>16</v>
       </c>
       <c r="G256" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H256" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
@@ -26227,13 +26227,13 @@
         <v>2106</v>
       </c>
       <c r="F414" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G414" s="2">
         <v>0</v>
       </c>
       <c r="H414" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.25">
@@ -27813,13 +27813,13 @@
         <v>2606</v>
       </c>
       <c r="F475" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G475" s="2">
         <v>0</v>
       </c>
       <c r="H475" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.25">
@@ -32253,13 +32253,13 @@
         <v>2619</v>
       </c>
       <c r="F646" s="2">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G646" s="2">
         <v>0</v>
       </c>
       <c r="H646" s="2">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.25">
@@ -32279,13 +32279,13 @@
         <v>2619</v>
       </c>
       <c r="F647" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G647" s="2">
         <v>0</v>
       </c>
       <c r="H647" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="648" spans="1:8" x14ac:dyDescent="0.25">
@@ -32981,13 +32981,13 @@
         <v>2619</v>
       </c>
       <c r="F674" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G674" s="2">
         <v>0</v>
       </c>
       <c r="H674" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="675" spans="1:8" x14ac:dyDescent="0.25">
@@ -34827,13 +34827,13 @@
         <v>2284</v>
       </c>
       <c r="F745" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G745" s="2">
         <v>0</v>
       </c>
       <c r="H745" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="746" spans="1:8" x14ac:dyDescent="0.25">
@@ -35035,13 +35035,13 @@
         <v>2284</v>
       </c>
       <c r="F753" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G753" s="2">
         <v>0</v>
       </c>
       <c r="H753" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="754" spans="1:8" x14ac:dyDescent="0.25">
@@ -37921,13 +37921,13 @@
         <v>2122</v>
       </c>
       <c r="F864" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G864" s="2">
         <v>0</v>
       </c>
       <c r="H864" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="865" spans="1:8" x14ac:dyDescent="0.25">
@@ -38961,13 +38961,13 @@
         <v>2566</v>
       </c>
       <c r="F904" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G904" s="2">
         <v>0</v>
       </c>
       <c r="H904" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="905" spans="1:8" x14ac:dyDescent="0.25">
@@ -39117,13 +39117,13 @@
         <v>2957</v>
       </c>
       <c r="F910" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G910" s="2">
         <v>0</v>
       </c>
       <c r="H910" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="911" spans="1:8" x14ac:dyDescent="0.25">
@@ -39559,13 +39559,13 @@
         <v>2968</v>
       </c>
       <c r="F927" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G927" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H927" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="928" spans="1:8" x14ac:dyDescent="0.25">
@@ -48788,10 +48788,10 @@
         <v>9</v>
       </c>
       <c r="G1282" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1282" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1283" spans="1:8" x14ac:dyDescent="0.25">
@@ -53234,10 +53234,10 @@
         <v>39</v>
       </c>
       <c r="G1453" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1453" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1454" spans="1:8" x14ac:dyDescent="0.25">
@@ -75487,13 +75487,13 @@
         <v>4410</v>
       </c>
       <c r="F2309" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G2309" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2309" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2310" spans="1:8" x14ac:dyDescent="0.25">
@@ -85235,13 +85235,13 @@
         <v>2174</v>
       </c>
       <c r="F2684" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G2684" s="2">
         <v>0</v>
       </c>
       <c r="H2684" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2685" spans="1:8" x14ac:dyDescent="0.25">
@@ -85599,13 +85599,13 @@
         <v>2448</v>
       </c>
       <c r="F2698" s="2">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G2698" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2698" s="2">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2699" spans="1:8" x14ac:dyDescent="0.25">
@@ -86691,13 +86691,13 @@
         <v>4939</v>
       </c>
       <c r="F2740" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2740" s="2">
         <v>0</v>
       </c>
       <c r="H2740" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2741" spans="1:8" x14ac:dyDescent="0.25">
@@ -89164,10 +89164,10 @@
         <v>13</v>
       </c>
       <c r="G2835" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2835" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2836" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B0CCC3B-9A72-4685-A605-9AF8C3EB20F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F7E833-A3B6-4CE1-92A2-8BA26353F6DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -15127,7 +15127,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -16403,13 +16403,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16507,13 +16507,13 @@
         <v>2114</v>
       </c>
       <c r="F40" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
       </c>
       <c r="H40" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -16949,13 +16949,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17469,13 +17469,13 @@
         <v>2142</v>
       </c>
       <c r="F77" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17495,13 +17495,13 @@
         <v>2142</v>
       </c>
       <c r="F78" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17651,13 +17651,13 @@
         <v>2142</v>
       </c>
       <c r="F84" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="G84" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>235</v>
+        <v>228</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17989,13 +17989,13 @@
         <v>2142</v>
       </c>
       <c r="F97" s="2">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>161</v>
+        <v>116</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18171,13 +18171,13 @@
         <v>2142</v>
       </c>
       <c r="F104" s="2">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="G104" s="2">
         <v>0</v>
       </c>
       <c r="H104" s="2">
-        <v>67</v>
+        <v>50</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -29293,13 +29293,13 @@
         <v>2371</v>
       </c>
       <c r="F532" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G532" s="2">
         <v>0</v>
       </c>
       <c r="H532" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.25">
@@ -33137,13 +33137,13 @@
         <v>2617</v>
       </c>
       <c r="F680" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G680" s="2">
         <v>0</v>
       </c>
       <c r="H680" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="681" spans="1:8" x14ac:dyDescent="0.25">
@@ -35035,13 +35035,13 @@
         <v>2282</v>
       </c>
       <c r="F753" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G753" s="2">
         <v>0</v>
       </c>
       <c r="H753" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="754" spans="1:8" x14ac:dyDescent="0.25">
@@ -37921,13 +37921,13 @@
         <v>2122</v>
       </c>
       <c r="F864" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G864" s="2">
         <v>0</v>
       </c>
       <c r="H864" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="865" spans="1:8" x14ac:dyDescent="0.25">
@@ -39559,13 +39559,13 @@
         <v>2966</v>
       </c>
       <c r="F927" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G927" s="2">
         <v>0</v>
       </c>
       <c r="H927" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="928" spans="1:8" x14ac:dyDescent="0.25">
@@ -45639,13 +45639,13 @@
         <v>3116</v>
       </c>
       <c r="F1161" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1161" s="2">
         <v>0</v>
       </c>
       <c r="H1161" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1162" spans="1:8" x14ac:dyDescent="0.25">
@@ -75487,13 +75487,13 @@
         <v>4408</v>
       </c>
       <c r="F2309" s="2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G2309" s="2">
         <v>0</v>
       </c>
       <c r="H2309" s="2">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2310" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F7E833-A3B6-4CE1-92A2-8BA26353F6DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9D46DE-58D3-43DD-9D5A-3C8F2CD52223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -15127,7 +15127,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -16403,13 +16403,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16949,13 +16949,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17495,13 +17495,13 @@
         <v>2142</v>
       </c>
       <c r="F78" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17651,13 +17651,13 @@
         <v>2142</v>
       </c>
       <c r="F84" s="2">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>228</v>
+        <v>214</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17989,13 +17989,13 @@
         <v>2142</v>
       </c>
       <c r="F97" s="2">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="G97" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H97" s="2">
-        <v>116</v>
+        <v>58</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18171,13 +18171,13 @@
         <v>2142</v>
       </c>
       <c r="F104" s="2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G104" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H104" s="2">
-        <v>50</v>
+        <v>27</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -27917,13 +27917,13 @@
         <v>2235</v>
       </c>
       <c r="F479" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G479" s="2">
         <v>0</v>
       </c>
       <c r="H479" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
@@ -28591,13 +28591,13 @@
         <v>2625</v>
       </c>
       <c r="F505" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G505" s="2">
         <v>0</v>
       </c>
       <c r="H505" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
@@ -32643,13 +32643,13 @@
         <v>2617</v>
       </c>
       <c r="F661" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G661" s="2">
         <v>0</v>
       </c>
       <c r="H661" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.25">
@@ -32981,13 +32981,13 @@
         <v>2617</v>
       </c>
       <c r="F674" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G674" s="2">
         <v>0</v>
       </c>
       <c r="H674" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="675" spans="1:8" x14ac:dyDescent="0.25">
@@ -33137,13 +33137,13 @@
         <v>2617</v>
       </c>
       <c r="F680" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G680" s="2">
         <v>0</v>
       </c>
       <c r="H680" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="681" spans="1:8" x14ac:dyDescent="0.25">
@@ -34723,13 +34723,13 @@
         <v>2282</v>
       </c>
       <c r="F741" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G741" s="2">
         <v>0</v>
       </c>
       <c r="H741" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="742" spans="1:8" x14ac:dyDescent="0.25">
@@ -35035,13 +35035,13 @@
         <v>2282</v>
       </c>
       <c r="F753" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G753" s="2">
         <v>0</v>
       </c>
       <c r="H753" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="754" spans="1:8" x14ac:dyDescent="0.25">
@@ -39117,13 +39117,13 @@
         <v>2955</v>
       </c>
       <c r="F910" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G910" s="2">
         <v>0</v>
       </c>
       <c r="H910" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="911" spans="1:8" x14ac:dyDescent="0.25">
@@ -39559,13 +39559,13 @@
         <v>2966</v>
       </c>
       <c r="F927" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G927" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H927" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="928" spans="1:8" x14ac:dyDescent="0.25">
@@ -44575,13 +44575,13 @@
         <v>3110</v>
       </c>
       <c r="F1120" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G1120" s="2">
         <v>0</v>
       </c>
       <c r="H1120" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1121" spans="1:8" x14ac:dyDescent="0.25">
@@ -45509,13 +45509,13 @@
         <v>2194</v>
       </c>
       <c r="F1156" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1156" s="2">
         <v>0</v>
       </c>
       <c r="H1156" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1157" spans="1:8" x14ac:dyDescent="0.25">
@@ -75487,13 +75487,13 @@
         <v>4408</v>
       </c>
       <c r="F2309" s="2">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G2309" s="2">
         <v>0</v>
       </c>
       <c r="H2309" s="2">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2310" spans="1:8" x14ac:dyDescent="0.25">
@@ -85599,13 +85599,13 @@
         <v>2446</v>
       </c>
       <c r="F2698" s="2">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G2698" s="2">
         <v>0</v>
       </c>
       <c r="H2698" s="2">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2699" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9D46DE-58D3-43DD-9D5A-3C8F2CD52223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094A5D3C-0C39-4B6A-9758-ACF09564B4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -16403,13 +16403,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16949,13 +16949,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17521,13 +17521,13 @@
         <v>2142</v>
       </c>
       <c r="F79" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G79" s="2">
         <v>0</v>
       </c>
       <c r="H79" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -17651,13 +17651,13 @@
         <v>2142</v>
       </c>
       <c r="F84" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17989,13 +17989,13 @@
         <v>2142</v>
       </c>
       <c r="F97" s="2">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="G97" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>58</v>
+        <v>36</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18041,13 +18041,13 @@
         <v>2103</v>
       </c>
       <c r="F99" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
       </c>
       <c r="H99" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -18171,13 +18171,13 @@
         <v>2142</v>
       </c>
       <c r="F104" s="2">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G104" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H104" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -28565,13 +28565,13 @@
         <v>2136</v>
       </c>
       <c r="F504" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G504" s="2">
         <v>0</v>
       </c>
       <c r="H504" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
@@ -28643,13 +28643,13 @@
         <v>2136</v>
       </c>
       <c r="F507" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G507" s="2">
         <v>0</v>
       </c>
       <c r="H507" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.25">
@@ -39117,13 +39117,13 @@
         <v>2955</v>
       </c>
       <c r="F910" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G910" s="2">
         <v>0</v>
       </c>
       <c r="H910" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="911" spans="1:8" x14ac:dyDescent="0.25">
@@ -39559,10 +39559,10 @@
         <v>2966</v>
       </c>
       <c r="F927" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G927" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H927" s="2">
         <v>1</v>
@@ -48785,13 +48785,13 @@
         <v>2203</v>
       </c>
       <c r="F1282" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1282" s="2">
         <v>0</v>
       </c>
       <c r="H1282" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1283" spans="1:8" x14ac:dyDescent="0.25">
@@ -49903,13 +49903,13 @@
         <v>2203</v>
       </c>
       <c r="F1325" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1325" s="2">
         <v>0</v>
       </c>
       <c r="H1325" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1326" spans="1:8" x14ac:dyDescent="0.25">
@@ -75487,13 +75487,13 @@
         <v>4408</v>
       </c>
       <c r="F2309" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G2309" s="2">
         <v>0</v>
       </c>
       <c r="H2309" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2310" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094A5D3C-0C39-4B6A-9758-ACF09564B4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{143E752B-0CB4-48CF-BDD8-61EEEB0C88D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -15127,7 +15127,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -16403,13 +16403,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -17079,13 +17079,13 @@
         <v>2118</v>
       </c>
       <c r="F62" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -17651,13 +17651,13 @@
         <v>2142</v>
       </c>
       <c r="F84" s="2">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17989,13 +17989,13 @@
         <v>2142</v>
       </c>
       <c r="F97" s="2">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18171,13 +18171,13 @@
         <v>2142</v>
       </c>
       <c r="F104" s="2">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G104" s="2">
         <v>0</v>
       </c>
       <c r="H104" s="2">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -32253,13 +32253,13 @@
         <v>2617</v>
       </c>
       <c r="F646" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G646" s="2">
         <v>0</v>
       </c>
       <c r="H646" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.25">
@@ -33137,13 +33137,13 @@
         <v>2617</v>
       </c>
       <c r="F680" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G680" s="2">
         <v>0</v>
       </c>
       <c r="H680" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="681" spans="1:8" x14ac:dyDescent="0.25">
@@ -35035,13 +35035,13 @@
         <v>2282</v>
       </c>
       <c r="F753" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G753" s="2">
         <v>0</v>
       </c>
       <c r="H753" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="754" spans="1:8" x14ac:dyDescent="0.25">
@@ -75487,13 +75487,13 @@
         <v>4408</v>
       </c>
       <c r="F2309" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G2309" s="2">
         <v>0</v>
       </c>
       <c r="H2309" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2310" spans="1:8" x14ac:dyDescent="0.25">
@@ -85599,13 +85599,13 @@
         <v>2446</v>
       </c>
       <c r="F2698" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G2698" s="2">
         <v>0</v>
       </c>
       <c r="H2698" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2699" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{143E752B-0CB4-48CF-BDD8-61EEEB0C88D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06CF6599-453A-4913-BC92-43A0FED86C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -15127,7 +15127,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -16507,13 +16507,13 @@
         <v>2114</v>
       </c>
       <c r="F40" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
       </c>
       <c r="H40" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -16767,13 +16767,13 @@
         <v>2113</v>
       </c>
       <c r="F50" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G50" s="2">
         <v>0</v>
       </c>
       <c r="H50" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -17651,13 +17651,13 @@
         <v>2142</v>
       </c>
       <c r="F84" s="2">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>200</v>
+        <v>184</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17989,13 +17989,13 @@
         <v>2142</v>
       </c>
       <c r="F97" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18171,13 +18171,13 @@
         <v>2142</v>
       </c>
       <c r="F104" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G104" s="2">
         <v>0</v>
       </c>
       <c r="H104" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -28591,13 +28591,13 @@
         <v>2625</v>
       </c>
       <c r="F505" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G505" s="2">
         <v>0</v>
       </c>
       <c r="H505" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
@@ -34723,13 +34723,13 @@
         <v>2282</v>
       </c>
       <c r="F741" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G741" s="2">
         <v>0</v>
       </c>
       <c r="H741" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="742" spans="1:8" x14ac:dyDescent="0.25">
@@ -34853,13 +34853,13 @@
         <v>2282</v>
       </c>
       <c r="F746" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G746" s="2">
         <v>0</v>
       </c>
       <c r="H746" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="747" spans="1:8" x14ac:dyDescent="0.25">
@@ -39559,13 +39559,13 @@
         <v>2966</v>
       </c>
       <c r="F927" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G927" s="2">
         <v>0</v>
       </c>
       <c r="H927" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="928" spans="1:8" x14ac:dyDescent="0.25">
@@ -75487,13 +75487,13 @@
         <v>4408</v>
       </c>
       <c r="F2309" s="2">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G2309" s="2">
         <v>0</v>
       </c>
       <c r="H2309" s="2">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2310" spans="1:8" x14ac:dyDescent="0.25">
@@ -85599,13 +85599,13 @@
         <v>2446</v>
       </c>
       <c r="F2698" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G2698" s="2">
         <v>0</v>
       </c>
       <c r="H2698" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2699" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06CF6599-453A-4913-BC92-43A0FED86C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C43EB6-F79B-45E7-A831-88979520755A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11297" uniqueCount="5009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11305" uniqueCount="5013">
   <si>
     <t>No</t>
   </si>
@@ -15063,6 +15063,18 @@
   </si>
   <si>
     <t>ACC KIT SE KU 2</t>
+  </si>
+  <si>
+    <t>AHPS0003012</t>
+  </si>
+  <si>
+    <t>HRC23 ELGT NAV PL SHIRT S</t>
+  </si>
+  <si>
+    <t>AHPS0004012</t>
+  </si>
+  <si>
+    <t>HRC23 SPORTY NAVY POLO S</t>
   </si>
 </sst>
 </file>
@@ -15463,7 +15475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F25B32B2-47AD-4A50-A408-222CF682F986}">
-  <dimension ref="A1:H2836"/>
+  <dimension ref="A1:H2838"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -16403,13 +16415,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="2">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16715,13 +16727,13 @@
         <v>2113</v>
       </c>
       <c r="F48" s="2">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="2">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -16897,13 +16909,13 @@
         <v>2116</v>
       </c>
       <c r="F55" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G55" s="2">
         <v>0</v>
       </c>
       <c r="H55" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -16949,13 +16961,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="G57" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="2">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17469,13 +17481,13 @@
         <v>2142</v>
       </c>
       <c r="F77" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G77" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H77" s="2">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17495,13 +17507,13 @@
         <v>2142</v>
       </c>
       <c r="F78" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G78" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17524,10 +17536,10 @@
         <v>91</v>
       </c>
       <c r="G79" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H79" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -17651,13 +17663,13 @@
         <v>2142</v>
       </c>
       <c r="F84" s="2">
-        <v>184</v>
+        <v>411</v>
       </c>
       <c r="G84" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H84" s="2">
-        <v>184</v>
+        <v>408</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17989,13 +18001,13 @@
         <v>2142</v>
       </c>
       <c r="F97" s="2">
-        <v>3</v>
+        <v>388</v>
       </c>
       <c r="G97" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H97" s="2">
-        <v>3</v>
+        <v>386</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18067,13 +18079,13 @@
         <v>2103</v>
       </c>
       <c r="F100" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G100" s="2">
         <v>0</v>
       </c>
       <c r="H100" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -18171,13 +18183,13 @@
         <v>2142</v>
       </c>
       <c r="F104" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G104" s="2">
         <v>0</v>
       </c>
       <c r="H104" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -18275,13 +18287,13 @@
         <v>2142</v>
       </c>
       <c r="F108" s="2">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
       </c>
       <c r="H108" s="2">
-        <v>33</v>
+        <v>53</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -28747,13 +28759,13 @@
         <v>2625</v>
       </c>
       <c r="F511" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G511" s="2">
         <v>0</v>
       </c>
       <c r="H511" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512" spans="1:8" x14ac:dyDescent="0.25">
@@ -32305,13 +32317,13 @@
         <v>2617</v>
       </c>
       <c r="F648" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G648" s="2">
         <v>0</v>
       </c>
       <c r="H648" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="649" spans="1:8" x14ac:dyDescent="0.25">
@@ -33033,13 +33045,13 @@
         <v>2108</v>
       </c>
       <c r="F676" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G676" s="2">
         <v>0</v>
       </c>
       <c r="H676" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="677" spans="1:8" x14ac:dyDescent="0.25">
@@ -34723,13 +34735,13 @@
         <v>2282</v>
       </c>
       <c r="F741" s="2">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="G741" s="2">
         <v>0</v>
       </c>
       <c r="H741" s="2">
-        <v>48</v>
+        <v>112</v>
       </c>
     </row>
     <row r="742" spans="1:8" x14ac:dyDescent="0.25">
@@ -34853,13 +34865,13 @@
         <v>2282</v>
       </c>
       <c r="F746" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G746" s="2">
         <v>0</v>
       </c>
       <c r="H746" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="747" spans="1:8" x14ac:dyDescent="0.25">
@@ -34931,13 +34943,13 @@
         <v>2282</v>
       </c>
       <c r="F749" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G749" s="2">
         <v>0</v>
       </c>
       <c r="H749" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="750" spans="1:8" x14ac:dyDescent="0.25">
@@ -35035,13 +35047,13 @@
         <v>2282</v>
       </c>
       <c r="F753" s="2">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="G753" s="2">
         <v>0</v>
       </c>
       <c r="H753" s="2">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="754" spans="1:8" x14ac:dyDescent="0.25">
@@ -38961,13 +38973,13 @@
         <v>2564</v>
       </c>
       <c r="F904" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G904" s="2">
         <v>0</v>
       </c>
       <c r="H904" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="905" spans="1:8" x14ac:dyDescent="0.25">
@@ -39117,13 +39129,13 @@
         <v>2955</v>
       </c>
       <c r="F910" s="2">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="G910" s="2">
         <v>0</v>
       </c>
       <c r="H910" s="2">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="911" spans="1:8" x14ac:dyDescent="0.25">
@@ -39559,13 +39571,13 @@
         <v>2966</v>
       </c>
       <c r="F927" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G927" s="2">
         <v>0</v>
       </c>
       <c r="H927" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="928" spans="1:8" x14ac:dyDescent="0.25">
@@ -45642,10 +45654,10 @@
         <v>4</v>
       </c>
       <c r="G1161" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H1161" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1162" spans="1:8" x14ac:dyDescent="0.25">
@@ -75487,13 +75499,13 @@
         <v>4408</v>
       </c>
       <c r="F2309" s="2">
-        <v>58</v>
+        <v>256</v>
       </c>
       <c r="G2309" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H2309" s="2">
-        <v>58</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2310" spans="1:8" x14ac:dyDescent="0.25">
@@ -86691,13 +86703,13 @@
         <v>4937</v>
       </c>
       <c r="F2740" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2740" s="2">
         <v>0</v>
       </c>
       <c r="H2740" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2741" spans="1:8" x14ac:dyDescent="0.25">
@@ -87407,10 +87419,10 @@
         <v>2767</v>
       </c>
       <c r="B2768" s="2" t="s">
-        <v>1970</v>
+        <v>5009</v>
       </c>
       <c r="C2768" s="2" t="s">
-        <v>1971</v>
+        <v>5010</v>
       </c>
       <c r="D2768" s="2" t="s">
         <v>2081</v>
@@ -87419,13 +87431,13 @@
         <v>2106</v>
       </c>
       <c r="F2768" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2768" s="2">
         <v>0</v>
       </c>
       <c r="H2768" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2769" spans="1:8" x14ac:dyDescent="0.25">
@@ -87433,25 +87445,25 @@
         <v>2768</v>
       </c>
       <c r="B2769" s="2" t="s">
-        <v>4965</v>
+        <v>5011</v>
       </c>
       <c r="C2769" s="2" t="s">
-        <v>4966</v>
+        <v>5012</v>
       </c>
       <c r="D2769" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2769" s="2" t="s">
-        <v>3354</v>
+        <v>2106</v>
       </c>
       <c r="F2769" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2769" s="2">
         <v>0</v>
       </c>
       <c r="H2769" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2770" spans="1:8" x14ac:dyDescent="0.25">
@@ -87459,25 +87471,25 @@
         <v>2769</v>
       </c>
       <c r="B2770" s="2" t="s">
-        <v>4967</v>
+        <v>1970</v>
       </c>
       <c r="C2770" s="2" t="s">
-        <v>4968</v>
+        <v>1971</v>
       </c>
       <c r="D2770" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2770" s="2" t="s">
-        <v>3354</v>
+        <v>2106</v>
       </c>
       <c r="F2770" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2770" s="2">
         <v>0</v>
       </c>
       <c r="H2770" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2771" spans="1:8" x14ac:dyDescent="0.25">
@@ -87485,10 +87497,10 @@
         <v>2770</v>
       </c>
       <c r="B2771" s="2" t="s">
-        <v>1972</v>
+        <v>4965</v>
       </c>
       <c r="C2771" s="2" t="s">
-        <v>1973</v>
+        <v>4966</v>
       </c>
       <c r="D2771" s="2" t="s">
         <v>2081</v>
@@ -87497,13 +87509,13 @@
         <v>3354</v>
       </c>
       <c r="F2771" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2771" s="2">
         <v>0</v>
       </c>
       <c r="H2771" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2772" spans="1:8" x14ac:dyDescent="0.25">
@@ -87511,10 +87523,10 @@
         <v>2771</v>
       </c>
       <c r="B2772" s="2" t="s">
-        <v>4969</v>
+        <v>4967</v>
       </c>
       <c r="C2772" s="2" t="s">
-        <v>4970</v>
+        <v>4968</v>
       </c>
       <c r="D2772" s="2" t="s">
         <v>2081</v>
@@ -87523,13 +87535,13 @@
         <v>3354</v>
       </c>
       <c r="F2772" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2772" s="2">
         <v>0</v>
       </c>
       <c r="H2772" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2773" spans="1:8" x14ac:dyDescent="0.25">
@@ -87537,25 +87549,25 @@
         <v>2772</v>
       </c>
       <c r="B2773" s="2" t="s">
-        <v>4971</v>
+        <v>1972</v>
       </c>
       <c r="C2773" s="2" t="s">
-        <v>4972</v>
+        <v>1973</v>
       </c>
       <c r="D2773" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2773" s="2" t="s">
-        <v>2106</v>
+        <v>3354</v>
       </c>
       <c r="F2773" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2773" s="2">
         <v>0</v>
       </c>
       <c r="H2773" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2774" spans="1:8" x14ac:dyDescent="0.25">
@@ -87563,16 +87575,16 @@
         <v>2773</v>
       </c>
       <c r="B2774" s="2" t="s">
-        <v>4973</v>
+        <v>4969</v>
       </c>
       <c r="C2774" s="2" t="s">
-        <v>4974</v>
+        <v>4970</v>
       </c>
       <c r="D2774" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2774" s="2" t="s">
-        <v>2175</v>
+        <v>3354</v>
       </c>
       <c r="F2774" s="2">
         <v>0</v>
@@ -87589,16 +87601,16 @@
         <v>2774</v>
       </c>
       <c r="B2775" s="2" t="s">
-        <v>4975</v>
+        <v>4971</v>
       </c>
       <c r="C2775" s="2" t="s">
-        <v>4976</v>
+        <v>4972</v>
       </c>
       <c r="D2775" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2775" s="2" t="s">
-        <v>3354</v>
+        <v>2106</v>
       </c>
       <c r="F2775" s="2">
         <v>0</v>
@@ -87615,25 +87627,25 @@
         <v>2775</v>
       </c>
       <c r="B2776" s="2" t="s">
-        <v>1974</v>
+        <v>4973</v>
       </c>
       <c r="C2776" s="2" t="s">
-        <v>1975</v>
+        <v>4974</v>
       </c>
       <c r="D2776" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2776" s="2" t="s">
-        <v>3286</v>
+        <v>2175</v>
       </c>
       <c r="F2776" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2776" s="2">
         <v>0</v>
       </c>
       <c r="H2776" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2777" spans="1:8" x14ac:dyDescent="0.25">
@@ -87641,16 +87653,16 @@
         <v>2776</v>
       </c>
       <c r="B2777" s="2" t="s">
-        <v>1976</v>
+        <v>4975</v>
       </c>
       <c r="C2777" s="2" t="s">
-        <v>1977</v>
+        <v>4976</v>
       </c>
       <c r="D2777" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2777" s="2" t="s">
-        <v>3286</v>
+        <v>3354</v>
       </c>
       <c r="F2777" s="2">
         <v>0</v>
@@ -87667,25 +87679,25 @@
         <v>2777</v>
       </c>
       <c r="B2778" s="2" t="s">
-        <v>4977</v>
+        <v>1974</v>
       </c>
       <c r="C2778" s="2" t="s">
-        <v>4978</v>
+        <v>1975</v>
       </c>
       <c r="D2778" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2778" s="2" t="s">
-        <v>2103</v>
+        <v>3286</v>
       </c>
       <c r="F2778" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2778" s="2">
         <v>0</v>
       </c>
       <c r="H2778" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2779" spans="1:8" x14ac:dyDescent="0.25">
@@ -87693,25 +87705,25 @@
         <v>2778</v>
       </c>
       <c r="B2779" s="2" t="s">
-        <v>4979</v>
+        <v>1976</v>
       </c>
       <c r="C2779" s="2" t="s">
-        <v>4980</v>
+        <v>1977</v>
       </c>
       <c r="D2779" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2779" s="2" t="s">
-        <v>2175</v>
+        <v>3286</v>
       </c>
       <c r="F2779" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2779" s="2">
         <v>0</v>
       </c>
       <c r="H2779" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2780" spans="1:8" x14ac:dyDescent="0.25">
@@ -87719,16 +87731,16 @@
         <v>2779</v>
       </c>
       <c r="B2780" s="2" t="s">
-        <v>4981</v>
+        <v>4977</v>
       </c>
       <c r="C2780" s="2" t="s">
-        <v>4982</v>
+        <v>4978</v>
       </c>
       <c r="D2780" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2780" s="2" t="s">
-        <v>2175</v>
+        <v>2103</v>
       </c>
       <c r="F2780" s="2">
         <v>1</v>
@@ -87745,16 +87757,16 @@
         <v>2780</v>
       </c>
       <c r="B2781" s="2" t="s">
-        <v>1978</v>
+        <v>4979</v>
       </c>
       <c r="C2781" s="2" t="s">
-        <v>1979</v>
+        <v>4980</v>
       </c>
       <c r="D2781" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2781" s="2" t="s">
-        <v>3354</v>
+        <v>2175</v>
       </c>
       <c r="F2781" s="2">
         <v>1</v>
@@ -87771,25 +87783,25 @@
         <v>2781</v>
       </c>
       <c r="B2782" s="2" t="s">
-        <v>1980</v>
+        <v>4981</v>
       </c>
       <c r="C2782" s="2" t="s">
-        <v>1981</v>
+        <v>4982</v>
       </c>
       <c r="D2782" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2782" s="2" t="s">
-        <v>3354</v>
+        <v>2175</v>
       </c>
       <c r="F2782" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2782" s="2">
         <v>0</v>
       </c>
       <c r="H2782" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2783" spans="1:8" x14ac:dyDescent="0.25">
@@ -87797,16 +87809,16 @@
         <v>2782</v>
       </c>
       <c r="B2783" s="2" t="s">
-        <v>4983</v>
+        <v>1978</v>
       </c>
       <c r="C2783" s="2" t="s">
-        <v>4984</v>
+        <v>1979</v>
       </c>
       <c r="D2783" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2783" s="2" t="s">
-        <v>2103</v>
+        <v>3354</v>
       </c>
       <c r="F2783" s="2">
         <v>1</v>
@@ -87823,25 +87835,25 @@
         <v>2783</v>
       </c>
       <c r="B2784" s="2" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="C2784" s="2" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="D2784" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2784" s="2" t="s">
-        <v>4985</v>
+        <v>3354</v>
       </c>
       <c r="F2784" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2784" s="2">
         <v>0</v>
       </c>
       <c r="H2784" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2785" spans="1:8" x14ac:dyDescent="0.25">
@@ -87849,25 +87861,25 @@
         <v>2784</v>
       </c>
       <c r="B2785" s="2" t="s">
-        <v>1984</v>
+        <v>4983</v>
       </c>
       <c r="C2785" s="2" t="s">
-        <v>1985</v>
+        <v>4984</v>
       </c>
       <c r="D2785" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2785" s="2" t="s">
-        <v>4986</v>
+        <v>2103</v>
       </c>
       <c r="F2785" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2785" s="2">
         <v>0</v>
       </c>
       <c r="H2785" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2786" spans="1:8" x14ac:dyDescent="0.25">
@@ -87875,16 +87887,16 @@
         <v>2785</v>
       </c>
       <c r="B2786" s="2" t="s">
-        <v>4987</v>
+        <v>1982</v>
       </c>
       <c r="C2786" s="2" t="s">
-        <v>4988</v>
+        <v>1983</v>
       </c>
       <c r="D2786" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2786" s="2" t="s">
-        <v>4986</v>
+        <v>4985</v>
       </c>
       <c r="F2786" s="2">
         <v>0</v>
@@ -87901,25 +87913,25 @@
         <v>2786</v>
       </c>
       <c r="B2787" s="2" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="C2787" s="2" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="D2787" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2787" s="2" t="s">
-        <v>2106</v>
+        <v>4986</v>
       </c>
       <c r="F2787" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2787" s="2">
         <v>0</v>
       </c>
       <c r="H2787" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2788" spans="1:8" x14ac:dyDescent="0.25">
@@ -87927,16 +87939,16 @@
         <v>2787</v>
       </c>
       <c r="B2788" s="2" t="s">
-        <v>4989</v>
+        <v>4987</v>
       </c>
       <c r="C2788" s="2" t="s">
-        <v>4990</v>
+        <v>4988</v>
       </c>
       <c r="D2788" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2788" s="2" t="s">
-        <v>3354</v>
+        <v>4986</v>
       </c>
       <c r="F2788" s="2">
         <v>0</v>
@@ -87953,25 +87965,25 @@
         <v>2788</v>
       </c>
       <c r="B2789" s="2" t="s">
-        <v>4991</v>
+        <v>1986</v>
       </c>
       <c r="C2789" s="2" t="s">
-        <v>4992</v>
+        <v>1987</v>
       </c>
       <c r="D2789" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2789" s="2" t="s">
-        <v>3354</v>
+        <v>2106</v>
       </c>
       <c r="F2789" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2789" s="2">
         <v>0</v>
       </c>
       <c r="H2789" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2790" spans="1:8" x14ac:dyDescent="0.25">
@@ -87979,16 +87991,16 @@
         <v>2789</v>
       </c>
       <c r="B2790" s="2" t="s">
-        <v>2056</v>
+        <v>4989</v>
       </c>
       <c r="C2790" s="2" t="s">
-        <v>2057</v>
+        <v>4990</v>
       </c>
       <c r="D2790" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2790" s="2" t="s">
-        <v>2106</v>
+        <v>3354</v>
       </c>
       <c r="F2790" s="2">
         <v>0</v>
@@ -88005,25 +88017,25 @@
         <v>2790</v>
       </c>
       <c r="B2791" s="2" t="s">
-        <v>1988</v>
+        <v>4991</v>
       </c>
       <c r="C2791" s="2" t="s">
-        <v>1989</v>
+        <v>4992</v>
       </c>
       <c r="D2791" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2791" s="2" t="s">
-        <v>2106</v>
+        <v>3354</v>
       </c>
       <c r="F2791" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2791" s="2">
         <v>0</v>
       </c>
       <c r="H2791" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2792" spans="1:8" x14ac:dyDescent="0.25">
@@ -88031,16 +88043,16 @@
         <v>2791</v>
       </c>
       <c r="B2792" s="2" t="s">
-        <v>8</v>
+        <v>2056</v>
       </c>
       <c r="C2792" s="2" t="s">
-        <v>1990</v>
+        <v>2057</v>
       </c>
       <c r="D2792" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2792" s="2" t="s">
-        <v>3354</v>
+        <v>2106</v>
       </c>
       <c r="F2792" s="2">
         <v>0</v>
@@ -88057,10 +88069,10 @@
         <v>2792</v>
       </c>
       <c r="B2793" s="2" t="s">
-        <v>2058</v>
+        <v>1988</v>
       </c>
       <c r="C2793" s="2" t="s">
-        <v>2059</v>
+        <v>1989</v>
       </c>
       <c r="D2793" s="2" t="s">
         <v>2081</v>
@@ -88069,13 +88081,13 @@
         <v>2106</v>
       </c>
       <c r="F2793" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2793" s="2">
         <v>0</v>
       </c>
       <c r="H2793" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2794" spans="1:8" x14ac:dyDescent="0.25">
@@ -88083,25 +88095,25 @@
         <v>2793</v>
       </c>
       <c r="B2794" s="2" t="s">
-        <v>1991</v>
+        <v>8</v>
       </c>
       <c r="C2794" s="2" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="D2794" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2794" s="2" t="s">
-        <v>3286</v>
+        <v>3354</v>
       </c>
       <c r="F2794" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2794" s="2">
         <v>0</v>
       </c>
       <c r="H2794" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2795" spans="1:8" x14ac:dyDescent="0.25">
@@ -88109,16 +88121,16 @@
         <v>2794</v>
       </c>
       <c r="B2795" s="2" t="s">
-        <v>4993</v>
+        <v>2058</v>
       </c>
       <c r="C2795" s="2" t="s">
-        <v>4994</v>
+        <v>2059</v>
       </c>
       <c r="D2795" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2795" s="2" t="s">
-        <v>4995</v>
+        <v>2106</v>
       </c>
       <c r="F2795" s="2">
         <v>0</v>
@@ -88135,25 +88147,25 @@
         <v>2795</v>
       </c>
       <c r="B2796" s="2" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="C2796" s="2" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="D2796" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2796" s="2" t="s">
-        <v>3354</v>
+        <v>3286</v>
       </c>
       <c r="F2796" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2796" s="2">
         <v>0</v>
       </c>
       <c r="H2796" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2797" spans="1:8" x14ac:dyDescent="0.25">
@@ -88161,16 +88173,16 @@
         <v>2796</v>
       </c>
       <c r="B2797" s="2" t="s">
-        <v>4996</v>
+        <v>4993</v>
       </c>
       <c r="C2797" s="2" t="s">
-        <v>4997</v>
+        <v>4994</v>
       </c>
       <c r="D2797" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2797" s="2" t="s">
-        <v>3354</v>
+        <v>4995</v>
       </c>
       <c r="F2797" s="2">
         <v>0</v>
@@ -88187,10 +88199,10 @@
         <v>2797</v>
       </c>
       <c r="B2798" s="2" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="C2798" s="2" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="D2798" s="2" t="s">
         <v>2081</v>
@@ -88213,16 +88225,16 @@
         <v>2798</v>
       </c>
       <c r="B2799" s="2" t="s">
-        <v>2060</v>
+        <v>4996</v>
       </c>
       <c r="C2799" s="2" t="s">
-        <v>2061</v>
+        <v>4997</v>
       </c>
       <c r="D2799" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2799" s="2" t="s">
-        <v>2106</v>
+        <v>3354</v>
       </c>
       <c r="F2799" s="2">
         <v>0</v>
@@ -88239,16 +88251,16 @@
         <v>2799</v>
       </c>
       <c r="B2800" s="2" t="s">
-        <v>2062</v>
+        <v>1995</v>
       </c>
       <c r="C2800" s="2" t="s">
-        <v>2063</v>
+        <v>1996</v>
       </c>
       <c r="D2800" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2800" s="2" t="s">
-        <v>2106</v>
+        <v>3354</v>
       </c>
       <c r="F2800" s="2">
         <v>0</v>
@@ -88265,10 +88277,10 @@
         <v>2800</v>
       </c>
       <c r="B2801" s="2" t="s">
-        <v>2064</v>
+        <v>2060</v>
       </c>
       <c r="C2801" s="2" t="s">
-        <v>2065</v>
+        <v>2061</v>
       </c>
       <c r="D2801" s="2" t="s">
         <v>2081</v>
@@ -88291,10 +88303,10 @@
         <v>2801</v>
       </c>
       <c r="B2802" s="2" t="s">
-        <v>2066</v>
+        <v>2062</v>
       </c>
       <c r="C2802" s="2" t="s">
-        <v>2067</v>
+        <v>2063</v>
       </c>
       <c r="D2802" s="2" t="s">
         <v>2081</v>
@@ -88303,13 +88315,13 @@
         <v>2106</v>
       </c>
       <c r="F2802" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2802" s="2">
         <v>0</v>
       </c>
       <c r="H2802" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2803" spans="1:8" x14ac:dyDescent="0.25">
@@ -88317,10 +88329,10 @@
         <v>2802</v>
       </c>
       <c r="B2803" s="2" t="s">
-        <v>2068</v>
+        <v>2064</v>
       </c>
       <c r="C2803" s="2" t="s">
-        <v>2069</v>
+        <v>2065</v>
       </c>
       <c r="D2803" s="2" t="s">
         <v>2081</v>
@@ -88329,13 +88341,13 @@
         <v>2106</v>
       </c>
       <c r="F2803" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2803" s="2">
         <v>0</v>
       </c>
       <c r="H2803" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2804" spans="1:8" x14ac:dyDescent="0.25">
@@ -88343,25 +88355,25 @@
         <v>2803</v>
       </c>
       <c r="B2804" s="2" t="s">
-        <v>1997</v>
+        <v>2066</v>
       </c>
       <c r="C2804" s="2" t="s">
-        <v>1956</v>
+        <v>2067</v>
       </c>
       <c r="D2804" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2804" s="2" t="s">
-        <v>2172</v>
+        <v>2106</v>
       </c>
       <c r="F2804" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2804" s="2">
         <v>0</v>
       </c>
       <c r="H2804" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2805" spans="1:8" x14ac:dyDescent="0.25">
@@ -88369,25 +88381,25 @@
         <v>2804</v>
       </c>
       <c r="B2805" s="2" t="s">
-        <v>1998</v>
+        <v>2068</v>
       </c>
       <c r="C2805" s="2" t="s">
-        <v>1956</v>
+        <v>2069</v>
       </c>
       <c r="D2805" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2805" s="2" t="s">
-        <v>2172</v>
+        <v>2106</v>
       </c>
       <c r="F2805" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2805" s="2">
         <v>0</v>
       </c>
       <c r="H2805" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2806" spans="1:8" x14ac:dyDescent="0.25">
@@ -88395,25 +88407,25 @@
         <v>2805</v>
       </c>
       <c r="B2806" s="2" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="C2806" s="2" t="s">
-        <v>2000</v>
+        <v>1956</v>
       </c>
       <c r="D2806" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2806" s="2" t="s">
-        <v>2136</v>
+        <v>2172</v>
       </c>
       <c r="F2806" s="2">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G2806" s="2">
         <v>0</v>
       </c>
       <c r="H2806" s="2">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2807" spans="1:8" x14ac:dyDescent="0.25">
@@ -88421,10 +88433,10 @@
         <v>2806</v>
       </c>
       <c r="B2807" s="2" t="s">
-        <v>4998</v>
+        <v>1998</v>
       </c>
       <c r="C2807" s="2" t="s">
-        <v>2002</v>
+        <v>1956</v>
       </c>
       <c r="D2807" s="2" t="s">
         <v>2081</v>
@@ -88447,25 +88459,25 @@
         <v>2807</v>
       </c>
       <c r="B2808" s="2" t="s">
-        <v>4999</v>
+        <v>1999</v>
       </c>
       <c r="C2808" s="2" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="D2808" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2808" s="2" t="s">
-        <v>2172</v>
+        <v>2136</v>
       </c>
       <c r="F2808" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G2808" s="2">
         <v>0</v>
       </c>
       <c r="H2808" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2809" spans="1:8" x14ac:dyDescent="0.25">
@@ -88473,7 +88485,7 @@
         <v>2808</v>
       </c>
       <c r="B2809" s="2" t="s">
-        <v>5000</v>
+        <v>4998</v>
       </c>
       <c r="C2809" s="2" t="s">
         <v>2002</v>
@@ -88499,7 +88511,7 @@
         <v>2809</v>
       </c>
       <c r="B2810" s="2" t="s">
-        <v>2001</v>
+        <v>4999</v>
       </c>
       <c r="C2810" s="2" t="s">
         <v>2002</v>
@@ -88511,13 +88523,13 @@
         <v>2172</v>
       </c>
       <c r="F2810" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2810" s="2">
         <v>0</v>
       </c>
       <c r="H2810" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2811" spans="1:8" x14ac:dyDescent="0.25">
@@ -88525,10 +88537,10 @@
         <v>2810</v>
       </c>
       <c r="B2811" s="2" t="s">
-        <v>2003</v>
+        <v>5000</v>
       </c>
       <c r="C2811" s="2" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="D2811" s="2" t="s">
         <v>2081</v>
@@ -88551,7 +88563,7 @@
         <v>2811</v>
       </c>
       <c r="B2812" s="2" t="s">
-        <v>5001</v>
+        <v>2001</v>
       </c>
       <c r="C2812" s="2" t="s">
         <v>2002</v>
@@ -88563,13 +88575,13 @@
         <v>2172</v>
       </c>
       <c r="F2812" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G2812" s="2">
         <v>0</v>
       </c>
       <c r="H2812" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2813" spans="1:8" x14ac:dyDescent="0.25">
@@ -88577,10 +88589,10 @@
         <v>2812</v>
       </c>
       <c r="B2813" s="2" t="s">
-        <v>5002</v>
+        <v>2003</v>
       </c>
       <c r="C2813" s="2" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="D2813" s="2" t="s">
         <v>2081</v>
@@ -88603,7 +88615,7 @@
         <v>2813</v>
       </c>
       <c r="B2814" s="2" t="s">
-        <v>2005</v>
+        <v>5001</v>
       </c>
       <c r="C2814" s="2" t="s">
         <v>2002</v>
@@ -88615,13 +88627,13 @@
         <v>2172</v>
       </c>
       <c r="F2814" s="2">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G2814" s="2">
         <v>0</v>
       </c>
       <c r="H2814" s="2">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2815" spans="1:8" x14ac:dyDescent="0.25">
@@ -88629,7 +88641,7 @@
         <v>2814</v>
       </c>
       <c r="B2815" s="2" t="s">
-        <v>2006</v>
+        <v>5002</v>
       </c>
       <c r="C2815" s="2" t="s">
         <v>2002</v>
@@ -88655,7 +88667,7 @@
         <v>2815</v>
       </c>
       <c r="B2816" s="2" t="s">
-        <v>5003</v>
+        <v>2005</v>
       </c>
       <c r="C2816" s="2" t="s">
         <v>2002</v>
@@ -88667,13 +88679,13 @@
         <v>2172</v>
       </c>
       <c r="F2816" s="2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G2816" s="2">
         <v>0</v>
       </c>
       <c r="H2816" s="2">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2817" spans="1:8" x14ac:dyDescent="0.25">
@@ -88681,7 +88693,7 @@
         <v>2816</v>
       </c>
       <c r="B2817" s="2" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="C2817" s="2" t="s">
         <v>2002</v>
@@ -88693,13 +88705,13 @@
         <v>2172</v>
       </c>
       <c r="F2817" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G2817" s="2">
         <v>0</v>
       </c>
       <c r="H2817" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2818" spans="1:8" x14ac:dyDescent="0.25">
@@ -88707,7 +88719,7 @@
         <v>2817</v>
       </c>
       <c r="B2818" s="2" t="s">
-        <v>2008</v>
+        <v>5003</v>
       </c>
       <c r="C2818" s="2" t="s">
         <v>2002</v>
@@ -88733,25 +88745,25 @@
         <v>2818</v>
       </c>
       <c r="B2819" s="2" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="C2819" s="2" t="s">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="D2819" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2819" s="2" t="s">
-        <v>2113</v>
+        <v>2172</v>
       </c>
       <c r="F2819" s="2">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="G2819" s="2">
         <v>0</v>
       </c>
       <c r="H2819" s="2">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2820" spans="1:8" x14ac:dyDescent="0.25">
@@ -88759,25 +88771,25 @@
         <v>2819</v>
       </c>
       <c r="B2820" s="2" t="s">
-        <v>5004</v>
+        <v>2008</v>
       </c>
       <c r="C2820" s="2" t="s">
-        <v>256</v>
+        <v>2002</v>
       </c>
       <c r="D2820" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2820" s="2" t="s">
-        <v>2113</v>
+        <v>2172</v>
       </c>
       <c r="F2820" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2820" s="2">
         <v>0</v>
       </c>
       <c r="H2820" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2821" spans="1:8" x14ac:dyDescent="0.25">
@@ -88785,10 +88797,10 @@
         <v>2820</v>
       </c>
       <c r="B2821" s="2" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="C2821" s="2" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="D2821" s="2" t="s">
         <v>2081</v>
@@ -88797,13 +88809,13 @@
         <v>2113</v>
       </c>
       <c r="F2821" s="2">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="G2821" s="2">
         <v>0</v>
       </c>
       <c r="H2821" s="2">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2822" spans="1:8" x14ac:dyDescent="0.25">
@@ -88811,10 +88823,10 @@
         <v>2821</v>
       </c>
       <c r="B2822" s="2" t="s">
-        <v>2013</v>
+        <v>5004</v>
       </c>
       <c r="C2822" s="2" t="s">
-        <v>2014</v>
+        <v>256</v>
       </c>
       <c r="D2822" s="2" t="s">
         <v>2081</v>
@@ -88823,13 +88835,13 @@
         <v>2113</v>
       </c>
       <c r="F2822" s="2">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G2822" s="2">
         <v>0</v>
       </c>
       <c r="H2822" s="2">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2823" spans="1:8" x14ac:dyDescent="0.25">
@@ -88837,25 +88849,25 @@
         <v>2822</v>
       </c>
       <c r="B2823" s="2" t="s">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="C2823" s="2" t="s">
-        <v>1902</v>
+        <v>2012</v>
       </c>
       <c r="D2823" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2823" s="2" t="s">
-        <v>2136</v>
+        <v>2113</v>
       </c>
       <c r="F2823" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G2823" s="2">
         <v>0</v>
       </c>
       <c r="H2823" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2824" spans="1:8" x14ac:dyDescent="0.25">
@@ -88863,25 +88875,25 @@
         <v>2823</v>
       </c>
       <c r="B2824" s="2" t="s">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C2824" s="2" t="s">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="D2824" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2824" s="2" t="s">
-        <v>2172</v>
+        <v>2113</v>
       </c>
       <c r="F2824" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G2824" s="2">
         <v>0</v>
       </c>
       <c r="H2824" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2825" spans="1:8" x14ac:dyDescent="0.25">
@@ -88889,25 +88901,25 @@
         <v>2824</v>
       </c>
       <c r="B2825" s="2" t="s">
-        <v>5005</v>
+        <v>2015</v>
       </c>
       <c r="C2825" s="2" t="s">
-        <v>2018</v>
+        <v>1902</v>
       </c>
       <c r="D2825" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2825" s="2" t="s">
-        <v>2172</v>
+        <v>2136</v>
       </c>
       <c r="F2825" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2825" s="2">
         <v>0</v>
       </c>
       <c r="H2825" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2826" spans="1:8" x14ac:dyDescent="0.25">
@@ -88915,10 +88927,10 @@
         <v>2825</v>
       </c>
       <c r="B2826" s="2" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C2826" s="2" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="D2826" s="2" t="s">
         <v>2081</v>
@@ -88927,13 +88939,13 @@
         <v>2172</v>
       </c>
       <c r="F2826" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G2826" s="2">
         <v>0</v>
       </c>
       <c r="H2826" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2827" spans="1:8" x14ac:dyDescent="0.25">
@@ -88941,25 +88953,25 @@
         <v>2826</v>
       </c>
       <c r="B2827" s="2" t="s">
-        <v>2020</v>
+        <v>5005</v>
       </c>
       <c r="C2827" s="2" t="s">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="D2827" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2827" s="2" t="s">
-        <v>2109</v>
+        <v>2172</v>
       </c>
       <c r="F2827" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2827" s="2">
         <v>0</v>
       </c>
       <c r="H2827" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2828" spans="1:8" x14ac:dyDescent="0.25">
@@ -88967,25 +88979,25 @@
         <v>2827</v>
       </c>
       <c r="B2828" s="2" t="s">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C2828" s="2" t="s">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="D2828" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2828" s="2" t="s">
-        <v>2109</v>
+        <v>2172</v>
       </c>
       <c r="F2828" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2828" s="2">
         <v>0</v>
       </c>
       <c r="H2828" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2829" spans="1:8" x14ac:dyDescent="0.25">
@@ -88993,10 +89005,10 @@
         <v>2828</v>
       </c>
       <c r="B2829" s="2" t="s">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="C2829" s="2" t="s">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D2829" s="2" t="s">
         <v>2081</v>
@@ -89005,13 +89017,13 @@
         <v>2109</v>
       </c>
       <c r="F2829" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2829" s="2">
         <v>0</v>
       </c>
       <c r="H2829" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2830" spans="1:8" x14ac:dyDescent="0.25">
@@ -89019,10 +89031,10 @@
         <v>2829</v>
       </c>
       <c r="B2830" s="2" t="s">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="C2830" s="2" t="s">
-        <v>2027</v>
+        <v>2023</v>
       </c>
       <c r="D2830" s="2" t="s">
         <v>2081</v>
@@ -89031,13 +89043,13 @@
         <v>2109</v>
       </c>
       <c r="F2830" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2830" s="2">
         <v>0</v>
       </c>
       <c r="H2830" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2831" spans="1:8" x14ac:dyDescent="0.25">
@@ -89045,10 +89057,10 @@
         <v>2830</v>
       </c>
       <c r="B2831" s="2" t="s">
-        <v>2028</v>
+        <v>2024</v>
       </c>
       <c r="C2831" s="2" t="s">
-        <v>2029</v>
+        <v>2025</v>
       </c>
       <c r="D2831" s="2" t="s">
         <v>2081</v>
@@ -89071,10 +89083,10 @@
         <v>2831</v>
       </c>
       <c r="B2832" s="2" t="s">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="C2832" s="2" t="s">
-        <v>2031</v>
+        <v>2027</v>
       </c>
       <c r="D2832" s="2" t="s">
         <v>2081</v>
@@ -89097,10 +89109,10 @@
         <v>2832</v>
       </c>
       <c r="B2833" s="2" t="s">
-        <v>2032</v>
+        <v>2028</v>
       </c>
       <c r="C2833" s="2" t="s">
-        <v>2033</v>
+        <v>2029</v>
       </c>
       <c r="D2833" s="2" t="s">
         <v>2081</v>
@@ -89109,13 +89121,13 @@
         <v>2109</v>
       </c>
       <c r="F2833" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2833" s="2">
         <v>0</v>
       </c>
       <c r="H2833" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2834" spans="1:8" x14ac:dyDescent="0.25">
@@ -89123,25 +89135,25 @@
         <v>2833</v>
       </c>
       <c r="B2834" s="2" t="s">
-        <v>2034</v>
+        <v>2030</v>
       </c>
       <c r="C2834" s="2" t="s">
-        <v>2035</v>
+        <v>2031</v>
       </c>
       <c r="D2834" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2834" s="2" t="s">
-        <v>2090</v>
+        <v>2109</v>
       </c>
       <c r="F2834" s="2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G2834" s="2">
         <v>0</v>
       </c>
       <c r="H2834" s="2">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2835" spans="1:8" x14ac:dyDescent="0.25">
@@ -89149,25 +89161,25 @@
         <v>2834</v>
       </c>
       <c r="B2835" s="2" t="s">
-        <v>2036</v>
+        <v>2032</v>
       </c>
       <c r="C2835" s="2" t="s">
-        <v>2037</v>
+        <v>2033</v>
       </c>
       <c r="D2835" s="2" t="s">
         <v>2081</v>
       </c>
       <c r="E2835" s="2" t="s">
-        <v>2113</v>
+        <v>2109</v>
       </c>
       <c r="F2835" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G2835" s="2">
         <v>0</v>
       </c>
       <c r="H2835" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2836" spans="1:8" x14ac:dyDescent="0.25">
@@ -89175,24 +89187,76 @@
         <v>2835</v>
       </c>
       <c r="B2836" s="2" t="s">
+        <v>2034</v>
+      </c>
+      <c r="C2836" s="2" t="s">
+        <v>2035</v>
+      </c>
+      <c r="D2836" s="2" t="s">
+        <v>2081</v>
+      </c>
+      <c r="E2836" s="2" t="s">
+        <v>2090</v>
+      </c>
+      <c r="F2836" s="2">
+        <v>22</v>
+      </c>
+      <c r="G2836" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2836" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2837" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2837" s="2">
+        <v>2836</v>
+      </c>
+      <c r="B2837" s="2" t="s">
+        <v>2036</v>
+      </c>
+      <c r="C2837" s="2" t="s">
+        <v>2037</v>
+      </c>
+      <c r="D2837" s="2" t="s">
+        <v>2081</v>
+      </c>
+      <c r="E2837" s="2" t="s">
+        <v>2113</v>
+      </c>
+      <c r="F2837" s="2">
+        <v>12</v>
+      </c>
+      <c r="G2837" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2837" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2838" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2838" s="2">
+        <v>2837</v>
+      </c>
+      <c r="B2838" s="2" t="s">
         <v>2038</v>
       </c>
-      <c r="C2836" s="2" t="s">
+      <c r="C2838" s="2" t="s">
         <v>2039</v>
       </c>
-      <c r="D2836" s="2" t="s">
-        <v>2081</v>
-      </c>
-      <c r="E2836" s="2" t="s">
+      <c r="D2838" s="2" t="s">
+        <v>2081</v>
+      </c>
+      <c r="E2838" s="2" t="s">
         <v>2106</v>
       </c>
-      <c r="F2836" s="2">
+      <c r="F2838" s="2">
         <v>7</v>
       </c>
-      <c r="G2836" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2836" s="2">
+      <c r="G2838" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2838" s="2">
         <v>7</v>
       </c>
     </row>

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C43EB6-F79B-45E7-A831-88979520755A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB23A04C-F063-4D71-A3A8-831ED4C70898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -16415,10 +16415,10 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G36" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="2">
         <v>54</v>
@@ -16961,13 +16961,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G57" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17013,13 +17013,13 @@
         <v>2113</v>
       </c>
       <c r="F59" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G59" s="2">
         <v>0</v>
       </c>
       <c r="H59" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -17481,13 +17481,13 @@
         <v>2142</v>
       </c>
       <c r="F77" s="2">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G77" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17507,10 +17507,10 @@
         <v>2142</v>
       </c>
       <c r="F78" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G78" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" s="2">
         <v>35</v>
@@ -17533,10 +17533,10 @@
         <v>2142</v>
       </c>
       <c r="F79" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G79" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H79" s="2">
         <v>89</v>
@@ -17663,13 +17663,13 @@
         <v>2142</v>
       </c>
       <c r="F84" s="2">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="G84" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -18001,13 +18001,13 @@
         <v>2142</v>
       </c>
       <c r="F97" s="2">
-        <v>388</v>
+        <v>350</v>
       </c>
       <c r="G97" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>386</v>
+        <v>350</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18079,13 +18079,13 @@
         <v>2103</v>
       </c>
       <c r="F100" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G100" s="2">
         <v>0</v>
       </c>
       <c r="H100" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -18287,13 +18287,13 @@
         <v>2142</v>
       </c>
       <c r="F108" s="2">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
       </c>
       <c r="H108" s="2">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -28577,13 +28577,13 @@
         <v>2136</v>
       </c>
       <c r="F504" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G504" s="2">
         <v>0</v>
       </c>
       <c r="H504" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
@@ -29305,13 +29305,13 @@
         <v>2371</v>
       </c>
       <c r="F532" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G532" s="2">
         <v>0</v>
       </c>
       <c r="H532" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.25">
@@ -32655,13 +32655,13 @@
         <v>2617</v>
       </c>
       <c r="F661" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G661" s="2">
         <v>0</v>
       </c>
       <c r="H661" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.25">
@@ -32993,13 +32993,13 @@
         <v>2617</v>
       </c>
       <c r="F674" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G674" s="2">
         <v>0</v>
       </c>
       <c r="H674" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="675" spans="1:8" x14ac:dyDescent="0.25">
@@ -34735,13 +34735,13 @@
         <v>2282</v>
       </c>
       <c r="F741" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G741" s="2">
         <v>0</v>
       </c>
       <c r="H741" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="742" spans="1:8" x14ac:dyDescent="0.25">
@@ -34943,13 +34943,13 @@
         <v>2282</v>
       </c>
       <c r="F749" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G749" s="2">
         <v>0</v>
       </c>
       <c r="H749" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="750" spans="1:8" x14ac:dyDescent="0.25">
@@ -37933,13 +37933,13 @@
         <v>2122</v>
       </c>
       <c r="F864" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G864" s="2">
         <v>0</v>
       </c>
       <c r="H864" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="865" spans="1:8" x14ac:dyDescent="0.25">
@@ -39129,13 +39129,13 @@
         <v>2955</v>
       </c>
       <c r="F910" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G910" s="2">
         <v>0</v>
       </c>
       <c r="H910" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="911" spans="1:8" x14ac:dyDescent="0.25">
@@ -39571,13 +39571,13 @@
         <v>2966</v>
       </c>
       <c r="F927" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G927" s="2">
         <v>0</v>
       </c>
       <c r="H927" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="928" spans="1:8" x14ac:dyDescent="0.25">
@@ -45651,10 +45651,10 @@
         <v>3116</v>
       </c>
       <c r="F1161" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1161" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H1161" s="2">
         <v>0</v>
@@ -75499,13 +75499,13 @@
         <v>4408</v>
       </c>
       <c r="F2309" s="2">
-        <v>256</v>
+        <v>203</v>
       </c>
       <c r="G2309" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2309" s="2">
-        <v>251</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2310" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB23A04C-F063-4D71-A3A8-831ED4C70898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F15E23D-44D9-4348-A672-F63C8CE2D46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -16080,10 +16080,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -16415,13 +16415,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="2">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16522,10 +16522,10 @@
         <v>18</v>
       </c>
       <c r="G40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -16727,13 +16727,13 @@
         <v>2113</v>
       </c>
       <c r="F48" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="2">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -16964,10 +16964,10 @@
         <v>52</v>
       </c>
       <c r="G57" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17663,13 +17663,13 @@
         <v>2142</v>
       </c>
       <c r="F84" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G84" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H84" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -18001,13 +18001,13 @@
         <v>2142</v>
       </c>
       <c r="F97" s="2">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="G97" s="2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H97" s="2">
-        <v>350</v>
+        <v>302</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18287,13 +18287,13 @@
         <v>2142</v>
       </c>
       <c r="F108" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G108" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H108" s="2">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -21455,10 +21455,10 @@
         <v>2090</v>
       </c>
       <c r="F230" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G230" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H230" s="2">
         <v>0</v>
@@ -28606,10 +28606,10 @@
         <v>19</v>
       </c>
       <c r="G505" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H505" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
@@ -28863,13 +28863,13 @@
         <v>2593</v>
       </c>
       <c r="F515" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G515" s="2">
         <v>0</v>
       </c>
       <c r="H515" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.25">
@@ -32320,10 +32320,10 @@
         <v>4</v>
       </c>
       <c r="G648" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H648" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="649" spans="1:8" x14ac:dyDescent="0.25">
@@ -34868,10 +34868,10 @@
         <v>1</v>
       </c>
       <c r="G746" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H746" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="747" spans="1:8" x14ac:dyDescent="0.25">
@@ -35232,10 +35232,10 @@
         <v>3</v>
       </c>
       <c r="G760" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H760" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="761" spans="1:8" x14ac:dyDescent="0.25">
@@ -38973,13 +38973,13 @@
         <v>2564</v>
       </c>
       <c r="F904" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G904" s="2">
         <v>0</v>
       </c>
       <c r="H904" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="905" spans="1:8" x14ac:dyDescent="0.25">
@@ -39574,10 +39574,10 @@
         <v>13</v>
       </c>
       <c r="G927" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H927" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="928" spans="1:8" x14ac:dyDescent="0.25">
@@ -44590,10 +44590,10 @@
         <v>39</v>
       </c>
       <c r="G1120" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1120" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1121" spans="1:8" x14ac:dyDescent="0.25">
@@ -45344,10 +45344,10 @@
         <v>1</v>
       </c>
       <c r="G1149" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1149" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1150" spans="1:8" x14ac:dyDescent="0.25">
@@ -48904,10 +48904,10 @@
         <v>1</v>
       </c>
       <c r="G1286" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1286" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1287" spans="1:8" x14ac:dyDescent="0.25">
@@ -75499,13 +75499,13 @@
         <v>4408</v>
       </c>
       <c r="F2309" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G2309" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2309" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2310" spans="1:8" x14ac:dyDescent="0.25">
@@ -88809,13 +88809,13 @@
         <v>2113</v>
       </c>
       <c r="F2821" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G2821" s="2">
         <v>0</v>
       </c>
       <c r="H2821" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2822" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B312CEF-D93E-4656-9878-E5E1212F3281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56967ABF-FCB7-4B93-AB40-7D5A13145599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16421,13 +16421,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.15">
@@ -16785,13 +16785,13 @@
         <v>65</v>
       </c>
       <c r="F50" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50" s="2">
         <v>0</v>
       </c>
       <c r="H50" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.15">
@@ -16967,13 +16967,13 @@
         <v>65</v>
       </c>
       <c r="F57" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.15">
@@ -17487,13 +17487,13 @@
         <v>139</v>
       </c>
       <c r="F77" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.15">
@@ -17539,13 +17539,13 @@
         <v>139</v>
       </c>
       <c r="F79" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G79" s="2">
         <v>0</v>
       </c>
       <c r="H79" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.15">
@@ -17669,13 +17669,13 @@
         <v>139</v>
       </c>
       <c r="F84" s="2">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.15">
@@ -17981,13 +17981,13 @@
         <v>98</v>
       </c>
       <c r="F96" s="2">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G96" s="2">
         <v>2</v>
       </c>
       <c r="H96" s="2">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.15">
@@ -18007,13 +18007,13 @@
         <v>139</v>
       </c>
       <c r="F97" s="2">
-        <v>378</v>
+        <v>343</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>378</v>
+        <v>343</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.15">
@@ -18189,13 +18189,13 @@
         <v>139</v>
       </c>
       <c r="F104" s="2">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="G104" s="2">
         <v>0</v>
       </c>
       <c r="H104" s="2">
-        <v>268</v>
+        <v>254</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.15">
@@ -28661,13 +28661,13 @@
         <v>127</v>
       </c>
       <c r="F507" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G507" s="2">
         <v>0</v>
       </c>
       <c r="H507" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.15">
@@ -32349,13 +32349,13 @@
         <v>836</v>
       </c>
       <c r="F649" s="2">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G649" s="2">
         <v>0</v>
       </c>
       <c r="H649" s="2">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.15">
@@ -32739,13 +32739,13 @@
         <v>836</v>
       </c>
       <c r="F664" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G664" s="2">
         <v>0</v>
       </c>
       <c r="H664" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="665" spans="1:8" x14ac:dyDescent="0.15">
@@ -33077,13 +33077,13 @@
         <v>836</v>
       </c>
       <c r="F677" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G677" s="2">
         <v>0</v>
       </c>
       <c r="H677" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="678" spans="1:8" x14ac:dyDescent="0.15">
@@ -33233,13 +33233,13 @@
         <v>836</v>
       </c>
       <c r="F683" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G683" s="2">
         <v>0</v>
       </c>
       <c r="H683" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="684" spans="1:8" x14ac:dyDescent="0.15">
@@ -34819,13 +34819,13 @@
         <v>409</v>
       </c>
       <c r="F744" s="2">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G744" s="2">
         <v>0</v>
       </c>
       <c r="H744" s="2">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.15">
@@ -35131,13 +35131,13 @@
         <v>409</v>
       </c>
       <c r="F756" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G756" s="2">
         <v>0</v>
       </c>
       <c r="H756" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="757" spans="1:8" x14ac:dyDescent="0.15">
@@ -39655,13 +39655,13 @@
         <v>1536</v>
       </c>
       <c r="F930" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G930" s="2">
         <v>0</v>
       </c>
       <c r="H930" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="931" spans="1:8" x14ac:dyDescent="0.15">
@@ -44671,13 +44671,13 @@
         <v>1826</v>
       </c>
       <c r="F1123" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G1123" s="2">
         <v>0</v>
       </c>
       <c r="H1123" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1124" spans="1:8" x14ac:dyDescent="0.15">
@@ -49999,13 +49999,13 @@
         <v>304</v>
       </c>
       <c r="F1328" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1328" s="2">
         <v>0</v>
       </c>
       <c r="H1328" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1329" spans="1:8" x14ac:dyDescent="0.15">
@@ -75635,13 +75635,13 @@
         <v>4020</v>
       </c>
       <c r="F2314" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G2314" s="2">
         <v>0</v>
       </c>
       <c r="H2314" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2315" spans="1:8" x14ac:dyDescent="0.15">
@@ -84941,13 +84941,13 @@
         <v>242</v>
       </c>
       <c r="F2672" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2672" s="2">
         <v>0</v>
       </c>
       <c r="H2672" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2673" spans="1:8" x14ac:dyDescent="0.15">
@@ -86865,13 +86865,13 @@
         <v>4825</v>
       </c>
       <c r="F2746" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2746" s="2">
         <v>0</v>
       </c>
       <c r="H2746" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2747" spans="1:8" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56967ABF-FCB7-4B93-AB40-7D5A13145599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{906E0A24-4C9C-4FAA-A504-AC6F862D4407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16424,10 +16424,10 @@
         <v>41</v>
       </c>
       <c r="G36" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H36" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.15">
@@ -16970,10 +16970,10 @@
         <v>45</v>
       </c>
       <c r="G57" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.15">
@@ -17487,13 +17487,13 @@
         <v>139</v>
       </c>
       <c r="F77" s="2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.15">
@@ -17669,13 +17669,13 @@
         <v>139</v>
       </c>
       <c r="F84" s="2">
-        <v>919</v>
+        <v>900</v>
       </c>
       <c r="G84" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H84" s="2">
-        <v>919</v>
+        <v>894</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.15">
@@ -17981,13 +17981,13 @@
         <v>98</v>
       </c>
       <c r="F96" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G96" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H96" s="2">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.15">
@@ -18007,13 +18007,13 @@
         <v>139</v>
       </c>
       <c r="F97" s="2">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="G97" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H97" s="2">
-        <v>343</v>
+        <v>320</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.15">
@@ -18059,13 +18059,13 @@
         <v>39</v>
       </c>
       <c r="F99" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
       </c>
       <c r="H99" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.15">
@@ -18189,13 +18189,13 @@
         <v>139</v>
       </c>
       <c r="F104" s="2">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="G104" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H104" s="2">
-        <v>254</v>
+        <v>238</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.15">
@@ -29392,10 +29392,10 @@
         <v>28</v>
       </c>
       <c r="G535" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H535" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.15">
@@ -33366,10 +33366,10 @@
         <v>1</v>
       </c>
       <c r="G688" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H688" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="689" spans="1:8" x14ac:dyDescent="0.15">
@@ -34510,10 +34510,10 @@
         <v>1</v>
       </c>
       <c r="G732" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H732" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="733" spans="1:8" x14ac:dyDescent="0.15">
@@ -39213,13 +39213,13 @@
         <v>1516</v>
       </c>
       <c r="F913" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G913" s="2">
         <v>0</v>
       </c>
       <c r="H913" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="914" spans="1:8" x14ac:dyDescent="0.15">
@@ -44671,13 +44671,13 @@
         <v>1826</v>
       </c>
       <c r="F1123" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G1123" s="2">
         <v>0</v>
       </c>
       <c r="H1123" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1124" spans="1:8" x14ac:dyDescent="0.15">
@@ -62742,10 +62742,10 @@
         <v>2</v>
       </c>
       <c r="G1818" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1818" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1819" spans="1:8" x14ac:dyDescent="0.15">
@@ -75635,13 +75635,13 @@
         <v>4020</v>
       </c>
       <c r="F2314" s="2">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="G2314" s="2">
         <v>0</v>
       </c>
       <c r="H2314" s="2">
-        <v>164</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2315" spans="1:8" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{906E0A24-4C9C-4FAA-A504-AC6F862D4407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E57F60FE-F8BE-4174-BC44-632CCBA40639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16421,13 +16421,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="2">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G36" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.15">
@@ -16733,13 +16733,13 @@
         <v>65</v>
       </c>
       <c r="F48" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.15">
@@ -16967,13 +16967,13 @@
         <v>65</v>
       </c>
       <c r="F57" s="2">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G57" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.15">
@@ -17487,13 +17487,13 @@
         <v>139</v>
       </c>
       <c r="F77" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.15">
@@ -17513,13 +17513,13 @@
         <v>139</v>
       </c>
       <c r="F78" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.15">
@@ -17669,13 +17669,13 @@
         <v>139</v>
       </c>
       <c r="F84" s="2">
-        <v>900</v>
+        <v>870</v>
       </c>
       <c r="G84" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>894</v>
+        <v>870</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.15">
@@ -17981,13 +17981,13 @@
         <v>98</v>
       </c>
       <c r="F96" s="2">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G96" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H96" s="2">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.15">
@@ -18007,13 +18007,13 @@
         <v>139</v>
       </c>
       <c r="F97" s="2">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="G97" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>320</v>
+        <v>307</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.15">
@@ -18059,13 +18059,13 @@
         <v>39</v>
       </c>
       <c r="F99" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
       </c>
       <c r="H99" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.15">
@@ -18189,13 +18189,13 @@
         <v>139</v>
       </c>
       <c r="F104" s="2">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="G104" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H104" s="2">
-        <v>238</v>
+        <v>224</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.15">
@@ -18293,13 +18293,13 @@
         <v>139</v>
       </c>
       <c r="F108" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
       </c>
       <c r="H108" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.15">
@@ -28013,13 +28013,13 @@
         <v>344</v>
       </c>
       <c r="F482" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G482" s="2">
         <v>0</v>
       </c>
       <c r="H482" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.15">
@@ -28661,13 +28661,13 @@
         <v>127</v>
       </c>
       <c r="F507" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G507" s="2">
         <v>0</v>
       </c>
       <c r="H507" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.15">
@@ -28739,13 +28739,13 @@
         <v>127</v>
       </c>
       <c r="F510" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G510" s="2">
         <v>0</v>
       </c>
       <c r="H510" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="511" spans="1:8" x14ac:dyDescent="0.15">
@@ -28843,13 +28843,13 @@
         <v>856</v>
       </c>
       <c r="F514" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G514" s="2">
         <v>0</v>
       </c>
       <c r="H514" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.15">
@@ -29389,10 +29389,10 @@
         <v>524</v>
       </c>
       <c r="F535" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G535" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H535" s="2">
         <v>27</v>
@@ -32297,13 +32297,13 @@
         <v>836</v>
       </c>
       <c r="F647" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G647" s="2">
         <v>0</v>
       </c>
       <c r="H647" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="648" spans="1:8" x14ac:dyDescent="0.15">
@@ -32349,13 +32349,13 @@
         <v>836</v>
       </c>
       <c r="F649" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G649" s="2">
         <v>0</v>
       </c>
       <c r="H649" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.15">
@@ -32739,13 +32739,13 @@
         <v>836</v>
       </c>
       <c r="F664" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G664" s="2">
         <v>0</v>
       </c>
       <c r="H664" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="665" spans="1:8" x14ac:dyDescent="0.15">
@@ -33077,13 +33077,13 @@
         <v>836</v>
       </c>
       <c r="F677" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G677" s="2">
         <v>0</v>
       </c>
       <c r="H677" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="678" spans="1:8" x14ac:dyDescent="0.15">
@@ -33363,10 +33363,10 @@
         <v>810</v>
       </c>
       <c r="F688" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G688" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H688" s="2">
         <v>0</v>
@@ -34507,10 +34507,10 @@
         <v>836</v>
       </c>
       <c r="F732" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G732" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H732" s="2">
         <v>0</v>
@@ -34819,13 +34819,13 @@
         <v>409</v>
       </c>
       <c r="F744" s="2">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G744" s="2">
         <v>0</v>
       </c>
       <c r="H744" s="2">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.15">
@@ -38017,13 +38017,13 @@
         <v>111</v>
       </c>
       <c r="F867" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G867" s="2">
         <v>0</v>
       </c>
       <c r="H867" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="868" spans="1:8" x14ac:dyDescent="0.15">
@@ -39213,13 +39213,13 @@
         <v>1516</v>
       </c>
       <c r="F913" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G913" s="2">
         <v>0</v>
       </c>
       <c r="H913" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="914" spans="1:8" x14ac:dyDescent="0.15">
@@ -44671,13 +44671,13 @@
         <v>1826</v>
       </c>
       <c r="F1123" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G1123" s="2">
         <v>0</v>
       </c>
       <c r="H1123" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1124" spans="1:8" x14ac:dyDescent="0.15">
@@ -45605,13 +45605,13 @@
         <v>295</v>
       </c>
       <c r="F1159" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1159" s="2">
         <v>0</v>
       </c>
       <c r="H1159" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1160" spans="1:8" x14ac:dyDescent="0.15">
@@ -49037,13 +49037,13 @@
         <v>98</v>
       </c>
       <c r="F1291" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1291" s="2">
         <v>0</v>
       </c>
       <c r="H1291" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1292" spans="1:8" x14ac:dyDescent="0.15">
@@ -53431,13 +53431,13 @@
         <v>635</v>
       </c>
       <c r="F1460" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1460" s="2">
         <v>0</v>
       </c>
       <c r="H1460" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1461" spans="1:8" x14ac:dyDescent="0.15">
@@ -55615,13 +55615,13 @@
         <v>44</v>
       </c>
       <c r="F1544" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1544" s="2">
         <v>0</v>
       </c>
       <c r="H1544" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1545" spans="1:8" x14ac:dyDescent="0.15">
@@ -62739,10 +62739,10 @@
         <v>17</v>
       </c>
       <c r="F1818" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1818" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1818" s="2">
         <v>1</v>
@@ -75635,13 +75635,13 @@
         <v>4020</v>
       </c>
       <c r="F2314" s="2">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G2314" s="2">
         <v>0</v>
       </c>
       <c r="H2314" s="2">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2315" spans="1:8" x14ac:dyDescent="0.15">
@@ -85695,13 +85695,13 @@
         <v>65</v>
       </c>
       <c r="F2701" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2701" s="2">
         <v>0</v>
       </c>
       <c r="H2701" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2702" spans="1:8" x14ac:dyDescent="0.15">
@@ -87255,13 +87255,13 @@
         <v>524</v>
       </c>
       <c r="F2761" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2761" s="2">
         <v>0</v>
       </c>
       <c r="H2761" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2762" spans="1:8" x14ac:dyDescent="0.15">
@@ -89439,13 +89439,13 @@
         <v>65</v>
       </c>
       <c r="F2845" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G2845" s="2">
         <v>0</v>
       </c>
       <c r="H2845" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2846" spans="1:8" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E57F60FE-F8BE-4174-BC44-632CCBA40639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CA094F2-D6B8-4024-939C-998A47556C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16421,13 +16421,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.15">
@@ -17487,13 +17487,13 @@
         <v>139</v>
       </c>
       <c r="F77" s="2">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.15">
@@ -17669,13 +17669,13 @@
         <v>139</v>
       </c>
       <c r="F84" s="2">
-        <v>870</v>
+        <v>852</v>
       </c>
       <c r="G84" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" s="2">
-        <v>870</v>
+        <v>851</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.15">
@@ -17981,13 +17981,13 @@
         <v>98</v>
       </c>
       <c r="F96" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G96" s="2">
         <v>2</v>
       </c>
       <c r="H96" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.15">
@@ -18007,13 +18007,13 @@
         <v>139</v>
       </c>
       <c r="F97" s="2">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="G97" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H97" s="2">
-        <v>307</v>
+        <v>289</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.15">
@@ -18189,13 +18189,13 @@
         <v>139</v>
       </c>
       <c r="F104" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="G104" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H104" s="2">
-        <v>224</v>
+        <v>214</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.15">
@@ -35131,13 +35131,13 @@
         <v>409</v>
       </c>
       <c r="F756" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G756" s="2">
         <v>0</v>
       </c>
       <c r="H756" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="757" spans="1:8" x14ac:dyDescent="0.15">
@@ -44671,13 +44671,13 @@
         <v>1826</v>
       </c>
       <c r="F1123" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G1123" s="2">
         <v>0</v>
       </c>
       <c r="H1123" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1124" spans="1:8" x14ac:dyDescent="0.15">
@@ -53431,13 +53431,13 @@
         <v>635</v>
       </c>
       <c r="F1460" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1460" s="2">
         <v>0</v>
       </c>
       <c r="H1460" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1461" spans="1:8" x14ac:dyDescent="0.15">
@@ -75635,13 +75635,13 @@
         <v>4020</v>
       </c>
       <c r="F2314" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G2314" s="2">
         <v>0</v>
       </c>
       <c r="H2314" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2315" spans="1:8" x14ac:dyDescent="0.15">
@@ -89023,13 +89023,13 @@
         <v>65</v>
       </c>
       <c r="F2829" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G2829" s="2">
         <v>0</v>
       </c>
       <c r="H2829" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2830" spans="1:8" x14ac:dyDescent="0.15">
@@ -89439,13 +89439,13 @@
         <v>65</v>
       </c>
       <c r="F2845" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2845" s="2">
         <v>0</v>
       </c>
       <c r="H2845" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2846" spans="1:8" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626998CC-31B7-4C32-977C-5BCB38FCD6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E5E60C5-8EB4-4B7A-A48A-AD3C0A334092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="17835" windowHeight="14475" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -17009,13 +17009,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17529,13 +17529,13 @@
         <v>2142</v>
       </c>
       <c r="F77" s="2">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17555,13 +17555,13 @@
         <v>2142</v>
       </c>
       <c r="F78" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17711,13 +17711,13 @@
         <v>2142</v>
       </c>
       <c r="F84" s="2">
-        <v>835</v>
+        <v>807</v>
       </c>
       <c r="G84" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>827</v>
+        <v>807</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -18023,13 +18023,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G96" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H96" s="2">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -18049,13 +18049,13 @@
         <v>2142</v>
       </c>
       <c r="F97" s="2">
-        <v>274</v>
+        <v>249</v>
       </c>
       <c r="G97" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>270</v>
+        <v>249</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18231,13 +18231,13 @@
         <v>2142</v>
       </c>
       <c r="F104" s="2">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="G104" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H104" s="2">
-        <v>199</v>
+        <v>190</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -28703,13 +28703,13 @@
         <v>2136</v>
       </c>
       <c r="F507" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G507" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H507" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.25">
@@ -29431,13 +29431,13 @@
         <v>2371</v>
       </c>
       <c r="F535" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G535" s="2">
         <v>1</v>
       </c>
       <c r="H535" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.25">
@@ -32391,10 +32391,10 @@
         <v>2617</v>
       </c>
       <c r="F649" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G649" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H649" s="2">
         <v>60</v>
@@ -32963,10 +32963,10 @@
         <v>2617</v>
       </c>
       <c r="F671" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G671" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H671" s="2">
         <v>5</v>
@@ -33223,10 +33223,10 @@
         <v>2103</v>
       </c>
       <c r="F681" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G681" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H681" s="2">
         <v>1</v>
@@ -33275,10 +33275,10 @@
         <v>2617</v>
       </c>
       <c r="F683" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G683" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H683" s="2">
         <v>10</v>
@@ -35069,10 +35069,10 @@
         <v>2282</v>
       </c>
       <c r="F752" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G752" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H752" s="2">
         <v>4</v>
@@ -35173,10 +35173,10 @@
         <v>2282</v>
       </c>
       <c r="F756" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G756" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H756" s="2">
         <v>33</v>
@@ -39255,10 +39255,10 @@
         <v>2955</v>
       </c>
       <c r="F913" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G913" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H913" s="2">
         <v>28</v>
@@ -75677,13 +75677,13 @@
         <v>4408</v>
       </c>
       <c r="F2314" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G2314" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2314" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2315" spans="1:8" x14ac:dyDescent="0.25">
@@ -89065,13 +89065,13 @@
         <v>2113</v>
       </c>
       <c r="F2829" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G2829" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2829" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2830" spans="1:8" x14ac:dyDescent="0.25">
@@ -89120,10 +89120,10 @@
         <v>13</v>
       </c>
       <c r="G2831" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2831" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2832" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2611DB7-79D5-41AF-B719-CCB8959AA294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92011447-C182-427F-834F-291CF4C08B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17489,10 +17489,10 @@
         <v>53</v>
       </c>
       <c r="G77" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.15">
@@ -17515,10 +17515,10 @@
         <v>28</v>
       </c>
       <c r="G78" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.15">
@@ -17671,10 +17671,10 @@
         <v>711</v>
       </c>
       <c r="G84" s="1">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="H84" s="1">
-        <v>711</v>
+        <v>657</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.15">
@@ -17983,10 +17983,10 @@
         <v>76</v>
       </c>
       <c r="G96" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H96" s="1">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.15">
@@ -18006,13 +18006,13 @@
         <v>139</v>
       </c>
       <c r="F97" s="1">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G97" s="1">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H97" s="1">
-        <v>137</v>
+        <v>119</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.15">
@@ -18191,10 +18191,10 @@
         <v>92</v>
       </c>
       <c r="G104" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H104" s="1">
-        <v>92</v>
+        <v>67</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.15">
@@ -18295,10 +18295,10 @@
         <v>30</v>
       </c>
       <c r="G108" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H108" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.15">
@@ -22347,10 +22347,10 @@
         <v>15</v>
       </c>
       <c r="G264" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H264" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.15">
@@ -28663,10 +28663,10 @@
         <v>46</v>
       </c>
       <c r="G507" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H507" s="1">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.15">
@@ -31859,10 +31859,10 @@
         <v>13</v>
       </c>
       <c r="G630" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H630" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="631" spans="1:8" x14ac:dyDescent="0.15">
@@ -32299,10 +32299,10 @@
         <v>17</v>
       </c>
       <c r="G647" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H647" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="648" spans="1:8" x14ac:dyDescent="0.15">
@@ -32585,10 +32585,10 @@
         <v>14</v>
       </c>
       <c r="G658" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H658" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="659" spans="1:8" x14ac:dyDescent="0.15">
@@ -32741,10 +32741,10 @@
         <v>1</v>
       </c>
       <c r="G664" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H664" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="665" spans="1:8" x14ac:dyDescent="0.15">
@@ -33079,10 +33079,10 @@
         <v>8</v>
       </c>
       <c r="G677" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H677" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="678" spans="1:8" x14ac:dyDescent="0.15">
@@ -34821,10 +34821,10 @@
         <v>78</v>
       </c>
       <c r="G744" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H744" s="1">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.15">
@@ -44673,10 +44673,10 @@
         <v>31</v>
       </c>
       <c r="G1123" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1123" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1124" spans="1:8" x14ac:dyDescent="0.15">
@@ -48727,10 +48727,10 @@
         <v>1</v>
       </c>
       <c r="G1279" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1279" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1280" spans="1:8" x14ac:dyDescent="0.15">
@@ -48987,10 +48987,10 @@
         <v>5</v>
       </c>
       <c r="G1289" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1289" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1290" spans="1:8" x14ac:dyDescent="0.15">
@@ -51093,10 +51093,10 @@
         <v>9</v>
       </c>
       <c r="G1370" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1370" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1371" spans="1:8" x14ac:dyDescent="0.15">
@@ -75634,13 +75634,13 @@
         <v>4020</v>
       </c>
       <c r="F2314" s="1">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G2314" s="1">
         <v>0</v>
       </c>
       <c r="H2314" s="1">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2315" spans="1:8" x14ac:dyDescent="0.15">
@@ -89025,10 +89025,10 @@
         <v>30</v>
       </c>
       <c r="G2829" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2829" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2830" spans="1:8" x14ac:dyDescent="0.15">
@@ -89441,10 +89441,10 @@
         <v>3</v>
       </c>
       <c r="G2845" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2845" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2846" spans="1:8" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92011447-C182-427F-834F-291CF4C08B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28BFEACF-0FB0-4B39-A56C-5E090EC4D01F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17096,13 +17096,13 @@
         <v>107</v>
       </c>
       <c r="F62" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G62" s="1">
         <v>0</v>
       </c>
       <c r="H62" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.15">
@@ -17486,13 +17486,13 @@
         <v>139</v>
       </c>
       <c r="F77" s="1">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G77" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" s="1">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.15">
@@ -17512,13 +17512,13 @@
         <v>139</v>
       </c>
       <c r="F78" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G78" s="1">
         <v>1</v>
       </c>
       <c r="H78" s="1">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.15">
@@ -17668,13 +17668,13 @@
         <v>139</v>
       </c>
       <c r="F84" s="1">
-        <v>711</v>
+        <v>640</v>
       </c>
       <c r="G84" s="1">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="H84" s="1">
-        <v>657</v>
+        <v>624</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.15">
@@ -17980,10 +17980,10 @@
         <v>98</v>
       </c>
       <c r="F96" s="1">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G96" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H96" s="1">
         <v>72</v>
@@ -18006,13 +18006,13 @@
         <v>139</v>
       </c>
       <c r="F97" s="1">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="G97" s="1">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H97" s="1">
-        <v>119</v>
+        <v>98</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.15">
@@ -18188,13 +18188,13 @@
         <v>139</v>
       </c>
       <c r="F104" s="1">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="G104" s="1">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="H104" s="1">
-        <v>67</v>
+        <v>49</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.15">
@@ -18292,13 +18292,13 @@
         <v>139</v>
       </c>
       <c r="F108" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G108" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H108" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.15">
@@ -22344,10 +22344,10 @@
         <v>26</v>
       </c>
       <c r="F264" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G264" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H264" s="1">
         <v>14</v>
@@ -27778,13 +27778,13 @@
         <v>127</v>
       </c>
       <c r="F473" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G473" s="1">
         <v>0</v>
       </c>
       <c r="H473" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.15">
@@ -28660,13 +28660,13 @@
         <v>127</v>
       </c>
       <c r="F507" s="1">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G507" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H507" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.15">
@@ -31856,13 +31856,13 @@
         <v>1049</v>
       </c>
       <c r="F630" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G630" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H630" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="631" spans="1:8" x14ac:dyDescent="0.15">
@@ -32296,10 +32296,10 @@
         <v>836</v>
       </c>
       <c r="F647" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G647" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H647" s="1">
         <v>16</v>
@@ -32400,13 +32400,13 @@
         <v>836</v>
       </c>
       <c r="F651" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G651" s="1">
         <v>0</v>
       </c>
       <c r="H651" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="652" spans="1:8" x14ac:dyDescent="0.15">
@@ -32582,10 +32582,10 @@
         <v>836</v>
       </c>
       <c r="F658" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G658" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H658" s="1">
         <v>13</v>
@@ -32738,10 +32738,10 @@
         <v>836</v>
       </c>
       <c r="F664" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G664" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H664" s="1">
         <v>0</v>
@@ -33050,13 +33050,13 @@
         <v>836</v>
       </c>
       <c r="F676" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G676" s="1">
         <v>0</v>
       </c>
       <c r="H676" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="677" spans="1:8" x14ac:dyDescent="0.15">
@@ -33076,10 +33076,10 @@
         <v>836</v>
       </c>
       <c r="F677" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G677" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H677" s="1">
         <v>5</v>
@@ -34818,13 +34818,13 @@
         <v>409</v>
       </c>
       <c r="F744" s="1">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G744" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H744" s="1">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.15">
@@ -35078,13 +35078,13 @@
         <v>409</v>
       </c>
       <c r="F754" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G754" s="1">
         <v>0</v>
       </c>
       <c r="H754" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="755" spans="1:8" x14ac:dyDescent="0.15">
@@ -35130,13 +35130,13 @@
         <v>409</v>
       </c>
       <c r="F756" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G756" s="1">
         <v>0</v>
       </c>
       <c r="H756" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="757" spans="1:8" x14ac:dyDescent="0.15">
@@ -35312,13 +35312,13 @@
         <v>409</v>
       </c>
       <c r="F763" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G763" s="1">
         <v>0</v>
       </c>
       <c r="H763" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="764" spans="1:8" x14ac:dyDescent="0.15">
@@ -44670,10 +44670,10 @@
         <v>1826</v>
       </c>
       <c r="F1123" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G1123" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1123" s="1">
         <v>30</v>
@@ -48724,10 +48724,10 @@
         <v>304</v>
       </c>
       <c r="F1279" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1279" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1279" s="1">
         <v>0</v>
@@ -48984,10 +48984,10 @@
         <v>304</v>
       </c>
       <c r="F1289" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1289" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1289" s="1">
         <v>4</v>
@@ -51090,10 +51090,10 @@
         <v>2226</v>
       </c>
       <c r="F1370" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1370" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1370" s="1">
         <v>8</v>
@@ -51142,13 +51142,13 @@
         <v>2226</v>
       </c>
       <c r="F1372" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1372" s="1">
         <v>0</v>
       </c>
       <c r="H1372" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1373" spans="1:8" x14ac:dyDescent="0.15">
@@ -75634,13 +75634,13 @@
         <v>4020</v>
       </c>
       <c r="F2314" s="1">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="G2314" s="1">
         <v>0</v>
       </c>
       <c r="H2314" s="1">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2315" spans="1:8" x14ac:dyDescent="0.15">
@@ -84004,10 +84004,10 @@
         <v>127</v>
       </c>
       <c r="F2636" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2636" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2636" s="1">
         <v>0</v>
@@ -86916,13 +86916,13 @@
         <v>242</v>
       </c>
       <c r="F2748" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2748" s="1">
         <v>0</v>
       </c>
       <c r="H2748" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2749" spans="1:8" x14ac:dyDescent="0.15">
@@ -89022,13 +89022,13 @@
         <v>65</v>
       </c>
       <c r="F2829" s="1">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G2829" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2829" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2830" spans="1:8" x14ac:dyDescent="0.15">
@@ -89438,10 +89438,10 @@
         <v>65</v>
       </c>
       <c r="F2845" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2845" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2845" s="1">
         <v>2</v>

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28BFEACF-0FB0-4B39-A56C-5E090EC4D01F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E3D251-6365-45DE-BF6A-BB0F89B5963E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16420,13 +16420,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.15">
@@ -16966,13 +16966,13 @@
         <v>65</v>
       </c>
       <c r="F57" s="1">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G57" s="1">
         <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.15">
@@ -17512,10 +17512,10 @@
         <v>139</v>
       </c>
       <c r="F78" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G78" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" s="1">
         <v>25</v>
@@ -17668,13 +17668,13 @@
         <v>139</v>
       </c>
       <c r="F84" s="1">
-        <v>640</v>
+        <v>597</v>
       </c>
       <c r="G84" s="1">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H84" s="1">
-        <v>624</v>
+        <v>594</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.15">
@@ -18006,13 +18006,13 @@
         <v>139</v>
       </c>
       <c r="F97" s="1">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="G97" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H97" s="1">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.15">
@@ -18188,13 +18188,13 @@
         <v>139</v>
       </c>
       <c r="F104" s="1">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="G104" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H104" s="1">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.15">
@@ -18292,13 +18292,13 @@
         <v>139</v>
       </c>
       <c r="F108" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G108" s="1">
         <v>1</v>
       </c>
       <c r="H108" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.15">
@@ -28660,13 +28660,13 @@
         <v>127</v>
       </c>
       <c r="F507" s="1">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G507" s="1">
         <v>0</v>
       </c>
       <c r="H507" s="1">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.15">
@@ -29388,13 +29388,13 @@
         <v>524</v>
       </c>
       <c r="F535" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G535" s="1">
         <v>0</v>
       </c>
       <c r="H535" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.15">
@@ -31856,13 +31856,13 @@
         <v>1049</v>
       </c>
       <c r="F630" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G630" s="1">
         <v>0</v>
       </c>
       <c r="H630" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="631" spans="1:8" x14ac:dyDescent="0.15">
@@ -32348,13 +32348,13 @@
         <v>836</v>
       </c>
       <c r="F649" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G649" s="1">
         <v>0</v>
       </c>
       <c r="H649" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.15">
@@ -33076,13 +33076,13 @@
         <v>836</v>
       </c>
       <c r="F677" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G677" s="1">
         <v>0</v>
       </c>
       <c r="H677" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="678" spans="1:8" x14ac:dyDescent="0.15">
@@ -34818,13 +34818,13 @@
         <v>409</v>
       </c>
       <c r="F744" s="1">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G744" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H744" s="1">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.15">
@@ -34922,13 +34922,13 @@
         <v>409</v>
       </c>
       <c r="F748" s="1">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G748" s="1">
         <v>0</v>
       </c>
       <c r="H748" s="1">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="749" spans="1:8" x14ac:dyDescent="0.15">
@@ -39056,13 +39056,13 @@
         <v>766</v>
       </c>
       <c r="F907" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G907" s="1">
         <v>0</v>
       </c>
       <c r="H907" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="908" spans="1:8" x14ac:dyDescent="0.15">
@@ -39212,13 +39212,13 @@
         <v>1516</v>
       </c>
       <c r="F913" s="1">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G913" s="1">
         <v>0</v>
       </c>
       <c r="H913" s="1">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="914" spans="1:8" x14ac:dyDescent="0.15">
@@ -50076,13 +50076,13 @@
         <v>304</v>
       </c>
       <c r="F1331" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G1331" s="1">
         <v>0</v>
       </c>
       <c r="H1331" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1332" spans="1:8" x14ac:dyDescent="0.15">
@@ -75634,13 +75634,13 @@
         <v>4020</v>
       </c>
       <c r="F2314" s="1">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G2314" s="1">
         <v>0</v>
       </c>
       <c r="H2314" s="1">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2315" spans="1:8" x14ac:dyDescent="0.15">
@@ -85408,13 +85408,13 @@
         <v>242</v>
       </c>
       <c r="F2690" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2690" s="1">
         <v>0</v>
       </c>
       <c r="H2690" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2691" spans="1:8" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E3D251-6365-45DE-BF6A-BB0F89B5963E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE6A1518-F339-4F95-9F98-7B77F045E7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17489,10 +17489,10 @@
         <v>48</v>
       </c>
       <c r="G77" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.15">
@@ -17512,13 +17512,13 @@
         <v>139</v>
       </c>
       <c r="F78" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G78" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="1">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.15">
@@ -17668,13 +17668,13 @@
         <v>139</v>
       </c>
       <c r="F84" s="1">
-        <v>597</v>
+        <v>582</v>
       </c>
       <c r="G84" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H84" s="1">
-        <v>594</v>
+        <v>576</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.15">
@@ -17980,13 +17980,13 @@
         <v>98</v>
       </c>
       <c r="F96" s="1">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G96" s="1">
         <v>2</v>
       </c>
       <c r="H96" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.15">
@@ -18006,13 +18006,13 @@
         <v>139</v>
       </c>
       <c r="F97" s="1">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G97" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H97" s="1">
-        <v>93</v>
+        <v>78</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.15">
@@ -18058,13 +18058,13 @@
         <v>39</v>
       </c>
       <c r="F99" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G99" s="1">
         <v>0</v>
       </c>
       <c r="H99" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.15">
@@ -18188,13 +18188,13 @@
         <v>139</v>
       </c>
       <c r="F104" s="1">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G104" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H104" s="1">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.15">
@@ -18292,13 +18292,13 @@
         <v>139</v>
       </c>
       <c r="F108" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G108" s="1">
         <v>1</v>
       </c>
       <c r="H108" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.15">
@@ -28660,13 +28660,13 @@
         <v>127</v>
       </c>
       <c r="F507" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G507" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H507" s="1">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.15">
@@ -28738,13 +28738,13 @@
         <v>127</v>
       </c>
       <c r="F510" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G510" s="1">
         <v>0</v>
       </c>
       <c r="H510" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="511" spans="1:8" x14ac:dyDescent="0.15">
@@ -32348,13 +32348,13 @@
         <v>836</v>
       </c>
       <c r="F649" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G649" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H649" s="1">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.15">
@@ -33076,13 +33076,13 @@
         <v>836</v>
       </c>
       <c r="F677" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G677" s="1">
         <v>0</v>
       </c>
       <c r="H677" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="678" spans="1:8" x14ac:dyDescent="0.15">
@@ -33102,13 +33102,13 @@
         <v>836</v>
       </c>
       <c r="F678" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G678" s="1">
         <v>0</v>
       </c>
       <c r="H678" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="679" spans="1:8" x14ac:dyDescent="0.15">
@@ -34818,13 +34818,13 @@
         <v>409</v>
       </c>
       <c r="F744" s="1">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G744" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H744" s="1">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.15">
@@ -34922,13 +34922,13 @@
         <v>409</v>
       </c>
       <c r="F748" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G748" s="1">
         <v>0</v>
       </c>
       <c r="H748" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="749" spans="1:8" x14ac:dyDescent="0.15">
@@ -34948,13 +34948,13 @@
         <v>409</v>
       </c>
       <c r="F749" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G749" s="1">
         <v>0</v>
       </c>
       <c r="H749" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="750" spans="1:8" x14ac:dyDescent="0.15">
@@ -35026,13 +35026,13 @@
         <v>409</v>
       </c>
       <c r="F752" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G752" s="1">
         <v>0</v>
       </c>
       <c r="H752" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.15">
@@ -39215,10 +39215,10 @@
         <v>19</v>
       </c>
       <c r="G913" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H913" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="914" spans="1:8" x14ac:dyDescent="0.15">
@@ -39550,13 +39550,13 @@
         <v>1536</v>
       </c>
       <c r="F926" s="1">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G926" s="1">
         <v>0</v>
       </c>
       <c r="H926" s="1">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="927" spans="1:8" x14ac:dyDescent="0.15">
@@ -50547,10 +50547,10 @@
         <v>1</v>
       </c>
       <c r="G1349" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1349" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1350" spans="1:8" x14ac:dyDescent="0.15">
@@ -51090,13 +51090,13 @@
         <v>2226</v>
       </c>
       <c r="F1370" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1370" s="1">
         <v>0</v>
       </c>
       <c r="H1370" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1371" spans="1:8" x14ac:dyDescent="0.15">
@@ -75634,13 +75634,13 @@
         <v>4020</v>
       </c>
       <c r="F2314" s="1">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G2314" s="1">
         <v>0</v>
       </c>
       <c r="H2314" s="1">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2315" spans="1:8" x14ac:dyDescent="0.15">
@@ -85226,13 +85226,13 @@
         <v>242</v>
       </c>
       <c r="F2683" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2683" s="1">
         <v>0</v>
       </c>
       <c r="H2683" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2684" spans="1:8" x14ac:dyDescent="0.15">
@@ -89022,13 +89022,13 @@
         <v>65</v>
       </c>
       <c r="F2829" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G2829" s="1">
         <v>0</v>
       </c>
       <c r="H2829" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2830" spans="1:8" x14ac:dyDescent="0.15">
@@ -89438,13 +89438,13 @@
         <v>65</v>
       </c>
       <c r="F2845" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2845" s="1">
         <v>0</v>
       </c>
       <c r="H2845" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2846" spans="1:8" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE6A1518-F339-4F95-9F98-7B77F045E7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE867FF-1DA2-4BF1-849B-A0C1124FA56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16420,13 +16420,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.15">
@@ -16524,13 +16524,13 @@
         <v>70</v>
       </c>
       <c r="F40" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.15">
@@ -16732,13 +16732,13 @@
         <v>65</v>
       </c>
       <c r="F48" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="1">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.15">
@@ -16966,13 +16966,13 @@
         <v>65</v>
       </c>
       <c r="F57" s="1">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="G57" s="1">
         <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>17</v>
+        <v>74</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.15">
@@ -17018,13 +17018,13 @@
         <v>65</v>
       </c>
       <c r="F59" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G59" s="1">
         <v>0</v>
       </c>
       <c r="H59" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.15">
@@ -17099,10 +17099,10 @@
         <v>1</v>
       </c>
       <c r="G62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.15">
@@ -17486,13 +17486,13 @@
         <v>139</v>
       </c>
       <c r="F77" s="1">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="G77" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H77" s="1">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.15">
@@ -17512,13 +17512,13 @@
         <v>139</v>
       </c>
       <c r="F78" s="1">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G78" s="1">
         <v>1</v>
       </c>
       <c r="H78" s="1">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.15">
@@ -17538,13 +17538,13 @@
         <v>139</v>
       </c>
       <c r="F79" s="1">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G79" s="1">
         <v>0</v>
       </c>
       <c r="H79" s="1">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.15">
@@ -17668,13 +17668,13 @@
         <v>139</v>
       </c>
       <c r="F84" s="1">
-        <v>582</v>
+        <v>564</v>
       </c>
       <c r="G84" s="1">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="H84" s="1">
-        <v>576</v>
+        <v>538</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.15">
@@ -18006,13 +18006,13 @@
         <v>139</v>
       </c>
       <c r="F97" s="1">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="G97" s="1">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="H97" s="1">
-        <v>78</v>
+        <v>54</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.15">
@@ -18188,13 +18188,13 @@
         <v>139</v>
       </c>
       <c r="F104" s="1">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G104" s="1">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H104" s="1">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.15">
@@ -28660,13 +28660,13 @@
         <v>127</v>
       </c>
       <c r="F507" s="1">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G507" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H507" s="1">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.15">
@@ -32348,13 +32348,13 @@
         <v>836</v>
       </c>
       <c r="F649" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G649" s="1">
         <v>1</v>
       </c>
       <c r="H649" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.15">
@@ -33053,10 +33053,10 @@
         <v>1</v>
       </c>
       <c r="G676" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H676" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="677" spans="1:8" x14ac:dyDescent="0.15">
@@ -34402,13 +34402,13 @@
         <v>836</v>
       </c>
       <c r="F728" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G728" s="1">
         <v>0</v>
       </c>
       <c r="H728" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="729" spans="1:8" x14ac:dyDescent="0.15">
@@ -34818,13 +34818,13 @@
         <v>409</v>
       </c>
       <c r="F744" s="1">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G744" s="1">
         <v>1</v>
       </c>
       <c r="H744" s="1">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.15">
@@ -39212,10 +39212,10 @@
         <v>1516</v>
       </c>
       <c r="F913" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G913" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H913" s="1">
         <v>18</v>
@@ -39654,13 +39654,13 @@
         <v>1536</v>
       </c>
       <c r="F930" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G930" s="1">
         <v>0</v>
       </c>
       <c r="H930" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="931" spans="1:8" x14ac:dyDescent="0.15">
@@ -50544,10 +50544,10 @@
         <v>2226</v>
       </c>
       <c r="F1349" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1349" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1349" s="1">
         <v>0</v>
@@ -51090,13 +51090,13 @@
         <v>2226</v>
       </c>
       <c r="F1370" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1370" s="1">
         <v>0</v>
       </c>
       <c r="H1370" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1371" spans="1:8" x14ac:dyDescent="0.15">
@@ -55565,10 +55565,10 @@
         <v>7</v>
       </c>
       <c r="G1542" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1542" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1543" spans="1:8" x14ac:dyDescent="0.15">
@@ -75634,13 +75634,13 @@
         <v>4020</v>
       </c>
       <c r="F2314" s="1">
-        <v>91</v>
+        <v>188</v>
       </c>
       <c r="G2314" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2314" s="1">
-        <v>91</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2315" spans="1:8" x14ac:dyDescent="0.15">
@@ -81456,13 +81456,13 @@
         <v>2281</v>
       </c>
       <c r="F2538" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2538" s="1">
         <v>0</v>
       </c>
       <c r="H2538" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2539" spans="1:8" x14ac:dyDescent="0.15">
@@ -85775,10 +85775,10 @@
         <v>45</v>
       </c>
       <c r="G2704" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2704" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2705" spans="1:8" x14ac:dyDescent="0.15">
@@ -86919,10 +86919,10 @@
         <v>12</v>
       </c>
       <c r="G2748" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2748" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2749" spans="1:8" x14ac:dyDescent="0.15">
@@ -89022,13 +89022,13 @@
         <v>65</v>
       </c>
       <c r="F2829" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G2829" s="1">
         <v>0</v>
       </c>
       <c r="H2829" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2830" spans="1:8" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAA613EC-9F97-416D-9BF6-79AABA6851F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8245102D-7DFA-4E7F-9D32-9A617C0BFD7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -16463,13 +16463,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16567,13 +16567,13 @@
         <v>2114</v>
       </c>
       <c r="F40" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
       </c>
       <c r="H40" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -16775,13 +16775,13 @@
         <v>2113</v>
       </c>
       <c r="F48" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="2">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -16957,13 +16957,13 @@
         <v>2116</v>
       </c>
       <c r="F55" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G55" s="2">
         <v>0</v>
       </c>
       <c r="H55" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -17009,13 +17009,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17711,13 +17711,13 @@
         <v>2142</v>
       </c>
       <c r="F84" s="2">
-        <v>518</v>
+        <v>483</v>
       </c>
       <c r="G84" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H84" s="2">
-        <v>517</v>
+        <v>475</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -18049,13 +18049,13 @@
         <v>2142</v>
       </c>
       <c r="F97" s="2">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="G97" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H97" s="2">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18127,13 +18127,13 @@
         <v>2103</v>
       </c>
       <c r="F100" s="2">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="G100" s="2">
         <v>0</v>
       </c>
       <c r="H100" s="2">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -18335,13 +18335,13 @@
         <v>2142</v>
       </c>
       <c r="F108" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
       </c>
       <c r="H108" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -28055,13 +28055,13 @@
         <v>2235</v>
       </c>
       <c r="F482" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G482" s="2">
         <v>0</v>
       </c>
       <c r="H482" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.25">
@@ -28703,13 +28703,13 @@
         <v>2136</v>
       </c>
       <c r="F507" s="2">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G507" s="2">
         <v>0</v>
       </c>
       <c r="H507" s="2">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.25">
@@ -28940,10 +28940,10 @@
         <v>2</v>
       </c>
       <c r="G516" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H516" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.25">
@@ -29431,13 +29431,13 @@
         <v>2371</v>
       </c>
       <c r="F535" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G535" s="2">
         <v>0</v>
       </c>
       <c r="H535" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.25">
@@ -32391,13 +32391,13 @@
         <v>2617</v>
       </c>
       <c r="F649" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G649" s="2">
         <v>0</v>
       </c>
       <c r="H649" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.25">
@@ -34445,13 +34445,13 @@
         <v>2617</v>
       </c>
       <c r="F728" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G728" s="2">
         <v>0</v>
       </c>
       <c r="H728" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="729" spans="1:8" x14ac:dyDescent="0.25">
@@ -34861,13 +34861,13 @@
         <v>2282</v>
       </c>
       <c r="F744" s="2">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G744" s="2">
         <v>0</v>
       </c>
       <c r="H744" s="2">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.25">
@@ -34965,13 +34965,13 @@
         <v>2282</v>
       </c>
       <c r="F748" s="2">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G748" s="2">
         <v>0</v>
       </c>
       <c r="H748" s="2">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="749" spans="1:8" x14ac:dyDescent="0.25">
@@ -35069,13 +35069,13 @@
         <v>2282</v>
       </c>
       <c r="F752" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G752" s="2">
         <v>0</v>
       </c>
       <c r="H752" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.25">
@@ -38059,13 +38059,13 @@
         <v>2122</v>
       </c>
       <c r="F867" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G867" s="2">
         <v>0</v>
       </c>
       <c r="H867" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="868" spans="1:8" x14ac:dyDescent="0.25">
@@ -39099,13 +39099,13 @@
         <v>2564</v>
       </c>
       <c r="F907" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G907" s="2">
         <v>0</v>
       </c>
       <c r="H907" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="908" spans="1:8" x14ac:dyDescent="0.25">
@@ -39255,13 +39255,13 @@
         <v>2955</v>
       </c>
       <c r="F913" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G913" s="2">
         <v>0</v>
       </c>
       <c r="H913" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="914" spans="1:8" x14ac:dyDescent="0.25">
@@ -39593,13 +39593,13 @@
         <v>2966</v>
       </c>
       <c r="F926" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G926" s="2">
         <v>0</v>
       </c>
       <c r="H926" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="927" spans="1:8" x14ac:dyDescent="0.25">
@@ -39697,13 +39697,13 @@
         <v>2966</v>
       </c>
       <c r="F930" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G930" s="2">
         <v>0</v>
       </c>
       <c r="H930" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="931" spans="1:8" x14ac:dyDescent="0.25">
@@ -45647,13 +45647,13 @@
         <v>2194</v>
       </c>
       <c r="F1159" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1159" s="2">
         <v>0</v>
       </c>
       <c r="H1159" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1160" spans="1:8" x14ac:dyDescent="0.25">
@@ -48923,13 +48923,13 @@
         <v>2203</v>
       </c>
       <c r="F1285" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G1285" s="2">
         <v>0</v>
       </c>
       <c r="H1285" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1286" spans="1:8" x14ac:dyDescent="0.25">
@@ -49027,13 +49027,13 @@
         <v>2203</v>
       </c>
       <c r="F1289" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1289" s="2">
         <v>0</v>
       </c>
       <c r="H1289" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1290" spans="1:8" x14ac:dyDescent="0.25">
@@ -51136,10 +51136,10 @@
         <v>6</v>
       </c>
       <c r="G1370" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1370" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1371" spans="1:8" x14ac:dyDescent="0.25">
@@ -51211,13 +51211,13 @@
         <v>3315</v>
       </c>
       <c r="F1373" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1373" s="2">
         <v>0</v>
       </c>
       <c r="H1373" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1374" spans="1:8" x14ac:dyDescent="0.25">
@@ -75677,13 +75677,13 @@
         <v>4408</v>
       </c>
       <c r="F2314" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G2314" s="2">
         <v>0</v>
       </c>
       <c r="H2314" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2315" spans="1:8" x14ac:dyDescent="0.25">
@@ -77445,13 +77445,13 @@
         <v>2387</v>
       </c>
       <c r="F2382" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2382" s="2">
         <v>0</v>
       </c>
       <c r="H2382" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2383" spans="1:8" x14ac:dyDescent="0.25">
@@ -85451,13 +85451,13 @@
         <v>2172</v>
       </c>
       <c r="F2690" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2690" s="2">
         <v>0</v>
       </c>
       <c r="H2690" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2691" spans="1:8" x14ac:dyDescent="0.25">
@@ -85815,13 +85815,13 @@
         <v>2446</v>
       </c>
       <c r="F2704" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G2704" s="2">
         <v>0</v>
       </c>
       <c r="H2704" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2705" spans="1:8" x14ac:dyDescent="0.25">
@@ -86959,13 +86959,13 @@
         <v>2172</v>
       </c>
       <c r="F2748" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G2748" s="2">
         <v>0</v>
       </c>
       <c r="H2748" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2749" spans="1:8" x14ac:dyDescent="0.25">
@@ -89065,13 +89065,13 @@
         <v>2113</v>
       </c>
       <c r="F2829" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G2829" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2829" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2830" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8245102D-7DFA-4E7F-9D32-9A617C0BFD7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DAA9E8-567F-4CDB-99F5-501110AB38D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -16775,10 +16775,10 @@
         <v>2113</v>
       </c>
       <c r="F48" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="2">
         <v>27</v>
@@ -17711,10 +17711,10 @@
         <v>2142</v>
       </c>
       <c r="F84" s="2">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="G84" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H84" s="2">
         <v>475</v>
@@ -18049,10 +18049,10 @@
         <v>2142</v>
       </c>
       <c r="F97" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G97" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H97" s="2">
         <v>21</v>
@@ -28937,10 +28937,10 @@
         <v>2625</v>
       </c>
       <c r="F516" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G516" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H516" s="2">
         <v>1</v>
@@ -51133,10 +51133,10 @@
         <v>3315</v>
       </c>
       <c r="F1370" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1370" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1370" s="2">
         <v>5</v>
@@ -89065,10 +89065,10 @@
         <v>2113</v>
       </c>
       <c r="F2829" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2829" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2829" s="2">
         <v>25</v>

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E925D0-5281-40B6-B116-FAFF11B71E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EDBCF6E-BDE1-49A4-9BE7-568CB09E5814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16420,13 +16420,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.15">
@@ -16524,10 +16524,10 @@
         <v>70</v>
       </c>
       <c r="F40" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="1">
         <v>13</v>
@@ -16732,13 +16732,13 @@
         <v>65</v>
       </c>
       <c r="F48" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G48" s="1">
         <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.15">
@@ -16969,10 +16969,10 @@
         <v>68</v>
       </c>
       <c r="G57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.15">
@@ -17486,13 +17486,13 @@
         <v>139</v>
       </c>
       <c r="F77" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G77" s="1">
         <v>0</v>
       </c>
       <c r="H77" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.15">
@@ -17512,13 +17512,13 @@
         <v>139</v>
       </c>
       <c r="F78" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G78" s="1">
         <v>0</v>
       </c>
       <c r="H78" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.15">
@@ -17668,13 +17668,13 @@
         <v>139</v>
       </c>
       <c r="F84" s="1">
-        <v>457</v>
+        <v>428</v>
       </c>
       <c r="G84" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H84" s="1">
-        <v>450</v>
+        <v>418</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.15">
@@ -18006,13 +18006,13 @@
         <v>139</v>
       </c>
       <c r="F97" s="1">
-        <v>10</v>
+        <v>449</v>
       </c>
       <c r="G97" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H97" s="1">
-        <v>2</v>
+        <v>440</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.15">
@@ -18061,10 +18061,10 @@
         <v>22</v>
       </c>
       <c r="G99" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H99" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.15">
@@ -18084,13 +18084,13 @@
         <v>39</v>
       </c>
       <c r="F100" s="1">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G100" s="1">
         <v>0</v>
       </c>
       <c r="H100" s="1">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.15">
@@ -28660,10 +28660,10 @@
         <v>127</v>
       </c>
       <c r="F507" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G507" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H507" s="1">
         <v>13</v>
@@ -29414,10 +29414,10 @@
         <v>42</v>
       </c>
       <c r="F536" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G536" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H536" s="1">
         <v>24</v>
@@ -32348,13 +32348,13 @@
         <v>836</v>
       </c>
       <c r="F649" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G649" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H649" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.15">
@@ -32920,10 +32920,10 @@
         <v>836</v>
       </c>
       <c r="F671" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G671" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H671" s="1">
         <v>3</v>
@@ -34818,13 +34818,13 @@
         <v>409</v>
       </c>
       <c r="F744" s="1">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G744" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H744" s="1">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.15">
@@ -35026,10 +35026,10 @@
         <v>409</v>
       </c>
       <c r="F752" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G752" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H752" s="1">
         <v>0</v>
@@ -38019,10 +38019,10 @@
         <v>37</v>
       </c>
       <c r="G867" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H867" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="868" spans="1:8" x14ac:dyDescent="0.15">
@@ -39059,10 +39059,10 @@
         <v>9</v>
       </c>
       <c r="G907" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H907" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="908" spans="1:8" x14ac:dyDescent="0.15">
@@ -44670,10 +44670,10 @@
         <v>1826</v>
       </c>
       <c r="F1123" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G1123" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1123" s="1">
         <v>29</v>
@@ -49351,10 +49351,10 @@
         <v>11</v>
       </c>
       <c r="G1303" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1303" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1304" spans="1:8" x14ac:dyDescent="0.15">
@@ -75634,13 +75634,13 @@
         <v>4020</v>
       </c>
       <c r="F2314" s="1">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G2314" s="1">
         <v>0</v>
       </c>
       <c r="H2314" s="1">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2315" spans="1:8" x14ac:dyDescent="0.15">
@@ -85408,13 +85408,13 @@
         <v>242</v>
       </c>
       <c r="F2690" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2690" s="1">
         <v>0</v>
       </c>
       <c r="H2690" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2691" spans="1:8" x14ac:dyDescent="0.15">
@@ -86864,13 +86864,13 @@
         <v>4825</v>
       </c>
       <c r="F2746" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2746" s="1">
         <v>0</v>
       </c>
       <c r="H2746" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2747" spans="1:8" x14ac:dyDescent="0.15">
@@ -86916,13 +86916,13 @@
         <v>242</v>
       </c>
       <c r="F2748" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G2748" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2748" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2749" spans="1:8" x14ac:dyDescent="0.15">
@@ -89438,13 +89438,13 @@
         <v>65</v>
       </c>
       <c r="F2845" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2845" s="1">
         <v>0</v>
       </c>
       <c r="H2845" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2846" spans="1:8" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E57DB9-AB59-46C1-BB6B-F2E52B81F909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8477601D-58AC-4398-8220-CACF6E120700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="12690" windowHeight="14475" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
+    <workbookView xWindow="2340" yWindow="1725" windowWidth="12690" windowHeight="14475" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -16021,13 +16021,13 @@
         <v>2106</v>
       </c>
       <c r="F19" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
       </c>
       <c r="H19" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -16463,13 +16463,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -17009,13 +17009,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17139,13 +17139,13 @@
         <v>2118</v>
       </c>
       <c r="F62" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -17555,13 +17555,13 @@
         <v>2142</v>
       </c>
       <c r="F78" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17711,13 +17711,13 @@
         <v>2142</v>
       </c>
       <c r="F84" s="2">
-        <v>390</v>
+        <v>361</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>390</v>
+        <v>361</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -18023,13 +18023,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G96" s="2">
         <v>2</v>
       </c>
       <c r="H96" s="2">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -18049,13 +18049,13 @@
         <v>2142</v>
       </c>
       <c r="F97" s="2">
-        <v>420</v>
+        <v>397</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
       </c>
       <c r="H97" s="2">
-        <v>420</v>
+        <v>397</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18127,13 +18127,13 @@
         <v>2103</v>
       </c>
       <c r="F100" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="G100" s="2">
         <v>0</v>
       </c>
       <c r="H100" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -18335,13 +18335,13 @@
         <v>2142</v>
       </c>
       <c r="F108" s="2">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
       </c>
       <c r="H108" s="2">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -28703,13 +28703,13 @@
         <v>2136</v>
       </c>
       <c r="F507" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="G507" s="2">
         <v>0</v>
       </c>
       <c r="H507" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.25">
@@ -28729,13 +28729,13 @@
         <v>2625</v>
       </c>
       <c r="F508" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G508" s="2">
         <v>0</v>
       </c>
       <c r="H508" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="509" spans="1:8" x14ac:dyDescent="0.25">
@@ -31899,13 +31899,13 @@
         <v>2720</v>
       </c>
       <c r="F630" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G630" s="2">
         <v>0</v>
       </c>
       <c r="H630" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="631" spans="1:8" x14ac:dyDescent="0.25">
@@ -32391,13 +32391,13 @@
         <v>2617</v>
       </c>
       <c r="F649" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G649" s="2">
         <v>0</v>
       </c>
       <c r="H649" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.25">
@@ -32573,13 +32573,13 @@
         <v>2136</v>
       </c>
       <c r="F656" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G656" s="2">
         <v>0</v>
       </c>
       <c r="H656" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="657" spans="1:8" x14ac:dyDescent="0.25">
@@ -33171,13 +33171,13 @@
         <v>2108</v>
       </c>
       <c r="F679" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G679" s="2">
         <v>0</v>
       </c>
       <c r="H679" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="680" spans="1:8" x14ac:dyDescent="0.25">
@@ -33275,13 +33275,13 @@
         <v>2617</v>
       </c>
       <c r="F683" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G683" s="2">
         <v>0</v>
       </c>
       <c r="H683" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="684" spans="1:8" x14ac:dyDescent="0.25">
@@ -34367,13 +34367,13 @@
         <v>2106</v>
       </c>
       <c r="F725" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G725" s="2">
         <v>0</v>
       </c>
       <c r="H725" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="726" spans="1:8" x14ac:dyDescent="0.25">
@@ -34861,13 +34861,13 @@
         <v>2282</v>
       </c>
       <c r="F744" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G744" s="2">
         <v>0</v>
       </c>
       <c r="H744" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.25">
@@ -35173,13 +35173,13 @@
         <v>2282</v>
       </c>
       <c r="F756" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G756" s="2">
         <v>0</v>
       </c>
       <c r="H756" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="757" spans="1:8" x14ac:dyDescent="0.25">
@@ -38059,13 +38059,13 @@
         <v>2122</v>
       </c>
       <c r="F867" s="2">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="G867" s="2">
         <v>0</v>
       </c>
       <c r="H867" s="2">
-        <v>36</v>
+        <v>56</v>
       </c>
     </row>
     <row r="868" spans="1:8" x14ac:dyDescent="0.25">
@@ -39255,13 +39255,13 @@
         <v>2955</v>
       </c>
       <c r="F913" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G913" s="2">
         <v>0</v>
       </c>
       <c r="H913" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="914" spans="1:8" x14ac:dyDescent="0.25">
@@ -44713,13 +44713,13 @@
         <v>3110</v>
       </c>
       <c r="F1123" s="2">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="G1123" s="2">
         <v>0</v>
       </c>
       <c r="H1123" s="2">
-        <v>28</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1124" spans="1:8" x14ac:dyDescent="0.25">
@@ -51133,13 +51133,13 @@
         <v>3315</v>
       </c>
       <c r="F1370" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1370" s="2">
         <v>0</v>
       </c>
       <c r="H1370" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1371" spans="1:8" x14ac:dyDescent="0.25">
@@ -75677,13 +75677,13 @@
         <v>4408</v>
       </c>
       <c r="F2314" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="G2314" s="2">
         <v>0</v>
       </c>
       <c r="H2314" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2315" spans="1:8" x14ac:dyDescent="0.25">
@@ -81499,13 +81499,13 @@
         <v>3354</v>
       </c>
       <c r="F2538" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2538" s="2">
         <v>0</v>
       </c>
       <c r="H2538" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2539" spans="1:8" x14ac:dyDescent="0.25">
@@ -85451,13 +85451,13 @@
         <v>2172</v>
       </c>
       <c r="F2690" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2690" s="2">
         <v>0</v>
       </c>
       <c r="H2690" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2691" spans="1:8" x14ac:dyDescent="0.25">
@@ -86959,13 +86959,13 @@
         <v>2172</v>
       </c>
       <c r="F2748" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G2748" s="2">
         <v>0</v>
       </c>
       <c r="H2748" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2749" spans="1:8" x14ac:dyDescent="0.25">
@@ -89065,13 +89065,13 @@
         <v>2113</v>
       </c>
       <c r="F2829" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G2829" s="2">
         <v>0</v>
       </c>
       <c r="H2829" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2830" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8477601D-58AC-4398-8220-CACF6E120700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B395CAF-55D8-4E11-A18E-4FB53D956E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1725" windowWidth="12690" windowHeight="14475" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -16463,13 +16463,13 @@
         <v>2113</v>
       </c>
       <c r="F36" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16775,13 +16775,13 @@
         <v>2113</v>
       </c>
       <c r="F48" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -17009,13 +17009,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17555,13 +17555,13 @@
         <v>2142</v>
       </c>
       <c r="F78" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17711,13 +17711,13 @@
         <v>2142</v>
       </c>
       <c r="F84" s="2">
-        <v>361</v>
+        <v>337</v>
       </c>
       <c r="G84" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H84" s="2">
-        <v>361</v>
+        <v>326</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -18023,13 +18023,13 @@
         <v>2116</v>
       </c>
       <c r="F96" s="2">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G96" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H96" s="2">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -18049,13 +18049,13 @@
         <v>2142</v>
       </c>
       <c r="F97" s="2">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="G97" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H97" s="2">
-        <v>397</v>
+        <v>374</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -18127,13 +18127,13 @@
         <v>2103</v>
       </c>
       <c r="F100" s="2">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="G100" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H100" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -18335,13 +18335,13 @@
         <v>2142</v>
       </c>
       <c r="F108" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G108" s="2">
         <v>1</v>
       </c>
       <c r="H108" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -28055,13 +28055,13 @@
         <v>2235</v>
       </c>
       <c r="F482" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G482" s="2">
         <v>0</v>
       </c>
       <c r="H482" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.25">
@@ -28703,13 +28703,13 @@
         <v>2136</v>
       </c>
       <c r="F507" s="2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G507" s="2">
         <v>0</v>
       </c>
       <c r="H507" s="2">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.25">
@@ -28729,13 +28729,13 @@
         <v>2625</v>
       </c>
       <c r="F508" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G508" s="2">
         <v>0</v>
       </c>
       <c r="H508" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="509" spans="1:8" x14ac:dyDescent="0.25">
@@ -32391,13 +32391,13 @@
         <v>2617</v>
       </c>
       <c r="F649" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G649" s="2">
         <v>0</v>
       </c>
       <c r="H649" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.25">
@@ -33171,13 +33171,13 @@
         <v>2108</v>
       </c>
       <c r="F679" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G679" s="2">
         <v>0</v>
       </c>
       <c r="H679" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="680" spans="1:8" x14ac:dyDescent="0.25">
@@ -34861,13 +34861,13 @@
         <v>2282</v>
       </c>
       <c r="F744" s="2">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G744" s="2">
         <v>0</v>
       </c>
       <c r="H744" s="2">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.25">
@@ -34965,13 +34965,13 @@
         <v>2282</v>
       </c>
       <c r="F748" s="2">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G748" s="2">
         <v>0</v>
       </c>
       <c r="H748" s="2">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="749" spans="1:8" x14ac:dyDescent="0.25">
@@ -35173,13 +35173,13 @@
         <v>2282</v>
       </c>
       <c r="F756" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G756" s="2">
         <v>0</v>
       </c>
       <c r="H756" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="757" spans="1:8" x14ac:dyDescent="0.25">
@@ -38059,13 +38059,13 @@
         <v>2122</v>
       </c>
       <c r="F867" s="2">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G867" s="2">
         <v>0</v>
       </c>
       <c r="H867" s="2">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="868" spans="1:8" x14ac:dyDescent="0.25">
@@ -39099,13 +39099,13 @@
         <v>2564</v>
       </c>
       <c r="F907" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G907" s="2">
         <v>0</v>
       </c>
       <c r="H907" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="908" spans="1:8" x14ac:dyDescent="0.25">
@@ -39697,13 +39697,13 @@
         <v>2966</v>
       </c>
       <c r="F930" s="2">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G930" s="2">
         <v>0</v>
       </c>
       <c r="H930" s="2">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="931" spans="1:8" x14ac:dyDescent="0.25">
@@ -44713,13 +44713,13 @@
         <v>3110</v>
       </c>
       <c r="F1123" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G1123" s="2">
         <v>0</v>
       </c>
       <c r="H1123" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1124" spans="1:8" x14ac:dyDescent="0.25">
@@ -45647,13 +45647,13 @@
         <v>2194</v>
       </c>
       <c r="F1159" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1159" s="2">
         <v>0</v>
       </c>
       <c r="H1159" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1160" spans="1:8" x14ac:dyDescent="0.25">
@@ -75677,13 +75677,13 @@
         <v>4408</v>
       </c>
       <c r="F2314" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G2314" s="2">
         <v>0</v>
       </c>
       <c r="H2314" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2315" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF452C77-4AC2-4352-B3ED-0AE40BFACE1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F6B68F-3CD2-407B-971C-71C4BB5D2447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16732,13 +16732,13 @@
         <v>65</v>
       </c>
       <c r="F48" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G48" s="1">
         <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.15">
@@ -16969,10 +16969,10 @@
         <v>57</v>
       </c>
       <c r="G57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.15">
@@ -17512,13 +17512,13 @@
         <v>139</v>
       </c>
       <c r="F78" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G78" s="1">
         <v>0</v>
       </c>
       <c r="H78" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.15">
@@ -17671,10 +17671,10 @@
         <v>304</v>
       </c>
       <c r="G84" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H84" s="1">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.15">
@@ -17983,10 +17983,10 @@
         <v>59</v>
       </c>
       <c r="G96" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H96" s="1">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.15">
@@ -18006,13 +18006,13 @@
         <v>139</v>
       </c>
       <c r="F97" s="1">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="G97" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H97" s="1">
-        <v>351</v>
+        <v>330</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.15">
@@ -18061,10 +18061,10 @@
         <v>20</v>
       </c>
       <c r="G99" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.15">
@@ -18295,10 +18295,10 @@
         <v>36</v>
       </c>
       <c r="G108" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H108" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.15">
@@ -27388,13 +27388,13 @@
         <v>127</v>
       </c>
       <c r="F458" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G458" s="1">
         <v>0</v>
       </c>
       <c r="H458" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.15">
@@ -28660,13 +28660,13 @@
         <v>127</v>
       </c>
       <c r="F507" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G507" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H507" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.15">
@@ -29388,13 +29388,13 @@
         <v>524</v>
       </c>
       <c r="F535" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G535" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H535" s="1">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.15">
@@ -34821,10 +34821,10 @@
         <v>52</v>
       </c>
       <c r="G744" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H744" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.15">
@@ -39654,13 +39654,13 @@
         <v>1536</v>
       </c>
       <c r="F930" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G930" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H930" s="1">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="931" spans="1:8" x14ac:dyDescent="0.15">
@@ -40463,10 +40463,10 @@
         <v>1</v>
       </c>
       <c r="G961" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H961" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="962" spans="1:8" x14ac:dyDescent="0.15">
@@ -48880,13 +48880,13 @@
         <v>304</v>
       </c>
       <c r="F1285" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1285" s="1">
         <v>0</v>
       </c>
       <c r="H1285" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1286" spans="1:8" x14ac:dyDescent="0.15">
@@ -51093,10 +51093,10 @@
         <v>3</v>
       </c>
       <c r="G1370" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1370" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1371" spans="1:8" x14ac:dyDescent="0.15">
@@ -65523,10 +65523,10 @@
         <v>1</v>
       </c>
       <c r="G1925" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1925" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1926" spans="1:8" x14ac:dyDescent="0.15">
@@ -68123,10 +68123,10 @@
         <v>1</v>
       </c>
       <c r="G2025" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2025" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2026" spans="1:8" x14ac:dyDescent="0.15">
@@ -75634,13 +75634,13 @@
         <v>4020</v>
       </c>
       <c r="F2314" s="1">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="G2314" s="1">
         <v>0</v>
       </c>
       <c r="H2314" s="1">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2315" spans="1:8" x14ac:dyDescent="0.15">
@@ -85226,13 +85226,13 @@
         <v>242</v>
       </c>
       <c r="F2683" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2683" s="1">
         <v>0</v>
       </c>
       <c r="H2683" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2684" spans="1:8" x14ac:dyDescent="0.15">
@@ -86916,13 +86916,13 @@
         <v>242</v>
       </c>
       <c r="F2748" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2748" s="1">
         <v>0</v>
       </c>
       <c r="H2748" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2749" spans="1:8" x14ac:dyDescent="0.15">
@@ -89025,10 +89025,10 @@
         <v>23</v>
       </c>
       <c r="G2829" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2829" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2830" spans="1:8" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F6B68F-3CD2-407B-971C-71C4BB5D2447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4C2E6F-613F-4F90-984F-D4DF2011A02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16966,13 +16966,13 @@
         <v>65</v>
       </c>
       <c r="F57" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
       </c>
       <c r="H57" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.15">
@@ -17489,10 +17489,10 @@
         <v>49</v>
       </c>
       <c r="G77" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.15">
@@ -17515,10 +17515,10 @@
         <v>27</v>
       </c>
       <c r="G78" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H78" s="1">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.15">
@@ -17668,13 +17668,13 @@
         <v>139</v>
       </c>
       <c r="F84" s="1">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="G84" s="1">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H84" s="1">
-        <v>295</v>
+        <v>270</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.15">
@@ -17980,13 +17980,13 @@
         <v>98</v>
       </c>
       <c r="F96" s="1">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G96" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H96" s="1">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.15">
@@ -18006,13 +18006,13 @@
         <v>139</v>
       </c>
       <c r="F97" s="1">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="G97" s="1">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="H97" s="1">
-        <v>330</v>
+        <v>304</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.15">
@@ -18058,10 +18058,10 @@
         <v>39</v>
       </c>
       <c r="F99" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G99" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" s="1">
         <v>19</v>
@@ -18087,10 +18087,10 @@
         <v>164</v>
       </c>
       <c r="G100" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H100" s="1">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.15">
@@ -18292,10 +18292,10 @@
         <v>139</v>
       </c>
       <c r="F108" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G108" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H108" s="1">
         <v>34</v>
@@ -28660,13 +28660,13 @@
         <v>127</v>
       </c>
       <c r="F507" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G507" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H507" s="1">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.15">
@@ -29388,10 +29388,10 @@
         <v>524</v>
       </c>
       <c r="F535" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G535" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H535" s="1">
         <v>19</v>
@@ -32351,10 +32351,10 @@
         <v>37</v>
       </c>
       <c r="G649" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H649" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.15">
@@ -34818,13 +34818,13 @@
         <v>409</v>
       </c>
       <c r="F744" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G744" s="1">
         <v>1</v>
       </c>
       <c r="H744" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.15">
@@ -39654,13 +39654,13 @@
         <v>1536</v>
       </c>
       <c r="F930" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G930" s="1">
         <v>2</v>
       </c>
       <c r="H930" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="931" spans="1:8" x14ac:dyDescent="0.15">
@@ -44673,10 +44673,10 @@
         <v>47</v>
       </c>
       <c r="G1123" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1123" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1124" spans="1:8" x14ac:dyDescent="0.15">
@@ -51090,10 +51090,10 @@
         <v>2226</v>
       </c>
       <c r="F1370" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1370" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1370" s="1">
         <v>2</v>
@@ -75634,13 +75634,13 @@
         <v>4020</v>
       </c>
       <c r="F2314" s="1">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G2314" s="1">
         <v>0</v>
       </c>
       <c r="H2314" s="1">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2315" spans="1:8" x14ac:dyDescent="0.15">
@@ -85775,10 +85775,10 @@
         <v>42</v>
       </c>
       <c r="G2704" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2704" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2705" spans="1:8" x14ac:dyDescent="0.15">
@@ -89022,10 +89022,10 @@
         <v>65</v>
       </c>
       <c r="F2829" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2829" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2829" s="1">
         <v>22</v>

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4C2E6F-613F-4F90-984F-D4DF2011A02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A129CA-839F-48EA-B4E5-14B3F797F7AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16420,13 +16420,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.15">
@@ -16732,13 +16732,13 @@
         <v>65</v>
       </c>
       <c r="F48" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G48" s="1">
         <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.15">
@@ -16966,13 +16966,13 @@
         <v>65</v>
       </c>
       <c r="F57" s="1">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G57" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.15">
@@ -17486,13 +17486,13 @@
         <v>139</v>
       </c>
       <c r="F77" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G77" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H77" s="1">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.15">
@@ -17512,13 +17512,13 @@
         <v>139</v>
       </c>
       <c r="F78" s="1">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G78" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.15">
@@ -17668,13 +17668,13 @@
         <v>139</v>
       </c>
       <c r="F84" s="1">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="G84" s="1">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H84" s="1">
-        <v>270</v>
+        <v>260</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.15">
@@ -17980,13 +17980,13 @@
         <v>98</v>
       </c>
       <c r="F96" s="1">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G96" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H96" s="1">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.15">
@@ -18006,13 +18006,13 @@
         <v>139</v>
       </c>
       <c r="F97" s="1">
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="G97" s="1">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H97" s="1">
-        <v>304</v>
+        <v>281</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.15">
@@ -18058,13 +18058,13 @@
         <v>39</v>
       </c>
       <c r="F99" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G99" s="1">
         <v>0</v>
       </c>
       <c r="H99" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.15">
@@ -18084,13 +18084,13 @@
         <v>39</v>
       </c>
       <c r="F100" s="1">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G100" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H100" s="1">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.15">
@@ -20602,13 +20602,13 @@
         <v>17</v>
       </c>
       <c r="F197" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G197" s="1">
         <v>0</v>
       </c>
       <c r="H197" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.15">
@@ -27911,10 +27911,10 @@
         <v>7</v>
       </c>
       <c r="G478" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H478" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.15">
@@ -28660,13 +28660,13 @@
         <v>127</v>
       </c>
       <c r="F507" s="1">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G507" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H507" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.15">
@@ -32348,13 +32348,13 @@
         <v>836</v>
       </c>
       <c r="F649" s="1">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G649" s="1">
         <v>1</v>
       </c>
       <c r="H649" s="1">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.15">
@@ -34818,13 +34818,13 @@
         <v>409</v>
       </c>
       <c r="F744" s="1">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G744" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H744" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.15">
@@ -39056,13 +39056,13 @@
         <v>766</v>
       </c>
       <c r="F907" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G907" s="1">
         <v>0</v>
       </c>
       <c r="H907" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="908" spans="1:8" x14ac:dyDescent="0.15">
@@ -39628,13 +39628,13 @@
         <v>1536</v>
       </c>
       <c r="F929" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G929" s="1">
         <v>0</v>
       </c>
       <c r="H929" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="930" spans="1:8" x14ac:dyDescent="0.15">
@@ -39654,13 +39654,13 @@
         <v>1536</v>
       </c>
       <c r="F930" s="1">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G930" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H930" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="931" spans="1:8" x14ac:dyDescent="0.15">
@@ -44670,10 +44670,10 @@
         <v>1826</v>
       </c>
       <c r="F1123" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G1123" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1123" s="1">
         <v>46</v>
@@ -75634,13 +75634,13 @@
         <v>4020</v>
       </c>
       <c r="F2314" s="1">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G2314" s="1">
         <v>0</v>
       </c>
       <c r="H2314" s="1">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2315" spans="1:8" x14ac:dyDescent="0.15">
@@ -85772,13 +85772,13 @@
         <v>619</v>
       </c>
       <c r="F2704" s="1">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G2704" s="1">
         <v>1</v>
       </c>
       <c r="H2704" s="1">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2705" spans="1:8" x14ac:dyDescent="0.15">
@@ -89022,13 +89022,13 @@
         <v>65</v>
       </c>
       <c r="F2829" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G2829" s="1">
         <v>0</v>
       </c>
       <c r="H2829" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2830" spans="1:8" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3F2125-BD38-4529-BBA1-328ACD9202D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DAE0E8-31FC-4C88-B4B4-0B69B12D67D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16750,10 +16750,10 @@
         <v>65</v>
       </c>
       <c r="F48" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="1">
         <v>17</v>
@@ -17400,13 +17400,13 @@
         <v>42</v>
       </c>
       <c r="F73" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G73" s="1">
         <v>0</v>
       </c>
       <c r="H73" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.15">
@@ -17559,10 +17559,10 @@
         <v>21</v>
       </c>
       <c r="G79" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.15">
@@ -17712,13 +17712,13 @@
         <v>139</v>
       </c>
       <c r="F85" s="1">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G85" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H85" s="1">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.15">
@@ -18024,13 +18024,13 @@
         <v>98</v>
       </c>
       <c r="F97" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G97" s="1">
         <v>4</v>
       </c>
       <c r="H97" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.15">
@@ -18050,13 +18050,13 @@
         <v>139</v>
       </c>
       <c r="F98" s="1">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="G98" s="1">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H98" s="1">
-        <v>213</v>
+        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.15">
@@ -18102,13 +18102,13 @@
         <v>39</v>
       </c>
       <c r="F100" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G100" s="1">
         <v>1</v>
       </c>
       <c r="H100" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.15">
@@ -18128,13 +18128,13 @@
         <v>39</v>
       </c>
       <c r="F101" s="1">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G101" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H101" s="1">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.15">
@@ -18336,13 +18336,13 @@
         <v>139</v>
       </c>
       <c r="F109" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G109" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H109" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.15">
@@ -18852,13 +18852,13 @@
         <v>242</v>
       </c>
       <c r="F129" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G129" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H129" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.15">
@@ -27955,10 +27955,10 @@
         <v>6</v>
       </c>
       <c r="G479" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H479" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.15">
@@ -29432,10 +29432,10 @@
         <v>524</v>
       </c>
       <c r="F536" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G536" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H536" s="1">
         <v>17</v>
@@ -29461,10 +29461,10 @@
         <v>24</v>
       </c>
       <c r="G537" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H537" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.15">
@@ -33172,10 +33172,10 @@
         <v>836</v>
       </c>
       <c r="F680" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G680" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H680" s="1">
         <v>3</v>
@@ -33198,10 +33198,10 @@
         <v>44</v>
       </c>
       <c r="F681" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G681" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H681" s="1">
         <v>8</v>
@@ -35018,10 +35018,10 @@
         <v>409</v>
       </c>
       <c r="F751" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G751" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H751" s="1">
         <v>20</v>
@@ -38086,10 +38086,10 @@
         <v>111</v>
       </c>
       <c r="F869" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G869" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H869" s="1">
         <v>43</v>
@@ -39282,13 +39282,13 @@
         <v>1516</v>
       </c>
       <c r="F915" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G915" s="1">
         <v>1</v>
       </c>
       <c r="H915" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="916" spans="1:8" x14ac:dyDescent="0.15">
@@ -39724,13 +39724,13 @@
         <v>1536</v>
       </c>
       <c r="F932" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G932" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H932" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="933" spans="1:8" x14ac:dyDescent="0.15">
@@ -51160,10 +51160,10 @@
         <v>2226</v>
       </c>
       <c r="F1372" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G1372" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1372" s="1">
         <v>14</v>
@@ -63276,13 +63276,13 @@
         <v>3124</v>
       </c>
       <c r="F1838" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1838" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1838" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1839" spans="1:8" x14ac:dyDescent="0.15">
@@ -75730,13 +75730,13 @@
         <v>4020</v>
       </c>
       <c r="F2317" s="1">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G2317" s="1">
         <v>1</v>
       </c>
       <c r="H2317" s="1">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2318" spans="1:8" x14ac:dyDescent="0.15">
@@ -87012,10 +87012,10 @@
         <v>242</v>
       </c>
       <c r="F2751" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G2751" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2751" s="1">
         <v>16</v>
@@ -89118,10 +89118,10 @@
         <v>65</v>
       </c>
       <c r="F2832" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2832" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2832" s="1">
         <v>14</v>

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DAE0E8-31FC-4C88-B4B4-0B69B12D67D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE37B3B-0B82-4F28-AB16-9C1C347F6D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17400,13 +17400,13 @@
         <v>42</v>
       </c>
       <c r="F73" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G73" s="1">
         <v>0</v>
       </c>
       <c r="H73" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.15">
@@ -17530,13 +17530,13 @@
         <v>139</v>
       </c>
       <c r="F78" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G78" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="1">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.15">
@@ -17556,10 +17556,10 @@
         <v>139</v>
       </c>
       <c r="F79" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G79" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" s="1">
         <v>20</v>
@@ -17712,13 +17712,13 @@
         <v>139</v>
       </c>
       <c r="F85" s="1">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="G85" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H85" s="1">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.15">
@@ -18024,13 +18024,13 @@
         <v>98</v>
       </c>
       <c r="F97" s="1">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G97" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H97" s="1">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.15">
@@ -18050,13 +18050,13 @@
         <v>139</v>
       </c>
       <c r="F98" s="1">
-        <v>213</v>
+        <v>183</v>
       </c>
       <c r="G98" s="1">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="H98" s="1">
-        <v>192</v>
+        <v>171</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.15">
@@ -18102,10 +18102,10 @@
         <v>39</v>
       </c>
       <c r="F100" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G100" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100" s="1">
         <v>25</v>
@@ -18128,13 +18128,13 @@
         <v>39</v>
       </c>
       <c r="F101" s="1">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="G101" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H101" s="1">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.15">
@@ -18336,10 +18336,10 @@
         <v>139</v>
       </c>
       <c r="F109" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G109" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H109" s="1">
         <v>28</v>
@@ -18852,13 +18852,13 @@
         <v>242</v>
       </c>
       <c r="F129" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G129" s="1">
         <v>1</v>
       </c>
       <c r="H129" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.15">
@@ -27952,13 +27952,13 @@
         <v>810</v>
       </c>
       <c r="F479" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G479" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H479" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.15">
@@ -29458,10 +29458,10 @@
         <v>42</v>
       </c>
       <c r="F537" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G537" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H537" s="1">
         <v>23</v>
@@ -34891,10 +34891,10 @@
         <v>44</v>
       </c>
       <c r="G746" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H746" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="747" spans="1:8" x14ac:dyDescent="0.15">
@@ -35200,13 +35200,13 @@
         <v>409</v>
       </c>
       <c r="F758" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G758" s="1">
         <v>0</v>
       </c>
       <c r="H758" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="759" spans="1:8" x14ac:dyDescent="0.15">
@@ -39282,10 +39282,10 @@
         <v>1516</v>
       </c>
       <c r="F915" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G915" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H915" s="1">
         <v>3</v>
@@ -39724,13 +39724,13 @@
         <v>1536</v>
       </c>
       <c r="F932" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G932" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H932" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="933" spans="1:8" x14ac:dyDescent="0.15">
@@ -44740,13 +44740,13 @@
         <v>1826</v>
       </c>
       <c r="F1125" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G1125" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1125" s="1">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1126" spans="1:8" x14ac:dyDescent="0.15">
@@ -63276,13 +63276,13 @@
         <v>3124</v>
       </c>
       <c r="F1838" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1838" s="1">
         <v>1</v>
       </c>
       <c r="H1838" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1839" spans="1:8" x14ac:dyDescent="0.15">
@@ -75730,13 +75730,13 @@
         <v>4020</v>
       </c>
       <c r="F2317" s="1">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G2317" s="1">
         <v>1</v>
       </c>
       <c r="H2317" s="1">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2318" spans="1:8" x14ac:dyDescent="0.15">
@@ -85868,13 +85868,13 @@
         <v>619</v>
       </c>
       <c r="F2707" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G2707" s="1">
         <v>0</v>
       </c>
       <c r="H2707" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2708" spans="1:8" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE37B3B-0B82-4F28-AB16-9C1C347F6D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D9AB5D-DE9E-4E02-BBAB-2A8DF672A3B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16984,13 +16984,13 @@
         <v>65</v>
       </c>
       <c r="F57" s="1">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G57" s="1">
         <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.15">
@@ -17114,13 +17114,13 @@
         <v>107</v>
       </c>
       <c r="F62" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G62" s="1">
         <v>0</v>
       </c>
       <c r="H62" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.15">
@@ -17400,13 +17400,13 @@
         <v>42</v>
       </c>
       <c r="F73" s="1">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G73" s="1">
         <v>0</v>
       </c>
       <c r="H73" s="1">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.15">
@@ -17530,13 +17530,13 @@
         <v>139</v>
       </c>
       <c r="F78" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G78" s="1">
         <v>1</v>
       </c>
       <c r="H78" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.15">
@@ -17712,13 +17712,13 @@
         <v>139</v>
       </c>
       <c r="F85" s="1">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="G85" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85" s="1">
-        <v>213</v>
+        <v>192</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.15">
@@ -18050,13 +18050,13 @@
         <v>139</v>
       </c>
       <c r="F98" s="1">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="G98" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H98" s="1">
-        <v>171</v>
+        <v>161</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.15">
@@ -18128,13 +18128,13 @@
         <v>39</v>
       </c>
       <c r="F101" s="1">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G101" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H101" s="1">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.15">
@@ -32421,10 +32421,10 @@
         <v>33</v>
       </c>
       <c r="G651" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H651" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="652" spans="1:8" x14ac:dyDescent="0.15">
@@ -34394,13 +34394,13 @@
         <v>42</v>
       </c>
       <c r="F727" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G727" s="1">
         <v>0</v>
       </c>
       <c r="H727" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="728" spans="1:8" x14ac:dyDescent="0.15">
@@ -34888,13 +34888,13 @@
         <v>409</v>
       </c>
       <c r="F746" s="1">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G746" s="1">
         <v>1</v>
       </c>
       <c r="H746" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="747" spans="1:8" x14ac:dyDescent="0.15">
@@ -34992,13 +34992,13 @@
         <v>409</v>
       </c>
       <c r="F750" s="1">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G750" s="1">
         <v>0</v>
       </c>
       <c r="H750" s="1">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="751" spans="1:8" x14ac:dyDescent="0.15">
@@ -38086,13 +38086,13 @@
         <v>111</v>
       </c>
       <c r="F869" s="1">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G869" s="1">
         <v>0</v>
       </c>
       <c r="H869" s="1">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="870" spans="1:8" x14ac:dyDescent="0.15">
@@ -39724,13 +39724,13 @@
         <v>1536</v>
       </c>
       <c r="F932" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G932" s="1">
         <v>0</v>
       </c>
       <c r="H932" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="933" spans="1:8" x14ac:dyDescent="0.15">
@@ -44740,10 +44740,10 @@
         <v>1826</v>
       </c>
       <c r="F1125" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G1125" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1125" s="1">
         <v>42</v>
@@ -51160,13 +51160,13 @@
         <v>2226</v>
       </c>
       <c r="F1372" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G1372" s="1">
         <v>0</v>
       </c>
       <c r="H1372" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1373" spans="1:8" x14ac:dyDescent="0.15">
@@ -75730,13 +75730,13 @@
         <v>4020</v>
       </c>
       <c r="F2317" s="1">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="G2317" s="1">
         <v>1</v>
       </c>
       <c r="H2317" s="1">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2318" spans="1:8" x14ac:dyDescent="0.15">
@@ -89118,13 +89118,13 @@
         <v>65</v>
       </c>
       <c r="F2832" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G2832" s="1">
         <v>0</v>
       </c>
       <c r="H2832" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2833" spans="1:8" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D9AB5D-DE9E-4E02-BBAB-2A8DF672A3B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D13C63CB-E0E9-40AF-B86C-E6EC17A39AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16984,13 +16984,13 @@
         <v>65</v>
       </c>
       <c r="F57" s="1">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G57" s="1">
         <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.15">
@@ -17400,13 +17400,13 @@
         <v>42</v>
       </c>
       <c r="F73" s="1">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G73" s="1">
         <v>0</v>
       </c>
       <c r="H73" s="1">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.15">
@@ -17530,13 +17530,13 @@
         <v>139</v>
       </c>
       <c r="F78" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G78" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.15">
@@ -17556,13 +17556,13 @@
         <v>139</v>
       </c>
       <c r="F79" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G79" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" s="1">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.15">
@@ -17712,13 +17712,13 @@
         <v>139</v>
       </c>
       <c r="F85" s="1">
-        <v>192</v>
+        <v>695</v>
       </c>
       <c r="G85" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H85" s="1">
-        <v>192</v>
+        <v>692</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.15">
@@ -18024,13 +18024,13 @@
         <v>98</v>
       </c>
       <c r="F97" s="1">
-        <v>36</v>
+        <v>234</v>
       </c>
       <c r="G97" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H97" s="1">
-        <v>34</v>
+        <v>230</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.15">
@@ -18050,13 +18050,13 @@
         <v>139</v>
       </c>
       <c r="F98" s="1">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="G98" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H98" s="1">
-        <v>161</v>
+        <v>147</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.15">
@@ -18128,13 +18128,13 @@
         <v>39</v>
       </c>
       <c r="F101" s="1">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="G101" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H101" s="1">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.15">
@@ -18852,13 +18852,13 @@
         <v>242</v>
       </c>
       <c r="F129" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G129" s="1">
         <v>1</v>
       </c>
       <c r="H129" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.15">
@@ -18904,13 +18904,13 @@
         <v>247</v>
       </c>
       <c r="F131" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G131" s="1">
         <v>0</v>
       </c>
       <c r="H131" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.15">
@@ -26343,10 +26343,10 @@
         <v>2</v>
       </c>
       <c r="G417" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H417" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.15">
@@ -29435,10 +29435,10 @@
         <v>17</v>
       </c>
       <c r="G536" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H536" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="537" spans="1:8" x14ac:dyDescent="0.15">
@@ -32418,10 +32418,10 @@
         <v>836</v>
       </c>
       <c r="F651" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G651" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H651" s="1">
         <v>32</v>
@@ -32655,10 +32655,10 @@
         <v>13</v>
       </c>
       <c r="G660" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H660" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.15">
@@ -32889,10 +32889,10 @@
         <v>3</v>
       </c>
       <c r="G669" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H669" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="670" spans="1:8" x14ac:dyDescent="0.15">
@@ -33146,13 +33146,13 @@
         <v>836</v>
       </c>
       <c r="F679" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G679" s="1">
         <v>0</v>
       </c>
       <c r="H679" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="680" spans="1:8" x14ac:dyDescent="0.15">
@@ -33302,13 +33302,13 @@
         <v>836</v>
       </c>
       <c r="F685" s="1">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G685" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H685" s="1">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="686" spans="1:8" x14ac:dyDescent="0.15">
@@ -34888,13 +34888,13 @@
         <v>409</v>
       </c>
       <c r="F746" s="1">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G746" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H746" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="747" spans="1:8" x14ac:dyDescent="0.15">
@@ -34992,13 +34992,13 @@
         <v>409</v>
       </c>
       <c r="F750" s="1">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G750" s="1">
         <v>0</v>
       </c>
       <c r="H750" s="1">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="751" spans="1:8" x14ac:dyDescent="0.15">
@@ -35018,10 +35018,10 @@
         <v>409</v>
       </c>
       <c r="F751" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G751" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H751" s="1">
         <v>20</v>
@@ -35203,10 +35203,10 @@
         <v>38</v>
       </c>
       <c r="G758" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H758" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="759" spans="1:8" x14ac:dyDescent="0.15">
@@ -38086,13 +38086,13 @@
         <v>111</v>
       </c>
       <c r="F869" s="1">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G869" s="1">
         <v>0</v>
       </c>
       <c r="H869" s="1">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="870" spans="1:8" x14ac:dyDescent="0.15">
@@ -39126,13 +39126,13 @@
         <v>766</v>
       </c>
       <c r="F909" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G909" s="1">
         <v>0</v>
       </c>
       <c r="H909" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="910" spans="1:8" x14ac:dyDescent="0.15">
@@ -39282,13 +39282,13 @@
         <v>1516</v>
       </c>
       <c r="F915" s="1">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G915" s="1">
         <v>0</v>
       </c>
       <c r="H915" s="1">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="916" spans="1:8" x14ac:dyDescent="0.15">
@@ -39724,13 +39724,13 @@
         <v>1536</v>
       </c>
       <c r="F932" s="1">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="G932" s="1">
         <v>0</v>
       </c>
       <c r="H932" s="1">
-        <v>0</v>
+        <v>142</v>
       </c>
     </row>
     <row r="933" spans="1:8" x14ac:dyDescent="0.15">
@@ -45804,13 +45804,13 @@
         <v>1869</v>
       </c>
       <c r="F1166" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G1166" s="1">
         <v>0</v>
       </c>
       <c r="H1166" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1167" spans="1:8" x14ac:dyDescent="0.15">
@@ -63276,13 +63276,13 @@
         <v>3124</v>
       </c>
       <c r="F1838" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1838" s="1">
         <v>1</v>
       </c>
       <c r="H1838" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1839" spans="1:8" x14ac:dyDescent="0.15">
@@ -63354,13 +63354,13 @@
         <v>42</v>
       </c>
       <c r="F1841" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1841" s="1">
         <v>0</v>
       </c>
       <c r="H1841" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1842" spans="1:8" x14ac:dyDescent="0.15">
@@ -67852,13 +67852,13 @@
         <v>2372</v>
       </c>
       <c r="F2014" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2014" s="1">
         <v>0</v>
       </c>
       <c r="H2014" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2015" spans="1:8" x14ac:dyDescent="0.15">
@@ -75730,13 +75730,13 @@
         <v>4020</v>
       </c>
       <c r="F2317" s="1">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="G2317" s="1">
         <v>1</v>
       </c>
       <c r="H2317" s="1">
-        <v>104</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2318" spans="1:8" x14ac:dyDescent="0.15">
@@ -85322,13 +85322,13 @@
         <v>242</v>
       </c>
       <c r="F2686" s="1">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G2686" s="1">
         <v>0</v>
       </c>
       <c r="H2686" s="1">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2687" spans="1:8" x14ac:dyDescent="0.15">
@@ -85790,13 +85790,13 @@
         <v>65</v>
       </c>
       <c r="F2704" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G2704" s="1">
         <v>0</v>
       </c>
       <c r="H2704" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2705" spans="1:8" x14ac:dyDescent="0.15">
@@ -87012,13 +87012,13 @@
         <v>242</v>
       </c>
       <c r="F2751" s="1">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="G2751" s="1">
         <v>0</v>
       </c>
       <c r="H2751" s="1">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2752" spans="1:8" x14ac:dyDescent="0.15">
@@ -88442,13 +88442,13 @@
         <v>42</v>
       </c>
       <c r="F2806" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2806" s="1">
         <v>0</v>
       </c>
       <c r="H2806" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2807" spans="1:8" x14ac:dyDescent="0.15">
@@ -88780,13 +88780,13 @@
         <v>127</v>
       </c>
       <c r="F2819" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G2819" s="1">
         <v>0</v>
       </c>
       <c r="H2819" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2820" spans="1:8" x14ac:dyDescent="0.15">
@@ -89196,13 +89196,13 @@
         <v>65</v>
       </c>
       <c r="F2835" s="1">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G2835" s="1">
         <v>0</v>
       </c>
       <c r="H2835" s="1">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2836" spans="1:8" x14ac:dyDescent="0.15">
@@ -89560,13 +89560,13 @@
         <v>42</v>
       </c>
       <c r="F2849" s="1">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G2849" s="1">
         <v>0</v>
       </c>
       <c r="H2849" s="1">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D13C63CB-E0E9-40AF-B86C-E6EC17A39AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D49765-2AB1-4055-BCFC-D9C9334C072E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16750,13 +16750,13 @@
         <v>65</v>
       </c>
       <c r="F48" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G48" s="1">
         <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.15">
@@ -16984,13 +16984,13 @@
         <v>65</v>
       </c>
       <c r="F57" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G57" s="1">
         <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.15">
@@ -17400,13 +17400,13 @@
         <v>42</v>
       </c>
       <c r="F73" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G73" s="1">
         <v>0</v>
       </c>
       <c r="H73" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.15">
@@ -17556,10 +17556,10 @@
         <v>139</v>
       </c>
       <c r="F79" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G79" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" s="1">
         <v>17</v>
@@ -17712,13 +17712,13 @@
         <v>139</v>
       </c>
       <c r="F85" s="1">
-        <v>695</v>
+        <v>666</v>
       </c>
       <c r="G85" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H85" s="1">
-        <v>692</v>
+        <v>662</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.15">
@@ -18024,13 +18024,13 @@
         <v>98</v>
       </c>
       <c r="F97" s="1">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="G97" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H97" s="1">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.15">
@@ -18050,13 +18050,13 @@
         <v>139</v>
       </c>
       <c r="F98" s="1">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="G98" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H98" s="1">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.15">
@@ -18128,13 +18128,13 @@
         <v>39</v>
       </c>
       <c r="F101" s="1">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G101" s="1">
         <v>5</v>
       </c>
       <c r="H101" s="1">
-        <v>127</v>
+        <v>113</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.15">
@@ -18336,13 +18336,13 @@
         <v>139</v>
       </c>
       <c r="F109" s="1">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G109" s="1">
         <v>1</v>
       </c>
       <c r="H109" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.15">
@@ -18852,13 +18852,13 @@
         <v>242</v>
       </c>
       <c r="F129" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G129" s="1">
         <v>1</v>
       </c>
       <c r="H129" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.15">
@@ -18904,13 +18904,13 @@
         <v>247</v>
       </c>
       <c r="F131" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G131" s="1">
         <v>0</v>
       </c>
       <c r="H131" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.15">
@@ -26340,10 +26340,10 @@
         <v>344</v>
       </c>
       <c r="F417" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G417" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H417" s="1">
         <v>1</v>
@@ -29432,10 +29432,10 @@
         <v>524</v>
       </c>
       <c r="F536" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G536" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H536" s="1">
         <v>16</v>
@@ -32264,10 +32264,10 @@
         <v>42</v>
       </c>
       <c r="F645" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G645" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H645" s="1">
         <v>0</v>
@@ -32418,13 +32418,13 @@
         <v>836</v>
       </c>
       <c r="F651" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G651" s="1">
         <v>0</v>
       </c>
       <c r="H651" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="652" spans="1:8" x14ac:dyDescent="0.15">
@@ -32652,10 +32652,10 @@
         <v>836</v>
       </c>
       <c r="F660" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G660" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H660" s="1">
         <v>12</v>
@@ -32886,10 +32886,10 @@
         <v>836</v>
       </c>
       <c r="F669" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G669" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H669" s="1">
         <v>2</v>
@@ -33146,13 +33146,13 @@
         <v>836</v>
       </c>
       <c r="F679" s="1">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G679" s="1">
         <v>0</v>
       </c>
       <c r="H679" s="1">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="680" spans="1:8" x14ac:dyDescent="0.15">
@@ -33302,10 +33302,10 @@
         <v>836</v>
       </c>
       <c r="F685" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G685" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H685" s="1">
         <v>18</v>
@@ -34888,13 +34888,13 @@
         <v>409</v>
       </c>
       <c r="F746" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G746" s="1">
         <v>0</v>
       </c>
       <c r="H746" s="1">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="747" spans="1:8" x14ac:dyDescent="0.15">
@@ -34992,13 +34992,13 @@
         <v>409</v>
       </c>
       <c r="F750" s="1">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G750" s="1">
         <v>0</v>
       </c>
       <c r="H750" s="1">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="751" spans="1:8" x14ac:dyDescent="0.15">
@@ -35018,10 +35018,10 @@
         <v>409</v>
       </c>
       <c r="F751" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G751" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H751" s="1">
         <v>20</v>
@@ -35200,10 +35200,10 @@
         <v>409</v>
       </c>
       <c r="F758" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G758" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H758" s="1">
         <v>37</v>
@@ -38086,13 +38086,13 @@
         <v>111</v>
       </c>
       <c r="F869" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G869" s="1">
         <v>0</v>
       </c>
       <c r="H869" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="870" spans="1:8" x14ac:dyDescent="0.15">
@@ -39126,13 +39126,13 @@
         <v>766</v>
       </c>
       <c r="F909" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G909" s="1">
         <v>0</v>
       </c>
       <c r="H909" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="910" spans="1:8" x14ac:dyDescent="0.15">
@@ -39282,13 +39282,13 @@
         <v>1516</v>
       </c>
       <c r="F915" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G915" s="1">
         <v>0</v>
       </c>
       <c r="H915" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="916" spans="1:8" x14ac:dyDescent="0.15">
@@ -39724,13 +39724,13 @@
         <v>1536</v>
       </c>
       <c r="F932" s="1">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="G932" s="1">
         <v>0</v>
       </c>
       <c r="H932" s="1">
-        <v>142</v>
+        <v>133</v>
       </c>
     </row>
     <row r="933" spans="1:8" x14ac:dyDescent="0.15">
@@ -45674,13 +45674,13 @@
         <v>295</v>
       </c>
       <c r="F1161" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1161" s="1">
         <v>0</v>
       </c>
       <c r="H1161" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1162" spans="1:8" x14ac:dyDescent="0.15">
@@ -48950,13 +48950,13 @@
         <v>304</v>
       </c>
       <c r="F1287" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1287" s="1">
         <v>0</v>
       </c>
       <c r="H1287" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1288" spans="1:8" x14ac:dyDescent="0.15">
@@ -50068,13 +50068,13 @@
         <v>304</v>
       </c>
       <c r="F1330" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1330" s="1">
         <v>0</v>
       </c>
       <c r="H1330" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1331" spans="1:8" x14ac:dyDescent="0.15">
@@ -51160,13 +51160,13 @@
         <v>2226</v>
       </c>
       <c r="F1372" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G1372" s="1">
         <v>0</v>
       </c>
       <c r="H1372" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1373" spans="1:8" x14ac:dyDescent="0.15">
@@ -63276,13 +63276,13 @@
         <v>3124</v>
       </c>
       <c r="F1838" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1838" s="1">
         <v>1</v>
       </c>
       <c r="H1838" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1839" spans="1:8" x14ac:dyDescent="0.15">
@@ -75730,13 +75730,13 @@
         <v>4020</v>
       </c>
       <c r="F2317" s="1">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G2317" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2317" s="1">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2318" spans="1:8" x14ac:dyDescent="0.15">
@@ -85322,13 +85322,13 @@
         <v>242</v>
       </c>
       <c r="F2686" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G2686" s="1">
         <v>0</v>
       </c>
       <c r="H2686" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2687" spans="1:8" x14ac:dyDescent="0.15">
@@ -85790,13 +85790,13 @@
         <v>65</v>
       </c>
       <c r="F2704" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G2704" s="1">
         <v>0</v>
       </c>
       <c r="H2704" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2705" spans="1:8" x14ac:dyDescent="0.15">
@@ -87012,13 +87012,13 @@
         <v>242</v>
       </c>
       <c r="F2751" s="1">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G2751" s="1">
         <v>0</v>
       </c>
       <c r="H2751" s="1">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2752" spans="1:8" x14ac:dyDescent="0.15">
@@ -89118,13 +89118,13 @@
         <v>65</v>
       </c>
       <c r="F2832" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2832" s="1">
         <v>0</v>
       </c>
       <c r="H2832" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2833" spans="1:8" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D49765-2AB1-4055-BCFC-D9C9334C072E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E948854B-0329-42EF-848B-27744A2CB8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16545,10 +16545,10 @@
         <v>12</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.15">
@@ -17088,13 +17088,13 @@
         <v>65</v>
       </c>
       <c r="F61" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G61" s="1">
         <v>0</v>
       </c>
       <c r="H61" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.15">
@@ -17533,10 +17533,10 @@
         <v>41</v>
       </c>
       <c r="G78" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.15">
@@ -17559,10 +17559,10 @@
         <v>17</v>
       </c>
       <c r="G79" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.15">
@@ -17712,13 +17712,13 @@
         <v>139</v>
       </c>
       <c r="F85" s="1">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="G85" s="1">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="H85" s="1">
-        <v>662</v>
+        <v>636</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.15">
@@ -18027,10 +18027,10 @@
         <v>228</v>
       </c>
       <c r="G97" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H97" s="1">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.15">
@@ -18050,13 +18050,13 @@
         <v>139</v>
       </c>
       <c r="F98" s="1">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G98" s="1">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="H98" s="1">
-        <v>136</v>
+        <v>104</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.15">
@@ -18105,10 +18105,10 @@
         <v>25</v>
       </c>
       <c r="G100" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.15">
@@ -18128,13 +18128,13 @@
         <v>39</v>
       </c>
       <c r="F101" s="1">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G101" s="1">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H101" s="1">
-        <v>113</v>
+        <v>97</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.15">
@@ -18336,13 +18336,13 @@
         <v>139</v>
       </c>
       <c r="F109" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G109" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H109" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.15">
@@ -32421,10 +32421,10 @@
         <v>31</v>
       </c>
       <c r="G651" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H651" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="652" spans="1:8" x14ac:dyDescent="0.15">
@@ -33149,10 +33149,10 @@
         <v>16</v>
       </c>
       <c r="G679" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H679" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="680" spans="1:8" x14ac:dyDescent="0.15">
@@ -34891,10 +34891,10 @@
         <v>34</v>
       </c>
       <c r="G746" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H746" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="747" spans="1:8" x14ac:dyDescent="0.15">
@@ -35021,10 +35021,10 @@
         <v>20</v>
       </c>
       <c r="G751" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H751" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="752" spans="1:8" x14ac:dyDescent="0.15">
@@ -39285,10 +39285,10 @@
         <v>8</v>
       </c>
       <c r="G915" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H915" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="916" spans="1:8" x14ac:dyDescent="0.15">
@@ -45804,13 +45804,13 @@
         <v>1869</v>
       </c>
       <c r="F1166" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G1166" s="1">
         <v>0</v>
       </c>
       <c r="H1166" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1167" spans="1:8" x14ac:dyDescent="0.15">
@@ -48950,13 +48950,13 @@
         <v>304</v>
       </c>
       <c r="F1287" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1287" s="1">
         <v>0</v>
       </c>
       <c r="H1287" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1288" spans="1:8" x14ac:dyDescent="0.15">
@@ -51163,10 +51163,10 @@
         <v>9</v>
       </c>
       <c r="G1372" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1372" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1373" spans="1:8" x14ac:dyDescent="0.15">
@@ -75730,13 +75730,13 @@
         <v>4020</v>
       </c>
       <c r="F2317" s="1">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G2317" s="1">
         <v>2</v>
       </c>
       <c r="H2317" s="1">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2318" spans="1:8" x14ac:dyDescent="0.15">
@@ -85793,10 +85793,10 @@
         <v>14</v>
       </c>
       <c r="G2704" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2704" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2705" spans="1:8" x14ac:dyDescent="0.15">
@@ -89121,10 +89121,10 @@
         <v>10</v>
       </c>
       <c r="G2832" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2832" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2833" spans="1:8" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65A16BC-C951-4AF4-B301-03060170F22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C5E12E7-AA1E-4441-AAAF-4C03F62C1F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -17479,13 +17479,13 @@
         <v>2106</v>
       </c>
       <c r="F73" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -17687,13 +17687,13 @@
         <v>2142</v>
       </c>
       <c r="F81" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G81" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -17713,10 +17713,10 @@
         <v>2142</v>
       </c>
       <c r="F82" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G82" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H82" s="2">
         <v>13</v>
@@ -17739,13 +17739,13 @@
         <v>2142</v>
       </c>
       <c r="F83" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -17869,13 +17869,13 @@
         <v>2142</v>
       </c>
       <c r="F88" s="2">
-        <v>254</v>
+        <v>218</v>
       </c>
       <c r="G88" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H88" s="2">
-        <v>248</v>
+        <v>216</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -18181,13 +18181,13 @@
         <v>2116</v>
       </c>
       <c r="F100" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G100" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H100" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -18207,13 +18207,13 @@
         <v>2142</v>
       </c>
       <c r="F101" s="2">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="G101" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H101" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -22366,10 +22366,10 @@
         <v>4</v>
       </c>
       <c r="G261" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H261" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
@@ -24937,13 +24937,13 @@
         <v>2090</v>
       </c>
       <c r="F360" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G360" s="2">
         <v>0</v>
       </c>
       <c r="H360" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.25">
@@ -28161,13 +28161,13 @@
         <v>2604</v>
       </c>
       <c r="F484" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G484" s="2">
         <v>0</v>
       </c>
       <c r="H484" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.25">
@@ -28913,13 +28913,13 @@
         <v>2136</v>
       </c>
       <c r="F513" s="2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G513" s="2">
         <v>1</v>
       </c>
       <c r="H513" s="2">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.25">
@@ -29667,13 +29667,13 @@
         <v>2106</v>
       </c>
       <c r="F542" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G542" s="2">
         <v>0</v>
       </c>
       <c r="H542" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="543" spans="1:8" x14ac:dyDescent="0.25">
@@ -32473,13 +32473,13 @@
         <v>2106</v>
       </c>
       <c r="F650" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G650" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H650" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="651" spans="1:8" x14ac:dyDescent="0.25">
@@ -32627,13 +32627,13 @@
         <v>2617</v>
       </c>
       <c r="F656" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G656" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H656" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="657" spans="1:8" x14ac:dyDescent="0.25">
@@ -33017,13 +33017,13 @@
         <v>2617</v>
       </c>
       <c r="F671" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G671" s="2">
         <v>0</v>
       </c>
       <c r="H671" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="672" spans="1:8" x14ac:dyDescent="0.25">
@@ -33199,13 +33199,13 @@
         <v>2617</v>
       </c>
       <c r="F678" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G678" s="2">
         <v>0</v>
       </c>
       <c r="H678" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="679" spans="1:8" x14ac:dyDescent="0.25">
@@ -35305,13 +35305,13 @@
         <v>2282</v>
       </c>
       <c r="F759" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G759" s="2">
         <v>0</v>
       </c>
       <c r="H759" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="760" spans="1:8" x14ac:dyDescent="0.25">
@@ -39491,10 +39491,10 @@
         <v>2955</v>
       </c>
       <c r="F920" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G920" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H920" s="2">
         <v>7</v>
@@ -39936,10 +39936,10 @@
         <v>93</v>
       </c>
       <c r="G937" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H937" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="938" spans="1:8" x14ac:dyDescent="0.25">
@@ -49266,10 +49266,10 @@
         <v>2</v>
       </c>
       <c r="G1296" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1296" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1297" spans="1:8" x14ac:dyDescent="0.25">
@@ -75965,13 +75965,13 @@
         <v>4408</v>
       </c>
       <c r="F2323" s="2">
-        <v>3</v>
+        <v>113</v>
       </c>
       <c r="G2323" s="2">
         <v>2</v>
       </c>
       <c r="H2323" s="2">
-        <v>1</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2324" spans="1:8" x14ac:dyDescent="0.25">
@@ -87195,10 +87195,10 @@
         <v>4937</v>
       </c>
       <c r="F2755" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2755" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2755" s="2">
         <v>13</v>
@@ -87247,13 +87247,13 @@
         <v>2172</v>
       </c>
       <c r="F2757" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2757" s="2">
         <v>0</v>
       </c>
       <c r="H2757" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2758" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C5E12E7-AA1E-4441-AAAF-4C03F62C1F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDD214B-C80D-4D13-B8A8-233655CAAFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69DFFCF3-4EBB-4C5E-9380-5C22F317BD78}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11373" uniqueCount="5047">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11373" uniqueCount="5046">
   <si>
     <t>No</t>
   </si>
@@ -15081,9 +15081,6 @@
   </si>
   <si>
     <t>CENTER PAD ADV160</t>
-  </si>
-  <si>
-    <t>12100K2PM00</t>
   </si>
   <si>
     <t>64300K0WW00</t>
@@ -17063,13 +17060,13 @@
         <v>2113</v>
       </c>
       <c r="F57" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17467,10 +17464,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
+        <v>5028</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>5029</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>5030</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>2081</v>
@@ -17493,10 +17490,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
+        <v>5034</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>5035</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>5036</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>2081</v>
@@ -17519,10 +17516,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
+        <v>5036</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>5037</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>5038</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>2081</v>
@@ -17545,10 +17542,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
+        <v>5038</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>5039</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>5040</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>2081</v>
@@ -17687,13 +17684,13 @@
         <v>2142</v>
       </c>
       <c r="F81" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G81" s="2">
         <v>0</v>
       </c>
       <c r="H81" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -17869,13 +17866,13 @@
         <v>2142</v>
       </c>
       <c r="F88" s="2">
-        <v>218</v>
+        <v>174</v>
       </c>
       <c r="G88" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H88" s="2">
-        <v>216</v>
+        <v>174</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -18181,13 +18178,13 @@
         <v>2116</v>
       </c>
       <c r="F100" s="2">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G100" s="2">
         <v>2</v>
       </c>
       <c r="H100" s="2">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -18207,13 +18204,13 @@
         <v>2142</v>
       </c>
       <c r="F101" s="2">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="G101" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H101" s="2">
-        <v>324</v>
+        <v>309</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -19049,10 +19046,10 @@
         <v>133</v>
       </c>
       <c r="B134" s="2" t="s">
+        <v>5040</v>
+      </c>
+      <c r="C134" s="2" t="s">
         <v>5041</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>5042</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>2081</v>
@@ -19087,13 +19084,13 @@
         <v>2173</v>
       </c>
       <c r="F135" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G135" s="2">
         <v>0</v>
       </c>
       <c r="H135" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -19335,10 +19332,10 @@
         <v>144</v>
       </c>
       <c r="B145" s="2" t="s">
+        <v>5042</v>
+      </c>
+      <c r="C145" s="2" t="s">
         <v>5043</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>5044</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>2081</v>
@@ -19347,13 +19344,13 @@
         <v>2136</v>
       </c>
       <c r="F145" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G145" s="2">
         <v>0</v>
       </c>
       <c r="H145" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -20872,7 +20869,7 @@
         <v>194</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>5015</v>
+        <v>195</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>2081</v>
@@ -22363,10 +22360,10 @@
         <v>2103</v>
       </c>
       <c r="F261" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G261" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H261" s="2">
         <v>3</v>
@@ -28913,13 +28910,13 @@
         <v>2136</v>
       </c>
       <c r="F513" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G513" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H513" s="2">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.25">
@@ -28939,13 +28936,13 @@
         <v>2625</v>
       </c>
       <c r="F514" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G514" s="2">
         <v>0</v>
       </c>
       <c r="H514" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.25">
@@ -29667,13 +29664,13 @@
         <v>2106</v>
       </c>
       <c r="F542" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G542" s="2">
         <v>0</v>
       </c>
       <c r="H542" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="543" spans="1:8" x14ac:dyDescent="0.25">
@@ -32461,10 +32458,10 @@
         <v>649</v>
       </c>
       <c r="B650" s="2" t="s">
+        <v>5030</v>
+      </c>
+      <c r="C650" s="2" t="s">
         <v>5031</v>
-      </c>
-      <c r="C650" s="2" t="s">
-        <v>5032</v>
       </c>
       <c r="D650" s="2" t="s">
         <v>2081</v>
@@ -32627,13 +32624,13 @@
         <v>2617</v>
       </c>
       <c r="F656" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G656" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H656" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="657" spans="1:8" x14ac:dyDescent="0.25">
@@ -33017,13 +33014,13 @@
         <v>2617</v>
       </c>
       <c r="F671" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G671" s="2">
         <v>0</v>
       </c>
       <c r="H671" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="672" spans="1:8" x14ac:dyDescent="0.25">
@@ -33199,13 +33196,13 @@
         <v>2617</v>
       </c>
       <c r="F678" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G678" s="2">
         <v>0</v>
       </c>
       <c r="H678" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="679" spans="1:8" x14ac:dyDescent="0.25">
@@ -33511,13 +33508,13 @@
         <v>2617</v>
       </c>
       <c r="F690" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G690" s="2">
         <v>0</v>
       </c>
       <c r="H690" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="691" spans="1:8" x14ac:dyDescent="0.25">
@@ -33537,13 +33534,13 @@
         <v>2617</v>
       </c>
       <c r="F691" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G691" s="2">
         <v>0</v>
       </c>
       <c r="H691" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="692" spans="1:8" x14ac:dyDescent="0.25">
@@ -35227,13 +35224,13 @@
         <v>2282</v>
       </c>
       <c r="F756" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G756" s="2">
         <v>0</v>
       </c>
       <c r="H756" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="757" spans="1:8" x14ac:dyDescent="0.25">
@@ -35305,13 +35302,13 @@
         <v>2282</v>
       </c>
       <c r="F759" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G759" s="2">
         <v>0</v>
       </c>
       <c r="H759" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="760" spans="1:8" x14ac:dyDescent="0.25">
@@ -35409,13 +35406,13 @@
         <v>2282</v>
       </c>
       <c r="F763" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G763" s="2">
         <v>0</v>
       </c>
       <c r="H763" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="764" spans="1:8" x14ac:dyDescent="0.25">
@@ -38295,13 +38292,13 @@
         <v>2122</v>
       </c>
       <c r="F874" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G874" s="2">
         <v>0</v>
       </c>
       <c r="H874" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="875" spans="1:8" x14ac:dyDescent="0.25">
@@ -39335,13 +39332,13 @@
         <v>2564</v>
       </c>
       <c r="F914" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G914" s="2">
         <v>0</v>
       </c>
       <c r="H914" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="915" spans="1:8" x14ac:dyDescent="0.25">
@@ -39491,13 +39488,13 @@
         <v>2955</v>
       </c>
       <c r="F920" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G920" s="2">
         <v>0</v>
       </c>
       <c r="H920" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="921" spans="1:8" x14ac:dyDescent="0.25">
@@ -39933,13 +39930,13 @@
         <v>2966</v>
       </c>
       <c r="F937" s="2">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G937" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H937" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="938" spans="1:8" x14ac:dyDescent="0.25">
@@ -44949,13 +44946,13 @@
         <v>3110</v>
       </c>
       <c r="F1130" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G1130" s="2">
         <v>0</v>
       </c>
       <c r="H1130" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1131" spans="1:8" x14ac:dyDescent="0.25">
@@ -49081,13 +49078,13 @@
         <v>2634</v>
       </c>
       <c r="F1289" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1289" s="2">
         <v>0</v>
       </c>
       <c r="H1289" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1290" spans="1:8" x14ac:dyDescent="0.25">
@@ -49263,10 +49260,10 @@
         <v>2203</v>
       </c>
       <c r="F1296" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1296" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1296" s="2">
         <v>1</v>
@@ -50277,13 +50274,13 @@
         <v>2203</v>
       </c>
       <c r="F1335" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1335" s="2">
         <v>0</v>
       </c>
       <c r="H1335" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1336" spans="1:8" x14ac:dyDescent="0.25">
@@ -63343,7 +63340,7 @@
         <v>1837</v>
       </c>
       <c r="B1838" s="2" t="s">
-        <v>5016</v>
+        <v>5015</v>
       </c>
       <c r="C1838" s="2" t="s">
         <v>3844</v>
@@ -63551,10 +63548,10 @@
         <v>1845</v>
       </c>
       <c r="B1846" s="2" t="s">
+        <v>5032</v>
+      </c>
+      <c r="C1846" s="2" t="s">
         <v>5033</v>
-      </c>
-      <c r="C1846" s="2" t="s">
-        <v>5034</v>
       </c>
       <c r="D1846" s="2" t="s">
         <v>2081</v>
@@ -63785,10 +63782,10 @@
         <v>1854</v>
       </c>
       <c r="B1855" s="2" t="s">
+        <v>5016</v>
+      </c>
+      <c r="C1855" s="2" t="s">
         <v>5017</v>
-      </c>
-      <c r="C1855" s="2" t="s">
-        <v>5018</v>
       </c>
       <c r="D1855" s="2" t="s">
         <v>2081</v>
@@ -73041,10 +73038,10 @@
         <v>2210</v>
       </c>
       <c r="B2211" s="2" t="s">
+        <v>5044</v>
+      </c>
+      <c r="C2211" s="2" t="s">
         <v>5045</v>
-      </c>
-      <c r="C2211" s="2" t="s">
-        <v>5046</v>
       </c>
       <c r="D2211" s="2" t="s">
         <v>2081</v>
@@ -75965,13 +75962,13 @@
         <v>4408</v>
       </c>
       <c r="F2323" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G2323" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2323" s="2">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2324" spans="1:8" x14ac:dyDescent="0.25">
@@ -79957,10 +79954,10 @@
         <v>2476</v>
       </c>
       <c r="B2477" s="2" t="s">
+        <v>5018</v>
+      </c>
+      <c r="C2477" s="2" t="s">
         <v>5019</v>
-      </c>
-      <c r="C2477" s="2" t="s">
-        <v>5020</v>
       </c>
       <c r="D2477" s="2" t="s">
         <v>2081</v>
@@ -86025,13 +86022,13 @@
         <v>2113</v>
       </c>
       <c r="F2710" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2710" s="2">
         <v>0</v>
       </c>
       <c r="H2710" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2711" spans="1:8" x14ac:dyDescent="0.25">
@@ -86103,13 +86100,13 @@
         <v>2446</v>
       </c>
       <c r="F2713" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G2713" s="2">
         <v>0</v>
       </c>
       <c r="H2713" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2714" spans="1:8" x14ac:dyDescent="0.25">
@@ -87247,13 +87244,13 @@
         <v>2172</v>
       </c>
       <c r="F2757" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G2757" s="2">
         <v>0</v>
       </c>
       <c r="H2757" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2758" spans="1:8" x14ac:dyDescent="0.25">
@@ -87547,10 +87544,10 @@
         <v>2768</v>
       </c>
       <c r="B2769" s="2" t="s">
+        <v>5020</v>
+      </c>
+      <c r="C2769" s="2" t="s">
         <v>5021</v>
-      </c>
-      <c r="C2769" s="2" t="s">
-        <v>5022</v>
       </c>
       <c r="D2769" s="2" t="s">
         <v>2081</v>
@@ -87573,10 +87570,10 @@
         <v>2769</v>
       </c>
       <c r="B2770" s="2" t="s">
+        <v>5022</v>
+      </c>
+      <c r="C2770" s="2" t="s">
         <v>5023</v>
-      </c>
-      <c r="C2770" s="2" t="s">
-        <v>5024</v>
       </c>
       <c r="D2770" s="2" t="s">
         <v>2081</v>
@@ -87963,10 +87960,10 @@
         <v>2784</v>
       </c>
       <c r="B2785" s="2" t="s">
+        <v>5024</v>
+      </c>
+      <c r="C2785" s="2" t="s">
         <v>5025</v>
-      </c>
-      <c r="C2785" s="2" t="s">
-        <v>5026</v>
       </c>
       <c r="D2785" s="2" t="s">
         <v>2081</v>
@@ -87989,10 +87986,10 @@
         <v>2785</v>
       </c>
       <c r="B2786" s="2" t="s">
+        <v>5026</v>
+      </c>
+      <c r="C2786" s="2" t="s">
         <v>5027</v>
-      </c>
-      <c r="C2786" s="2" t="s">
-        <v>5028</v>
       </c>
       <c r="D2786" s="2" t="s">
         <v>2081</v>

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{361869EA-DC7E-4272-B9ED-DA390AF32F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7E266A-CD41-4840-B25E-A9327FCD61BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{552CD280-2CBB-478B-8720-DE884677C382}"/>
   </bookViews>
@@ -16512,13 +16512,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="2">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G36" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16824,13 +16824,13 @@
         <v>65</v>
       </c>
       <c r="F48" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -17058,13 +17058,13 @@
         <v>65</v>
       </c>
       <c r="F57" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17188,13 +17188,13 @@
         <v>107</v>
       </c>
       <c r="F62" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -17526,13 +17526,13 @@
         <v>132</v>
       </c>
       <c r="F75" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
       </c>
       <c r="H75" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -17682,13 +17682,13 @@
         <v>148</v>
       </c>
       <c r="F81" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G81" s="2">
         <v>0</v>
       </c>
       <c r="H81" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -17708,13 +17708,13 @@
         <v>148</v>
       </c>
       <c r="F82" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G82" s="2">
         <v>0</v>
       </c>
       <c r="H82" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -17734,13 +17734,13 @@
         <v>148</v>
       </c>
       <c r="F83" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G83" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" s="2">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -17864,13 +17864,13 @@
         <v>148</v>
       </c>
       <c r="F88" s="2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G88" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H88" s="2">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -18176,13 +18176,13 @@
         <v>98</v>
       </c>
       <c r="F100" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G100" s="2">
         <v>2</v>
       </c>
       <c r="H100" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -18202,13 +18202,13 @@
         <v>148</v>
       </c>
       <c r="F101" s="2">
-        <v>646</v>
+        <v>604</v>
       </c>
       <c r="G101" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H101" s="2">
-        <v>644</v>
+        <v>601</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -18384,13 +18384,13 @@
         <v>148</v>
       </c>
       <c r="F108" s="2">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="G108" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H108" s="2">
-        <v>207</v>
+        <v>195</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -19082,13 +19082,13 @@
         <v>261</v>
       </c>
       <c r="F135" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G135" s="2">
         <v>0</v>
       </c>
       <c r="H135" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -28908,13 +28908,13 @@
         <v>127</v>
       </c>
       <c r="F513" s="2">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G513" s="2">
         <v>0</v>
       </c>
       <c r="H513" s="2">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.25">
@@ -33012,13 +33012,13 @@
         <v>854</v>
       </c>
       <c r="F671" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G671" s="2">
         <v>0</v>
       </c>
       <c r="H671" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="672" spans="1:8" x14ac:dyDescent="0.25">
@@ -34572,13 +34572,13 @@
         <v>42</v>
       </c>
       <c r="F731" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G731" s="2">
         <v>0</v>
       </c>
       <c r="H731" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="732" spans="1:8" x14ac:dyDescent="0.25">
@@ -35092,13 +35092,13 @@
         <v>428</v>
       </c>
       <c r="F751" s="2">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G751" s="2">
         <v>0</v>
       </c>
       <c r="H751" s="2">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="752" spans="1:8" x14ac:dyDescent="0.25">
@@ -35196,13 +35196,13 @@
         <v>428</v>
       </c>
       <c r="F755" s="2">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G755" s="2">
         <v>0</v>
       </c>
       <c r="H755" s="2">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="756" spans="1:8" x14ac:dyDescent="0.25">
@@ -38290,13 +38290,13 @@
         <v>111</v>
       </c>
       <c r="F874" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G874" s="2">
         <v>0</v>
       </c>
       <c r="H874" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="875" spans="1:8" x14ac:dyDescent="0.25">
@@ -39330,13 +39330,13 @@
         <v>784</v>
       </c>
       <c r="F914" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G914" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H914" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="915" spans="1:8" x14ac:dyDescent="0.25">
@@ -39486,13 +39486,13 @@
         <v>1536</v>
       </c>
       <c r="F920" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G920" s="2">
         <v>0</v>
       </c>
       <c r="H920" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="921" spans="1:8" x14ac:dyDescent="0.25">
@@ -39928,13 +39928,13 @@
         <v>1556</v>
       </c>
       <c r="F937" s="2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G937" s="2">
         <v>0</v>
       </c>
       <c r="H937" s="2">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="938" spans="1:8" x14ac:dyDescent="0.25">
@@ -49154,13 +49154,13 @@
         <v>323</v>
       </c>
       <c r="F1292" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1292" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1292" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1293" spans="1:8" x14ac:dyDescent="0.25">
@@ -50350,13 +50350,13 @@
         <v>323</v>
       </c>
       <c r="F1338" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1338" s="2">
         <v>0</v>
       </c>
       <c r="H1338" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1339" spans="1:8" x14ac:dyDescent="0.25">
@@ -55891,10 +55891,10 @@
         <v>15</v>
       </c>
       <c r="G1551" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1551" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1552" spans="1:8" x14ac:dyDescent="0.25">
@@ -63558,13 +63558,13 @@
         <v>42</v>
       </c>
       <c r="F1846" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1846" s="2">
         <v>0</v>
       </c>
       <c r="H1846" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1847" spans="1:8" x14ac:dyDescent="0.25">
@@ -68082,13 +68082,13 @@
         <v>65</v>
       </c>
       <c r="F2020" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2020" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2020" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2021" spans="1:8" x14ac:dyDescent="0.25">
@@ -69746,13 +69746,13 @@
         <v>562</v>
       </c>
       <c r="F2084" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2084" s="2">
         <v>0</v>
       </c>
       <c r="H2084" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2085" spans="1:8" x14ac:dyDescent="0.25">
@@ -75960,13 +75960,13 @@
         <v>4047</v>
       </c>
       <c r="F2323" s="2">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="G2323" s="2">
         <v>1</v>
       </c>
       <c r="H2323" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2324" spans="1:8" x14ac:dyDescent="0.25">
@@ -85266,10 +85266,10 @@
         <v>254</v>
       </c>
       <c r="F2681" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2681" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2681" s="2">
         <v>12</v>
@@ -86020,13 +86020,13 @@
         <v>65</v>
       </c>
       <c r="F2710" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G2710" s="2">
         <v>0</v>
       </c>
       <c r="H2710" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2711" spans="1:8" x14ac:dyDescent="0.25">
@@ -87242,13 +87242,13 @@
         <v>254</v>
       </c>
       <c r="F2757" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G2757" s="2">
         <v>0</v>
       </c>
       <c r="H2757" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2758" spans="1:8" x14ac:dyDescent="0.25">
@@ -89348,10 +89348,10 @@
         <v>65</v>
       </c>
       <c r="F2838" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2838" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2838" s="2">
         <v>10</v>

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B193224-4A0E-4ECA-889F-3BE7A1A52971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF99993-BEBB-48D0-8BFA-250D895B1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{552CD280-2CBB-478B-8720-DE884677C382}"/>
   </bookViews>
@@ -15252,7 +15252,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -16527,13 +16527,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -17073,13 +17073,13 @@
         <v>65</v>
       </c>
       <c r="F57" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17749,13 +17749,13 @@
         <v>148</v>
       </c>
       <c r="F83" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -17775,13 +17775,13 @@
         <v>148</v>
       </c>
       <c r="F84" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17931,13 +17931,13 @@
         <v>148</v>
       </c>
       <c r="F90" s="2">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G90" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" s="2">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -18243,13 +18243,13 @@
         <v>98</v>
       </c>
       <c r="F102" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G102" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H102" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -18269,13 +18269,13 @@
         <v>148</v>
       </c>
       <c r="F103" s="2">
-        <v>682</v>
+        <v>639</v>
       </c>
       <c r="G103" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H103" s="2">
-        <v>682</v>
+        <v>635</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -18451,13 +18451,13 @@
         <v>148</v>
       </c>
       <c r="F110" s="2">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G110" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H110" s="2">
-        <v>127</v>
+        <v>115</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -28975,13 +28975,13 @@
         <v>127</v>
       </c>
       <c r="F515" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G515" s="2">
         <v>0</v>
       </c>
       <c r="H515" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.25">
@@ -40021,13 +40021,13 @@
         <v>1556</v>
       </c>
       <c r="F940" s="2">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G940" s="2">
         <v>0</v>
       </c>
       <c r="H940" s="2">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="941" spans="1:8" x14ac:dyDescent="0.25">
@@ -45037,13 +45037,13 @@
         <v>1846</v>
       </c>
       <c r="F1133" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G1133" s="2">
         <v>0</v>
       </c>
       <c r="H1133" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1134" spans="1:8" x14ac:dyDescent="0.25">
@@ -54317,13 +54317,13 @@
         <v>2478</v>
       </c>
       <c r="F1490" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1490" s="2">
         <v>0</v>
       </c>
       <c r="H1490" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1491" spans="1:8" x14ac:dyDescent="0.25">
@@ -76053,13 +76053,13 @@
         <v>4047</v>
       </c>
       <c r="F2326" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G2326" s="2">
         <v>1</v>
       </c>
       <c r="H2326" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2327" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF99993-BEBB-48D0-8BFA-250D895B1543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0165E1-DFB5-4BF0-8189-F8D0EE84442E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{552CD280-2CBB-478B-8720-DE884677C382}"/>
   </bookViews>
@@ -16839,13 +16839,13 @@
         <v>65</v>
       </c>
       <c r="F48" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -17489,13 +17489,13 @@
         <v>42</v>
       </c>
       <c r="F73" s="2">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <v>25</v>
+        <v>59</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -17515,13 +17515,13 @@
         <v>132</v>
       </c>
       <c r="F74" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G74" s="2">
         <v>0</v>
       </c>
       <c r="H74" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -17541,13 +17541,13 @@
         <v>132</v>
       </c>
       <c r="F75" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
       </c>
       <c r="H75" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -17749,13 +17749,13 @@
         <v>148</v>
       </c>
       <c r="F83" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -17775,13 +17775,13 @@
         <v>148</v>
       </c>
       <c r="F84" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G84" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17931,13 +17931,13 @@
         <v>148</v>
       </c>
       <c r="F90" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G90" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H90" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -18243,13 +18243,13 @@
         <v>98</v>
       </c>
       <c r="F102" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G102" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H102" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -18269,13 +18269,13 @@
         <v>148</v>
       </c>
       <c r="F103" s="2">
-        <v>639</v>
+        <v>622</v>
       </c>
       <c r="G103" s="2">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H103" s="2">
-        <v>635</v>
+        <v>602</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -18451,13 +18451,13 @@
         <v>148</v>
       </c>
       <c r="F110" s="2">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G110" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H110" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -19409,13 +19409,13 @@
         <v>127</v>
       </c>
       <c r="F147" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G147" s="2">
         <v>0</v>
       </c>
       <c r="H147" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -29105,13 +29105,13 @@
         <v>874</v>
       </c>
       <c r="F520" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G520" s="2">
         <v>0</v>
       </c>
       <c r="H520" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.25">
@@ -33082,10 +33082,10 @@
         <v>15</v>
       </c>
       <c r="G673" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H673" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
@@ -33261,13 +33261,13 @@
         <v>854</v>
       </c>
       <c r="F680" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G680" s="2">
         <v>0</v>
       </c>
       <c r="H680" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="681" spans="1:8" x14ac:dyDescent="0.25">
@@ -33420,10 +33420,10 @@
         <v>13</v>
       </c>
       <c r="G686" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H686" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="687" spans="1:8" x14ac:dyDescent="0.25">
@@ -35266,10 +35266,10 @@
         <v>33</v>
       </c>
       <c r="G757" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H757" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="758" spans="1:8" x14ac:dyDescent="0.25">
@@ -35367,13 +35367,13 @@
         <v>428</v>
       </c>
       <c r="F761" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G761" s="2">
         <v>0</v>
       </c>
       <c r="H761" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="762" spans="1:8" x14ac:dyDescent="0.25">
@@ -39579,13 +39579,13 @@
         <v>1536</v>
       </c>
       <c r="F923" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G923" s="2">
         <v>0</v>
       </c>
       <c r="H923" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="924" spans="1:8" x14ac:dyDescent="0.25">
@@ -40021,13 +40021,13 @@
         <v>1556</v>
       </c>
       <c r="F940" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G940" s="2">
         <v>0</v>
       </c>
       <c r="H940" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="941" spans="1:8" x14ac:dyDescent="0.25">
@@ -63573,13 +63573,13 @@
         <v>3145</v>
       </c>
       <c r="F1846" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1846" s="2">
         <v>0</v>
       </c>
       <c r="H1846" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1847" spans="1:8" x14ac:dyDescent="0.25">
@@ -76053,13 +76053,13 @@
         <v>4047</v>
       </c>
       <c r="F2326" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G2326" s="2">
         <v>1</v>
       </c>
       <c r="H2326" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2327" spans="1:8" x14ac:dyDescent="0.25">
@@ -86191,13 +86191,13 @@
         <v>637</v>
       </c>
       <c r="F2716" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G2716" s="2">
         <v>0</v>
       </c>
       <c r="H2716" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2717" spans="1:8" x14ac:dyDescent="0.25">
@@ -89441,13 +89441,13 @@
         <v>65</v>
       </c>
       <c r="F2841" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G2841" s="2">
         <v>0</v>
       </c>
       <c r="H2841" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2842" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0165E1-DFB5-4BF0-8189-F8D0EE84442E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E489D028-B71F-4827-8B5F-6676F5C40053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{552CD280-2CBB-478B-8720-DE884677C382}"/>
   </bookViews>
@@ -16527,13 +16527,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16579,13 +16579,13 @@
         <v>70</v>
       </c>
       <c r="F38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="2">
         <v>0</v>
       </c>
       <c r="H38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -17024,10 +17024,10 @@
         <v>12</v>
       </c>
       <c r="G55" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -17073,13 +17073,13 @@
         <v>65</v>
       </c>
       <c r="F57" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17489,13 +17489,13 @@
         <v>42</v>
       </c>
       <c r="F73" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -17541,13 +17541,13 @@
         <v>132</v>
       </c>
       <c r="F75" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
       </c>
       <c r="H75" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -17619,13 +17619,13 @@
         <v>127</v>
       </c>
       <c r="F78" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17749,13 +17749,13 @@
         <v>148</v>
       </c>
       <c r="F83" s="2">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="2">
-        <v>129</v>
+        <v>120</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -17775,13 +17775,13 @@
         <v>148</v>
       </c>
       <c r="F84" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="G84" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17801,13 +17801,13 @@
         <v>148</v>
       </c>
       <c r="F85" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G85" s="2">
         <v>0</v>
       </c>
       <c r="H85" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -17931,13 +17931,13 @@
         <v>148</v>
       </c>
       <c r="F90" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G90" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H90" s="2">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -18243,13 +18243,13 @@
         <v>98</v>
       </c>
       <c r="F102" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G102" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H102" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -18269,13 +18269,13 @@
         <v>148</v>
       </c>
       <c r="F103" s="2">
-        <v>622</v>
+        <v>459</v>
       </c>
       <c r="G103" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H103" s="2">
-        <v>602</v>
+        <v>459</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -18321,13 +18321,13 @@
         <v>39</v>
       </c>
       <c r="F105" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G105" s="2">
         <v>0</v>
       </c>
       <c r="H105" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -18451,13 +18451,13 @@
         <v>148</v>
       </c>
       <c r="F110" s="2">
-        <v>108</v>
+        <v>47</v>
       </c>
       <c r="G110" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H110" s="2">
-        <v>100</v>
+        <v>47</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -18555,13 +18555,13 @@
         <v>148</v>
       </c>
       <c r="F114" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G114" s="2">
         <v>1</v>
       </c>
       <c r="H114" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -19123,13 +19123,13 @@
         <v>127</v>
       </c>
       <c r="F136" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G136" s="2">
         <v>0</v>
       </c>
       <c r="H136" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -19149,13 +19149,13 @@
         <v>261</v>
       </c>
       <c r="F137" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G137" s="2">
         <v>0</v>
       </c>
       <c r="H137" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -21723,13 +21723,13 @@
         <v>127</v>
       </c>
       <c r="F236" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G236" s="2">
         <v>0</v>
       </c>
       <c r="H236" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
@@ -28975,13 +28975,13 @@
         <v>127</v>
       </c>
       <c r="F515" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G515" s="2">
         <v>0</v>
       </c>
       <c r="H515" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.25">
@@ -29105,13 +29105,13 @@
         <v>874</v>
       </c>
       <c r="F520" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G520" s="2">
         <v>0</v>
       </c>
       <c r="H520" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.25">
@@ -29703,13 +29703,13 @@
         <v>224</v>
       </c>
       <c r="F543" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G543" s="2">
         <v>0</v>
       </c>
       <c r="H543" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="544" spans="1:8" x14ac:dyDescent="0.25">
@@ -32689,13 +32689,13 @@
         <v>854</v>
       </c>
       <c r="F658" s="2">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G658" s="2">
         <v>0</v>
       </c>
       <c r="H658" s="2">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="659" spans="1:8" x14ac:dyDescent="0.25">
@@ -33079,13 +33079,13 @@
         <v>854</v>
       </c>
       <c r="F673" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G673" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H673" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
@@ -33261,13 +33261,13 @@
         <v>854</v>
       </c>
       <c r="F680" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G680" s="2">
         <v>0</v>
       </c>
       <c r="H680" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="681" spans="1:8" x14ac:dyDescent="0.25">
@@ -33417,13 +33417,13 @@
         <v>854</v>
       </c>
       <c r="F686" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G686" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H686" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="687" spans="1:8" x14ac:dyDescent="0.25">
@@ -33573,13 +33573,13 @@
         <v>854</v>
       </c>
       <c r="F692" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G692" s="2">
         <v>0</v>
       </c>
       <c r="H692" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="693" spans="1:8" x14ac:dyDescent="0.25">
@@ -34639,13 +34639,13 @@
         <v>42</v>
       </c>
       <c r="F733" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G733" s="2">
         <v>0</v>
       </c>
       <c r="H733" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="734" spans="1:8" x14ac:dyDescent="0.25">
@@ -35159,13 +35159,13 @@
         <v>428</v>
       </c>
       <c r="F753" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G753" s="2">
         <v>0</v>
       </c>
       <c r="H753" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="754" spans="1:8" x14ac:dyDescent="0.25">
@@ -35263,13 +35263,13 @@
         <v>428</v>
       </c>
       <c r="F757" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G757" s="2">
         <v>1</v>
       </c>
       <c r="H757" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="758" spans="1:8" x14ac:dyDescent="0.25">
@@ -35471,13 +35471,13 @@
         <v>428</v>
       </c>
       <c r="F765" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G765" s="2">
         <v>0</v>
       </c>
       <c r="H765" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="766" spans="1:8" x14ac:dyDescent="0.25">
@@ -39579,13 +39579,13 @@
         <v>1536</v>
       </c>
       <c r="F923" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G923" s="2">
         <v>0</v>
       </c>
       <c r="H923" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="924" spans="1:8" x14ac:dyDescent="0.25">
@@ -40021,13 +40021,13 @@
         <v>1556</v>
       </c>
       <c r="F940" s="2">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="G940" s="2">
         <v>0</v>
       </c>
       <c r="H940" s="2">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="941" spans="1:8" x14ac:dyDescent="0.25">
@@ -45037,13 +45037,13 @@
         <v>1846</v>
       </c>
       <c r="F1133" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G1133" s="2">
         <v>0</v>
       </c>
       <c r="H1133" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1134" spans="1:8" x14ac:dyDescent="0.25">
@@ -46101,13 +46101,13 @@
         <v>1889</v>
       </c>
       <c r="F1174" s="2">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G1174" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H1174" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1175" spans="1:8" x14ac:dyDescent="0.25">
@@ -51509,13 +51509,13 @@
         <v>2246</v>
       </c>
       <c r="F1382" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1382" s="2">
         <v>0</v>
       </c>
       <c r="H1382" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1383" spans="1:8" x14ac:dyDescent="0.25">
@@ -53797,13 +53797,13 @@
         <v>653</v>
       </c>
       <c r="F1470" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1470" s="2">
         <v>0</v>
       </c>
       <c r="H1470" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1471" spans="1:8" x14ac:dyDescent="0.25">
@@ -63677,13 +63677,13 @@
         <v>3154</v>
       </c>
       <c r="F1850" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1850" s="2">
         <v>0</v>
       </c>
       <c r="H1850" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1851" spans="1:8" x14ac:dyDescent="0.25">
@@ -76053,13 +76053,13 @@
         <v>4047</v>
       </c>
       <c r="F2326" s="2">
-        <v>169</v>
+        <v>130</v>
       </c>
       <c r="G2326" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H2326" s="2">
-        <v>168</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2327" spans="1:8" x14ac:dyDescent="0.25">
@@ -85359,13 +85359,13 @@
         <v>254</v>
       </c>
       <c r="F2684" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G2684" s="2">
         <v>0</v>
       </c>
       <c r="H2684" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2685" spans="1:8" x14ac:dyDescent="0.25">
@@ -86191,13 +86191,13 @@
         <v>637</v>
       </c>
       <c r="F2716" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2716" s="2">
         <v>0</v>
       </c>
       <c r="H2716" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2717" spans="1:8" x14ac:dyDescent="0.25">
@@ -87283,13 +87283,13 @@
         <v>4854</v>
       </c>
       <c r="F2758" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2758" s="2">
         <v>0</v>
       </c>
       <c r="H2758" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2759" spans="1:8" x14ac:dyDescent="0.25">
@@ -89441,13 +89441,13 @@
         <v>65</v>
       </c>
       <c r="F2841" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G2841" s="2">
         <v>0</v>
       </c>
       <c r="H2841" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2842" spans="1:8" x14ac:dyDescent="0.25">
@@ -89857,13 +89857,13 @@
         <v>65</v>
       </c>
       <c r="F2857" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2857" s="2">
         <v>0</v>
       </c>
       <c r="H2857" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2858" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E489D028-B71F-4827-8B5F-6676F5C40053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B2963A-3B00-4C87-AE99-E554B4EAF6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{552CD280-2CBB-478B-8720-DE884677C382}"/>
   </bookViews>
@@ -17489,13 +17489,13 @@
         <v>42</v>
       </c>
       <c r="F73" s="2">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -17749,13 +17749,13 @@
         <v>148</v>
       </c>
       <c r="F83" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -17931,13 +17931,13 @@
         <v>148</v>
       </c>
       <c r="F90" s="2">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G90" s="2">
         <v>0</v>
       </c>
       <c r="H90" s="2">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -18269,13 +18269,13 @@
         <v>148</v>
       </c>
       <c r="F103" s="2">
-        <v>459</v>
+        <v>421</v>
       </c>
       <c r="G103" s="2">
         <v>0</v>
       </c>
       <c r="H103" s="2">
-        <v>459</v>
+        <v>421</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -18321,13 +18321,13 @@
         <v>39</v>
       </c>
       <c r="F105" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G105" s="2">
         <v>0</v>
       </c>
       <c r="H105" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -18451,13 +18451,13 @@
         <v>148</v>
       </c>
       <c r="F110" s="2">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G110" s="2">
         <v>0</v>
       </c>
       <c r="H110" s="2">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -32689,13 +32689,13 @@
         <v>854</v>
       </c>
       <c r="F658" s="2">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G658" s="2">
         <v>0</v>
       </c>
       <c r="H658" s="2">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="659" spans="1:8" x14ac:dyDescent="0.25">
@@ -33079,13 +33079,13 @@
         <v>854</v>
       </c>
       <c r="F673" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G673" s="2">
         <v>0</v>
       </c>
       <c r="H673" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
@@ -33417,13 +33417,13 @@
         <v>854</v>
       </c>
       <c r="F686" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G686" s="2">
         <v>0</v>
       </c>
       <c r="H686" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="687" spans="1:8" x14ac:dyDescent="0.25">
@@ -34769,13 +34769,13 @@
         <v>854</v>
       </c>
       <c r="F738" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G738" s="2">
         <v>0</v>
       </c>
       <c r="H738" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="739" spans="1:8" x14ac:dyDescent="0.25">
@@ -35159,13 +35159,13 @@
         <v>428</v>
       </c>
       <c r="F753" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G753" s="2">
         <v>0</v>
       </c>
       <c r="H753" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="754" spans="1:8" x14ac:dyDescent="0.25">
@@ -35263,13 +35263,13 @@
         <v>428</v>
       </c>
       <c r="F757" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G757" s="2">
         <v>1</v>
       </c>
       <c r="H757" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="758" spans="1:8" x14ac:dyDescent="0.25">
@@ -39917,13 +39917,13 @@
         <v>1556</v>
       </c>
       <c r="F936" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G936" s="2">
         <v>0</v>
       </c>
       <c r="H936" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="937" spans="1:8" x14ac:dyDescent="0.25">
@@ -40021,13 +40021,13 @@
         <v>1556</v>
       </c>
       <c r="F940" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G940" s="2">
         <v>0</v>
       </c>
       <c r="H940" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="941" spans="1:8" x14ac:dyDescent="0.25">
@@ -45037,13 +45037,13 @@
         <v>1846</v>
       </c>
       <c r="F1133" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G1133" s="2">
         <v>0</v>
       </c>
       <c r="H1133" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1134" spans="1:8" x14ac:dyDescent="0.25">
@@ -76053,13 +76053,13 @@
         <v>4047</v>
       </c>
       <c r="F2326" s="2">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G2326" s="2">
         <v>5</v>
       </c>
       <c r="H2326" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2327" spans="1:8" x14ac:dyDescent="0.25">
@@ -85645,13 +85645,13 @@
         <v>254</v>
       </c>
       <c r="F2695" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2695" s="2">
         <v>0</v>
       </c>
       <c r="H2695" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2696" spans="1:8" x14ac:dyDescent="0.25">
@@ -86113,13 +86113,13 @@
         <v>65</v>
       </c>
       <c r="F2713" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2713" s="2">
         <v>0</v>
       </c>
       <c r="H2713" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2714" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C1539E-ADD1-4452-BC2E-6B85B1BAC0CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9737CCA-9892-4623-A262-FFFCCC321704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{552CD280-2CBB-478B-8720-DE884677C382}"/>
   </bookViews>
@@ -16623,13 +16623,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16935,13 +16935,13 @@
         <v>65</v>
       </c>
       <c r="F48" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -17117,10 +17117,10 @@
         <v>98</v>
       </c>
       <c r="F55" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G55" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" s="2">
         <v>11</v>
@@ -17299,13 +17299,13 @@
         <v>107</v>
       </c>
       <c r="F62" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -17585,13 +17585,13 @@
         <v>42</v>
       </c>
       <c r="F73" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -18027,13 +18027,13 @@
         <v>148</v>
       </c>
       <c r="F90" s="2">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G90" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H90" s="2">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -18365,13 +18365,13 @@
         <v>98</v>
       </c>
       <c r="F103" s="2">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G103" s="2">
         <v>2</v>
       </c>
       <c r="H103" s="2">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -18391,13 +18391,13 @@
         <v>148</v>
       </c>
       <c r="F104" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="G104" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H104" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -18677,13 +18677,13 @@
         <v>148</v>
       </c>
       <c r="F115" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G115" s="2">
         <v>1</v>
       </c>
       <c r="H115" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -29097,13 +29097,13 @@
         <v>127</v>
       </c>
       <c r="F516" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G516" s="2">
         <v>0</v>
       </c>
       <c r="H516" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.25">
@@ -32811,13 +32811,13 @@
         <v>854</v>
       </c>
       <c r="F659" s="2">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G659" s="2">
         <v>0</v>
       </c>
       <c r="H659" s="2">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="660" spans="1:8" x14ac:dyDescent="0.25">
@@ -33539,13 +33539,13 @@
         <v>854</v>
       </c>
       <c r="F687" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G687" s="2">
         <v>0</v>
       </c>
       <c r="H687" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="688" spans="1:8" x14ac:dyDescent="0.25">
@@ -33591,13 +33591,13 @@
         <v>44</v>
       </c>
       <c r="F689" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G689" s="2">
         <v>0</v>
       </c>
       <c r="H689" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="690" spans="1:8" x14ac:dyDescent="0.25">
@@ -33695,13 +33695,13 @@
         <v>854</v>
       </c>
       <c r="F693" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G693" s="2">
         <v>0</v>
       </c>
       <c r="H693" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="694" spans="1:8" x14ac:dyDescent="0.25">
@@ -34761,13 +34761,13 @@
         <v>42</v>
       </c>
       <c r="F734" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G734" s="2">
         <v>0</v>
       </c>
       <c r="H734" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="735" spans="1:8" x14ac:dyDescent="0.25">
@@ -34891,13 +34891,13 @@
         <v>854</v>
       </c>
       <c r="F739" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G739" s="2">
         <v>0</v>
       </c>
       <c r="H739" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="740" spans="1:8" x14ac:dyDescent="0.25">
@@ -35281,13 +35281,13 @@
         <v>428</v>
       </c>
       <c r="F754" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G754" s="2">
         <v>0</v>
       </c>
       <c r="H754" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="755" spans="1:8" x14ac:dyDescent="0.25">
@@ -35385,13 +35385,13 @@
         <v>428</v>
       </c>
       <c r="F758" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G758" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H758" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="759" spans="1:8" x14ac:dyDescent="0.25">
@@ -35593,13 +35593,13 @@
         <v>428</v>
       </c>
       <c r="F766" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G766" s="2">
         <v>0</v>
       </c>
       <c r="H766" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="767" spans="1:8" x14ac:dyDescent="0.25">
@@ -38505,13 +38505,13 @@
         <v>111</v>
       </c>
       <c r="F878" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G878" s="2">
         <v>0</v>
       </c>
       <c r="H878" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="879" spans="1:8" x14ac:dyDescent="0.25">
@@ -39701,13 +39701,13 @@
         <v>1536</v>
       </c>
       <c r="F924" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G924" s="2">
         <v>0</v>
       </c>
       <c r="H924" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="925" spans="1:8" x14ac:dyDescent="0.25">
@@ -40926,10 +40926,10 @@
         <v>1</v>
       </c>
       <c r="G971" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H971" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="972" spans="1:8" x14ac:dyDescent="0.25">
@@ -46275,10 +46275,10 @@
         <v>1889</v>
       </c>
       <c r="F1177" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G1177" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H1177" s="2">
         <v>15</v>
@@ -49525,13 +49525,13 @@
         <v>323</v>
       </c>
       <c r="F1302" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1302" s="2">
         <v>0</v>
       </c>
       <c r="H1302" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1303" spans="1:8" x14ac:dyDescent="0.25">
@@ -50539,13 +50539,13 @@
         <v>323</v>
       </c>
       <c r="F1341" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1341" s="2">
         <v>0</v>
       </c>
       <c r="H1341" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1342" spans="1:8" x14ac:dyDescent="0.25">
@@ -50617,13 +50617,13 @@
         <v>323</v>
       </c>
       <c r="F1344" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1344" s="2">
         <v>0</v>
       </c>
       <c r="H1344" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1345" spans="1:8" x14ac:dyDescent="0.25">
@@ -51709,13 +51709,13 @@
         <v>2246</v>
       </c>
       <c r="F1386" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1386" s="2">
         <v>0</v>
       </c>
       <c r="H1386" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1387" spans="1:8" x14ac:dyDescent="0.25">
@@ -76409,13 +76409,13 @@
         <v>4047</v>
       </c>
       <c r="F2336" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G2336" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2336" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2337" spans="1:8" x14ac:dyDescent="0.25">
@@ -85897,13 +85897,13 @@
         <v>254</v>
       </c>
       <c r="F2701" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G2701" s="2">
         <v>0</v>
       </c>
       <c r="H2701" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2702" spans="1:8" x14ac:dyDescent="0.25">
@@ -87847,13 +87847,13 @@
         <v>4854</v>
       </c>
       <c r="F2776" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2776" s="2">
         <v>0</v>
       </c>
       <c r="H2776" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2777" spans="1:8" x14ac:dyDescent="0.25">
@@ -90031,13 +90031,13 @@
         <v>65</v>
       </c>
       <c r="F2860" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G2860" s="2">
         <v>0</v>
       </c>
       <c r="H2860" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2861" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9737CCA-9892-4623-A262-FFFCCC321704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A80755-5533-4F17-A4F3-5940AEE5E192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{552CD280-2CBB-478B-8720-DE884677C382}"/>
   </bookViews>
@@ -16623,13 +16623,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16938,10 +16938,10 @@
         <v>6</v>
       </c>
       <c r="G48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -17585,13 +17585,13 @@
         <v>42</v>
       </c>
       <c r="F73" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -17611,13 +17611,13 @@
         <v>132</v>
       </c>
       <c r="F74" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G74" s="2">
         <v>0</v>
       </c>
       <c r="H74" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -17848,10 +17848,10 @@
         <v>118</v>
       </c>
       <c r="G83" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -17871,13 +17871,13 @@
         <v>148</v>
       </c>
       <c r="F84" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17900,10 +17900,10 @@
         <v>68</v>
       </c>
       <c r="G85" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -18027,13 +18027,13 @@
         <v>148</v>
       </c>
       <c r="F90" s="2">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G90" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H90" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -18365,13 +18365,13 @@
         <v>98</v>
       </c>
       <c r="F103" s="2">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G103" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H103" s="2">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -18391,13 +18391,13 @@
         <v>148</v>
       </c>
       <c r="F104" s="2">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="G104" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H104" s="2">
-        <v>351</v>
+        <v>330</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -18680,10 +18680,10 @@
         <v>8</v>
       </c>
       <c r="G115" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H115" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -29097,13 +29097,13 @@
         <v>127</v>
       </c>
       <c r="F516" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G516" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H516" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.25">
@@ -29126,10 +29126,10 @@
         <v>11</v>
       </c>
       <c r="G517" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H517" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.25">
@@ -32811,13 +32811,13 @@
         <v>854</v>
       </c>
       <c r="F659" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G659" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H659" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="660" spans="1:8" x14ac:dyDescent="0.25">
@@ -33201,13 +33201,13 @@
         <v>854</v>
       </c>
       <c r="F674" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G674" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H674" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="675" spans="1:8" x14ac:dyDescent="0.25">
@@ -33539,13 +33539,13 @@
         <v>854</v>
       </c>
       <c r="F687" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G687" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H687" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="688" spans="1:8" x14ac:dyDescent="0.25">
@@ -33698,10 +33698,10 @@
         <v>5</v>
       </c>
       <c r="G693" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H693" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="694" spans="1:8" x14ac:dyDescent="0.25">
@@ -35281,13 +35281,13 @@
         <v>428</v>
       </c>
       <c r="F754" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G754" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H754" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="755" spans="1:8" x14ac:dyDescent="0.25">
@@ -35596,10 +35596,10 @@
         <v>20</v>
       </c>
       <c r="G766" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H766" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="767" spans="1:8" x14ac:dyDescent="0.25">
@@ -38508,10 +38508,10 @@
         <v>14</v>
       </c>
       <c r="G878" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H878" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="879" spans="1:8" x14ac:dyDescent="0.25">
@@ -40143,13 +40143,13 @@
         <v>1556</v>
       </c>
       <c r="F941" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G941" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H941" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="942" spans="1:8" x14ac:dyDescent="0.25">
@@ -45211,13 +45211,13 @@
         <v>1846</v>
       </c>
       <c r="F1136" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G1136" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1136" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1137" spans="1:8" x14ac:dyDescent="0.25">
@@ -76409,13 +76409,13 @@
         <v>4047</v>
       </c>
       <c r="F2336" s="2">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G2336" s="2">
         <v>1</v>
       </c>
       <c r="H2336" s="2">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2337" spans="1:8" x14ac:dyDescent="0.25">
@@ -86732,10 +86732,10 @@
         <v>29</v>
       </c>
       <c r="G2733" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2733" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2734" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5FC6102-511B-4D87-9ACE-30A4D3B4AE1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B2F269-29A1-4986-8B2D-A9F95F32BE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{552CD280-2CBB-478B-8720-DE884677C382}"/>
   </bookViews>
@@ -16668,13 +16668,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -17630,13 +17630,13 @@
         <v>42</v>
       </c>
       <c r="F73" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -17682,13 +17682,13 @@
         <v>132</v>
       </c>
       <c r="F75" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
       </c>
       <c r="H75" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -18176,13 +18176,13 @@
         <v>44</v>
       </c>
       <c r="F94" s="2">
-        <v>249</v>
+        <v>187</v>
       </c>
       <c r="G94" s="2">
         <v>0</v>
       </c>
       <c r="H94" s="2">
-        <v>249</v>
+        <v>187</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -18202,13 +18202,13 @@
         <v>148</v>
       </c>
       <c r="F95" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G95" s="2">
         <v>0</v>
       </c>
       <c r="H95" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -18436,13 +18436,13 @@
         <v>98</v>
       </c>
       <c r="F104" s="2">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G104" s="2">
         <v>2</v>
       </c>
       <c r="H104" s="2">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -18462,13 +18462,13 @@
         <v>148</v>
       </c>
       <c r="F105" s="2">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="G105" s="2">
         <v>0</v>
       </c>
       <c r="H105" s="2">
-        <v>318</v>
+        <v>300</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -18514,13 +18514,13 @@
         <v>39</v>
       </c>
       <c r="F107" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G107" s="2">
         <v>0</v>
       </c>
       <c r="H107" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -18748,13 +18748,13 @@
         <v>148</v>
       </c>
       <c r="F116" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G116" s="2">
         <v>1</v>
       </c>
       <c r="H116" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -29194,13 +29194,13 @@
         <v>127</v>
       </c>
       <c r="F518" s="2">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="G518" s="2">
         <v>0</v>
       </c>
       <c r="H518" s="2">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.25">
@@ -32934,13 +32934,13 @@
         <v>854</v>
       </c>
       <c r="F662" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G662" s="2">
         <v>0</v>
       </c>
       <c r="H662" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.25">
@@ -33324,13 +33324,13 @@
         <v>854</v>
       </c>
       <c r="F677" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G677" s="2">
         <v>0</v>
       </c>
       <c r="H677" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="678" spans="1:8" x14ac:dyDescent="0.25">
@@ -33714,13 +33714,13 @@
         <v>44</v>
       </c>
       <c r="F692" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G692" s="2">
         <v>0</v>
       </c>
       <c r="H692" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="693" spans="1:8" x14ac:dyDescent="0.25">
@@ -34884,13 +34884,13 @@
         <v>42</v>
       </c>
       <c r="F737" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G737" s="2">
         <v>0</v>
       </c>
       <c r="H737" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="738" spans="1:8" x14ac:dyDescent="0.25">
@@ -35014,13 +35014,13 @@
         <v>854</v>
       </c>
       <c r="F742" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G742" s="2">
         <v>0</v>
       </c>
       <c r="H742" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="743" spans="1:8" x14ac:dyDescent="0.25">
@@ -35404,13 +35404,13 @@
         <v>428</v>
       </c>
       <c r="F757" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G757" s="2">
         <v>0</v>
       </c>
       <c r="H757" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="758" spans="1:8" x14ac:dyDescent="0.25">
@@ -35508,13 +35508,13 @@
         <v>428</v>
       </c>
       <c r="F761" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G761" s="2">
         <v>0</v>
       </c>
       <c r="H761" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="762" spans="1:8" x14ac:dyDescent="0.25">
@@ -35534,13 +35534,13 @@
         <v>428</v>
       </c>
       <c r="F762" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G762" s="2">
         <v>0</v>
       </c>
       <c r="H762" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="763" spans="1:8" x14ac:dyDescent="0.25">
@@ -38628,13 +38628,13 @@
         <v>111</v>
       </c>
       <c r="F881" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G881" s="2">
         <v>0</v>
       </c>
       <c r="H881" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="882" spans="1:8" x14ac:dyDescent="0.25">
@@ -39824,13 +39824,13 @@
         <v>1536</v>
       </c>
       <c r="F927" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G927" s="2">
         <v>0</v>
       </c>
       <c r="H927" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="928" spans="1:8" x14ac:dyDescent="0.25">
@@ -40266,13 +40266,13 @@
         <v>1556</v>
       </c>
       <c r="F944" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G944" s="2">
         <v>0</v>
       </c>
       <c r="H944" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="945" spans="1:8" x14ac:dyDescent="0.25">
@@ -49648,13 +49648,13 @@
         <v>323</v>
       </c>
       <c r="F1305" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1305" s="2">
         <v>0</v>
       </c>
       <c r="H1305" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1306" spans="1:8" x14ac:dyDescent="0.25">
@@ -50740,13 +50740,13 @@
         <v>323</v>
       </c>
       <c r="F1347" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1347" s="2">
         <v>0</v>
       </c>
       <c r="H1347" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1348" spans="1:8" x14ac:dyDescent="0.25">
@@ -54614,13 +54614,13 @@
         <v>2478</v>
       </c>
       <c r="F1496" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G1496" s="2">
         <v>0</v>
       </c>
       <c r="H1496" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1497" spans="1:8" x14ac:dyDescent="0.25">
@@ -76532,13 +76532,13 @@
         <v>4047</v>
       </c>
       <c r="F2339" s="2">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G2339" s="2">
         <v>1</v>
       </c>
       <c r="H2339" s="2">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2340" spans="1:8" x14ac:dyDescent="0.25">
@@ -86410,13 +86410,13 @@
         <v>254</v>
       </c>
       <c r="F2719" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G2719" s="2">
         <v>0</v>
       </c>
       <c r="H2719" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2720" spans="1:8" x14ac:dyDescent="0.25">
@@ -88152,13 +88152,13 @@
         <v>254</v>
       </c>
       <c r="F2786" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G2786" s="2">
         <v>0</v>
       </c>
       <c r="H2786" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2787" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B2F269-29A1-4986-8B2D-A9F95F32BE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBEEE8C-C67C-4862-8EDA-90CBD550BA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{552CD280-2CBB-478B-8720-DE884677C382}"/>
   </bookViews>
@@ -17630,13 +17630,13 @@
         <v>42</v>
       </c>
       <c r="F73" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -17890,13 +17890,13 @@
         <v>148</v>
       </c>
       <c r="F83" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -18176,13 +18176,13 @@
         <v>44</v>
       </c>
       <c r="F94" s="2">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="G94" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" s="2">
-        <v>187</v>
+        <v>168</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -18436,13 +18436,13 @@
         <v>98</v>
       </c>
       <c r="F104" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G104" s="2">
         <v>2</v>
       </c>
       <c r="H104" s="2">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -18462,13 +18462,13 @@
         <v>148</v>
       </c>
       <c r="F105" s="2">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="G105" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H105" s="2">
-        <v>300</v>
+        <v>279</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -27587,10 +27587,10 @@
         <v>16</v>
       </c>
       <c r="G456" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H456" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.25">
@@ -28523,10 +28523,10 @@
         <v>1</v>
       </c>
       <c r="G492" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H492" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.25">
@@ -32419,10 +32419,10 @@
         <v>9</v>
       </c>
       <c r="G642" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H642" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="643" spans="1:8" x14ac:dyDescent="0.25">
@@ -40269,10 +40269,10 @@
         <v>26</v>
       </c>
       <c r="G944" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H944" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="945" spans="1:8" x14ac:dyDescent="0.25">
@@ -41046,10 +41046,10 @@
         <v>35</v>
       </c>
       <c r="F974" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G974" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H974" s="2">
         <v>0</v>
@@ -50665,10 +50665,10 @@
         <v>2</v>
       </c>
       <c r="G1344" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1344" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1345" spans="1:8" x14ac:dyDescent="0.25">
@@ -54097,10 +54097,10 @@
         <v>1</v>
       </c>
       <c r="G1476" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1476" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1477" spans="1:8" x14ac:dyDescent="0.25">
@@ -76532,13 +76532,13 @@
         <v>4047</v>
       </c>
       <c r="F2339" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G2339" s="2">
         <v>1</v>
       </c>
       <c r="H2339" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2340" spans="1:8" x14ac:dyDescent="0.25">
@@ -90703,10 +90703,10 @@
         <v>6</v>
       </c>
       <c r="G2884" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2884" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2885" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBEEE8C-C67C-4862-8EDA-90CBD550BA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B64755E-96F0-40B1-B21C-CD6207833AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{552CD280-2CBB-478B-8720-DE884677C382}"/>
   </bookViews>
@@ -16668,13 +16668,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16772,13 +16772,13 @@
         <v>70</v>
       </c>
       <c r="F40" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
       </c>
       <c r="H40" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -16983,10 +16983,10 @@
         <v>4</v>
       </c>
       <c r="G48" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H48" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -17630,13 +17630,13 @@
         <v>42</v>
       </c>
       <c r="F73" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -17890,13 +17890,13 @@
         <v>148</v>
       </c>
       <c r="F83" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -17916,13 +17916,13 @@
         <v>148</v>
       </c>
       <c r="F84" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -17942,13 +17942,13 @@
         <v>148</v>
       </c>
       <c r="F85" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G85" s="2">
         <v>0</v>
       </c>
       <c r="H85" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -18176,13 +18176,13 @@
         <v>44</v>
       </c>
       <c r="F94" s="2">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="G94" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H94" s="2">
-        <v>168</v>
+        <v>143</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -18436,13 +18436,13 @@
         <v>98</v>
       </c>
       <c r="F104" s="2">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G104" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H104" s="2">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -18462,13 +18462,13 @@
         <v>148</v>
       </c>
       <c r="F105" s="2">
-        <v>284</v>
+        <v>227</v>
       </c>
       <c r="G105" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H105" s="2">
-        <v>279</v>
+        <v>218</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -18514,13 +18514,13 @@
         <v>39</v>
       </c>
       <c r="F107" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G107" s="2">
         <v>0</v>
       </c>
       <c r="H107" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -18748,13 +18748,13 @@
         <v>148</v>
       </c>
       <c r="F116" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G116" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H116" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -27584,10 +27584,10 @@
         <v>70</v>
       </c>
       <c r="F456" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G456" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H456" s="2">
         <v>0</v>
@@ -28520,10 +28520,10 @@
         <v>828</v>
       </c>
       <c r="F492" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G492" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H492" s="2">
         <v>0</v>
@@ -29197,10 +29197,10 @@
         <v>85</v>
       </c>
       <c r="G518" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H518" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.25">
@@ -29220,13 +29220,13 @@
         <v>874</v>
       </c>
       <c r="F519" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G519" s="2">
         <v>0</v>
       </c>
       <c r="H519" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
@@ -29922,13 +29922,13 @@
         <v>224</v>
       </c>
       <c r="F546" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G546" s="2">
         <v>0</v>
       </c>
       <c r="H546" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.25">
@@ -32416,10 +32416,10 @@
         <v>1067</v>
       </c>
       <c r="F642" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G642" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H642" s="2">
         <v>0</v>
@@ -32934,13 +32934,13 @@
         <v>854</v>
       </c>
       <c r="F662" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G662" s="2">
         <v>0</v>
       </c>
       <c r="H662" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.25">
@@ -33327,10 +33327,10 @@
         <v>2</v>
       </c>
       <c r="G677" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H677" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="678" spans="1:8" x14ac:dyDescent="0.25">
@@ -33818,13 +33818,13 @@
         <v>854</v>
       </c>
       <c r="F696" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G696" s="2">
         <v>0</v>
       </c>
       <c r="H696" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="697" spans="1:8" x14ac:dyDescent="0.25">
@@ -34884,13 +34884,13 @@
         <v>42</v>
       </c>
       <c r="F737" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G737" s="2">
         <v>0</v>
       </c>
       <c r="H737" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="738" spans="1:8" x14ac:dyDescent="0.25">
@@ -35014,13 +35014,13 @@
         <v>854</v>
       </c>
       <c r="F742" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G742" s="2">
         <v>0</v>
       </c>
       <c r="H742" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="743" spans="1:8" x14ac:dyDescent="0.25">
@@ -35612,13 +35612,13 @@
         <v>428</v>
       </c>
       <c r="F765" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G765" s="2">
         <v>0</v>
       </c>
       <c r="H765" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="766" spans="1:8" x14ac:dyDescent="0.25">
@@ -35716,13 +35716,13 @@
         <v>428</v>
       </c>
       <c r="F769" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G769" s="2">
         <v>0</v>
       </c>
       <c r="H769" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="770" spans="1:8" x14ac:dyDescent="0.25">
@@ -40162,13 +40162,13 @@
         <v>1556</v>
       </c>
       <c r="F940" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G940" s="2">
         <v>0</v>
       </c>
       <c r="H940" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="941" spans="1:8" x14ac:dyDescent="0.25">
@@ -40266,13 +40266,13 @@
         <v>1556</v>
       </c>
       <c r="F944" s="2">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G944" s="2">
         <v>1</v>
       </c>
       <c r="H944" s="2">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="945" spans="1:8" x14ac:dyDescent="0.25">
@@ -50662,13 +50662,13 @@
         <v>323</v>
       </c>
       <c r="F1344" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1344" s="2">
         <v>1</v>
       </c>
       <c r="H1344" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1345" spans="1:8" x14ac:dyDescent="0.25">
@@ -53990,13 +53990,13 @@
         <v>653</v>
       </c>
       <c r="F1472" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1472" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1472" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1473" spans="1:8" x14ac:dyDescent="0.25">
@@ -54094,10 +54094,10 @@
         <v>653</v>
       </c>
       <c r="F1476" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1476" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1476" s="2">
         <v>0</v>
@@ -76532,13 +76532,13 @@
         <v>4047</v>
       </c>
       <c r="F2339" s="2">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G2339" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2339" s="2">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2340" spans="1:8" x14ac:dyDescent="0.25">
@@ -88152,13 +88152,13 @@
         <v>254</v>
       </c>
       <c r="F2786" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G2786" s="2">
         <v>0</v>
       </c>
       <c r="H2786" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2787" spans="1:8" x14ac:dyDescent="0.25">
@@ -90284,13 +90284,13 @@
         <v>65</v>
       </c>
       <c r="F2868" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2868" s="2">
         <v>0</v>
       </c>
       <c r="H2868" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2869" spans="1:8" x14ac:dyDescent="0.25">
@@ -90700,13 +90700,13 @@
         <v>65</v>
       </c>
       <c r="F2884" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G2884" s="2">
         <v>1</v>
       </c>
       <c r="H2884" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2885" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60071CDB-77B6-49CC-B1B6-B8B8DF990537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529006A2-F77D-449D-982E-4AB675EA70CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{552CD280-2CBB-478B-8720-DE884677C382}"/>
   </bookViews>
@@ -16677,13 +16677,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16781,13 +16781,13 @@
         <v>70</v>
       </c>
       <c r="F40" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
       </c>
       <c r="H40" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -16989,13 +16989,13 @@
         <v>65</v>
       </c>
       <c r="F48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -17639,13 +17639,13 @@
         <v>42</v>
       </c>
       <c r="F73" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -17717,13 +17717,13 @@
         <v>132</v>
       </c>
       <c r="F76" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G76" s="2">
         <v>0</v>
       </c>
       <c r="H76" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -17769,13 +17769,13 @@
         <v>127</v>
       </c>
       <c r="F78" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -17899,13 +17899,13 @@
         <v>148</v>
       </c>
       <c r="F83" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -17925,13 +17925,13 @@
         <v>148</v>
       </c>
       <c r="F84" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -18185,13 +18185,13 @@
         <v>44</v>
       </c>
       <c r="F94" s="2">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="G94" s="2">
         <v>0</v>
       </c>
       <c r="H94" s="2">
-        <v>126</v>
+        <v>103</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -18445,13 +18445,13 @@
         <v>98</v>
       </c>
       <c r="F104" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G104" s="2">
         <v>2</v>
       </c>
       <c r="H104" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -18471,13 +18471,13 @@
         <v>148</v>
       </c>
       <c r="F105" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="G105" s="2">
         <v>0</v>
       </c>
       <c r="H105" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -18757,13 +18757,13 @@
         <v>148</v>
       </c>
       <c r="F116" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G116" s="2">
         <v>1</v>
       </c>
       <c r="H116" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -29203,13 +29203,13 @@
         <v>127</v>
       </c>
       <c r="F518" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G518" s="2">
         <v>0</v>
       </c>
       <c r="H518" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.25">
@@ -32943,13 +32943,13 @@
         <v>854</v>
       </c>
       <c r="F662" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G662" s="2">
         <v>0</v>
       </c>
       <c r="H662" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.25">
@@ -33333,13 +33333,13 @@
         <v>854</v>
       </c>
       <c r="F677" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G677" s="2">
         <v>0</v>
       </c>
       <c r="H677" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="678" spans="1:8" x14ac:dyDescent="0.25">
@@ -34893,13 +34893,13 @@
         <v>42</v>
       </c>
       <c r="F737" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G737" s="2">
         <v>0</v>
       </c>
       <c r="H737" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="738" spans="1:8" x14ac:dyDescent="0.25">
@@ -35413,13 +35413,13 @@
         <v>428</v>
       </c>
       <c r="F757" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G757" s="2">
         <v>0</v>
       </c>
       <c r="H757" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="758" spans="1:8" x14ac:dyDescent="0.25">
@@ -35725,13 +35725,13 @@
         <v>428</v>
       </c>
       <c r="F769" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G769" s="2">
         <v>0</v>
       </c>
       <c r="H769" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="770" spans="1:8" x14ac:dyDescent="0.25">
@@ -40275,13 +40275,13 @@
         <v>1556</v>
       </c>
       <c r="F944" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G944" s="2">
         <v>0</v>
       </c>
       <c r="H944" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="945" spans="1:8" x14ac:dyDescent="0.25">
@@ -49423,13 +49423,13 @@
         <v>98</v>
       </c>
       <c r="F1296" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1296" s="2">
         <v>0</v>
       </c>
       <c r="H1296" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1297" spans="1:8" x14ac:dyDescent="0.25">
@@ -49475,13 +49475,13 @@
         <v>912</v>
       </c>
       <c r="F1298" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1298" s="2">
         <v>0</v>
       </c>
       <c r="H1298" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1299" spans="1:8" x14ac:dyDescent="0.25">
@@ -54623,13 +54623,13 @@
         <v>2478</v>
       </c>
       <c r="F1496" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1496" s="2">
         <v>0</v>
       </c>
       <c r="H1496" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1497" spans="1:8" x14ac:dyDescent="0.25">
@@ -76567,13 +76567,13 @@
         <v>4047</v>
       </c>
       <c r="F2340" s="2">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G2340" s="2">
         <v>1</v>
       </c>
       <c r="H2340" s="2">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2341" spans="1:8" x14ac:dyDescent="0.25">
@@ -86211,13 +86211,13 @@
         <v>254</v>
       </c>
       <c r="F2711" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G2711" s="2">
         <v>0</v>
       </c>
       <c r="H2711" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2712" spans="1:8" x14ac:dyDescent="0.25">
@@ -87043,13 +87043,13 @@
         <v>637</v>
       </c>
       <c r="F2743" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G2743" s="2">
         <v>0</v>
       </c>
       <c r="H2743" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2744" spans="1:8" x14ac:dyDescent="0.25">
@@ -88187,13 +88187,13 @@
         <v>4854</v>
       </c>
       <c r="F2787" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2787" s="2">
         <v>0</v>
       </c>
       <c r="H2787" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2788" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28352DE9-E97F-44D7-B19C-992F471E32EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2F4B40-85B5-4998-BE9A-9D3FC4712C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{552CD280-2CBB-478B-8720-DE884677C382}"/>
   </bookViews>
@@ -16728,13 +16728,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -17274,13 +17274,13 @@
         <v>65</v>
       </c>
       <c r="F57" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17690,13 +17690,13 @@
         <v>42</v>
       </c>
       <c r="F73" s="2">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -17716,13 +17716,13 @@
         <v>132</v>
       </c>
       <c r="F74" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G74" s="2">
         <v>0</v>
       </c>
       <c r="H74" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -17742,13 +17742,13 @@
         <v>132</v>
       </c>
       <c r="F75" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
       </c>
       <c r="H75" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -17950,13 +17950,13 @@
         <v>148</v>
       </c>
       <c r="F83" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -17976,13 +17976,13 @@
         <v>148</v>
       </c>
       <c r="F84" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -18132,13 +18132,13 @@
         <v>148</v>
       </c>
       <c r="F90" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="G90" s="2">
         <v>0</v>
       </c>
       <c r="H90" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -18236,13 +18236,13 @@
         <v>44</v>
       </c>
       <c r="F94" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="G94" s="2">
         <v>0</v>
       </c>
       <c r="H94" s="2">
-        <v>129</v>
+        <v>84</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -18262,13 +18262,13 @@
         <v>148</v>
       </c>
       <c r="F95" s="2">
-        <v>502</v>
+        <v>478</v>
       </c>
       <c r="G95" s="2">
         <v>0</v>
       </c>
       <c r="H95" s="2">
-        <v>502</v>
+        <v>478</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -28918,13 +28918,13 @@
         <v>854</v>
       </c>
       <c r="F505" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G505" s="2">
         <v>0</v>
       </c>
       <c r="H505" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
@@ -29254,13 +29254,13 @@
         <v>127</v>
       </c>
       <c r="F518" s="2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G518" s="2">
         <v>0</v>
       </c>
       <c r="H518" s="2">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.25">
@@ -29280,13 +29280,13 @@
         <v>874</v>
       </c>
       <c r="F519" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G519" s="2">
         <v>0</v>
       </c>
       <c r="H519" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
@@ -32994,13 +32994,13 @@
         <v>854</v>
       </c>
       <c r="F662" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G662" s="2">
         <v>0</v>
       </c>
       <c r="H662" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.25">
@@ -34944,13 +34944,13 @@
         <v>42</v>
       </c>
       <c r="F737" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G737" s="2">
         <v>0</v>
       </c>
       <c r="H737" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="738" spans="1:8" x14ac:dyDescent="0.25">
@@ -35464,13 +35464,13 @@
         <v>428</v>
       </c>
       <c r="F757" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G757" s="2">
         <v>0</v>
       </c>
       <c r="H757" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="758" spans="1:8" x14ac:dyDescent="0.25">
@@ -38714,13 +38714,13 @@
         <v>111</v>
       </c>
       <c r="F882" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G882" s="2">
         <v>0</v>
       </c>
       <c r="H882" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="883" spans="1:8" x14ac:dyDescent="0.25">
@@ -39754,13 +39754,13 @@
         <v>784</v>
       </c>
       <c r="F922" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G922" s="2">
         <v>0</v>
       </c>
       <c r="H922" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="923" spans="1:8" x14ac:dyDescent="0.25">
@@ -39910,13 +39910,13 @@
         <v>1536</v>
       </c>
       <c r="F928" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G928" s="2">
         <v>0</v>
       </c>
       <c r="H928" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="929" spans="1:8" x14ac:dyDescent="0.25">
@@ -45446,13 +45446,13 @@
         <v>1846</v>
       </c>
       <c r="F1141" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G1141" s="2">
         <v>0</v>
       </c>
       <c r="H1141" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1142" spans="1:8" x14ac:dyDescent="0.25">
@@ -76852,13 +76852,13 @@
         <v>4047</v>
       </c>
       <c r="F2349" s="2">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G2349" s="2">
         <v>1</v>
       </c>
       <c r="H2349" s="2">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2350" spans="1:8" x14ac:dyDescent="0.25">
@@ -88576,13 +88576,13 @@
         <v>254</v>
       </c>
       <c r="F2800" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2800" s="2">
         <v>0</v>
       </c>
       <c r="H2800" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2801" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2F4B40-85B5-4998-BE9A-9D3FC4712C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34C6B62-B6A9-4C1A-BF81-3000C73A3A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{552CD280-2CBB-478B-8720-DE884677C382}"/>
   </bookViews>
@@ -16728,13 +16728,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="2">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -16832,13 +16832,13 @@
         <v>70</v>
       </c>
       <c r="F40" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G40" s="2">
         <v>0</v>
       </c>
       <c r="H40" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -17690,13 +17690,13 @@
         <v>42</v>
       </c>
       <c r="F73" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -17768,13 +17768,13 @@
         <v>132</v>
       </c>
       <c r="F76" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G76" s="2">
         <v>0</v>
       </c>
       <c r="H76" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -17950,13 +17950,13 @@
         <v>148</v>
       </c>
       <c r="F83" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -17976,13 +17976,13 @@
         <v>148</v>
       </c>
       <c r="F84" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -18002,13 +18002,13 @@
         <v>148</v>
       </c>
       <c r="F85" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G85" s="2">
         <v>0</v>
       </c>
       <c r="H85" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -18132,13 +18132,13 @@
         <v>148</v>
       </c>
       <c r="F90" s="2">
-        <v>295</v>
+        <v>266</v>
       </c>
       <c r="G90" s="2">
         <v>0</v>
       </c>
       <c r="H90" s="2">
-        <v>295</v>
+        <v>266</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -18236,13 +18236,13 @@
         <v>44</v>
       </c>
       <c r="F94" s="2">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="G94" s="2">
         <v>0</v>
       </c>
       <c r="H94" s="2">
-        <v>84</v>
+        <v>68</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -29254,13 +29254,13 @@
         <v>127</v>
       </c>
       <c r="F518" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G518" s="2">
         <v>0</v>
       </c>
       <c r="H518" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.25">
@@ -29280,13 +29280,13 @@
         <v>874</v>
       </c>
       <c r="F519" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G519" s="2">
         <v>0</v>
       </c>
       <c r="H519" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
@@ -32994,13 +32994,13 @@
         <v>854</v>
       </c>
       <c r="F662" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G662" s="2">
         <v>0</v>
       </c>
       <c r="H662" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.25">
@@ -33800,13 +33800,13 @@
         <v>854</v>
       </c>
       <c r="F693" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G693" s="2">
         <v>0</v>
       </c>
       <c r="H693" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="694" spans="1:8" x14ac:dyDescent="0.25">
@@ -35464,13 +35464,13 @@
         <v>428</v>
       </c>
       <c r="F757" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G757" s="2">
         <v>0</v>
       </c>
       <c r="H757" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="758" spans="1:8" x14ac:dyDescent="0.25">
@@ -35594,13 +35594,13 @@
         <v>428</v>
       </c>
       <c r="F762" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G762" s="2">
         <v>0</v>
       </c>
       <c r="H762" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="763" spans="1:8" x14ac:dyDescent="0.25">
@@ -35776,13 +35776,13 @@
         <v>428</v>
       </c>
       <c r="F769" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G769" s="2">
         <v>0</v>
       </c>
       <c r="H769" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="770" spans="1:8" x14ac:dyDescent="0.25">
@@ -45446,13 +45446,13 @@
         <v>1846</v>
       </c>
       <c r="F1141" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G1141" s="2">
         <v>0</v>
       </c>
       <c r="H1141" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1142" spans="1:8" x14ac:dyDescent="0.25">
@@ -46510,13 +46510,13 @@
         <v>1889</v>
       </c>
       <c r="F1182" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G1182" s="2">
         <v>0</v>
       </c>
       <c r="H1182" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1183" spans="1:8" x14ac:dyDescent="0.25">
@@ -90708,13 +90708,13 @@
         <v>65</v>
       </c>
       <c r="F2882" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2882" s="2">
         <v>0</v>
       </c>
       <c r="H2882" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2883" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B72D76-D702-4332-B39D-4C4AF35805D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB2ED85D-E80A-492E-B30B-245078C98C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{552CD280-2CBB-478B-8720-DE884677C382}"/>
   </bookViews>
@@ -16764,13 +16764,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="2">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="G36" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H36" s="2">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -17310,13 +17310,13 @@
         <v>65</v>
       </c>
       <c r="F57" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G57" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17440,13 +17440,13 @@
         <v>107</v>
       </c>
       <c r="F62" s="2">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="2">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -17726,13 +17726,13 @@
         <v>42</v>
       </c>
       <c r="F73" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -17778,13 +17778,13 @@
         <v>132</v>
       </c>
       <c r="F75" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
       </c>
       <c r="H75" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -17804,13 +17804,13 @@
         <v>132</v>
       </c>
       <c r="F76" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G76" s="2">
         <v>0</v>
       </c>
       <c r="H76" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -17986,13 +17986,13 @@
         <v>148</v>
       </c>
       <c r="F83" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -18168,13 +18168,13 @@
         <v>148</v>
       </c>
       <c r="F90" s="2">
-        <v>267</v>
+        <v>175</v>
       </c>
       <c r="G90" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H90" s="2">
-        <v>264</v>
+        <v>170</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -18298,13 +18298,13 @@
         <v>148</v>
       </c>
       <c r="F95" s="2">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="G95" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H95" s="2">
-        <v>404</v>
+        <v>375</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -18558,13 +18558,13 @@
         <v>148</v>
       </c>
       <c r="F105" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G105" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -18844,13 +18844,13 @@
         <v>148</v>
       </c>
       <c r="F116" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G116" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H116" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -28954,13 +28954,13 @@
         <v>854</v>
       </c>
       <c r="F505" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G505" s="2">
         <v>0</v>
       </c>
       <c r="H505" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
@@ -29290,13 +29290,13 @@
         <v>127</v>
       </c>
       <c r="F518" s="2">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="G518" s="2">
         <v>0</v>
       </c>
       <c r="H518" s="2">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.25">
@@ -30018,13 +30018,13 @@
         <v>224</v>
       </c>
       <c r="F546" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G546" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H546" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.25">
@@ -30044,13 +30044,13 @@
         <v>42</v>
       </c>
       <c r="F547" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G547" s="2">
         <v>0</v>
       </c>
       <c r="H547" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.25">
@@ -33030,13 +33030,13 @@
         <v>854</v>
       </c>
       <c r="F662" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G662" s="2">
         <v>0</v>
       </c>
       <c r="H662" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.25">
@@ -33836,13 +33836,13 @@
         <v>854</v>
       </c>
       <c r="F693" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G693" s="2">
         <v>0</v>
       </c>
       <c r="H693" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="694" spans="1:8" x14ac:dyDescent="0.25">
@@ -35110,13 +35110,13 @@
         <v>854</v>
       </c>
       <c r="F742" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G742" s="2">
         <v>0</v>
       </c>
       <c r="H742" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="743" spans="1:8" x14ac:dyDescent="0.25">
@@ -35500,13 +35500,13 @@
         <v>428</v>
       </c>
       <c r="F757" s="2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G757" s="2">
         <v>0</v>
       </c>
       <c r="H757" s="2">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="758" spans="1:8" x14ac:dyDescent="0.25">
@@ -35604,13 +35604,13 @@
         <v>428</v>
       </c>
       <c r="F761" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G761" s="2">
         <v>0</v>
       </c>
       <c r="H761" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="762" spans="1:8" x14ac:dyDescent="0.25">
@@ -35630,10 +35630,10 @@
         <v>428</v>
       </c>
       <c r="F762" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G762" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H762" s="2">
         <v>3</v>
@@ -35864,13 +35864,13 @@
         <v>428</v>
       </c>
       <c r="F771" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G771" s="2">
         <v>0</v>
       </c>
       <c r="H771" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="772" spans="1:8" x14ac:dyDescent="0.25">
@@ -38750,13 +38750,13 @@
         <v>111</v>
       </c>
       <c r="F882" s="2">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G882" s="2">
         <v>0</v>
       </c>
       <c r="H882" s="2">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="883" spans="1:8" x14ac:dyDescent="0.25">
@@ -39790,13 +39790,13 @@
         <v>784</v>
       </c>
       <c r="F922" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G922" s="2">
         <v>0</v>
       </c>
       <c r="H922" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="923" spans="1:8" x14ac:dyDescent="0.25">
@@ -39946,13 +39946,13 @@
         <v>1536</v>
       </c>
       <c r="F928" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G928" s="2">
         <v>0</v>
       </c>
       <c r="H928" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="929" spans="1:8" x14ac:dyDescent="0.25">
@@ -40388,13 +40388,13 @@
         <v>1556</v>
       </c>
       <c r="F945" s="2">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G945" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H945" s="2">
-        <v>54</v>
+        <v>38</v>
       </c>
     </row>
     <row r="946" spans="1:8" x14ac:dyDescent="0.25">
@@ -45482,13 +45482,13 @@
         <v>1846</v>
       </c>
       <c r="F1141" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G1141" s="2">
         <v>0</v>
       </c>
       <c r="H1141" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1142" spans="1:8" x14ac:dyDescent="0.25">
@@ -50914,13 +50914,13 @@
         <v>323</v>
       </c>
       <c r="F1350" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1350" s="2">
         <v>0</v>
       </c>
       <c r="H1350" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1351" spans="1:8" x14ac:dyDescent="0.25">
@@ -54164,13 +54164,13 @@
         <v>653</v>
       </c>
       <c r="F1475" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1475" s="2">
         <v>0</v>
       </c>
       <c r="H1475" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1476" spans="1:8" x14ac:dyDescent="0.25">
@@ -54788,13 +54788,13 @@
         <v>2478</v>
       </c>
       <c r="F1499" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G1499" s="2">
         <v>0</v>
       </c>
       <c r="H1499" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1500" spans="1:8" x14ac:dyDescent="0.25">
@@ -76914,13 +76914,13 @@
         <v>4047</v>
       </c>
       <c r="F2350" s="2">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G2350" s="2">
         <v>1</v>
       </c>
       <c r="H2350" s="2">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2351" spans="1:8" x14ac:dyDescent="0.25">
@@ -86610,13 +86610,13 @@
         <v>254</v>
       </c>
       <c r="F2723" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G2723" s="2">
         <v>0</v>
       </c>
       <c r="H2723" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2724" spans="1:8" x14ac:dyDescent="0.25">
@@ -86896,13 +86896,13 @@
         <v>254</v>
       </c>
       <c r="F2734" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2734" s="2">
         <v>0</v>
       </c>
       <c r="H2734" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2735" spans="1:8" x14ac:dyDescent="0.25">
@@ -88586,13 +88586,13 @@
         <v>4854</v>
       </c>
       <c r="F2799" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2799" s="2">
         <v>0</v>
       </c>
       <c r="H2799" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2800" spans="1:8" x14ac:dyDescent="0.25">
@@ -88638,13 +88638,13 @@
         <v>254</v>
       </c>
       <c r="F2801" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G2801" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2801" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2802" spans="1:8" x14ac:dyDescent="0.25">
@@ -90900,13 +90900,13 @@
         <v>65</v>
       </c>
       <c r="F2888" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G2888" s="2">
         <v>0</v>
       </c>
       <c r="H2888" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2889" spans="1:8" x14ac:dyDescent="0.25">
@@ -91316,13 +91316,13 @@
         <v>65</v>
       </c>
       <c r="F2904" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2904" s="2">
         <v>0</v>
       </c>
       <c r="H2904" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2905" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A52D30-FEAD-45E2-AE12-28126225A779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3D1432-675F-482C-81A1-E0962180E3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{552CD280-2CBB-478B-8720-DE884677C382}"/>
   </bookViews>
@@ -16767,13 +16767,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -17079,13 +17079,13 @@
         <v>65</v>
       </c>
       <c r="F48" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -17313,13 +17313,13 @@
         <v>65</v>
       </c>
       <c r="F57" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17729,13 +17729,13 @@
         <v>42</v>
       </c>
       <c r="F73" s="2">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -17781,13 +17781,13 @@
         <v>132</v>
       </c>
       <c r="F75" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
       </c>
       <c r="H75" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -17807,13 +17807,13 @@
         <v>132</v>
       </c>
       <c r="F76" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" s="2">
         <v>0</v>
       </c>
       <c r="H76" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -17989,13 +17989,13 @@
         <v>148</v>
       </c>
       <c r="F83" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -18015,13 +18015,13 @@
         <v>148</v>
       </c>
       <c r="F84" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -18041,13 +18041,13 @@
         <v>148</v>
       </c>
       <c r="F85" s="2">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G85" s="2">
         <v>0</v>
       </c>
       <c r="H85" s="2">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -18171,13 +18171,13 @@
         <v>148</v>
       </c>
       <c r="F90" s="2">
-        <v>614</v>
+        <v>485</v>
       </c>
       <c r="G90" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H90" s="2">
-        <v>614</v>
+        <v>483</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -18301,13 +18301,13 @@
         <v>148</v>
       </c>
       <c r="F95" s="2">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="G95" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" s="2">
-        <v>233</v>
+        <v>197</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -18587,13 +18587,13 @@
         <v>42</v>
       </c>
       <c r="F106" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G106" s="2">
         <v>0</v>
       </c>
       <c r="H106" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -18769,13 +18769,13 @@
         <v>148</v>
       </c>
       <c r="F113" s="2">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="G113" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H113" s="2">
-        <v>360</v>
+        <v>318</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -18873,13 +18873,13 @@
         <v>148</v>
       </c>
       <c r="F117" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G117" s="2">
         <v>1</v>
       </c>
       <c r="H117" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -29319,13 +29319,13 @@
         <v>127</v>
       </c>
       <c r="F519" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G519" s="2">
         <v>0</v>
       </c>
       <c r="H519" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
@@ -29345,13 +29345,13 @@
         <v>873</v>
       </c>
       <c r="F520" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G520" s="2">
         <v>0</v>
       </c>
       <c r="H520" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.25">
@@ -30047,13 +30047,13 @@
         <v>224</v>
       </c>
       <c r="F547" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G547" s="2">
         <v>0</v>
       </c>
       <c r="H547" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.25">
@@ -33085,13 +33085,13 @@
         <v>853</v>
       </c>
       <c r="F664" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G664" s="2">
         <v>0</v>
       </c>
       <c r="H664" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="665" spans="1:8" x14ac:dyDescent="0.25">
@@ -35529,13 +35529,13 @@
         <v>428</v>
       </c>
       <c r="F758" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G758" s="2">
         <v>0</v>
       </c>
       <c r="H758" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="759" spans="1:8" x14ac:dyDescent="0.25">
@@ -35633,13 +35633,13 @@
         <v>428</v>
       </c>
       <c r="F762" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G762" s="2">
         <v>0</v>
       </c>
       <c r="H762" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="763" spans="1:8" x14ac:dyDescent="0.25">
@@ -39819,13 +39819,13 @@
         <v>784</v>
       </c>
       <c r="F923" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G923" s="2">
         <v>0</v>
       </c>
       <c r="H923" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="924" spans="1:8" x14ac:dyDescent="0.25">
@@ -39975,13 +39975,13 @@
         <v>1535</v>
       </c>
       <c r="F929" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G929" s="2">
         <v>0</v>
       </c>
       <c r="H929" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="930" spans="1:8" x14ac:dyDescent="0.25">
@@ -40417,13 +40417,13 @@
         <v>1555</v>
       </c>
       <c r="F946" s="2">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G946" s="2">
         <v>0</v>
       </c>
       <c r="H946" s="2">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="947" spans="1:8" x14ac:dyDescent="0.25">
@@ -45511,13 +45511,13 @@
         <v>1845</v>
       </c>
       <c r="F1142" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G1142" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1142" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1143" spans="1:8" x14ac:dyDescent="0.25">
@@ -49828,10 +49828,10 @@
         <v>20</v>
       </c>
       <c r="G1308" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1308" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1309" spans="1:8" x14ac:dyDescent="0.25">
@@ -51957,13 +51957,13 @@
         <v>2244</v>
       </c>
       <c r="F1390" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G1390" s="2">
         <v>0</v>
       </c>
       <c r="H1390" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1391" spans="1:8" x14ac:dyDescent="0.25">
@@ -56403,13 +56403,13 @@
         <v>39</v>
       </c>
       <c r="F1561" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1561" s="2">
         <v>0</v>
       </c>
       <c r="H1561" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1562" spans="1:8" x14ac:dyDescent="0.25">
@@ -56611,13 +56611,13 @@
         <v>425</v>
       </c>
       <c r="F1569" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1569" s="2">
         <v>0</v>
       </c>
       <c r="H1569" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1570" spans="1:8" x14ac:dyDescent="0.25">
@@ -64853,10 +64853,10 @@
         <v>363</v>
       </c>
       <c r="F1886" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1886" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1886" s="2">
         <v>1</v>
@@ -68938,10 +68938,10 @@
         <v>1</v>
       </c>
       <c r="G2043" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2043" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2044" spans="1:8" x14ac:dyDescent="0.25">
@@ -76943,13 +76943,13 @@
         <v>4045</v>
       </c>
       <c r="F2351" s="2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G2351" s="2">
         <v>1</v>
       </c>
       <c r="H2351" s="2">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2352" spans="1:8" x14ac:dyDescent="0.25">
@@ -78633,13 +78633,13 @@
         <v>323</v>
       </c>
       <c r="F2416" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2416" s="2">
         <v>0</v>
       </c>
       <c r="H2416" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2417" spans="1:8" x14ac:dyDescent="0.25">
@@ -86925,13 +86925,13 @@
         <v>254</v>
       </c>
       <c r="F2735" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2735" s="2">
         <v>0</v>
       </c>
       <c r="H2735" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2736" spans="1:8" x14ac:dyDescent="0.25">
@@ -88618,10 +88618,10 @@
         <v>2</v>
       </c>
       <c r="G2800" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2800" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2801" spans="1:8" x14ac:dyDescent="0.25">
@@ -90929,13 +90929,13 @@
         <v>65</v>
       </c>
       <c r="F2889" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G2889" s="2">
         <v>0</v>
       </c>
       <c r="H2889" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2890" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3D1432-675F-482C-81A1-E0962180E3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE082ADF-854C-4703-A08F-93FDA203E1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{552CD280-2CBB-478B-8720-DE884677C382}"/>
   </bookViews>
@@ -16767,13 +16767,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -17313,13 +17313,13 @@
         <v>65</v>
       </c>
       <c r="F57" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17443,13 +17443,13 @@
         <v>107</v>
       </c>
       <c r="F62" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -17781,13 +17781,13 @@
         <v>132</v>
       </c>
       <c r="F75" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
       </c>
       <c r="H75" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -17989,13 +17989,13 @@
         <v>148</v>
       </c>
       <c r="F83" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -18041,13 +18041,13 @@
         <v>148</v>
       </c>
       <c r="F85" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G85" s="2">
         <v>0</v>
       </c>
       <c r="H85" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -18171,13 +18171,13 @@
         <v>148</v>
       </c>
       <c r="F90" s="2">
-        <v>485</v>
+        <v>452</v>
       </c>
       <c r="G90" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H90" s="2">
-        <v>483</v>
+        <v>452</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -18301,13 +18301,13 @@
         <v>148</v>
       </c>
       <c r="F95" s="2">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="G95" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95" s="2">
-        <v>197</v>
+        <v>174</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -18769,13 +18769,13 @@
         <v>148</v>
       </c>
       <c r="F113" s="2">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="G113" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H113" s="2">
-        <v>318</v>
+        <v>301</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -29319,13 +29319,13 @@
         <v>127</v>
       </c>
       <c r="F519" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G519" s="2">
         <v>0</v>
       </c>
       <c r="H519" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
@@ -29345,13 +29345,13 @@
         <v>873</v>
       </c>
       <c r="F520" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G520" s="2">
         <v>0</v>
       </c>
       <c r="H520" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.25">
@@ -33813,13 +33813,13 @@
         <v>853</v>
       </c>
       <c r="F692" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G692" s="2">
         <v>0</v>
       </c>
       <c r="H692" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="693" spans="1:8" x14ac:dyDescent="0.25">
@@ -33943,13 +33943,13 @@
         <v>853</v>
       </c>
       <c r="F697" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G697" s="2">
         <v>0</v>
       </c>
       <c r="H697" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="698" spans="1:8" x14ac:dyDescent="0.25">
@@ -35659,13 +35659,13 @@
         <v>428</v>
       </c>
       <c r="F763" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G763" s="2">
         <v>0</v>
       </c>
       <c r="H763" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="764" spans="1:8" x14ac:dyDescent="0.25">
@@ -35841,13 +35841,13 @@
         <v>428</v>
       </c>
       <c r="F770" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G770" s="2">
         <v>0</v>
       </c>
       <c r="H770" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="771" spans="1:8" x14ac:dyDescent="0.25">
@@ -40417,13 +40417,13 @@
         <v>1555</v>
       </c>
       <c r="F946" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G946" s="2">
         <v>0</v>
       </c>
       <c r="H946" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="947" spans="1:8" x14ac:dyDescent="0.25">
@@ -45511,10 +45511,10 @@
         <v>1845</v>
       </c>
       <c r="F1142" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G1142" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1142" s="2">
         <v>22</v>
@@ -49825,10 +49825,10 @@
         <v>323</v>
       </c>
       <c r="F1308" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G1308" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1308" s="2">
         <v>19</v>
@@ -51957,13 +51957,13 @@
         <v>2244</v>
       </c>
       <c r="F1390" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1390" s="2">
         <v>0</v>
       </c>
       <c r="H1390" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1391" spans="1:8" x14ac:dyDescent="0.25">
@@ -76943,13 +76943,13 @@
         <v>4045</v>
       </c>
       <c r="F2351" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G2351" s="2">
         <v>1</v>
       </c>
       <c r="H2351" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2352" spans="1:8" x14ac:dyDescent="0.25">
@@ -88615,10 +88615,10 @@
         <v>4852</v>
       </c>
       <c r="F2800" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2800" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2800" s="2">
         <v>1</v>
@@ -90929,13 +90929,13 @@
         <v>65</v>
       </c>
       <c r="F2889" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2889" s="2">
         <v>0</v>
       </c>
       <c r="H2889" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2890" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE082ADF-854C-4703-A08F-93FDA203E1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC08A54D-8671-45CF-B6DA-2B22F2070B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{552CD280-2CBB-478B-8720-DE884677C382}"/>
   </bookViews>
@@ -17443,13 +17443,13 @@
         <v>107</v>
       </c>
       <c r="F62" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -17729,13 +17729,13 @@
         <v>42</v>
       </c>
       <c r="F73" s="2">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <v>58</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -17781,13 +17781,13 @@
         <v>132</v>
       </c>
       <c r="F75" s="2">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
       </c>
       <c r="H75" s="2">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -17807,13 +17807,13 @@
         <v>132</v>
       </c>
       <c r="F76" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G76" s="2">
         <v>0</v>
       </c>
       <c r="H76" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -17833,13 +17833,13 @@
         <v>127</v>
       </c>
       <c r="F77" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G77" s="2">
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -17989,13 +17989,13 @@
         <v>148</v>
       </c>
       <c r="F83" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -18171,13 +18171,13 @@
         <v>148</v>
       </c>
       <c r="F90" s="2">
-        <v>452</v>
+        <v>422</v>
       </c>
       <c r="G90" s="2">
         <v>0</v>
       </c>
       <c r="H90" s="2">
-        <v>452</v>
+        <v>422</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -18301,13 +18301,13 @@
         <v>148</v>
       </c>
       <c r="F95" s="2">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="G95" s="2">
         <v>0</v>
       </c>
       <c r="H95" s="2">
-        <v>174</v>
+        <v>136</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -18587,13 +18587,13 @@
         <v>42</v>
       </c>
       <c r="F106" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G106" s="2">
         <v>0</v>
       </c>
       <c r="H106" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -18769,13 +18769,13 @@
         <v>148</v>
       </c>
       <c r="F113" s="2">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="G113" s="2">
         <v>0</v>
       </c>
       <c r="H113" s="2">
-        <v>301</v>
+        <v>290</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -18873,13 +18873,13 @@
         <v>148</v>
       </c>
       <c r="F117" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G117" s="2">
         <v>1</v>
       </c>
       <c r="H117" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -22067,13 +22067,13 @@
         <v>127</v>
       </c>
       <c r="F240" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G240" s="2">
         <v>0</v>
       </c>
       <c r="H240" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
@@ -29319,13 +29319,13 @@
         <v>127</v>
       </c>
       <c r="F519" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G519" s="2">
         <v>0</v>
       </c>
       <c r="H519" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
@@ -29345,13 +29345,13 @@
         <v>873</v>
       </c>
       <c r="F520" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G520" s="2">
         <v>0</v>
       </c>
       <c r="H520" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.25">
@@ -30047,13 +30047,13 @@
         <v>224</v>
       </c>
       <c r="F547" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G547" s="2">
         <v>0</v>
       </c>
       <c r="H547" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.25">
@@ -33631,13 +33631,13 @@
         <v>853</v>
       </c>
       <c r="F685" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G685" s="2">
         <v>0</v>
       </c>
       <c r="H685" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="686" spans="1:8" x14ac:dyDescent="0.25">
@@ -33839,13 +33839,13 @@
         <v>44</v>
       </c>
       <c r="F693" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G693" s="2">
         <v>0</v>
       </c>
       <c r="H693" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="694" spans="1:8" x14ac:dyDescent="0.25">
@@ -33865,13 +33865,13 @@
         <v>853</v>
       </c>
       <c r="F694" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G694" s="2">
         <v>0</v>
       </c>
       <c r="H694" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="695" spans="1:8" x14ac:dyDescent="0.25">
@@ -35659,13 +35659,13 @@
         <v>428</v>
       </c>
       <c r="F763" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G763" s="2">
         <v>0</v>
       </c>
       <c r="H763" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="764" spans="1:8" x14ac:dyDescent="0.25">
@@ -38779,13 +38779,13 @@
         <v>111</v>
       </c>
       <c r="F883" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G883" s="2">
         <v>0</v>
       </c>
       <c r="H883" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="884" spans="1:8" x14ac:dyDescent="0.25">
@@ -39819,13 +39819,13 @@
         <v>784</v>
       </c>
       <c r="F923" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G923" s="2">
         <v>0</v>
       </c>
       <c r="H923" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="924" spans="1:8" x14ac:dyDescent="0.25">
@@ -39975,13 +39975,13 @@
         <v>1535</v>
       </c>
       <c r="F929" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G929" s="2">
         <v>0</v>
       </c>
       <c r="H929" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="930" spans="1:8" x14ac:dyDescent="0.25">
@@ -40313,13 +40313,13 @@
         <v>1555</v>
       </c>
       <c r="F942" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G942" s="2">
         <v>0</v>
       </c>
       <c r="H942" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="943" spans="1:8" x14ac:dyDescent="0.25">
@@ -40417,13 +40417,13 @@
         <v>1555</v>
       </c>
       <c r="F946" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G946" s="2">
         <v>0</v>
       </c>
       <c r="H946" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="947" spans="1:8" x14ac:dyDescent="0.25">
@@ -45511,13 +45511,13 @@
         <v>1845</v>
       </c>
       <c r="F1142" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G1142" s="2">
         <v>0</v>
       </c>
       <c r="H1142" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1143" spans="1:8" x14ac:dyDescent="0.25">
@@ -51957,13 +51957,13 @@
         <v>2244</v>
       </c>
       <c r="F1390" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G1390" s="2">
         <v>0</v>
       </c>
       <c r="H1390" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1391" spans="1:8" x14ac:dyDescent="0.25">
@@ -64229,13 +64229,13 @@
         <v>42</v>
       </c>
       <c r="F1862" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1862" s="2">
         <v>0</v>
       </c>
       <c r="H1862" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1863" spans="1:8" x14ac:dyDescent="0.25">
@@ -76943,13 +76943,13 @@
         <v>4045</v>
       </c>
       <c r="F2351" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G2351" s="2">
         <v>1</v>
       </c>
       <c r="H2351" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2352" spans="1:8" x14ac:dyDescent="0.25">
@@ -88615,13 +88615,13 @@
         <v>4852</v>
       </c>
       <c r="F2800" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2800" s="2">
         <v>0</v>
       </c>
       <c r="H2800" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2801" spans="1:8" x14ac:dyDescent="0.25">
@@ -90929,13 +90929,13 @@
         <v>65</v>
       </c>
       <c r="F2889" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G2889" s="2">
         <v>0</v>
       </c>
       <c r="H2889" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2890" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC08A54D-8671-45CF-B6DA-2B22F2070B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D58749-9CD0-4E0A-94A4-BA1ABC9732EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{552CD280-2CBB-478B-8720-DE884677C382}"/>
   </bookViews>
@@ -17443,13 +17443,13 @@
         <v>107</v>
       </c>
       <c r="F62" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -17729,13 +17729,13 @@
         <v>42</v>
       </c>
       <c r="F73" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -18171,13 +18171,13 @@
         <v>148</v>
       </c>
       <c r="F90" s="2">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="G90" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H90" s="2">
-        <v>422</v>
+        <v>403</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -18301,13 +18301,13 @@
         <v>148</v>
       </c>
       <c r="F95" s="2">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="G95" s="2">
         <v>0</v>
       </c>
       <c r="H95" s="2">
-        <v>136</v>
+        <v>119</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -18769,13 +18769,13 @@
         <v>148</v>
       </c>
       <c r="F113" s="2">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G113" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H113" s="2">
-        <v>290</v>
+        <v>278</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -18873,13 +18873,13 @@
         <v>148</v>
       </c>
       <c r="F117" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G117" s="2">
         <v>1</v>
       </c>
       <c r="H117" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -28463,13 +28463,13 @@
         <v>127</v>
       </c>
       <c r="F486" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G486" s="2">
         <v>0</v>
       </c>
       <c r="H486" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.25">
@@ -33943,13 +33943,13 @@
         <v>853</v>
       </c>
       <c r="F697" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G697" s="2">
         <v>0</v>
       </c>
       <c r="H697" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="698" spans="1:8" x14ac:dyDescent="0.25">
@@ -35841,13 +35841,13 @@
         <v>428</v>
       </c>
       <c r="F770" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G770" s="2">
         <v>0</v>
       </c>
       <c r="H770" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="771" spans="1:8" x14ac:dyDescent="0.25">
@@ -38782,10 +38782,10 @@
         <v>46</v>
       </c>
       <c r="G883" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H883" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="884" spans="1:8" x14ac:dyDescent="0.25">
@@ -39975,13 +39975,13 @@
         <v>1535</v>
       </c>
       <c r="F929" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G929" s="2">
         <v>0</v>
       </c>
       <c r="H929" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="930" spans="1:8" x14ac:dyDescent="0.25">
@@ -40417,13 +40417,13 @@
         <v>1555</v>
       </c>
       <c r="F946" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G946" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H946" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="947" spans="1:8" x14ac:dyDescent="0.25">
@@ -41145,13 +41145,13 @@
         <v>35</v>
       </c>
       <c r="F974" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G974" s="2">
         <v>0</v>
       </c>
       <c r="H974" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="975" spans="1:8" x14ac:dyDescent="0.25">
@@ -76943,13 +76943,13 @@
         <v>4045</v>
       </c>
       <c r="F2351" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G2351" s="2">
         <v>1</v>
       </c>
       <c r="H2351" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2352" spans="1:8" x14ac:dyDescent="0.25">
@@ -90929,13 +90929,13 @@
         <v>65</v>
       </c>
       <c r="F2889" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G2889" s="2">
         <v>0</v>
       </c>
       <c r="H2889" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2890" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK HPN.xlsx
+++ b/STOK DEALER/STOK HPN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Document\ILHAM GUSRIANTO\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D58749-9CD0-4E0A-94A4-BA1ABC9732EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A3FF01-48AA-4417-AEA7-E5B9FC528E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{552CD280-2CBB-478B-8720-DE884677C382}"/>
   </bookViews>
@@ -16767,13 +16767,13 @@
         <v>65</v>
       </c>
       <c r="F36" s="2">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G36" s="2">
         <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -17079,13 +17079,13 @@
         <v>65</v>
       </c>
       <c r="F48" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G48" s="2">
         <v>0</v>
       </c>
       <c r="H48" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -17313,13 +17313,13 @@
         <v>65</v>
       </c>
       <c r="F57" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -17729,13 +17729,13 @@
         <v>42</v>
       </c>
       <c r="F73" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
       </c>
       <c r="H73" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -17781,13 +17781,13 @@
         <v>132</v>
       </c>
       <c r="F75" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
       </c>
       <c r="H75" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -17989,13 +17989,13 @@
         <v>148</v>
       </c>
       <c r="F83" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
       </c>
       <c r="H83" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -18015,13 +18015,13 @@
         <v>148</v>
       </c>
       <c r="F84" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -18041,13 +18041,13 @@
         <v>148</v>
       </c>
       <c r="F85" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G85" s="2">
         <v>0</v>
       </c>
       <c r="H85" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -18171,13 +18171,13 @@
         <v>148</v>
       </c>
       <c r="F90" s="2">
-        <v>407</v>
+        <v>328</v>
       </c>
       <c r="G90" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H90" s="2">
-        <v>403</v>
+        <v>328</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -18301,13 +18301,13 @@
         <v>148</v>
       </c>
       <c r="F95" s="2">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="G95" s="2">
         <v>0</v>
       </c>
       <c r="H95" s="2">
-        <v>119</v>
+        <v>81</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -18561,13 +18561,13 @@
         <v>148</v>
       </c>
       <c r="F105" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G105" s="2">
         <v>0</v>
       </c>
       <c r="H105" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -18587,13 +18587,13 @@
         <v>42</v>
       </c>
       <c r="F106" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G106" s="2">
         <v>0</v>
       </c>
       <c r="H106" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -18769,13 +18769,13 @@
         <v>148</v>
       </c>
       <c r="F113" s="2">
-        <v>280</v>
+        <v>251</v>
       </c>
       <c r="G113" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H113" s="2">
-        <v>278</v>
+        <v>251</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -18873,13 +18873,13 @@
         <v>148</v>
       </c>
       <c r="F117" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G117" s="2">
         <v>1</v>
       </c>
       <c r="H117" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -22483,13 +22483,13 @@
         <v>17</v>
       </c>
       <c r="F256" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G256" s="2">
         <v>0</v>
       </c>
       <c r="H256" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
@@ -29319,13 +29319,13 @@
         <v>127</v>
       </c>
       <c r="F519" s="2">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="G519" s="2">
         <v>0</v>
       </c>
       <c r="H519" s="2">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
@@ -29345,13 +29345,13 @@
         <v>873</v>
       </c>
       <c r="F520" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G520" s="2">
         <v>0</v>
       </c>
       <c r="H520" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.25">
@@ -30047,13 +30047,13 @@
         <v>224</v>
       </c>
       <c r="F547" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G547" s="2">
         <v>0</v>
       </c>
       <c r="H547" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.25">
@@ -33631,13 +33631,13 @@
         <v>853</v>
       </c>
       <c r="F685" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G685" s="2">
         <v>0</v>
       </c>
       <c r="H685" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="686" spans="1:8" x14ac:dyDescent="0.25">
@@ -33865,13 +33865,13 @@
         <v>853</v>
       </c>
       <c r="F694" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G694" s="2">
         <v>0</v>
       </c>
       <c r="H694" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="695" spans="1:8" x14ac:dyDescent="0.25">
@@ -35529,13 +35529,13 @@
         <v>428</v>
       </c>
       <c r="F758" s="2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G758" s="2">
         <v>0</v>
       </c>
       <c r="H758" s="2">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="759" spans="1:8" x14ac:dyDescent="0.25">
@@ -35633,13 +35633,13 @@
         <v>428</v>
       </c>
       <c r="F762" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G762" s="2">
         <v>0</v>
       </c>
       <c r="H762" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="763" spans="1:8" x14ac:dyDescent="0.25">
@@ -35659,13 +35659,13 @@
         <v>428</v>
       </c>
       <c r="F763" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G763" s="2">
         <v>0</v>
       </c>
       <c r="H763" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="764" spans="1:8" x14ac:dyDescent="0.25">
@@ -35841,13 +35841,13 @@
         <v>428</v>
       </c>
       <c r="F770" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G770" s="2">
         <v>0</v>
       </c>
       <c r="H770" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="771" spans="1:8" x14ac:dyDescent="0.25">
@@ -35945,13 +35945,13 @@
         <v>428</v>
       </c>
       <c r="F774" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G774" s="2">
         <v>0</v>
       </c>
       <c r="H774" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="775" spans="1:8" x14ac:dyDescent="0.25">
@@ -38779,13 +38779,13 @@
         <v>111</v>
       </c>
       <c r="F883" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G883" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H883" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="884" spans="1:8" x14ac:dyDescent="0.25">
@@ -39819,13 +39819,13 @@
         <v>784</v>
       </c>
       <c r="F923" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G923" s="2">
         <v>0</v>
       </c>
       <c r="H923" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="924" spans="1:8" x14ac:dyDescent="0.25">
@@ -39975,13 +39975,13 @@
         <v>1535</v>
       </c>
       <c r="F929" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G929" s="2">
         <v>0</v>
       </c>
       <c r="H929" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="930" spans="1:8" x14ac:dyDescent="0.25">
@@ -40417,13 +40417,13 @@
         <v>1555</v>
       </c>
       <c r="F946" s="2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G946" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H946" s="2">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="947" spans="1:8" x14ac:dyDescent="0.25">
@@ -49825,13 +49825,13 @@
         <v>323</v>
       </c>
       <c r="F1308" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G1308" s="2">
         <v>0</v>
       </c>
       <c r="H1308" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1309" spans="1:8" x14ac:dyDescent="0.25">
@@ -51957,13 +51957,13 @@
         <v>2244</v>
       </c>
       <c r="F1390" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1390" s="2">
         <v>0</v>
       </c>
       <c r="H1390" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1391" spans="1:8" x14ac:dyDescent="0.25">
@@ -76943,13 +76943,13 @@
         <v>4045</v>
       </c>
       <c r="F2351" s="2">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="G2351" s="2">
         <v>1</v>
       </c>
       <c r="H2351" s="2">
-        <v>3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2352" spans="1:8" x14ac:dyDescent="0.25">
@@ -87471,13 +87471,13 @@
         <v>637</v>
       </c>
       <c r="F2756" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2756" s="2">
         <v>0</v>
       </c>
       <c r="H2756" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2757" spans="1:8" x14ac:dyDescent="0.25">
@@ -88615,13 +88615,13 @@
         <v>4852</v>
       </c>
       <c r="F2800" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2800" s="2">
         <v>0</v>
       </c>
       <c r="H2800" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2801" spans="1:8" x14ac:dyDescent="0.25">
@@ -90929,13 +90929,13 @@
         <v>65</v>
       </c>
       <c r="F2889" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2889" s="2">
         <v>0</v>
       </c>
       <c r="H2889" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2890" spans="1:8" x14ac:dyDescent="0.25">
